--- a/artfynd/A 39666-2025 artfynd.xlsx
+++ b/artfynd/A 39666-2025 artfynd.xlsx
@@ -879,37 +879,38 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128728896</v>
+        <v>128728526</v>
       </c>
       <c r="B4" t="n">
-        <v>98588</v>
+        <v>57689</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>6</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -918,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>569601</v>
+        <v>569616</v>
       </c>
       <c r="R4" t="n">
-        <v>6958191</v>
+        <v>6958208</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -954,6 +955,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -980,7 +986,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128728526</v>
+        <v>128743246</v>
       </c>
       <c r="B5" t="n">
         <v>57689</v>
@@ -1009,21 +1015,16 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>569616</v>
+        <v>569648</v>
       </c>
       <c r="R5" t="n">
-        <v>6958208</v>
+        <v>6957944</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1060,7 +1061,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack av tretåig hackspett på Tall ( äldre och färska spår)</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1087,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128732983</v>
+        <v>128728896</v>
       </c>
       <c r="B6" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1117,7 +1118,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1126,10 +1127,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>569873</v>
+        <v>569601</v>
       </c>
       <c r="R6" t="n">
-        <v>6958099</v>
+        <v>6958191</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1188,45 +1189,49 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128743246</v>
+        <v>128732983</v>
       </c>
       <c r="B7" t="n">
-        <v>57689</v>
+        <v>98591</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>569648</v>
+        <v>569873</v>
       </c>
       <c r="R7" t="n">
-        <v>6957944</v>
+        <v>6958099</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1259,11 +1264,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall ( äldre och färska spår)</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1290,10 +1290,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128730130</v>
+        <v>128729409</v>
       </c>
       <c r="B8" t="n">
-        <v>57689</v>
+        <v>91466</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1301,39 +1301,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>569713</v>
+        <v>569700</v>
       </c>
       <c r="R8" t="n">
-        <v>6958138</v>
+        <v>6958164</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1366,11 +1361,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1397,10 +1387,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128729409</v>
+        <v>128730130</v>
       </c>
       <c r="B9" t="n">
-        <v>91466</v>
+        <v>57689</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1408,34 +1398,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>569700</v>
+        <v>569713</v>
       </c>
       <c r="R9" t="n">
-        <v>6958164</v>
+        <v>6958138</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1468,6 +1463,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1494,10 +1494,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128732217</v>
+        <v>128730571</v>
       </c>
       <c r="B10" t="n">
-        <v>57849</v>
+        <v>91484</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1505,48 +1505,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>569777</v>
+        <v>569660</v>
       </c>
       <c r="R10" t="n">
-        <v>6958189</v>
+        <v>6958074</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1579,11 +1565,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>2 talltitor kommer flygandes väldigt närgånget och varnar</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1610,7 +1591,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128732276</v>
+        <v>128743245</v>
       </c>
       <c r="B11" t="n">
         <v>57689</v>
@@ -1639,21 +1620,16 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>569841</v>
+        <v>569590</v>
       </c>
       <c r="R11" t="n">
-        <v>6958102</v>
+        <v>6958014</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1690,7 +1666,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack av tretåig hackspett på Tall ( färska spår)</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1717,10 +1693,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128730571</v>
+        <v>128732276</v>
       </c>
       <c r="B12" t="n">
-        <v>91484</v>
+        <v>57689</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1728,34 +1704,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>569660</v>
+        <v>569841</v>
       </c>
       <c r="R12" t="n">
-        <v>6958074</v>
+        <v>6958102</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1788,6 +1769,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1814,10 +1800,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128743245</v>
+        <v>128732765</v>
       </c>
       <c r="B13" t="n">
-        <v>57689</v>
+        <v>91762</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1825,21 +1811,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1849,10 +1835,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>569590</v>
+        <v>569827</v>
       </c>
       <c r="R13" t="n">
-        <v>6958014</v>
+        <v>6958133</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1885,11 +1871,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall ( färska spår)</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1916,10 +1897,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128732765</v>
+        <v>128732217</v>
       </c>
       <c r="B14" t="n">
-        <v>91762</v>
+        <v>57849</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1927,34 +1908,48 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>658</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>569827</v>
+        <v>569777</v>
       </c>
       <c r="R14" t="n">
-        <v>6958133</v>
+        <v>6958189</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1987,6 +1982,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>2 talltitor kommer flygandes väldigt närgånget och varnar</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2016,7 +2016,7 @@
         <v>128733181</v>
       </c>
       <c r="B15" t="n">
-        <v>98505</v>
+        <v>98508</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2220,7 +2220,7 @@
         <v>128731490</v>
       </c>
       <c r="B17" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2318,45 +2318,49 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128728515</v>
+        <v>128730429</v>
       </c>
       <c r="B18" t="n">
-        <v>97462</v>
+        <v>98591</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>569608</v>
+        <v>569683</v>
       </c>
       <c r="R18" t="n">
-        <v>6958227</v>
+        <v>6958128</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2415,49 +2419,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128730429</v>
+        <v>128728515</v>
       </c>
       <c r="B19" t="n">
-        <v>98588</v>
+        <v>97462</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>569683</v>
+        <v>569608</v>
       </c>
       <c r="R19" t="n">
-        <v>6958128</v>
+        <v>6958227</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2516,10 +2516,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128731107</v>
+        <v>128732359</v>
       </c>
       <c r="B20" t="n">
-        <v>57849</v>
+        <v>91466</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2527,39 +2527,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>569705</v>
+        <v>569820</v>
       </c>
       <c r="R20" t="n">
-        <v>6958098</v>
+        <v>6958107</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2618,49 +2613,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128730720</v>
+        <v>128731612</v>
       </c>
       <c r="B21" t="n">
-        <v>98588</v>
+        <v>91466</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>569692</v>
+        <v>569752</v>
       </c>
       <c r="R21" t="n">
-        <v>6958094</v>
+        <v>6958091</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2693,11 +2684,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ca</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2724,38 +2710,37 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128739020</v>
+        <v>128730720</v>
       </c>
       <c r="B22" t="n">
-        <v>57689</v>
+        <v>98591</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>50</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2764,10 +2749,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>569542</v>
+        <v>569692</v>
       </c>
       <c r="R22" t="n">
-        <v>6958049</v>
+        <v>6958094</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2804,7 +2789,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ca</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2831,32 +2816,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128728022</v>
+        <v>128743252</v>
       </c>
       <c r="B23" t="n">
-        <v>91431</v>
+        <v>98591</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2866,10 +2851,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>569583</v>
+        <v>569610</v>
       </c>
       <c r="R23" t="n">
-        <v>6958204</v>
+        <v>6958005</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2902,6 +2887,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>2 exemplar</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2928,32 +2918,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128732359</v>
+        <v>128728022</v>
       </c>
       <c r="B24" t="n">
-        <v>91466</v>
+        <v>91431</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2963,10 +2953,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>569820</v>
+        <v>569583</v>
       </c>
       <c r="R24" t="n">
-        <v>6958107</v>
+        <v>6958204</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3025,10 +3015,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128731612</v>
+        <v>128743262</v>
       </c>
       <c r="B25" t="n">
-        <v>91466</v>
+        <v>79089</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3036,21 +3026,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3060,10 +3050,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>569752</v>
+        <v>569732</v>
       </c>
       <c r="R25" t="n">
-        <v>6958091</v>
+        <v>6957870</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3122,10 +3112,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128743262</v>
+        <v>128739020</v>
       </c>
       <c r="B26" t="n">
-        <v>79089</v>
+        <v>57689</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3133,34 +3123,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>569732</v>
+        <v>569542</v>
       </c>
       <c r="R26" t="n">
-        <v>6957870</v>
+        <v>6958049</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3193,6 +3188,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3219,45 +3219,50 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128743252</v>
+        <v>128731107</v>
       </c>
       <c r="B27" t="n">
-        <v>98588</v>
+        <v>57849</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>569610</v>
+        <v>569705</v>
       </c>
       <c r="R27" t="n">
-        <v>6958005</v>
+        <v>6958098</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3290,11 +3295,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>2 exemplar</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3324,7 +3324,7 @@
         <v>128731489</v>
       </c>
       <c r="B28" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3422,50 +3422,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128731291</v>
+        <v>128729068</v>
       </c>
       <c r="B29" t="n">
-        <v>57689</v>
+        <v>80223</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>569726</v>
+        <v>569604</v>
       </c>
       <c r="R29" t="n">
-        <v>6958097</v>
+        <v>6958176</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3498,11 +3493,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på tall</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3529,7 +3519,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128728019</v>
+        <v>128731291</v>
       </c>
       <c r="B30" t="n">
         <v>57689</v>
@@ -3569,10 +3559,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>569577</v>
+        <v>569726</v>
       </c>
       <c r="R30" t="n">
-        <v>6958213</v>
+        <v>6958097</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3609,7 +3599,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>Ringhack av tretåig hackspett på tall</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3636,45 +3626,50 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128729068</v>
+        <v>128728019</v>
       </c>
       <c r="B31" t="n">
-        <v>80223</v>
+        <v>57689</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>569604</v>
+        <v>569577</v>
       </c>
       <c r="R31" t="n">
-        <v>6958176</v>
+        <v>6958213</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3707,6 +3702,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3733,38 +3733,42 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128730603</v>
+        <v>128728767</v>
       </c>
       <c r="B32" t="n">
-        <v>57689</v>
+        <v>92756</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -3773,10 +3777,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>569738</v>
+        <v>569639</v>
       </c>
       <c r="R32" t="n">
-        <v>6958117</v>
+        <v>6958231</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3813,7 +3817,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Äldre exemplar av ringhack på Tall från tretåig hackspett</t>
+          <t>4 äldre ett färskt års exemplar</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3840,10 +3844,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128730513</v>
+        <v>128730603</v>
       </c>
       <c r="B33" t="n">
-        <v>80194</v>
+        <v>57689</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3851,34 +3855,39 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>569656</v>
+        <v>569738</v>
       </c>
       <c r="R33" t="n">
-        <v>6958093</v>
+        <v>6958117</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3911,6 +3920,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Äldre exemplar av ringhack på Tall från tretåig hackspett</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4044,54 +4058,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128728767</v>
+        <v>128730513</v>
       </c>
       <c r="B35" t="n">
-        <v>92756</v>
+        <v>80194</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>569639</v>
+        <v>569656</v>
       </c>
       <c r="R35" t="n">
-        <v>6958231</v>
+        <v>6958093</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4124,11 +4129,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>4 äldre ett färskt års exemplar</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4155,7 +4155,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128731677</v>
+        <v>128728318</v>
       </c>
       <c r="B36" t="n">
         <v>79089</v>
@@ -4190,10 +4190,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>569769</v>
+        <v>569616</v>
       </c>
       <c r="R36" t="n">
-        <v>6958153</v>
+        <v>6958208</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4252,7 +4252,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128728318</v>
+        <v>128731677</v>
       </c>
       <c r="B37" t="n">
         <v>79089</v>
@@ -4287,10 +4287,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>569616</v>
+        <v>569769</v>
       </c>
       <c r="R37" t="n">
-        <v>6958208</v>
+        <v>6958153</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4349,45 +4349,50 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128743255</v>
+        <v>128729745</v>
       </c>
       <c r="B38" t="n">
-        <v>98588</v>
+        <v>57689</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>569613</v>
+        <v>569694</v>
       </c>
       <c r="R38" t="n">
-        <v>6957995</v>
+        <v>6958144</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4424,7 +4429,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>28 exemplar knärot</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4451,10 +4456,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128743254</v>
+        <v>128732677</v>
       </c>
       <c r="B39" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4479,17 +4484,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr"/>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>569547</v>
+        <v>569817</v>
       </c>
       <c r="R39" t="n">
-        <v>6958078</v>
+        <v>6958134</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4522,11 +4531,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>20 (ca) exemplar</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4553,50 +4557,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128729745</v>
+        <v>128743255</v>
       </c>
       <c r="B40" t="n">
-        <v>57689</v>
+        <v>98591</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>569694</v>
+        <v>569613</v>
       </c>
       <c r="R40" t="n">
-        <v>6958144</v>
+        <v>6957995</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4633,7 +4632,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>28 exemplar knärot</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4660,10 +4659,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128732677</v>
+        <v>128743254</v>
       </c>
       <c r="B41" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4688,21 +4687,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>569817</v>
+        <v>569547</v>
       </c>
       <c r="R41" t="n">
-        <v>6958134</v>
+        <v>6958078</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4735,6 +4730,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>20 (ca) exemplar</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4761,10 +4761,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128729439</v>
+        <v>128729962</v>
       </c>
       <c r="B42" t="n">
-        <v>91466</v>
+        <v>80194</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4772,21 +4772,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4796,10 +4796,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>569703</v>
+        <v>569643</v>
       </c>
       <c r="R42" t="n">
-        <v>6958175</v>
+        <v>6958117</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4965,10 +4965,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128729962</v>
+        <v>128729439</v>
       </c>
       <c r="B44" t="n">
-        <v>80194</v>
+        <v>91466</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4976,21 +4976,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5000,10 +5000,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>569643</v>
+        <v>569703</v>
       </c>
       <c r="R44" t="n">
-        <v>6958117</v>
+        <v>6958175</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5164,38 +5164,37 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128731799</v>
+        <v>128732627</v>
       </c>
       <c r="B46" t="n">
-        <v>57689</v>
+        <v>98591</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>6</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -5204,10 +5203,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>569774</v>
+        <v>569821</v>
       </c>
       <c r="R46" t="n">
-        <v>6958163</v>
+        <v>6958151</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5244,7 +5243,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>Kan finnas mer I blåbärsriset och mossan</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5271,38 +5270,37 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128732015</v>
+        <v>128728348</v>
       </c>
       <c r="B47" t="n">
-        <v>57689</v>
+        <v>98591</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>300</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -5311,10 +5309,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>569816</v>
+        <v>569616</v>
       </c>
       <c r="R47" t="n">
-        <v>6958081</v>
+        <v>6958208</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5347,11 +5345,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5378,37 +5371,38 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128728348</v>
+        <v>128731799</v>
       </c>
       <c r="B48" t="n">
-        <v>98588</v>
+        <v>57689</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>300</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -5417,10 +5411,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>569616</v>
+        <v>569774</v>
       </c>
       <c r="R48" t="n">
-        <v>6958208</v>
+        <v>6958163</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5453,6 +5447,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5479,7 +5478,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128728902</v>
+        <v>128732015</v>
       </c>
       <c r="B49" t="n">
         <v>57689</v>
@@ -5519,10 +5518,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>569673</v>
+        <v>569816</v>
       </c>
       <c r="R49" t="n">
-        <v>6958225</v>
+        <v>6958081</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5559,7 +5558,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5586,37 +5585,38 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128732627</v>
+        <v>128738187</v>
       </c>
       <c r="B50" t="n">
-        <v>98588</v>
+        <v>57689</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>6</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -5625,10 +5625,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>569821</v>
+        <v>569681</v>
       </c>
       <c r="R50" t="n">
-        <v>6958151</v>
+        <v>6957939</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5665,7 +5665,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Kan finnas mer I blåbärsriset och mossan</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5692,7 +5692,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128738187</v>
+        <v>128728902</v>
       </c>
       <c r="B51" t="n">
         <v>57689</v>
@@ -5732,10 +5732,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>569681</v>
+        <v>569673</v>
       </c>
       <c r="R51" t="n">
-        <v>6957939</v>
+        <v>6958225</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5772,7 +5772,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5799,45 +5799,49 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128731302</v>
+        <v>128729573</v>
       </c>
       <c r="B52" t="n">
-        <v>80154</v>
+        <v>98591</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>229497</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>569696</v>
+        <v>569706</v>
       </c>
       <c r="R52" t="n">
-        <v>6958031</v>
+        <v>6958159</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5896,49 +5900,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128729573</v>
+        <v>128731302</v>
       </c>
       <c r="B53" t="n">
-        <v>98588</v>
+        <v>80154</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>229497</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>569706</v>
+        <v>569696</v>
       </c>
       <c r="R53" t="n">
-        <v>6958159</v>
+        <v>6958031</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5997,7 +5997,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128732183</v>
+        <v>128738306</v>
       </c>
       <c r="B54" t="n">
         <v>57689</v>
@@ -6037,10 +6037,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>569777</v>
+        <v>569644</v>
       </c>
       <c r="R54" t="n">
-        <v>6958189</v>
+        <v>6957965</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6077,7 +6077,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6104,7 +6104,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128731037</v>
+        <v>128732183</v>
       </c>
       <c r="B55" t="n">
         <v>57689</v>
@@ -6135,7 +6135,7 @@
       <c r="I55" t="inlineStr"/>
       <c r="M55" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -6144,10 +6144,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>569673</v>
+        <v>569777</v>
       </c>
       <c r="R55" t="n">
-        <v>6958037</v>
+        <v>6958189</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6184,7 +6184,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6211,7 +6211,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128738306</v>
+        <v>128731037</v>
       </c>
       <c r="B56" t="n">
         <v>57689</v>
@@ -6242,7 +6242,7 @@
       <c r="I56" t="inlineStr"/>
       <c r="M56" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -6251,10 +6251,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>569644</v>
+        <v>569673</v>
       </c>
       <c r="R56" t="n">
-        <v>6957965</v>
+        <v>6958037</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6318,10 +6318,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128732124</v>
+        <v>128732806</v>
       </c>
       <c r="B57" t="n">
-        <v>80229</v>
+        <v>91477</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6329,21 +6329,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6463</v>
+        <v>1205</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6353,10 +6353,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>569816</v>
+        <v>569827</v>
       </c>
       <c r="R57" t="n">
-        <v>6958081</v>
+        <v>6958133</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6415,50 +6415,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128730490</v>
+        <v>128732719</v>
       </c>
       <c r="B58" t="n">
-        <v>57689</v>
+        <v>91920</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>569707</v>
+        <v>569821</v>
       </c>
       <c r="R58" t="n">
-        <v>6958131</v>
+        <v>6958151</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6491,11 +6486,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Både äldre och färska spår ( Ringhack av tretåig hackspett på tall)</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6522,10 +6512,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128730101</v>
+        <v>128728592</v>
       </c>
       <c r="B59" t="n">
-        <v>80230</v>
+        <v>80229</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6533,21 +6523,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6464</v>
+        <v>6463</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6557,10 +6547,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>569630</v>
+        <v>569604</v>
       </c>
       <c r="R59" t="n">
-        <v>6958139</v>
+        <v>6958176</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6619,10 +6609,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128730183</v>
+        <v>128732124</v>
       </c>
       <c r="B60" t="n">
-        <v>80154</v>
+        <v>80229</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6630,21 +6620,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>229497</v>
+        <v>6463</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6654,10 +6644,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>569630</v>
+        <v>569816</v>
       </c>
       <c r="R60" t="n">
-        <v>6958129</v>
+        <v>6958081</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6716,50 +6706,45 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128730422</v>
+        <v>128730101</v>
       </c>
       <c r="B61" t="n">
-        <v>57689</v>
+        <v>80230</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>569703</v>
+        <v>569630</v>
       </c>
       <c r="R61" t="n">
-        <v>6958116</v>
+        <v>6958139</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6792,11 +6777,6 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6823,50 +6803,45 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128739287</v>
+        <v>128731387</v>
       </c>
       <c r="B62" t="n">
-        <v>57689</v>
+        <v>80222</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>569481</v>
+        <v>569740</v>
       </c>
       <c r="R62" t="n">
-        <v>6958122</v>
+        <v>6958091</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6899,11 +6874,6 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6930,45 +6900,50 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128728592</v>
+        <v>128739287</v>
       </c>
       <c r="B63" t="n">
-        <v>80229</v>
+        <v>57689</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>569604</v>
+        <v>569481</v>
       </c>
       <c r="R63" t="n">
-        <v>6958176</v>
+        <v>6958122</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7001,6 +6976,11 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7027,45 +7007,50 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128732806</v>
+        <v>128730490</v>
       </c>
       <c r="B64" t="n">
-        <v>91477</v>
+        <v>57689</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1205</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>569827</v>
+        <v>569707</v>
       </c>
       <c r="R64" t="n">
-        <v>6958133</v>
+        <v>6958131</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7098,6 +7083,11 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Både äldre och färska spår ( Ringhack av tretåig hackspett på tall)</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7124,45 +7114,50 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128732719</v>
+        <v>128730422</v>
       </c>
       <c r="B65" t="n">
-        <v>91920</v>
+        <v>57689</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>569821</v>
+        <v>569703</v>
       </c>
       <c r="R65" t="n">
-        <v>6958151</v>
+        <v>6958116</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7195,6 +7190,11 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7221,10 +7221,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128731387</v>
+        <v>128730183</v>
       </c>
       <c r="B66" t="n">
-        <v>80222</v>
+        <v>80154</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7232,21 +7232,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6461</v>
+        <v>229497</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7256,10 +7256,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>569740</v>
+        <v>569630</v>
       </c>
       <c r="R66" t="n">
-        <v>6958091</v>
+        <v>6958129</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7318,10 +7318,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128730273</v>
+        <v>128729077</v>
       </c>
       <c r="B67" t="n">
-        <v>79089</v>
+        <v>80194</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7329,21 +7329,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7353,10 +7353,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>569692</v>
+        <v>569604</v>
       </c>
       <c r="R67" t="n">
-        <v>6958127</v>
+        <v>6958176</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7415,7 +7415,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128729077</v>
+        <v>128732112</v>
       </c>
       <c r="B68" t="n">
         <v>80194</v>
@@ -7450,10 +7450,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>569604</v>
+        <v>569824</v>
       </c>
       <c r="R68" t="n">
-        <v>6958176</v>
+        <v>6958091</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7512,10 +7512,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128732112</v>
+        <v>128730273</v>
       </c>
       <c r="B69" t="n">
-        <v>80194</v>
+        <v>79089</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7523,21 +7523,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7547,10 +7547,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>569824</v>
+        <v>569692</v>
       </c>
       <c r="R69" t="n">
-        <v>6958091</v>
+        <v>6958127</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7609,50 +7609,45 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128730998</v>
+        <v>128743263</v>
       </c>
       <c r="B70" t="n">
-        <v>57689</v>
+        <v>92790</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>5964</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>569670</v>
+        <v>569517</v>
       </c>
       <c r="R70" t="n">
-        <v>6958060</v>
+        <v>6958123</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7689,7 +7684,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Ringhack på tall. Även äldre</t>
+          <t>3 exemplar</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7716,10 +7711,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128730928</v>
+        <v>128731693</v>
       </c>
       <c r="B71" t="n">
-        <v>57689</v>
+        <v>91466</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7727,42 +7722,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>569673</v>
+        <v>569793</v>
       </c>
       <c r="R71" t="n">
-        <v>6958076</v>
+        <v>6958092</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7795,11 +7782,6 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Påbörjat bobygge av sannolikt tretåig hackspett. Ser ut att vara relativt färskt. 2 meter upp i död gran. Omkring 4,5 cm i diameter.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7826,7 +7808,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128728149</v>
+        <v>128732493</v>
       </c>
       <c r="B72" t="n">
         <v>57689</v>
@@ -7866,10 +7848,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>569585</v>
+        <v>569795</v>
       </c>
       <c r="R72" t="n">
-        <v>6958190</v>
+        <v>6958154</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7906,7 +7888,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7933,45 +7915,53 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128743263</v>
+        <v>128730928</v>
       </c>
       <c r="B73" t="n">
-        <v>92790</v>
+        <v>57689</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>5964</v>
+        <v>100109</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>569517</v>
+        <v>569673</v>
       </c>
       <c r="R73" t="n">
-        <v>6958123</v>
+        <v>6958076</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8008,7 +7998,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>3 exemplar</t>
+          <t>Påbörjat bobygge av sannolikt tretåig hackspett. Ser ut att vara relativt färskt. 2 meter upp i död gran. Omkring 4,5 cm i diameter.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8035,7 +8025,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128732493</v>
+        <v>128728149</v>
       </c>
       <c r="B74" t="n">
         <v>57689</v>
@@ -8075,10 +8065,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>569795</v>
+        <v>569585</v>
       </c>
       <c r="R74" t="n">
-        <v>6958154</v>
+        <v>6958190</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8115,7 +8105,7 @@
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8142,10 +8132,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128731693</v>
+        <v>128730998</v>
       </c>
       <c r="B75" t="n">
-        <v>91466</v>
+        <v>57689</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8153,34 +8143,39 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>569793</v>
+        <v>569670</v>
       </c>
       <c r="R75" t="n">
-        <v>6958092</v>
+        <v>6958060</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8213,6 +8208,11 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Ringhack på tall. Även äldre</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8346,49 +8346,45 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128732718</v>
+        <v>128743247</v>
       </c>
       <c r="B77" t="n">
-        <v>98588</v>
+        <v>57689</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>569834</v>
+        <v>569714</v>
       </c>
       <c r="R77" t="n">
-        <v>6958143</v>
+        <v>6957901</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8421,6 +8417,11 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på gran ( färska spår)</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8447,37 +8448,38 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128733005</v>
+        <v>128731284</v>
       </c>
       <c r="B78" t="n">
-        <v>98588</v>
+        <v>57849</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>7</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
@@ -8486,10 +8488,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>569882</v>
+        <v>569677</v>
       </c>
       <c r="R78" t="n">
-        <v>6958106</v>
+        <v>6958066</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8548,10 +8550,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128743247</v>
+        <v>128731100</v>
       </c>
       <c r="B79" t="n">
-        <v>57689</v>
+        <v>91484</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8559,21 +8561,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8583,10 +8585,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>569714</v>
+        <v>569688</v>
       </c>
       <c r="R79" t="n">
-        <v>6957901</v>
+        <v>6958069</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8619,11 +8621,6 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på gran ( färska spår)</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8650,38 +8647,37 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128731284</v>
+        <v>128732718</v>
       </c>
       <c r="B80" t="n">
-        <v>57849</v>
+        <v>98591</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>18</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
@@ -8690,10 +8686,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>569677</v>
+        <v>569834</v>
       </c>
       <c r="R80" t="n">
-        <v>6958066</v>
+        <v>6958143</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8752,45 +8748,49 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128731100</v>
+        <v>128733005</v>
       </c>
       <c r="B81" t="n">
-        <v>91484</v>
+        <v>98591</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>569688</v>
+        <v>569882</v>
       </c>
       <c r="R81" t="n">
-        <v>6958069</v>
+        <v>6958106</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8849,49 +8849,45 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128729895</v>
+        <v>128731226</v>
       </c>
       <c r="B82" t="n">
-        <v>98588</v>
+        <v>91484</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>569713</v>
+        <v>569705</v>
       </c>
       <c r="R82" t="n">
-        <v>6958138</v>
+        <v>6958098</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8950,10 +8946,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128731226</v>
+        <v>128743244</v>
       </c>
       <c r="B83" t="n">
-        <v>91484</v>
+        <v>91466</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8961,21 +8957,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8985,10 +8981,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>569705</v>
+        <v>569736</v>
       </c>
       <c r="R83" t="n">
-        <v>6958098</v>
+        <v>6957867</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9154,45 +9150,49 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128743244</v>
+        <v>128729895</v>
       </c>
       <c r="B85" t="n">
-        <v>91466</v>
+        <v>98591</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>569736</v>
+        <v>569713</v>
       </c>
       <c r="R85" t="n">
-        <v>6957867</v>
+        <v>6958138</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9254,7 +9254,7 @@
         <v>128743257</v>
       </c>
       <c r="B86" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9353,10 +9353,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128729666</v>
+        <v>128729069</v>
       </c>
       <c r="B87" t="n">
-        <v>57689</v>
+        <v>79089</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9364,39 +9364,34 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>569706</v>
+        <v>569699</v>
       </c>
       <c r="R87" t="n">
-        <v>6958159</v>
+        <v>6958200</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9429,11 +9424,6 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9460,10 +9450,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128727978</v>
+        <v>128728419</v>
       </c>
       <c r="B88" t="n">
-        <v>57689</v>
+        <v>79089</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9471,39 +9461,34 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>569564</v>
+        <v>569608</v>
       </c>
       <c r="R88" t="n">
-        <v>6958213</v>
+        <v>6958227</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9540,7 +9525,7 @@
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Riklig förekomst inom området</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9567,7 +9552,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128729069</v>
+        <v>128743261</v>
       </c>
       <c r="B89" t="n">
         <v>79089</v>
@@ -9602,10 +9587,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>569699</v>
+        <v>569495</v>
       </c>
       <c r="R89" t="n">
-        <v>6958200</v>
+        <v>6958117</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9664,10 +9649,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128728419</v>
+        <v>128729666</v>
       </c>
       <c r="B90" t="n">
-        <v>79089</v>
+        <v>57689</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9675,34 +9660,39 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P90" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>569608</v>
+        <v>569706</v>
       </c>
       <c r="R90" t="n">
-        <v>6958227</v>
+        <v>6958159</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9739,7 +9729,7 @@
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>Riklig förekomst inom området</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9766,45 +9756,50 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128738599</v>
+        <v>128727978</v>
       </c>
       <c r="B91" t="n">
-        <v>80154</v>
+        <v>57689</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>229497</v>
+        <v>100109</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P91" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>569608</v>
+        <v>569564</v>
       </c>
       <c r="R91" t="n">
-        <v>6958048</v>
+        <v>6958213</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9837,6 +9832,11 @@
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9863,32 +9863,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128743261</v>
+        <v>128738599</v>
       </c>
       <c r="B92" t="n">
-        <v>79089</v>
+        <v>80154</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9898,10 +9898,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>569495</v>
+        <v>569608</v>
       </c>
       <c r="R92" t="n">
-        <v>6958117</v>
+        <v>6958048</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9960,49 +9960,45 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128731648</v>
+        <v>128728152</v>
       </c>
       <c r="B93" t="n">
-        <v>98588</v>
+        <v>91466</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>119</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>569766</v>
+        <v>569577</v>
       </c>
       <c r="R93" t="n">
-        <v>6958144</v>
+        <v>6958213</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10035,11 +10031,6 @@
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC93" t="inlineStr">
-        <is>
-          <t>Ca ( möjligtvis fler)</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10066,10 +10057,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128728152</v>
+        <v>128728274</v>
       </c>
       <c r="B94" t="n">
-        <v>91466</v>
+        <v>57689</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10077,34 +10068,39 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P94" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>569577</v>
+        <v>569599</v>
       </c>
       <c r="R94" t="n">
-        <v>6958213</v>
+        <v>6958201</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10137,6 +10133,11 @@
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>Både äldre och färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10163,38 +10164,37 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128728274</v>
+        <v>128731648</v>
       </c>
       <c r="B95" t="n">
-        <v>57689</v>
+        <v>98591</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr"/>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>119</t>
         </is>
       </c>
       <c r="P95" t="inlineStr">
@@ -10203,10 +10203,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>569599</v>
+        <v>569766</v>
       </c>
       <c r="R95" t="n">
-        <v>6958201</v>
+        <v>6958144</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10243,7 +10243,7 @@
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>Både äldre och färska ringhack på tall</t>
+          <t>Ca ( möjligtvis fler)</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10273,7 +10273,7 @@
         <v>128743253</v>
       </c>
       <c r="B96" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10375,7 +10375,7 @@
         <v>128743256</v>
       </c>
       <c r="B97" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>

--- a/artfynd/A 39666-2025 artfynd.xlsx
+++ b/artfynd/A 39666-2025 artfynd.xlsx
@@ -2217,49 +2217,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128731490</v>
+        <v>128728515</v>
       </c>
       <c r="B17" t="n">
-        <v>98591</v>
+        <v>97462</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>569759</v>
+        <v>569608</v>
       </c>
       <c r="R17" t="n">
-        <v>6958118</v>
+        <v>6958227</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2318,7 +2314,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128730429</v>
+        <v>128731490</v>
       </c>
       <c r="B18" t="n">
         <v>98591</v>
@@ -2348,7 +2344,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2357,10 +2353,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>569683</v>
+        <v>569759</v>
       </c>
       <c r="R18" t="n">
-        <v>6958128</v>
+        <v>6958118</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2419,45 +2415,49 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128728515</v>
+        <v>128730429</v>
       </c>
       <c r="B19" t="n">
-        <v>97462</v>
+        <v>98591</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>569608</v>
+        <v>569683</v>
       </c>
       <c r="R19" t="n">
-        <v>6958227</v>
+        <v>6958128</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -3733,42 +3733,38 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128728767</v>
+        <v>128730603</v>
       </c>
       <c r="B32" t="n">
-        <v>92756</v>
+        <v>57689</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -3777,10 +3773,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>569639</v>
+        <v>569738</v>
       </c>
       <c r="R32" t="n">
-        <v>6958231</v>
+        <v>6958117</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3817,7 +3813,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>4 äldre ett färskt års exemplar</t>
+          <t>Äldre exemplar av ringhack på Tall från tretåig hackspett</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3844,38 +3840,38 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128730603</v>
+        <v>128728303</v>
       </c>
       <c r="B33" t="n">
-        <v>57689</v>
+        <v>57681</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>100110</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>J.F. Gmelin, 1788</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -3884,10 +3880,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>569738</v>
+        <v>569584</v>
       </c>
       <c r="R33" t="n">
-        <v>6958117</v>
+        <v>6958214</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3924,7 +3920,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Äldre exemplar av ringhack på Tall från tretåig hackspett</t>
+          <t>Hörs i närheten</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3951,10 +3947,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128728303</v>
+        <v>128728767</v>
       </c>
       <c r="B34" t="n">
-        <v>57681</v>
+        <v>92756</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3962,27 +3958,31 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100110</v>
+        <v>4364</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -3991,10 +3991,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>569584</v>
+        <v>569639</v>
       </c>
       <c r="R34" t="n">
-        <v>6958214</v>
+        <v>6958231</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4031,7 +4031,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Hörs i närheten</t>
+          <t>4 äldre ett färskt års exemplar</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4155,45 +4155,49 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128728318</v>
+        <v>128732677</v>
       </c>
       <c r="B36" t="n">
-        <v>79089</v>
+        <v>98591</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>569616</v>
+        <v>569817</v>
       </c>
       <c r="R36" t="n">
-        <v>6958208</v>
+        <v>6958134</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4252,32 +4256,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128731677</v>
+        <v>128743255</v>
       </c>
       <c r="B37" t="n">
-        <v>79089</v>
+        <v>98591</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4287,10 +4291,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>569769</v>
+        <v>569613</v>
       </c>
       <c r="R37" t="n">
-        <v>6958153</v>
+        <v>6957995</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4323,6 +4327,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>28 exemplar knärot</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4349,50 +4358,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128729745</v>
+        <v>128743254</v>
       </c>
       <c r="B38" t="n">
-        <v>57689</v>
+        <v>98591</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>569694</v>
+        <v>569547</v>
       </c>
       <c r="R38" t="n">
-        <v>6958144</v>
+        <v>6958078</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4429,7 +4433,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>20 (ca) exemplar</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4456,49 +4460,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128732677</v>
+        <v>128728318</v>
       </c>
       <c r="B39" t="n">
-        <v>98591</v>
+        <v>79089</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>569817</v>
+        <v>569616</v>
       </c>
       <c r="R39" t="n">
-        <v>6958134</v>
+        <v>6958208</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4557,32 +4557,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128743255</v>
+        <v>128731677</v>
       </c>
       <c r="B40" t="n">
-        <v>98591</v>
+        <v>79089</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4592,10 +4592,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>569613</v>
+        <v>569769</v>
       </c>
       <c r="R40" t="n">
-        <v>6957995</v>
+        <v>6958153</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4628,11 +4628,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>28 exemplar knärot</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4659,45 +4654,50 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128743254</v>
+        <v>128729745</v>
       </c>
       <c r="B41" t="n">
-        <v>98591</v>
+        <v>57689</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>569547</v>
+        <v>569694</v>
       </c>
       <c r="R41" t="n">
-        <v>6958078</v>
+        <v>6958144</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>20 (ca) exemplar</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4761,10 +4761,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128729962</v>
+        <v>128729439</v>
       </c>
       <c r="B42" t="n">
-        <v>80194</v>
+        <v>91466</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4772,21 +4772,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4796,10 +4796,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>569643</v>
+        <v>569703</v>
       </c>
       <c r="R42" t="n">
-        <v>6958117</v>
+        <v>6958175</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4858,10 +4858,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128730475</v>
+        <v>128729962</v>
       </c>
       <c r="B43" t="n">
-        <v>57689</v>
+        <v>80194</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4869,39 +4869,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>569675</v>
+        <v>569643</v>
       </c>
       <c r="R43" t="n">
-        <v>6958098</v>
+        <v>6958117</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4934,11 +4929,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4965,10 +4955,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128729439</v>
+        <v>128730475</v>
       </c>
       <c r="B44" t="n">
-        <v>91466</v>
+        <v>57689</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4976,34 +4966,39 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>569703</v>
+        <v>569675</v>
       </c>
       <c r="R44" t="n">
-        <v>6958175</v>
+        <v>6958098</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5036,6 +5031,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5799,49 +5799,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128729573</v>
+        <v>128731302</v>
       </c>
       <c r="B52" t="n">
-        <v>98591</v>
+        <v>80154</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>229497</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>569706</v>
+        <v>569696</v>
       </c>
       <c r="R52" t="n">
-        <v>6958159</v>
+        <v>6958031</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5900,45 +5896,49 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128731302</v>
+        <v>128729573</v>
       </c>
       <c r="B53" t="n">
-        <v>80154</v>
+        <v>98591</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>229497</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>569696</v>
+        <v>569706</v>
       </c>
       <c r="R53" t="n">
-        <v>6958031</v>
+        <v>6958159</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>

--- a/artfynd/A 39666-2025 artfynd.xlsx
+++ b/artfynd/A 39666-2025 artfynd.xlsx
@@ -772,7 +772,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128739007</v>
+        <v>128743246</v>
       </c>
       <c r="B3" t="n">
         <v>57689</v>
@@ -801,21 +801,16 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>569542</v>
+        <v>569648</v>
       </c>
       <c r="R3" t="n">
-        <v>6958069</v>
+        <v>6957944</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +847,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack av tretåig hackspett på Tall ( äldre och färska spår)</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -986,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128743246</v>
+        <v>128739007</v>
       </c>
       <c r="B5" t="n">
         <v>57689</v>
@@ -1015,16 +1010,21 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>569648</v>
+        <v>569542</v>
       </c>
       <c r="R5" t="n">
-        <v>6957944</v>
+        <v>6958069</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1061,7 +1061,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall ( äldre och färska spår)</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1088,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128728896</v>
+        <v>128732983</v>
       </c>
       <c r="B6" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1127,10 +1127,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>569601</v>
+        <v>569873</v>
       </c>
       <c r="R6" t="n">
-        <v>6958191</v>
+        <v>6958099</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1189,10 +1189,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128732983</v>
+        <v>128728896</v>
       </c>
       <c r="B7" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1219,7 +1219,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1228,10 +1228,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>569873</v>
+        <v>569601</v>
       </c>
       <c r="R7" t="n">
-        <v>6958099</v>
+        <v>6958191</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1293,7 +1293,7 @@
         <v>128729409</v>
       </c>
       <c r="B8" t="n">
-        <v>91466</v>
+        <v>91467</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1494,10 +1494,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128730571</v>
+        <v>128732765</v>
       </c>
       <c r="B10" t="n">
-        <v>91484</v>
+        <v>91763</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1505,21 +1505,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1529,10 +1529,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>569660</v>
+        <v>569827</v>
       </c>
       <c r="R10" t="n">
-        <v>6958074</v>
+        <v>6958133</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1591,7 +1591,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128743245</v>
+        <v>128732276</v>
       </c>
       <c r="B11" t="n">
         <v>57689</v>
@@ -1620,16 +1620,21 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>569590</v>
+        <v>569841</v>
       </c>
       <c r="R11" t="n">
-        <v>6958014</v>
+        <v>6958102</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1666,7 +1671,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall ( färska spår)</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1693,7 +1698,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128732276</v>
+        <v>128743245</v>
       </c>
       <c r="B12" t="n">
         <v>57689</v>
@@ -1722,21 +1727,16 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>569841</v>
+        <v>569590</v>
       </c>
       <c r="R12" t="n">
-        <v>6958102</v>
+        <v>6958014</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack av tretåig hackspett på Tall ( färska spår)</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1800,10 +1800,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128732765</v>
+        <v>128730571</v>
       </c>
       <c r="B13" t="n">
-        <v>91762</v>
+        <v>91485</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1811,21 +1811,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1835,10 +1835,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>569827</v>
+        <v>569660</v>
       </c>
       <c r="R13" t="n">
-        <v>6958133</v>
+        <v>6958074</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2016,7 +2016,7 @@
         <v>128733181</v>
       </c>
       <c r="B15" t="n">
-        <v>98508</v>
+        <v>98509</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2110,38 +2110,37 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128731601</v>
+        <v>128731490</v>
       </c>
       <c r="B16" t="n">
-        <v>57689</v>
+        <v>98592</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>20</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2150,10 +2149,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>569752</v>
+        <v>569759</v>
       </c>
       <c r="R16" t="n">
-        <v>6958091</v>
+        <v>6958118</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2186,11 +2185,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2220,7 +2214,7 @@
         <v>128728515</v>
       </c>
       <c r="B17" t="n">
-        <v>97462</v>
+        <v>97463</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2314,37 +2308,38 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128731490</v>
+        <v>128731601</v>
       </c>
       <c r="B18" t="n">
-        <v>98591</v>
+        <v>57689</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>20</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2353,10 +2348,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>569759</v>
+        <v>569752</v>
       </c>
       <c r="R18" t="n">
-        <v>6958118</v>
+        <v>6958091</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2389,6 +2384,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2418,7 +2418,7 @@
         <v>128730429</v>
       </c>
       <c r="B19" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2516,10 +2516,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128732359</v>
+        <v>128731107</v>
       </c>
       <c r="B20" t="n">
-        <v>91466</v>
+        <v>57849</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2527,34 +2527,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>569820</v>
+        <v>569705</v>
       </c>
       <c r="R20" t="n">
-        <v>6958107</v>
+        <v>6958098</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2613,45 +2618,49 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128731612</v>
+        <v>128730720</v>
       </c>
       <c r="B21" t="n">
-        <v>91466</v>
+        <v>98592</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>569752</v>
+        <v>569692</v>
       </c>
       <c r="R21" t="n">
-        <v>6958091</v>
+        <v>6958094</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2684,6 +2693,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ca</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2710,10 +2724,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128730720</v>
+        <v>128743252</v>
       </c>
       <c r="B22" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2738,21 +2752,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>569692</v>
+        <v>569610</v>
       </c>
       <c r="R22" t="n">
-        <v>6958094</v>
+        <v>6958005</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2789,7 +2799,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ca</t>
+          <t>2 exemplar</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2816,32 +2826,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128743252</v>
+        <v>128732359</v>
       </c>
       <c r="B23" t="n">
-        <v>98591</v>
+        <v>91467</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2851,10 +2861,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>569610</v>
+        <v>569820</v>
       </c>
       <c r="R23" t="n">
-        <v>6958005</v>
+        <v>6958107</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2887,11 +2897,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>2 exemplar</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2918,32 +2923,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128728022</v>
+        <v>128731612</v>
       </c>
       <c r="B24" t="n">
-        <v>91431</v>
+        <v>91467</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2953,10 +2958,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>569583</v>
+        <v>569752</v>
       </c>
       <c r="R24" t="n">
-        <v>6958204</v>
+        <v>6958091</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3015,32 +3020,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128743262</v>
+        <v>128728022</v>
       </c>
       <c r="B25" t="n">
-        <v>79089</v>
+        <v>91432</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3050,10 +3055,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>569732</v>
+        <v>569583</v>
       </c>
       <c r="R25" t="n">
-        <v>6957870</v>
+        <v>6958204</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3112,10 +3117,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128739020</v>
+        <v>128743262</v>
       </c>
       <c r="B26" t="n">
-        <v>57689</v>
+        <v>79089</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3123,39 +3128,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>569542</v>
+        <v>569732</v>
       </c>
       <c r="R26" t="n">
-        <v>6958049</v>
+        <v>6957870</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3188,11 +3188,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3219,10 +3214,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128731107</v>
+        <v>128739020</v>
       </c>
       <c r="B27" t="n">
-        <v>57849</v>
+        <v>57689</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3230,27 +3225,27 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3259,10 +3254,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>569705</v>
+        <v>569542</v>
       </c>
       <c r="R27" t="n">
-        <v>6958098</v>
+        <v>6958049</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3295,6 +3290,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3321,37 +3321,38 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128731489</v>
+        <v>128731291</v>
       </c>
       <c r="B28" t="n">
-        <v>98591</v>
+        <v>57689</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>45</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3360,10 +3361,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>569752</v>
+        <v>569726</v>
       </c>
       <c r="R28" t="n">
-        <v>6958091</v>
+        <v>6958097</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3396,6 +3397,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på tall</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3422,45 +3428,50 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128729068</v>
+        <v>128728019</v>
       </c>
       <c r="B29" t="n">
-        <v>80223</v>
+        <v>57689</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>569604</v>
+        <v>569577</v>
       </c>
       <c r="R29" t="n">
-        <v>6958176</v>
+        <v>6958213</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3493,6 +3504,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3519,50 +3535,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128731291</v>
+        <v>128729068</v>
       </c>
       <c r="B30" t="n">
-        <v>57689</v>
+        <v>80223</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>569726</v>
+        <v>569604</v>
       </c>
       <c r="R30" t="n">
-        <v>6958097</v>
+        <v>6958176</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3595,11 +3606,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på tall</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3626,38 +3632,37 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128728019</v>
+        <v>128731489</v>
       </c>
       <c r="B31" t="n">
-        <v>57689</v>
+        <v>98592</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>45</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -3666,10 +3671,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>569577</v>
+        <v>569752</v>
       </c>
       <c r="R31" t="n">
-        <v>6958213</v>
+        <v>6958091</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3702,11 +3707,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3733,38 +3733,38 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128730603</v>
+        <v>128728303</v>
       </c>
       <c r="B32" t="n">
-        <v>57689</v>
+        <v>57681</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>100110</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>J.F. Gmelin, 1788</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -3773,10 +3773,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>569738</v>
+        <v>569584</v>
       </c>
       <c r="R32" t="n">
-        <v>6958117</v>
+        <v>6958214</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3813,7 +3813,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Äldre exemplar av ringhack på Tall från tretåig hackspett</t>
+          <t>Hörs i närheten</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3840,38 +3840,38 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128728303</v>
+        <v>128730603</v>
       </c>
       <c r="B33" t="n">
-        <v>57681</v>
+        <v>57689</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100110</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -3880,10 +3880,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>569584</v>
+        <v>569738</v>
       </c>
       <c r="R33" t="n">
-        <v>6958214</v>
+        <v>6958117</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3920,7 +3920,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Hörs i närheten</t>
+          <t>Äldre exemplar av ringhack på Tall från tretåig hackspett</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3950,7 +3950,7 @@
         <v>128728767</v>
       </c>
       <c r="B34" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4155,37 +4155,38 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128732677</v>
+        <v>128729745</v>
       </c>
       <c r="B36" t="n">
-        <v>98591</v>
+        <v>57689</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>12</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4194,10 +4195,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>569817</v>
+        <v>569694</v>
       </c>
       <c r="R36" t="n">
-        <v>6958134</v>
+        <v>6958144</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4230,6 +4231,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4256,32 +4262,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128743255</v>
+        <v>128728318</v>
       </c>
       <c r="B37" t="n">
-        <v>98591</v>
+        <v>79089</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4291,10 +4297,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>569613</v>
+        <v>569616</v>
       </c>
       <c r="R37" t="n">
-        <v>6957995</v>
+        <v>6958208</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4327,11 +4333,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>28 exemplar knärot</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4358,32 +4359,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128743254</v>
+        <v>128731677</v>
       </c>
       <c r="B38" t="n">
-        <v>98591</v>
+        <v>79089</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4393,10 +4394,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>569547</v>
+        <v>569769</v>
       </c>
       <c r="R38" t="n">
-        <v>6958078</v>
+        <v>6958153</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4429,11 +4430,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>20 (ca) exemplar</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4460,45 +4456,49 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128728318</v>
+        <v>128732677</v>
       </c>
       <c r="B39" t="n">
-        <v>79089</v>
+        <v>98592</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>569616</v>
+        <v>569817</v>
       </c>
       <c r="R39" t="n">
-        <v>6958208</v>
+        <v>6958134</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4557,32 +4557,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128731677</v>
+        <v>128743254</v>
       </c>
       <c r="B40" t="n">
-        <v>79089</v>
+        <v>98592</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4592,10 +4592,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>569769</v>
+        <v>569547</v>
       </c>
       <c r="R40" t="n">
-        <v>6958153</v>
+        <v>6958078</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4628,6 +4628,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>20 (ca) exemplar</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4654,50 +4659,45 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128729745</v>
+        <v>128743255</v>
       </c>
       <c r="B41" t="n">
-        <v>57689</v>
+        <v>98592</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>569694</v>
+        <v>569613</v>
       </c>
       <c r="R41" t="n">
-        <v>6958144</v>
+        <v>6957995</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>28 exemplar knärot</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4764,7 +4764,7 @@
         <v>128729439</v>
       </c>
       <c r="B42" t="n">
-        <v>91466</v>
+        <v>91467</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5164,10 +5164,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128732627</v>
+        <v>128728348</v>
       </c>
       <c r="B46" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5194,7 +5194,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>300</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -5203,10 +5203,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>569821</v>
+        <v>569616</v>
       </c>
       <c r="R46" t="n">
-        <v>6958151</v>
+        <v>6958208</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5239,11 +5239,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Kan finnas mer I blåbärsriset och mossan</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5270,10 +5265,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128728348</v>
+        <v>128732627</v>
       </c>
       <c r="B47" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5300,7 +5295,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -5309,10 +5304,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>569616</v>
+        <v>569821</v>
       </c>
       <c r="R47" t="n">
-        <v>6958208</v>
+        <v>6958151</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5345,6 +5340,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Kan finnas mer I blåbärsriset och mossan</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5371,7 +5371,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128731799</v>
+        <v>128728902</v>
       </c>
       <c r="B48" t="n">
         <v>57689</v>
@@ -5402,7 +5402,7 @@
       <c r="I48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -5411,10 +5411,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>569774</v>
+        <v>569673</v>
       </c>
       <c r="R48" t="n">
-        <v>6958163</v>
+        <v>6958225</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5478,7 +5478,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128732015</v>
+        <v>128731799</v>
       </c>
       <c r="B49" t="n">
         <v>57689</v>
@@ -5509,7 +5509,7 @@
       <c r="I49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -5518,10 +5518,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>569816</v>
+        <v>569774</v>
       </c>
       <c r="R49" t="n">
-        <v>6958081</v>
+        <v>6958163</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5558,7 +5558,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5585,7 +5585,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128738187</v>
+        <v>128732015</v>
       </c>
       <c r="B50" t="n">
         <v>57689</v>
@@ -5625,10 +5625,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>569681</v>
+        <v>569816</v>
       </c>
       <c r="R50" t="n">
-        <v>6957939</v>
+        <v>6958081</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5692,7 +5692,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128728902</v>
+        <v>128738187</v>
       </c>
       <c r="B51" t="n">
         <v>57689</v>
@@ -5732,10 +5732,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>569673</v>
+        <v>569681</v>
       </c>
       <c r="R51" t="n">
-        <v>6958225</v>
+        <v>6957939</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5772,7 +5772,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5899,7 +5899,7 @@
         <v>128729573</v>
       </c>
       <c r="B53" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5997,7 +5997,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128738306</v>
+        <v>128731037</v>
       </c>
       <c r="B54" t="n">
         <v>57689</v>
@@ -6028,7 +6028,7 @@
       <c r="I54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -6037,10 +6037,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>569644</v>
+        <v>569673</v>
       </c>
       <c r="R54" t="n">
-        <v>6957965</v>
+        <v>6958037</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6104,7 +6104,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128732183</v>
+        <v>128738306</v>
       </c>
       <c r="B55" t="n">
         <v>57689</v>
@@ -6144,10 +6144,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>569777</v>
+        <v>569644</v>
       </c>
       <c r="R55" t="n">
-        <v>6958189</v>
+        <v>6957965</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6184,7 +6184,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6211,7 +6211,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128731037</v>
+        <v>128732183</v>
       </c>
       <c r="B56" t="n">
         <v>57689</v>
@@ -6242,7 +6242,7 @@
       <c r="I56" t="inlineStr"/>
       <c r="M56" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -6251,10 +6251,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>569673</v>
+        <v>569777</v>
       </c>
       <c r="R56" t="n">
-        <v>6958037</v>
+        <v>6958189</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6291,7 +6291,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6321,7 +6321,7 @@
         <v>128732806</v>
       </c>
       <c r="B57" t="n">
-        <v>91477</v>
+        <v>91478</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6418,7 +6418,7 @@
         <v>128732719</v>
       </c>
       <c r="B58" t="n">
-        <v>91920</v>
+        <v>91921</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6900,7 +6900,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128739287</v>
+        <v>128730490</v>
       </c>
       <c r="B63" t="n">
         <v>57689</v>
@@ -6940,10 +6940,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>569481</v>
+        <v>569707</v>
       </c>
       <c r="R63" t="n">
-        <v>6958122</v>
+        <v>6958131</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6980,7 +6980,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Både äldre och färska spår ( Ringhack av tretåig hackspett på tall)</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7007,7 +7007,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128730490</v>
+        <v>128730422</v>
       </c>
       <c r="B64" t="n">
         <v>57689</v>
@@ -7047,10 +7047,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>569707</v>
+        <v>569703</v>
       </c>
       <c r="R64" t="n">
-        <v>6958131</v>
+        <v>6958116</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7087,7 +7087,7 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Både äldre och färska spår ( Ringhack av tretåig hackspett på tall)</t>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7114,7 +7114,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128730422</v>
+        <v>128739287</v>
       </c>
       <c r="B65" t="n">
         <v>57689</v>
@@ -7154,10 +7154,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>569703</v>
+        <v>569481</v>
       </c>
       <c r="R65" t="n">
-        <v>6958116</v>
+        <v>6958122</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7194,7 +7194,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7318,10 +7318,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128729077</v>
+        <v>128730273</v>
       </c>
       <c r="B67" t="n">
-        <v>80194</v>
+        <v>79089</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7329,21 +7329,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7353,10 +7353,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>569604</v>
+        <v>569692</v>
       </c>
       <c r="R67" t="n">
-        <v>6958176</v>
+        <v>6958127</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7415,7 +7415,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128732112</v>
+        <v>128729077</v>
       </c>
       <c r="B68" t="n">
         <v>80194</v>
@@ -7450,10 +7450,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>569824</v>
+        <v>569604</v>
       </c>
       <c r="R68" t="n">
-        <v>6958091</v>
+        <v>6958176</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7512,10 +7512,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128730273</v>
+        <v>128732112</v>
       </c>
       <c r="B69" t="n">
-        <v>79089</v>
+        <v>80194</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7523,21 +7523,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7547,10 +7547,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>569692</v>
+        <v>569824</v>
       </c>
       <c r="R69" t="n">
-        <v>6958127</v>
+        <v>6958091</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7609,45 +7609,50 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128743263</v>
+        <v>128728149</v>
       </c>
       <c r="B70" t="n">
-        <v>92790</v>
+        <v>57689</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>5964</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>569517</v>
+        <v>569585</v>
       </c>
       <c r="R70" t="n">
-        <v>6958123</v>
+        <v>6958190</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7684,7 +7689,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>3 exemplar</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7711,10 +7716,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128731693</v>
+        <v>128732493</v>
       </c>
       <c r="B71" t="n">
-        <v>91466</v>
+        <v>57689</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7722,34 +7727,39 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>569793</v>
+        <v>569795</v>
       </c>
       <c r="R71" t="n">
-        <v>6958092</v>
+        <v>6958154</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7782,6 +7792,11 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7808,7 +7823,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128732493</v>
+        <v>128730998</v>
       </c>
       <c r="B72" t="n">
         <v>57689</v>
@@ -7848,10 +7863,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>569795</v>
+        <v>569670</v>
       </c>
       <c r="R72" t="n">
-        <v>6958154</v>
+        <v>6958060</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7888,7 +7903,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>Ringhack på tall. Även äldre</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8025,10 +8040,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128728149</v>
+        <v>128731693</v>
       </c>
       <c r="B74" t="n">
-        <v>57689</v>
+        <v>91467</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8036,39 +8051,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>569585</v>
+        <v>569793</v>
       </c>
       <c r="R74" t="n">
-        <v>6958190</v>
+        <v>6958092</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8101,11 +8111,6 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8132,50 +8137,45 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128730998</v>
+        <v>128743263</v>
       </c>
       <c r="B75" t="n">
-        <v>57689</v>
+        <v>92791</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100109</v>
+        <v>5964</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>569670</v>
+        <v>569517</v>
       </c>
       <c r="R75" t="n">
-        <v>6958060</v>
+        <v>6958123</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8212,7 +8212,7 @@
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>Ringhack på tall. Även äldre</t>
+          <t>3 exemplar</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8239,38 +8239,37 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128732848</v>
+        <v>128733005</v>
       </c>
       <c r="B76" t="n">
-        <v>57689</v>
+        <v>98592</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>7</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
@@ -8279,10 +8278,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>569873</v>
+        <v>569882</v>
       </c>
       <c r="R76" t="n">
-        <v>6958099</v>
+        <v>6958106</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8315,11 +8314,6 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8346,45 +8340,49 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128743247</v>
+        <v>128732718</v>
       </c>
       <c r="B77" t="n">
-        <v>57689</v>
+        <v>98592</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>569714</v>
+        <v>569834</v>
       </c>
       <c r="R77" t="n">
-        <v>6957901</v>
+        <v>6958143</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8417,11 +8415,6 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på gran ( färska spår)</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8448,10 +8441,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128731284</v>
+        <v>128743247</v>
       </c>
       <c r="B78" t="n">
-        <v>57849</v>
+        <v>57689</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8459,39 +8452,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>569677</v>
+        <v>569714</v>
       </c>
       <c r="R78" t="n">
-        <v>6958066</v>
+        <v>6957901</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8524,6 +8512,11 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på gran ( färska spår)</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8550,10 +8543,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128731100</v>
+        <v>128732848</v>
       </c>
       <c r="B79" t="n">
-        <v>91484</v>
+        <v>57689</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8561,34 +8554,39 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>569688</v>
+        <v>569873</v>
       </c>
       <c r="R79" t="n">
-        <v>6958069</v>
+        <v>6958099</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8621,6 +8619,11 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8647,49 +8650,45 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128732718</v>
+        <v>128731100</v>
       </c>
       <c r="B80" t="n">
-        <v>98591</v>
+        <v>91485</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>569834</v>
+        <v>569688</v>
       </c>
       <c r="R80" t="n">
-        <v>6958143</v>
+        <v>6958069</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8748,37 +8747,38 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128733005</v>
+        <v>128731284</v>
       </c>
       <c r="B81" t="n">
-        <v>98591</v>
+        <v>57849</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>7</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
@@ -8787,10 +8787,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>569882</v>
+        <v>569677</v>
       </c>
       <c r="R81" t="n">
-        <v>6958106</v>
+        <v>6958066</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8849,10 +8849,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128731226</v>
+        <v>128743244</v>
       </c>
       <c r="B82" t="n">
-        <v>91484</v>
+        <v>91467</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8860,21 +8860,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8884,10 +8884,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>569705</v>
+        <v>569736</v>
       </c>
       <c r="R82" t="n">
-        <v>6958098</v>
+        <v>6957867</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8946,10 +8946,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128743244</v>
+        <v>128731226</v>
       </c>
       <c r="B83" t="n">
-        <v>91466</v>
+        <v>91485</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8957,21 +8957,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8981,10 +8981,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>569736</v>
+        <v>569705</v>
       </c>
       <c r="R83" t="n">
-        <v>6957867</v>
+        <v>6958098</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9150,10 +9150,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128729895</v>
+        <v>128743257</v>
       </c>
       <c r="B85" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9178,21 +9178,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
+      <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>569713</v>
+        <v>569656</v>
       </c>
       <c r="R85" t="n">
-        <v>6958138</v>
+        <v>6957942</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9225,6 +9221,11 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>23 exemplar (ca)</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9251,10 +9252,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128743257</v>
+        <v>128729895</v>
       </c>
       <c r="B86" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9279,17 +9280,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I86" t="inlineStr"/>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
       <c r="P86" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>569656</v>
+        <v>569713</v>
       </c>
       <c r="R86" t="n">
-        <v>6957942</v>
+        <v>6958138</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9322,11 +9327,6 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>23 exemplar (ca)</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9353,10 +9353,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128729069</v>
+        <v>128727978</v>
       </c>
       <c r="B87" t="n">
-        <v>79089</v>
+        <v>57689</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9364,34 +9364,39 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>569699</v>
+        <v>569564</v>
       </c>
       <c r="R87" t="n">
-        <v>6958200</v>
+        <v>6958213</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9424,6 +9429,11 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9450,10 +9460,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128728419</v>
+        <v>128729666</v>
       </c>
       <c r="B88" t="n">
-        <v>79089</v>
+        <v>57689</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9461,34 +9471,39 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>569608</v>
+        <v>569706</v>
       </c>
       <c r="R88" t="n">
-        <v>6958227</v>
+        <v>6958159</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9525,7 +9540,7 @@
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>Riklig förekomst inom området</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9552,32 +9567,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128743261</v>
+        <v>128738599</v>
       </c>
       <c r="B89" t="n">
-        <v>79089</v>
+        <v>80154</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9587,10 +9602,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>569495</v>
+        <v>569608</v>
       </c>
       <c r="R89" t="n">
-        <v>6958117</v>
+        <v>6958048</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9649,10 +9664,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128729666</v>
+        <v>128729069</v>
       </c>
       <c r="B90" t="n">
-        <v>57689</v>
+        <v>79089</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9660,39 +9675,34 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P90" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>569706</v>
+        <v>569699</v>
       </c>
       <c r="R90" t="n">
-        <v>6958159</v>
+        <v>6958200</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9725,11 +9735,6 @@
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9756,10 +9761,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128727978</v>
+        <v>128728419</v>
       </c>
       <c r="B91" t="n">
-        <v>57689</v>
+        <v>79089</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9767,39 +9772,34 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P91" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>569564</v>
+        <v>569608</v>
       </c>
       <c r="R91" t="n">
-        <v>6958213</v>
+        <v>6958227</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9836,7 +9836,7 @@
       </c>
       <c r="AC91" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Riklig förekomst inom området</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9863,32 +9863,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128738599</v>
+        <v>128743261</v>
       </c>
       <c r="B92" t="n">
-        <v>80154</v>
+        <v>79089</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9898,10 +9898,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>569608</v>
+        <v>569495</v>
       </c>
       <c r="R92" t="n">
-        <v>6958048</v>
+        <v>6958117</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9960,45 +9960,49 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128728152</v>
+        <v>128731648</v>
       </c>
       <c r="B93" t="n">
-        <v>91466</v>
+        <v>98592</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>569577</v>
+        <v>569766</v>
       </c>
       <c r="R93" t="n">
-        <v>6958213</v>
+        <v>6958144</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10031,6 +10035,11 @@
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>Ca ( möjligtvis fler)</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10057,50 +10066,45 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128728274</v>
+        <v>128743256</v>
       </c>
       <c r="B94" t="n">
-        <v>57689</v>
+        <v>98592</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P94" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>569599</v>
+        <v>569647</v>
       </c>
       <c r="R94" t="n">
-        <v>6958201</v>
+        <v>6957950</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10137,7 +10141,7 @@
       </c>
       <c r="AC94" t="inlineStr">
         <is>
-          <t>Både äldre och färska ringhack på tall</t>
+          <t>23 exemplar</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10164,49 +10168,45 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128731648</v>
+        <v>128728152</v>
       </c>
       <c r="B95" t="n">
-        <v>98591</v>
+        <v>91467</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>119</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>569766</v>
+        <v>569577</v>
       </c>
       <c r="R95" t="n">
-        <v>6958144</v>
+        <v>6958213</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10239,11 +10239,6 @@
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>Ca ( möjligtvis fler)</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10270,45 +10265,50 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128743253</v>
+        <v>128728274</v>
       </c>
       <c r="B96" t="n">
-        <v>98591</v>
+        <v>57689</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P96" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>569641</v>
+        <v>569599</v>
       </c>
       <c r="R96" t="n">
-        <v>6957953</v>
+        <v>6958201</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10345,7 +10345,7 @@
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>55 exemplar knärötter</t>
+          <t>Både äldre och färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10372,10 +10372,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128743256</v>
+        <v>128743253</v>
       </c>
       <c r="B97" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10407,10 +10407,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>569647</v>
+        <v>569641</v>
       </c>
       <c r="R97" t="n">
-        <v>6957950</v>
+        <v>6957953</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10447,7 +10447,7 @@
       </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>23 exemplar</t>
+          <t>55 exemplar knärötter</t>
         </is>
       </c>
       <c r="AD97" t="b">

--- a/artfynd/A 39666-2025 artfynd.xlsx
+++ b/artfynd/A 39666-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128732386</v>
+        <v>128739007</v>
       </c>
       <c r="B2" t="n">
-        <v>80194</v>
+        <v>57716</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>569785</v>
+        <v>569542</v>
       </c>
       <c r="R2" t="n">
-        <v>6958124</v>
+        <v>6958069</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128743246</v>
+        <v>128732386</v>
       </c>
       <c r="B3" t="n">
-        <v>57689</v>
+        <v>80221</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>569648</v>
+        <v>569785</v>
       </c>
       <c r="R3" t="n">
-        <v>6957944</v>
+        <v>6958124</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -843,11 +853,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall ( äldre och färska spår)</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -874,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128728526</v>
+        <v>128743246</v>
       </c>
       <c r="B4" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -903,21 +908,16 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>569616</v>
+        <v>569648</v>
       </c>
       <c r="R4" t="n">
-        <v>6958208</v>
+        <v>6957944</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -954,7 +954,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack av tretåig hackspett på Tall ( äldre och färska spår)</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128739007</v>
+        <v>128728526</v>
       </c>
       <c r="B5" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>569542</v>
+        <v>569616</v>
       </c>
       <c r="R5" t="n">
-        <v>6958069</v>
+        <v>6958208</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128732983</v>
+        <v>128728896</v>
       </c>
       <c r="B6" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1127,10 +1127,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>569873</v>
+        <v>569601</v>
       </c>
       <c r="R6" t="n">
-        <v>6958099</v>
+        <v>6958191</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1189,10 +1189,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128728896</v>
+        <v>128732983</v>
       </c>
       <c r="B7" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1219,7 +1219,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1228,10 +1228,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>569601</v>
+        <v>569873</v>
       </c>
       <c r="R7" t="n">
-        <v>6958191</v>
+        <v>6958099</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1293,7 +1293,7 @@
         <v>128729409</v>
       </c>
       <c r="B8" t="n">
-        <v>91467</v>
+        <v>91494</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1390,7 +1390,7 @@
         <v>128730130</v>
       </c>
       <c r="B9" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1497,7 +1497,7 @@
         <v>128732765</v>
       </c>
       <c r="B10" t="n">
-        <v>91763</v>
+        <v>91790</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1591,10 +1591,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128732276</v>
+        <v>128730571</v>
       </c>
       <c r="B11" t="n">
-        <v>57689</v>
+        <v>91512</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1602,39 +1602,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>569841</v>
+        <v>569660</v>
       </c>
       <c r="R11" t="n">
-        <v>6958102</v>
+        <v>6958074</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1667,11 +1662,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1701,7 +1691,7 @@
         <v>128743245</v>
       </c>
       <c r="B12" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1800,10 +1790,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128730571</v>
+        <v>128732276</v>
       </c>
       <c r="B13" t="n">
-        <v>91485</v>
+        <v>57716</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1811,34 +1801,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>569660</v>
+        <v>569841</v>
       </c>
       <c r="R13" t="n">
-        <v>6958074</v>
+        <v>6958102</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1871,6 +1866,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1900,7 +1900,7 @@
         <v>128732217</v>
       </c>
       <c r="B14" t="n">
-        <v>57849</v>
+        <v>57876</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2016,7 +2016,7 @@
         <v>128733181</v>
       </c>
       <c r="B15" t="n">
-        <v>98509</v>
+        <v>98536</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2110,37 +2110,38 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128731490</v>
+        <v>128731601</v>
       </c>
       <c r="B16" t="n">
-        <v>98592</v>
+        <v>57716</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>20</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2149,10 +2150,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>569759</v>
+        <v>569752</v>
       </c>
       <c r="R16" t="n">
-        <v>6958118</v>
+        <v>6958091</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2185,6 +2186,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2214,7 +2220,7 @@
         <v>128728515</v>
       </c>
       <c r="B17" t="n">
-        <v>97463</v>
+        <v>97490</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2308,38 +2314,37 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128731601</v>
+        <v>128731490</v>
       </c>
       <c r="B18" t="n">
-        <v>57689</v>
+        <v>98619</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>20</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2348,10 +2353,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>569752</v>
+        <v>569759</v>
       </c>
       <c r="R18" t="n">
-        <v>6958091</v>
+        <v>6958118</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2384,11 +2389,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2418,7 +2418,7 @@
         <v>128730429</v>
       </c>
       <c r="B19" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2516,10 +2516,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128731107</v>
+        <v>128732359</v>
       </c>
       <c r="B20" t="n">
-        <v>57849</v>
+        <v>91494</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2527,39 +2527,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>569705</v>
+        <v>569820</v>
       </c>
       <c r="R20" t="n">
-        <v>6958098</v>
+        <v>6958107</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2618,49 +2613,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128730720</v>
+        <v>128731612</v>
       </c>
       <c r="B21" t="n">
-        <v>98592</v>
+        <v>91494</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>569692</v>
+        <v>569752</v>
       </c>
       <c r="R21" t="n">
-        <v>6958094</v>
+        <v>6958091</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2693,11 +2684,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ca</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2724,32 +2710,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128743252</v>
+        <v>128728022</v>
       </c>
       <c r="B22" t="n">
-        <v>98592</v>
+        <v>91459</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2759,10 +2745,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>569610</v>
+        <v>569583</v>
       </c>
       <c r="R22" t="n">
-        <v>6958005</v>
+        <v>6958204</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2795,11 +2781,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>2 exemplar</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2826,10 +2807,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128732359</v>
+        <v>128743262</v>
       </c>
       <c r="B23" t="n">
-        <v>91467</v>
+        <v>79116</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2837,21 +2818,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2861,10 +2842,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>569820</v>
+        <v>569732</v>
       </c>
       <c r="R23" t="n">
-        <v>6958107</v>
+        <v>6957870</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2923,10 +2904,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128731612</v>
+        <v>128739020</v>
       </c>
       <c r="B24" t="n">
-        <v>91467</v>
+        <v>57716</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2934,34 +2915,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>569752</v>
+        <v>569542</v>
       </c>
       <c r="R24" t="n">
-        <v>6958091</v>
+        <v>6958049</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2994,6 +2980,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3020,45 +3011,50 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128728022</v>
+        <v>128731107</v>
       </c>
       <c r="B25" t="n">
-        <v>91432</v>
+        <v>57876</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5447</v>
+        <v>103021</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>569583</v>
+        <v>569705</v>
       </c>
       <c r="R25" t="n">
-        <v>6958204</v>
+        <v>6958098</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3117,45 +3113,49 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128743262</v>
+        <v>128730720</v>
       </c>
       <c r="B26" t="n">
-        <v>79089</v>
+        <v>98619</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>569732</v>
+        <v>569692</v>
       </c>
       <c r="R26" t="n">
-        <v>6957870</v>
+        <v>6958094</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3188,6 +3188,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ca</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3214,50 +3219,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128739020</v>
+        <v>128743252</v>
       </c>
       <c r="B27" t="n">
-        <v>57689</v>
+        <v>98619</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>569542</v>
+        <v>569610</v>
       </c>
       <c r="R27" t="n">
-        <v>6958049</v>
+        <v>6958005</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3294,7 +3294,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>2 exemplar</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3321,50 +3321,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128731291</v>
+        <v>128729068</v>
       </c>
       <c r="B28" t="n">
-        <v>57689</v>
+        <v>80250</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>569726</v>
+        <v>569604</v>
       </c>
       <c r="R28" t="n">
-        <v>6958097</v>
+        <v>6958176</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3397,11 +3392,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på tall</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3428,10 +3418,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128728019</v>
+        <v>128731291</v>
       </c>
       <c r="B29" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3468,10 +3458,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>569577</v>
+        <v>569726</v>
       </c>
       <c r="R29" t="n">
-        <v>6958213</v>
+        <v>6958097</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3508,7 +3498,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>Ringhack av tretåig hackspett på tall</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3535,45 +3525,50 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128729068</v>
+        <v>128728019</v>
       </c>
       <c r="B30" t="n">
-        <v>80223</v>
+        <v>57716</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>569604</v>
+        <v>569577</v>
       </c>
       <c r="R30" t="n">
-        <v>6958176</v>
+        <v>6958213</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3606,6 +3601,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3635,7 +3635,7 @@
         <v>128731489</v>
       </c>
       <c r="B31" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3736,7 +3736,7 @@
         <v>128728303</v>
       </c>
       <c r="B32" t="n">
-        <v>57681</v>
+        <v>57708</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3843,7 +3843,7 @@
         <v>128730603</v>
       </c>
       <c r="B33" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3950,7 +3950,7 @@
         <v>128728767</v>
       </c>
       <c r="B34" t="n">
-        <v>92757</v>
+        <v>92784</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4061,7 +4061,7 @@
         <v>128730513</v>
       </c>
       <c r="B35" t="n">
-        <v>80194</v>
+        <v>80221</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4155,38 +4155,37 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128729745</v>
+        <v>128732677</v>
       </c>
       <c r="B36" t="n">
-        <v>57689</v>
+        <v>98619</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>12</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4195,10 +4194,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>569694</v>
+        <v>569817</v>
       </c>
       <c r="R36" t="n">
-        <v>6958144</v>
+        <v>6958134</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4231,11 +4230,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4262,32 +4256,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128728318</v>
+        <v>128743255</v>
       </c>
       <c r="B37" t="n">
-        <v>79089</v>
+        <v>98619</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4297,10 +4291,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>569616</v>
+        <v>569613</v>
       </c>
       <c r="R37" t="n">
-        <v>6958208</v>
+        <v>6957995</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4333,6 +4327,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>28 exemplar knärot</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4359,32 +4358,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128731677</v>
+        <v>128743254</v>
       </c>
       <c r="B38" t="n">
-        <v>79089</v>
+        <v>98619</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4394,10 +4393,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>569769</v>
+        <v>569547</v>
       </c>
       <c r="R38" t="n">
-        <v>6958153</v>
+        <v>6958078</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4430,6 +4429,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>20 (ca) exemplar</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4456,49 +4460,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128732677</v>
+        <v>128728318</v>
       </c>
       <c r="B39" t="n">
-        <v>98592</v>
+        <v>79116</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>569817</v>
+        <v>569616</v>
       </c>
       <c r="R39" t="n">
-        <v>6958134</v>
+        <v>6958208</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4557,32 +4557,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128743254</v>
+        <v>128731677</v>
       </c>
       <c r="B40" t="n">
-        <v>98592</v>
+        <v>79116</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4592,10 +4592,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>569547</v>
+        <v>569769</v>
       </c>
       <c r="R40" t="n">
-        <v>6958078</v>
+        <v>6958153</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4628,11 +4628,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>20 (ca) exemplar</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4659,45 +4654,50 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128743255</v>
+        <v>128729745</v>
       </c>
       <c r="B41" t="n">
-        <v>98592</v>
+        <v>57716</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>569613</v>
+        <v>569694</v>
       </c>
       <c r="R41" t="n">
-        <v>6957995</v>
+        <v>6958144</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>28 exemplar knärot</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4761,10 +4761,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128729439</v>
+        <v>128728473</v>
       </c>
       <c r="B42" t="n">
-        <v>91467</v>
+        <v>57876</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4772,34 +4772,39 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>569703</v>
+        <v>569608</v>
       </c>
       <c r="R42" t="n">
-        <v>6958175</v>
+        <v>6958227</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4858,10 +4863,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128729962</v>
+        <v>128729439</v>
       </c>
       <c r="B43" t="n">
-        <v>80194</v>
+        <v>91494</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4869,21 +4874,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4893,10 +4898,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>569643</v>
+        <v>569703</v>
       </c>
       <c r="R43" t="n">
-        <v>6958117</v>
+        <v>6958175</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4955,10 +4960,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128730475</v>
+        <v>128729962</v>
       </c>
       <c r="B44" t="n">
-        <v>57689</v>
+        <v>80221</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4966,39 +4971,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>569675</v>
+        <v>569643</v>
       </c>
       <c r="R44" t="n">
-        <v>6958098</v>
+        <v>6958117</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5031,11 +5031,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5062,10 +5057,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128728473</v>
+        <v>128730475</v>
       </c>
       <c r="B45" t="n">
-        <v>57849</v>
+        <v>57716</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5073,27 +5068,27 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="M45" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -5102,10 +5097,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>569608</v>
+        <v>569675</v>
       </c>
       <c r="R45" t="n">
-        <v>6958227</v>
+        <v>6958098</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5138,6 +5133,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5164,37 +5164,38 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128728348</v>
+        <v>128731799</v>
       </c>
       <c r="B46" t="n">
-        <v>98592</v>
+        <v>57716</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>300</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -5203,10 +5204,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>569616</v>
+        <v>569774</v>
       </c>
       <c r="R46" t="n">
-        <v>6958208</v>
+        <v>6958163</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5239,6 +5240,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5265,37 +5271,38 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128732627</v>
+        <v>128732015</v>
       </c>
       <c r="B47" t="n">
-        <v>98592</v>
+        <v>57716</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>6</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -5304,10 +5311,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>569821</v>
+        <v>569816</v>
       </c>
       <c r="R47" t="n">
-        <v>6958151</v>
+        <v>6958081</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5344,7 +5351,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Kan finnas mer I blåbärsriset och mossan</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5374,7 +5381,7 @@
         <v>128728902</v>
       </c>
       <c r="B48" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5478,10 +5485,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128731799</v>
+        <v>128738187</v>
       </c>
       <c r="B49" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5509,7 +5516,7 @@
       <c r="I49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -5518,10 +5525,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>569774</v>
+        <v>569681</v>
       </c>
       <c r="R49" t="n">
-        <v>6958163</v>
+        <v>6957939</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5558,7 +5565,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5585,38 +5592,37 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128732015</v>
+        <v>128732627</v>
       </c>
       <c r="B50" t="n">
-        <v>57689</v>
+        <v>98619</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>6</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -5625,10 +5631,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>569816</v>
+        <v>569821</v>
       </c>
       <c r="R50" t="n">
-        <v>6958081</v>
+        <v>6958151</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5665,7 +5671,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Kan finnas mer I blåbärsriset och mossan</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5692,38 +5698,37 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128738187</v>
+        <v>128728348</v>
       </c>
       <c r="B51" t="n">
-        <v>57689</v>
+        <v>98619</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>300</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -5732,10 +5737,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>569681</v>
+        <v>569616</v>
       </c>
       <c r="R51" t="n">
-        <v>6957939</v>
+        <v>6958208</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5768,11 +5773,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5802,7 +5802,7 @@
         <v>128731302</v>
       </c>
       <c r="B52" t="n">
-        <v>80154</v>
+        <v>80181</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5899,7 +5899,7 @@
         <v>128729573</v>
       </c>
       <c r="B53" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5997,10 +5997,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128731037</v>
+        <v>128732183</v>
       </c>
       <c r="B54" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6028,7 +6028,7 @@
       <c r="I54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -6037,10 +6037,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>569673</v>
+        <v>569777</v>
       </c>
       <c r="R54" t="n">
-        <v>6958037</v>
+        <v>6958189</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6077,7 +6077,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6104,10 +6104,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128738306</v>
+        <v>128731037</v>
       </c>
       <c r="B55" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6135,7 +6135,7 @@
       <c r="I55" t="inlineStr"/>
       <c r="M55" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -6144,10 +6144,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>569644</v>
+        <v>569673</v>
       </c>
       <c r="R55" t="n">
-        <v>6957965</v>
+        <v>6958037</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6211,10 +6211,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128732183</v>
+        <v>128738306</v>
       </c>
       <c r="B56" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6251,10 +6251,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>569777</v>
+        <v>569644</v>
       </c>
       <c r="R56" t="n">
-        <v>6958189</v>
+        <v>6957965</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6291,7 +6291,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6318,10 +6318,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128732806</v>
+        <v>128728592</v>
       </c>
       <c r="B57" t="n">
-        <v>91478</v>
+        <v>80256</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6329,21 +6329,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1205</v>
+        <v>6463</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6353,10 +6353,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>569827</v>
+        <v>569604</v>
       </c>
       <c r="R57" t="n">
-        <v>6958133</v>
+        <v>6958176</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6415,32 +6415,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128732719</v>
+        <v>128732124</v>
       </c>
       <c r="B58" t="n">
-        <v>91921</v>
+        <v>80256</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1209</v>
+        <v>6463</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6450,10 +6450,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>569821</v>
+        <v>569816</v>
       </c>
       <c r="R58" t="n">
-        <v>6958151</v>
+        <v>6958081</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6512,10 +6512,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128728592</v>
+        <v>128730101</v>
       </c>
       <c r="B59" t="n">
-        <v>80229</v>
+        <v>80257</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6523,21 +6523,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6463</v>
+        <v>6464</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6547,10 +6547,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>569604</v>
+        <v>569630</v>
       </c>
       <c r="R59" t="n">
-        <v>6958176</v>
+        <v>6958139</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6609,10 +6609,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128732124</v>
+        <v>128731387</v>
       </c>
       <c r="B60" t="n">
-        <v>80229</v>
+        <v>80249</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6620,21 +6620,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6463</v>
+        <v>6461</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6644,10 +6644,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>569816</v>
+        <v>569740</v>
       </c>
       <c r="R60" t="n">
-        <v>6958081</v>
+        <v>6958091</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6706,45 +6706,50 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128730101</v>
+        <v>128730490</v>
       </c>
       <c r="B61" t="n">
-        <v>80230</v>
+        <v>57716</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>569630</v>
+        <v>569707</v>
       </c>
       <c r="R61" t="n">
-        <v>6958139</v>
+        <v>6958131</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6777,6 +6782,11 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Både äldre och färska spår ( Ringhack av tretåig hackspett på tall)</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6803,10 +6813,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128731387</v>
+        <v>128730183</v>
       </c>
       <c r="B62" t="n">
-        <v>80222</v>
+        <v>80181</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6814,21 +6824,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6461</v>
+        <v>229497</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6838,10 +6848,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>569740</v>
+        <v>569630</v>
       </c>
       <c r="R62" t="n">
-        <v>6958091</v>
+        <v>6958129</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6900,50 +6910,45 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128730490</v>
+        <v>128732806</v>
       </c>
       <c r="B63" t="n">
-        <v>57689</v>
+        <v>91505</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>1205</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>569707</v>
+        <v>569827</v>
       </c>
       <c r="R63" t="n">
-        <v>6958131</v>
+        <v>6958133</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6976,11 +6981,6 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Både äldre och färska spår ( Ringhack av tretåig hackspett på tall)</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7007,50 +7007,45 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128730422</v>
+        <v>128732719</v>
       </c>
       <c r="B64" t="n">
-        <v>57689</v>
+        <v>91948</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>569703</v>
+        <v>569821</v>
       </c>
       <c r="R64" t="n">
-        <v>6958116</v>
+        <v>6958151</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7083,11 +7078,6 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7117,7 +7107,7 @@
         <v>128739287</v>
       </c>
       <c r="B65" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7221,45 +7211,50 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128730183</v>
+        <v>128730422</v>
       </c>
       <c r="B66" t="n">
-        <v>80154</v>
+        <v>57716</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>229497</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>569630</v>
+        <v>569703</v>
       </c>
       <c r="R66" t="n">
-        <v>6958129</v>
+        <v>6958116</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7292,6 +7287,11 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7318,10 +7318,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128730273</v>
+        <v>128729077</v>
       </c>
       <c r="B67" t="n">
-        <v>79089</v>
+        <v>80221</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7329,21 +7329,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7353,10 +7353,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>569692</v>
+        <v>569604</v>
       </c>
       <c r="R67" t="n">
-        <v>6958127</v>
+        <v>6958176</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7415,10 +7415,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128729077</v>
+        <v>128730273</v>
       </c>
       <c r="B68" t="n">
-        <v>80194</v>
+        <v>79116</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7426,21 +7426,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7450,10 +7450,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>569604</v>
+        <v>569692</v>
       </c>
       <c r="R68" t="n">
-        <v>6958176</v>
+        <v>6958127</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7515,7 +7515,7 @@
         <v>128732112</v>
       </c>
       <c r="B69" t="n">
-        <v>80194</v>
+        <v>80221</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7609,10 +7609,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128728149</v>
+        <v>128732493</v>
       </c>
       <c r="B70" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7649,10 +7649,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>569585</v>
+        <v>569795</v>
       </c>
       <c r="R70" t="n">
-        <v>6958190</v>
+        <v>6958154</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7689,7 +7689,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7716,10 +7716,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128732493</v>
+        <v>128728149</v>
       </c>
       <c r="B71" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7756,10 +7756,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>569795</v>
+        <v>569585</v>
       </c>
       <c r="R71" t="n">
-        <v>6958154</v>
+        <v>6958190</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7796,7 +7796,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7823,10 +7823,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128730998</v>
+        <v>128730928</v>
       </c>
       <c r="B72" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7852,21 +7852,24 @@
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
       <c r="M72" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>569670</v>
+        <v>569673</v>
       </c>
       <c r="R72" t="n">
-        <v>6958060</v>
+        <v>6958076</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7903,7 +7906,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Ringhack på tall. Även äldre</t>
+          <t>Påbörjat bobygge av sannolikt tretåig hackspett. Ser ut att vara relativt färskt. 2 meter upp i död gran. Omkring 4,5 cm i diameter.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7930,10 +7933,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128730928</v>
+        <v>128731693</v>
       </c>
       <c r="B73" t="n">
-        <v>57689</v>
+        <v>91494</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7941,42 +7944,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>569673</v>
+        <v>569793</v>
       </c>
       <c r="R73" t="n">
-        <v>6958076</v>
+        <v>6958092</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8009,11 +8004,6 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Påbörjat bobygge av sannolikt tretåig hackspett. Ser ut att vara relativt färskt. 2 meter upp i död gran. Omkring 4,5 cm i diameter.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8040,32 +8030,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128731693</v>
+        <v>128743263</v>
       </c>
       <c r="B74" t="n">
-        <v>91467</v>
+        <v>92818</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1202</v>
+        <v>5964</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8075,10 +8065,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>569793</v>
+        <v>569517</v>
       </c>
       <c r="R74" t="n">
-        <v>6958092</v>
+        <v>6958123</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8111,6 +8101,11 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>3 exemplar</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8137,45 +8132,50 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128743263</v>
+        <v>128730998</v>
       </c>
       <c r="B75" t="n">
-        <v>92791</v>
+        <v>57716</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>5964</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>569517</v>
+        <v>569670</v>
       </c>
       <c r="R75" t="n">
-        <v>6958123</v>
+        <v>6958060</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8212,7 +8212,7 @@
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>3 exemplar</t>
+          <t>Ringhack på tall. Även äldre</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8239,49 +8239,45 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128733005</v>
+        <v>128731100</v>
       </c>
       <c r="B76" t="n">
-        <v>98592</v>
+        <v>91512</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>569882</v>
+        <v>569688</v>
       </c>
       <c r="R76" t="n">
-        <v>6958106</v>
+        <v>6958069</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8340,37 +8336,38 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128732718</v>
+        <v>128731284</v>
       </c>
       <c r="B77" t="n">
-        <v>98592</v>
+        <v>57876</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>18</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
@@ -8379,10 +8376,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>569834</v>
+        <v>569677</v>
       </c>
       <c r="R77" t="n">
-        <v>6958143</v>
+        <v>6958066</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8444,7 +8441,7 @@
         <v>128743247</v>
       </c>
       <c r="B78" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8546,7 +8543,7 @@
         <v>128732848</v>
       </c>
       <c r="B79" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8650,45 +8647,49 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128731100</v>
+        <v>128732718</v>
       </c>
       <c r="B80" t="n">
-        <v>91485</v>
+        <v>98619</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>569688</v>
+        <v>569834</v>
       </c>
       <c r="R80" t="n">
-        <v>6958069</v>
+        <v>6958143</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8747,38 +8748,37 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128731284</v>
+        <v>128733005</v>
       </c>
       <c r="B81" t="n">
-        <v>57849</v>
+        <v>98619</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>7</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
@@ -8787,10 +8787,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>569677</v>
+        <v>569882</v>
       </c>
       <c r="R81" t="n">
-        <v>6958066</v>
+        <v>6958106</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8852,7 +8852,7 @@
         <v>128743244</v>
       </c>
       <c r="B82" t="n">
-        <v>91467</v>
+        <v>91494</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8949,7 +8949,7 @@
         <v>128731226</v>
       </c>
       <c r="B83" t="n">
-        <v>91485</v>
+        <v>91512</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9046,7 +9046,7 @@
         <v>128728434</v>
       </c>
       <c r="B84" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9150,10 +9150,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128743257</v>
+        <v>128729895</v>
       </c>
       <c r="B85" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9178,17 +9178,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I85" t="inlineStr"/>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>569656</v>
+        <v>569713</v>
       </c>
       <c r="R85" t="n">
-        <v>6957942</v>
+        <v>6958138</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9221,11 +9225,6 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>23 exemplar (ca)</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9252,10 +9251,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128729895</v>
+        <v>128743257</v>
       </c>
       <c r="B86" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9280,21 +9279,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
+      <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>569713</v>
+        <v>569656</v>
       </c>
       <c r="R86" t="n">
-        <v>6958138</v>
+        <v>6957942</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9327,6 +9322,11 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>23 exemplar (ca)</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9353,50 +9353,45 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128727978</v>
+        <v>128738599</v>
       </c>
       <c r="B87" t="n">
-        <v>57689</v>
+        <v>80181</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100109</v>
+        <v>229497</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>569564</v>
+        <v>569608</v>
       </c>
       <c r="R87" t="n">
-        <v>6958213</v>
+        <v>6958048</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9429,11 +9424,6 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9460,10 +9450,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128729666</v>
+        <v>128729069</v>
       </c>
       <c r="B88" t="n">
-        <v>57689</v>
+        <v>79116</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9471,39 +9461,34 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>569706</v>
+        <v>569699</v>
       </c>
       <c r="R88" t="n">
-        <v>6958159</v>
+        <v>6958200</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9536,11 +9521,6 @@
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9567,32 +9547,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128738599</v>
+        <v>128728419</v>
       </c>
       <c r="B89" t="n">
-        <v>80154</v>
+        <v>79116</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9605,7 +9585,7 @@
         <v>569608</v>
       </c>
       <c r="R89" t="n">
-        <v>6958048</v>
+        <v>6958227</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9638,6 +9618,11 @@
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>Riklig förekomst inom området</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9664,10 +9649,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128729069</v>
+        <v>128743261</v>
       </c>
       <c r="B90" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9699,10 +9684,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>569699</v>
+        <v>569495</v>
       </c>
       <c r="R90" t="n">
-        <v>6958200</v>
+        <v>6958117</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9761,10 +9746,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128728419</v>
+        <v>128727978</v>
       </c>
       <c r="B91" t="n">
-        <v>79089</v>
+        <v>57716</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9772,34 +9757,39 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P91" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>569608</v>
+        <v>569564</v>
       </c>
       <c r="R91" t="n">
-        <v>6958227</v>
+        <v>6958213</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9836,7 +9826,7 @@
       </c>
       <c r="AC91" t="inlineStr">
         <is>
-          <t>Riklig förekomst inom området</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9863,10 +9853,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128743261</v>
+        <v>128729666</v>
       </c>
       <c r="B92" t="n">
-        <v>79089</v>
+        <v>57716</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9874,34 +9864,39 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>569495</v>
+        <v>569706</v>
       </c>
       <c r="R92" t="n">
-        <v>6958117</v>
+        <v>6958159</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9934,6 +9929,11 @@
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -9960,37 +9960,38 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128731648</v>
+        <v>128728274</v>
       </c>
       <c r="B93" t="n">
-        <v>98592</v>
+        <v>57716</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>119</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P93" t="inlineStr">
@@ -9999,10 +10000,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>569766</v>
+        <v>569599</v>
       </c>
       <c r="R93" t="n">
-        <v>6958144</v>
+        <v>6958201</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10039,7 +10040,7 @@
       </c>
       <c r="AC93" t="inlineStr">
         <is>
-          <t>Ca ( möjligtvis fler)</t>
+          <t>Både äldre och färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10066,10 +10067,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128743256</v>
+        <v>128731648</v>
       </c>
       <c r="B94" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10094,17 +10095,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I94" t="inlineStr"/>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
       <c r="P94" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>569647</v>
+        <v>569766</v>
       </c>
       <c r="R94" t="n">
-        <v>6957950</v>
+        <v>6958144</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10141,7 +10146,7 @@
       </c>
       <c r="AC94" t="inlineStr">
         <is>
-          <t>23 exemplar</t>
+          <t>Ca ( möjligtvis fler)</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10168,32 +10173,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128728152</v>
+        <v>128743253</v>
       </c>
       <c r="B95" t="n">
-        <v>91467</v>
+        <v>98619</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10203,10 +10208,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>569577</v>
+        <v>569641</v>
       </c>
       <c r="R95" t="n">
-        <v>6958213</v>
+        <v>6957953</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10239,6 +10244,11 @@
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>55 exemplar knärötter</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10265,50 +10275,45 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128728274</v>
+        <v>128743256</v>
       </c>
       <c r="B96" t="n">
-        <v>57689</v>
+        <v>98619</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P96" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>569599</v>
+        <v>569647</v>
       </c>
       <c r="R96" t="n">
-        <v>6958201</v>
+        <v>6957950</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10345,7 +10350,7 @@
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>Både äldre och färska ringhack på tall</t>
+          <t>23 exemplar</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10372,32 +10377,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128743253</v>
+        <v>128728152</v>
       </c>
       <c r="B97" t="n">
-        <v>98592</v>
+        <v>91494</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10407,10 +10412,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>569641</v>
+        <v>569577</v>
       </c>
       <c r="R97" t="n">
-        <v>6957953</v>
+        <v>6958213</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10443,11 +10448,6 @@
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC97" t="inlineStr">
-        <is>
-          <t>55 exemplar knärötter</t>
         </is>
       </c>
       <c r="AD97" t="b">

--- a/artfynd/A 39666-2025 artfynd.xlsx
+++ b/artfynd/A 39666-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128739007</v>
+        <v>128732386</v>
       </c>
       <c r="B2" t="n">
-        <v>57716</v>
+        <v>80221</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,39 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>569542</v>
+        <v>569785</v>
       </c>
       <c r="R2" t="n">
-        <v>6958069</v>
+        <v>6958124</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128732386</v>
+        <v>128739007</v>
       </c>
       <c r="B3" t="n">
-        <v>80221</v>
+        <v>57716</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,34 +783,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>569785</v>
+        <v>569542</v>
       </c>
       <c r="R3" t="n">
-        <v>6958124</v>
+        <v>6958069</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -853,6 +848,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128743246</v>
+        <v>128728526</v>
       </c>
       <c r="B4" t="n">
         <v>57716</v>
@@ -908,16 +908,21 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>569648</v>
+        <v>569616</v>
       </c>
       <c r="R4" t="n">
-        <v>6957944</v>
+        <v>6958208</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -954,7 +959,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall ( äldre och färska spår)</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -981,7 +986,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128728526</v>
+        <v>128743246</v>
       </c>
       <c r="B5" t="n">
         <v>57716</v>
@@ -1010,21 +1015,16 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>569616</v>
+        <v>569648</v>
       </c>
       <c r="R5" t="n">
-        <v>6958208</v>
+        <v>6957944</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1061,7 +1061,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack av tretåig hackspett på Tall ( äldre och färska spår)</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1290,10 +1290,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128729409</v>
+        <v>128730130</v>
       </c>
       <c r="B8" t="n">
-        <v>91494</v>
+        <v>57716</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1301,34 +1301,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>569700</v>
+        <v>569713</v>
       </c>
       <c r="R8" t="n">
-        <v>6958164</v>
+        <v>6958138</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1361,6 +1366,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1387,10 +1397,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128730130</v>
+        <v>128729409</v>
       </c>
       <c r="B9" t="n">
-        <v>57716</v>
+        <v>91494</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1398,39 +1408,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>569713</v>
+        <v>569700</v>
       </c>
       <c r="R9" t="n">
-        <v>6958138</v>
+        <v>6958164</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1463,11 +1468,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1591,10 +1591,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128730571</v>
+        <v>128743245</v>
       </c>
       <c r="B11" t="n">
-        <v>91512</v>
+        <v>57716</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1602,21 +1602,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1626,10 +1626,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>569660</v>
+        <v>569590</v>
       </c>
       <c r="R11" t="n">
-        <v>6958074</v>
+        <v>6958014</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1662,6 +1662,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall ( färska spår)</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1688,7 +1693,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128743245</v>
+        <v>128732276</v>
       </c>
       <c r="B12" t="n">
         <v>57716</v>
@@ -1717,16 +1722,21 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>569590</v>
+        <v>569841</v>
       </c>
       <c r="R12" t="n">
-        <v>6958014</v>
+        <v>6958102</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1763,7 +1773,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall ( färska spår)</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1790,10 +1800,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128732276</v>
+        <v>128730571</v>
       </c>
       <c r="B13" t="n">
-        <v>57716</v>
+        <v>91512</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1801,39 +1811,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>569841</v>
+        <v>569660</v>
       </c>
       <c r="R13" t="n">
-        <v>6958102</v>
+        <v>6958074</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1866,11 +1871,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2110,50 +2110,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128731601</v>
+        <v>128728515</v>
       </c>
       <c r="B16" t="n">
-        <v>57716</v>
+        <v>97490</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>569752</v>
+        <v>569608</v>
       </c>
       <c r="R16" t="n">
-        <v>6958091</v>
+        <v>6958227</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2186,11 +2181,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2217,45 +2207,49 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128728515</v>
+        <v>128731490</v>
       </c>
       <c r="B17" t="n">
-        <v>97490</v>
+        <v>98619</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>569608</v>
+        <v>569759</v>
       </c>
       <c r="R17" t="n">
-        <v>6958227</v>
+        <v>6958118</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2314,7 +2308,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128731490</v>
+        <v>128730429</v>
       </c>
       <c r="B18" t="n">
         <v>98619</v>
@@ -2344,7 +2338,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>80</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2353,10 +2347,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>569759</v>
+        <v>569683</v>
       </c>
       <c r="R18" t="n">
-        <v>6958118</v>
+        <v>6958128</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2415,37 +2409,38 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128730429</v>
+        <v>128731601</v>
       </c>
       <c r="B19" t="n">
-        <v>98619</v>
+        <v>57716</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>80</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2454,10 +2449,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>569683</v>
+        <v>569752</v>
       </c>
       <c r="R19" t="n">
-        <v>6958128</v>
+        <v>6958091</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2490,6 +2485,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2710,32 +2710,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128728022</v>
+        <v>128743262</v>
       </c>
       <c r="B22" t="n">
-        <v>91459</v>
+        <v>79116</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2745,10 +2745,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>569583</v>
+        <v>569732</v>
       </c>
       <c r="R22" t="n">
-        <v>6958204</v>
+        <v>6957870</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2807,10 +2807,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128743262</v>
+        <v>128739020</v>
       </c>
       <c r="B23" t="n">
-        <v>79116</v>
+        <v>57716</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2818,34 +2818,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>569732</v>
+        <v>569542</v>
       </c>
       <c r="R23" t="n">
-        <v>6957870</v>
+        <v>6958049</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2878,6 +2883,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2904,38 +2914,37 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128739020</v>
+        <v>128730720</v>
       </c>
       <c r="B24" t="n">
-        <v>57716</v>
+        <v>98619</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>50</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -2944,10 +2953,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>569542</v>
+        <v>569692</v>
       </c>
       <c r="R24" t="n">
-        <v>6958049</v>
+        <v>6958094</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2984,7 +2993,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ca</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3011,50 +3020,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128731107</v>
+        <v>128743252</v>
       </c>
       <c r="B25" t="n">
-        <v>57876</v>
+        <v>98619</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>569705</v>
+        <v>569610</v>
       </c>
       <c r="R25" t="n">
-        <v>6958098</v>
+        <v>6958005</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3087,6 +3091,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>2 exemplar</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3113,49 +3122,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128730720</v>
+        <v>128728022</v>
       </c>
       <c r="B26" t="n">
-        <v>98619</v>
+        <v>91459</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>569692</v>
+        <v>569583</v>
       </c>
       <c r="R26" t="n">
-        <v>6958094</v>
+        <v>6958204</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3188,11 +3193,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ca</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3219,45 +3219,50 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128743252</v>
+        <v>128731107</v>
       </c>
       <c r="B27" t="n">
-        <v>98619</v>
+        <v>57876</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>569610</v>
+        <v>569705</v>
       </c>
       <c r="R27" t="n">
-        <v>6958005</v>
+        <v>6958098</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3290,11 +3295,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>2 exemplar</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3733,10 +3733,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128728303</v>
+        <v>128728767</v>
       </c>
       <c r="B32" t="n">
-        <v>57708</v>
+        <v>92784</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3744,27 +3744,31 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100110</v>
+        <v>4364</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -3773,10 +3777,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>569584</v>
+        <v>569639</v>
       </c>
       <c r="R32" t="n">
-        <v>6958214</v>
+        <v>6958231</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3813,7 +3817,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Hörs i närheten</t>
+          <t>4 äldre ett färskt års exemplar</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3840,10 +3844,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128730603</v>
+        <v>128730513</v>
       </c>
       <c r="B33" t="n">
-        <v>57716</v>
+        <v>80221</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3851,39 +3855,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>569738</v>
+        <v>569656</v>
       </c>
       <c r="R33" t="n">
-        <v>6958117</v>
+        <v>6958093</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3916,11 +3915,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Äldre exemplar av ringhack på Tall från tretåig hackspett</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3947,42 +3941,38 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128728767</v>
+        <v>128730603</v>
       </c>
       <c r="B34" t="n">
-        <v>92784</v>
+        <v>57716</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -3991,10 +3981,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>569639</v>
+        <v>569738</v>
       </c>
       <c r="R34" t="n">
-        <v>6958231</v>
+        <v>6958117</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4031,7 +4021,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>4 äldre ett färskt års exemplar</t>
+          <t>Äldre exemplar av ringhack på Tall från tretåig hackspett</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4058,45 +4048,50 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128730513</v>
+        <v>128728303</v>
       </c>
       <c r="B35" t="n">
-        <v>80221</v>
+        <v>57708</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>100110</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>J.F. Gmelin, 1788</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>569656</v>
+        <v>569584</v>
       </c>
       <c r="R35" t="n">
-        <v>6958093</v>
+        <v>6958214</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4129,6 +4124,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Hörs i närheten</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4155,49 +4155,45 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128732677</v>
+        <v>128728318</v>
       </c>
       <c r="B36" t="n">
-        <v>98619</v>
+        <v>79116</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>569817</v>
+        <v>569616</v>
       </c>
       <c r="R36" t="n">
-        <v>6958134</v>
+        <v>6958208</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4256,32 +4252,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128743255</v>
+        <v>128731677</v>
       </c>
       <c r="B37" t="n">
-        <v>98619</v>
+        <v>79116</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4291,10 +4287,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>569613</v>
+        <v>569769</v>
       </c>
       <c r="R37" t="n">
-        <v>6957995</v>
+        <v>6958153</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4327,11 +4323,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>28 exemplar knärot</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4358,45 +4349,50 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128743254</v>
+        <v>128729745</v>
       </c>
       <c r="B38" t="n">
-        <v>98619</v>
+        <v>57716</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>569547</v>
+        <v>569694</v>
       </c>
       <c r="R38" t="n">
-        <v>6958078</v>
+        <v>6958144</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4433,7 +4429,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>20 (ca) exemplar</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4460,45 +4456,49 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128728318</v>
+        <v>128732677</v>
       </c>
       <c r="B39" t="n">
-        <v>79116</v>
+        <v>98619</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>569616</v>
+        <v>569817</v>
       </c>
       <c r="R39" t="n">
-        <v>6958208</v>
+        <v>6958134</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4557,32 +4557,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128731677</v>
+        <v>128743255</v>
       </c>
       <c r="B40" t="n">
-        <v>79116</v>
+        <v>98619</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4592,10 +4592,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>569769</v>
+        <v>569613</v>
       </c>
       <c r="R40" t="n">
-        <v>6958153</v>
+        <v>6957995</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4628,6 +4628,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>28 exemplar knärot</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4654,50 +4659,45 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128729745</v>
+        <v>128743254</v>
       </c>
       <c r="B41" t="n">
-        <v>57716</v>
+        <v>98619</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>569694</v>
+        <v>569547</v>
       </c>
       <c r="R41" t="n">
-        <v>6958144</v>
+        <v>6958078</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>20 (ca) exemplar</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4761,10 +4761,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128728473</v>
+        <v>128729439</v>
       </c>
       <c r="B42" t="n">
-        <v>57876</v>
+        <v>91494</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4772,39 +4772,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>569608</v>
+        <v>569703</v>
       </c>
       <c r="R42" t="n">
-        <v>6958227</v>
+        <v>6958175</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4863,10 +4858,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128729439</v>
+        <v>128729962</v>
       </c>
       <c r="B43" t="n">
-        <v>91494</v>
+        <v>80221</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4874,21 +4869,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4898,10 +4893,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>569703</v>
+        <v>569643</v>
       </c>
       <c r="R43" t="n">
-        <v>6958175</v>
+        <v>6958117</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4960,10 +4955,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128729962</v>
+        <v>128730475</v>
       </c>
       <c r="B44" t="n">
-        <v>80221</v>
+        <v>57716</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4971,34 +4966,39 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>569643</v>
+        <v>569675</v>
       </c>
       <c r="R44" t="n">
-        <v>6958117</v>
+        <v>6958098</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5031,6 +5031,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5057,10 +5062,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128730475</v>
+        <v>128728473</v>
       </c>
       <c r="B45" t="n">
-        <v>57716</v>
+        <v>57876</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5068,27 +5073,27 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="M45" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -5097,10 +5102,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>569675</v>
+        <v>569608</v>
       </c>
       <c r="R45" t="n">
-        <v>6958098</v>
+        <v>6958227</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5133,11 +5138,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5164,7 +5164,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128731799</v>
+        <v>128732015</v>
       </c>
       <c r="B46" t="n">
         <v>57716</v>
@@ -5195,7 +5195,7 @@
       <c r="I46" t="inlineStr"/>
       <c r="M46" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -5204,10 +5204,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>569774</v>
+        <v>569816</v>
       </c>
       <c r="R46" t="n">
-        <v>6958163</v>
+        <v>6958081</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5244,7 +5244,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5271,38 +5271,37 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128732015</v>
+        <v>128732627</v>
       </c>
       <c r="B47" t="n">
-        <v>57716</v>
+        <v>98619</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>6</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -5311,10 +5310,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>569816</v>
+        <v>569821</v>
       </c>
       <c r="R47" t="n">
-        <v>6958081</v>
+        <v>6958151</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5351,7 +5350,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Kan finnas mer I blåbärsriset och mossan</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5378,38 +5377,37 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128728902</v>
+        <v>128728348</v>
       </c>
       <c r="B48" t="n">
-        <v>57716</v>
+        <v>98619</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>300</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -5418,10 +5416,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>569673</v>
+        <v>569616</v>
       </c>
       <c r="R48" t="n">
-        <v>6958225</v>
+        <v>6958208</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5454,11 +5452,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5485,7 +5478,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128738187</v>
+        <v>128731799</v>
       </c>
       <c r="B49" t="n">
         <v>57716</v>
@@ -5516,7 +5509,7 @@
       <c r="I49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -5525,10 +5518,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>569681</v>
+        <v>569774</v>
       </c>
       <c r="R49" t="n">
-        <v>6957939</v>
+        <v>6958163</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5565,7 +5558,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5592,37 +5585,38 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128732627</v>
+        <v>128738187</v>
       </c>
       <c r="B50" t="n">
-        <v>98619</v>
+        <v>57716</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>6</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -5631,10 +5625,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>569821</v>
+        <v>569681</v>
       </c>
       <c r="R50" t="n">
-        <v>6958151</v>
+        <v>6957939</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5671,7 +5665,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Kan finnas mer I blåbärsriset och mossan</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5698,37 +5692,38 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128728348</v>
+        <v>128728902</v>
       </c>
       <c r="B51" t="n">
-        <v>98619</v>
+        <v>57716</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>300</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -5737,10 +5732,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>569616</v>
+        <v>569673</v>
       </c>
       <c r="R51" t="n">
-        <v>6958208</v>
+        <v>6958225</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5773,6 +5768,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5997,7 +5997,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128732183</v>
+        <v>128738306</v>
       </c>
       <c r="B54" t="n">
         <v>57716</v>
@@ -6037,10 +6037,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>569777</v>
+        <v>569644</v>
       </c>
       <c r="R54" t="n">
-        <v>6958189</v>
+        <v>6957965</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6077,7 +6077,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6104,7 +6104,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128731037</v>
+        <v>128732183</v>
       </c>
       <c r="B55" t="n">
         <v>57716</v>
@@ -6135,7 +6135,7 @@
       <c r="I55" t="inlineStr"/>
       <c r="M55" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -6144,10 +6144,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>569673</v>
+        <v>569777</v>
       </c>
       <c r="R55" t="n">
-        <v>6958037</v>
+        <v>6958189</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6184,7 +6184,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6211,7 +6211,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128738306</v>
+        <v>128731037</v>
       </c>
       <c r="B56" t="n">
         <v>57716</v>
@@ -6242,7 +6242,7 @@
       <c r="I56" t="inlineStr"/>
       <c r="M56" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -6251,10 +6251,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>569644</v>
+        <v>569673</v>
       </c>
       <c r="R56" t="n">
-        <v>6957965</v>
+        <v>6958037</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6318,10 +6318,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128728592</v>
+        <v>128732806</v>
       </c>
       <c r="B57" t="n">
-        <v>80256</v>
+        <v>91505</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6329,21 +6329,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6463</v>
+        <v>1205</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6353,10 +6353,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>569604</v>
+        <v>569827</v>
       </c>
       <c r="R57" t="n">
-        <v>6958176</v>
+        <v>6958133</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6415,32 +6415,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128732124</v>
+        <v>128732719</v>
       </c>
       <c r="B58" t="n">
-        <v>80256</v>
+        <v>91948</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6463</v>
+        <v>1209</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6450,10 +6450,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>569816</v>
+        <v>569821</v>
       </c>
       <c r="R58" t="n">
-        <v>6958081</v>
+        <v>6958151</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6512,10 +6512,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128730101</v>
+        <v>128728592</v>
       </c>
       <c r="B59" t="n">
-        <v>80257</v>
+        <v>80256</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6523,21 +6523,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6464</v>
+        <v>6463</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6547,10 +6547,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>569630</v>
+        <v>569604</v>
       </c>
       <c r="R59" t="n">
-        <v>6958139</v>
+        <v>6958176</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6609,10 +6609,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128731387</v>
+        <v>128732124</v>
       </c>
       <c r="B60" t="n">
-        <v>80249</v>
+        <v>80256</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6620,21 +6620,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6461</v>
+        <v>6463</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6644,10 +6644,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>569740</v>
+        <v>569816</v>
       </c>
       <c r="R60" t="n">
-        <v>6958091</v>
+        <v>6958081</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6706,50 +6706,45 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128730490</v>
+        <v>128730101</v>
       </c>
       <c r="B61" t="n">
-        <v>57716</v>
+        <v>80257</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>569707</v>
+        <v>569630</v>
       </c>
       <c r="R61" t="n">
-        <v>6958131</v>
+        <v>6958139</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6782,11 +6777,6 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Både äldre och färska spår ( Ringhack av tretåig hackspett på tall)</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6813,10 +6803,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128730183</v>
+        <v>128731387</v>
       </c>
       <c r="B62" t="n">
-        <v>80181</v>
+        <v>80249</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6824,21 +6814,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>229497</v>
+        <v>6461</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6848,10 +6838,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>569630</v>
+        <v>569740</v>
       </c>
       <c r="R62" t="n">
-        <v>6958129</v>
+        <v>6958091</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6910,45 +6900,50 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128732806</v>
+        <v>128739287</v>
       </c>
       <c r="B63" t="n">
-        <v>91505</v>
+        <v>57716</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1205</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>569827</v>
+        <v>569481</v>
       </c>
       <c r="R63" t="n">
-        <v>6958133</v>
+        <v>6958122</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6981,6 +6976,11 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7007,45 +7007,50 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128732719</v>
+        <v>128730490</v>
       </c>
       <c r="B64" t="n">
-        <v>91948</v>
+        <v>57716</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>569821</v>
+        <v>569707</v>
       </c>
       <c r="R64" t="n">
-        <v>6958151</v>
+        <v>6958131</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7078,6 +7083,11 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Både äldre och färska spår ( Ringhack av tretåig hackspett på tall)</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7104,7 +7114,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128739287</v>
+        <v>128730422</v>
       </c>
       <c r="B65" t="n">
         <v>57716</v>
@@ -7144,10 +7154,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>569481</v>
+        <v>569703</v>
       </c>
       <c r="R65" t="n">
-        <v>6958122</v>
+        <v>6958116</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7184,7 +7194,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7211,50 +7221,45 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128730422</v>
+        <v>128730183</v>
       </c>
       <c r="B66" t="n">
-        <v>57716</v>
+        <v>80181</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>229497</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>569703</v>
+        <v>569630</v>
       </c>
       <c r="R66" t="n">
-        <v>6958116</v>
+        <v>6958129</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7287,11 +7292,6 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7609,50 +7609,45 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128732493</v>
+        <v>128743263</v>
       </c>
       <c r="B70" t="n">
-        <v>57716</v>
+        <v>92818</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>5964</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>569795</v>
+        <v>569517</v>
       </c>
       <c r="R70" t="n">
-        <v>6958154</v>
+        <v>6958123</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7689,7 +7684,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>3 exemplar</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7716,7 +7711,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128728149</v>
+        <v>128732493</v>
       </c>
       <c r="B71" t="n">
         <v>57716</v>
@@ -7756,10 +7751,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>569585</v>
+        <v>569795</v>
       </c>
       <c r="R71" t="n">
-        <v>6958190</v>
+        <v>6958154</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7796,7 +7791,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7933,10 +7928,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128731693</v>
+        <v>128728149</v>
       </c>
       <c r="B73" t="n">
-        <v>91494</v>
+        <v>57716</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7944,34 +7939,39 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>569793</v>
+        <v>569585</v>
       </c>
       <c r="R73" t="n">
-        <v>6958092</v>
+        <v>6958190</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8004,6 +8004,11 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8030,45 +8035,50 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128743263</v>
+        <v>128730998</v>
       </c>
       <c r="B74" t="n">
-        <v>92818</v>
+        <v>57716</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>5964</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>569517</v>
+        <v>569670</v>
       </c>
       <c r="R74" t="n">
-        <v>6958123</v>
+        <v>6958060</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8105,7 +8115,7 @@
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>3 exemplar</t>
+          <t>Ringhack på tall. Även äldre</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8132,10 +8142,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128730998</v>
+        <v>128731693</v>
       </c>
       <c r="B75" t="n">
-        <v>57716</v>
+        <v>91494</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8143,39 +8153,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>569670</v>
+        <v>569793</v>
       </c>
       <c r="R75" t="n">
-        <v>6958060</v>
+        <v>6958092</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8208,11 +8213,6 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Ringhack på tall. Även äldre</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8336,10 +8336,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128731284</v>
+        <v>128732848</v>
       </c>
       <c r="B77" t="n">
-        <v>57876</v>
+        <v>57716</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8347,27 +8347,27 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="M77" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
@@ -8376,10 +8376,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>569677</v>
+        <v>569873</v>
       </c>
       <c r="R77" t="n">
-        <v>6958066</v>
+        <v>6958099</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8412,6 +8412,11 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8540,10 +8545,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128732848</v>
+        <v>128731284</v>
       </c>
       <c r="B79" t="n">
-        <v>57716</v>
+        <v>57876</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8551,27 +8556,27 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="M79" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
@@ -8580,10 +8585,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>569873</v>
+        <v>569677</v>
       </c>
       <c r="R79" t="n">
-        <v>6958099</v>
+        <v>6958066</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8616,11 +8621,6 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9353,32 +9353,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128738599</v>
+        <v>128729069</v>
       </c>
       <c r="B87" t="n">
-        <v>80181</v>
+        <v>79116</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9388,10 +9388,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>569608</v>
+        <v>569699</v>
       </c>
       <c r="R87" t="n">
-        <v>6958048</v>
+        <v>6958200</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9450,7 +9450,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128729069</v>
+        <v>128728419</v>
       </c>
       <c r="B88" t="n">
         <v>79116</v>
@@ -9485,10 +9485,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>569699</v>
+        <v>569608</v>
       </c>
       <c r="R88" t="n">
-        <v>6958200</v>
+        <v>6958227</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9521,6 +9521,11 @@
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>Riklig förekomst inom området</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9547,7 +9552,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128728419</v>
+        <v>128743261</v>
       </c>
       <c r="B89" t="n">
         <v>79116</v>
@@ -9582,10 +9587,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>569608</v>
+        <v>569495</v>
       </c>
       <c r="R89" t="n">
-        <v>6958227</v>
+        <v>6958117</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9618,11 +9623,6 @@
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>Riklig förekomst inom området</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9649,10 +9649,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128743261</v>
+        <v>128729666</v>
       </c>
       <c r="B90" t="n">
-        <v>79116</v>
+        <v>57716</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9660,34 +9660,39 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P90" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>569495</v>
+        <v>569706</v>
       </c>
       <c r="R90" t="n">
-        <v>6958117</v>
+        <v>6958159</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9720,6 +9725,11 @@
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9853,50 +9863,45 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128729666</v>
+        <v>128738599</v>
       </c>
       <c r="B92" t="n">
-        <v>57716</v>
+        <v>80181</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>100109</v>
+        <v>229497</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>569706</v>
+        <v>569608</v>
       </c>
       <c r="R92" t="n">
-        <v>6958159</v>
+        <v>6958048</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9929,11 +9934,6 @@
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC92" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -9960,10 +9960,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128728274</v>
+        <v>128728152</v>
       </c>
       <c r="B93" t="n">
-        <v>57716</v>
+        <v>91494</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9971,39 +9971,34 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>569599</v>
+        <v>569577</v>
       </c>
       <c r="R93" t="n">
-        <v>6958201</v>
+        <v>6958213</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10036,11 +10031,6 @@
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC93" t="inlineStr">
-        <is>
-          <t>Både äldre och färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10067,37 +10057,38 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128731648</v>
+        <v>128728274</v>
       </c>
       <c r="B94" t="n">
-        <v>98619</v>
+        <v>57716</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>119</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P94" t="inlineStr">
@@ -10106,10 +10097,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>569766</v>
+        <v>569599</v>
       </c>
       <c r="R94" t="n">
-        <v>6958144</v>
+        <v>6958201</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10146,7 +10137,7 @@
       </c>
       <c r="AC94" t="inlineStr">
         <is>
-          <t>Ca ( möjligtvis fler)</t>
+          <t>Både äldre och färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10173,7 +10164,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128743253</v>
+        <v>128731648</v>
       </c>
       <c r="B95" t="n">
         <v>98619</v>
@@ -10201,17 +10192,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I95" t="inlineStr"/>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
       <c r="P95" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>569641</v>
+        <v>569766</v>
       </c>
       <c r="R95" t="n">
-        <v>6957953</v>
+        <v>6958144</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10248,7 +10243,7 @@
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>55 exemplar knärötter</t>
+          <t>Ca ( möjligtvis fler)</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10275,7 +10270,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128743256</v>
+        <v>128743253</v>
       </c>
       <c r="B96" t="n">
         <v>98619</v>
@@ -10310,10 +10305,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>569647</v>
+        <v>569641</v>
       </c>
       <c r="R96" t="n">
-        <v>6957950</v>
+        <v>6957953</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10350,7 +10345,7 @@
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>23 exemplar</t>
+          <t>55 exemplar knärötter</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10377,32 +10372,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128728152</v>
+        <v>128743256</v>
       </c>
       <c r="B97" t="n">
-        <v>91494</v>
+        <v>98619</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10412,10 +10407,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>569577</v>
+        <v>569647</v>
       </c>
       <c r="R97" t="n">
-        <v>6958213</v>
+        <v>6957950</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10448,6 +10443,11 @@
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>23 exemplar</t>
         </is>
       </c>
       <c r="AD97" t="b">

--- a/artfynd/A 39666-2025 artfynd.xlsx
+++ b/artfynd/A 39666-2025 artfynd.xlsx
@@ -675,45 +675,49 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128732386</v>
+        <v>128728896</v>
       </c>
       <c r="B2" t="n">
-        <v>80221</v>
+        <v>98625</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>569785</v>
+        <v>569601</v>
       </c>
       <c r="R2" t="n">
-        <v>6958124</v>
+        <v>6958191</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,38 +776,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128739007</v>
+        <v>128732983</v>
       </c>
       <c r="B3" t="n">
-        <v>57716</v>
+        <v>98625</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>15</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -812,10 +815,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>569542</v>
+        <v>569873</v>
       </c>
       <c r="R3" t="n">
-        <v>6958069</v>
+        <v>6958099</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -848,11 +851,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,10 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128728526</v>
+        <v>128732386</v>
       </c>
       <c r="B4" t="n">
-        <v>57716</v>
+        <v>80225</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,39 +888,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>569616</v>
+        <v>569785</v>
       </c>
       <c r="R4" t="n">
-        <v>6958208</v>
+        <v>6958124</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -955,11 +948,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -986,7 +974,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128743246</v>
+        <v>128739007</v>
       </c>
       <c r="B5" t="n">
         <v>57716</v>
@@ -1015,16 +1003,21 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>569648</v>
+        <v>569542</v>
       </c>
       <c r="R5" t="n">
-        <v>6957944</v>
+        <v>6958069</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1061,7 +1054,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall ( äldre och färska spår)</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1088,37 +1081,38 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128728896</v>
+        <v>128728526</v>
       </c>
       <c r="B6" t="n">
-        <v>98619</v>
+        <v>57716</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>6</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1127,10 +1121,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>569601</v>
+        <v>569616</v>
       </c>
       <c r="R6" t="n">
-        <v>6958191</v>
+        <v>6958208</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1163,6 +1157,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1189,49 +1188,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128732983</v>
+        <v>128743246</v>
       </c>
       <c r="B7" t="n">
-        <v>98619</v>
+        <v>57716</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>569873</v>
+        <v>569648</v>
       </c>
       <c r="R7" t="n">
-        <v>6958099</v>
+        <v>6957944</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1264,6 +1259,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall ( äldre och färska spår)</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1290,10 +1290,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128730130</v>
+        <v>128729409</v>
       </c>
       <c r="B8" t="n">
-        <v>57716</v>
+        <v>91499</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1301,39 +1301,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>569713</v>
+        <v>569700</v>
       </c>
       <c r="R8" t="n">
-        <v>6958138</v>
+        <v>6958164</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1366,11 +1361,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1397,10 +1387,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128729409</v>
+        <v>128730130</v>
       </c>
       <c r="B9" t="n">
-        <v>91494</v>
+        <v>57716</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1408,34 +1398,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>569700</v>
+        <v>569713</v>
       </c>
       <c r="R9" t="n">
-        <v>6958164</v>
+        <v>6958138</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1468,6 +1463,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1494,10 +1494,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128732765</v>
+        <v>128732217</v>
       </c>
       <c r="B10" t="n">
-        <v>91790</v>
+        <v>57876</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1505,34 +1505,48 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>658</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>569827</v>
+        <v>569777</v>
       </c>
       <c r="R10" t="n">
-        <v>6958133</v>
+        <v>6958189</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1565,6 +1579,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>2 talltitor kommer flygandes väldigt närgånget och varnar</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1591,10 +1610,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128743245</v>
+        <v>128730571</v>
       </c>
       <c r="B11" t="n">
-        <v>57716</v>
+        <v>91517</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1602,21 +1621,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1626,10 +1645,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>569590</v>
+        <v>569660</v>
       </c>
       <c r="R11" t="n">
-        <v>6958014</v>
+        <v>6958074</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1662,11 +1681,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall ( färska spår)</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1693,7 +1707,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128732276</v>
+        <v>128743245</v>
       </c>
       <c r="B12" t="n">
         <v>57716</v>
@@ -1722,21 +1736,16 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>569841</v>
+        <v>569590</v>
       </c>
       <c r="R12" t="n">
-        <v>6958102</v>
+        <v>6958014</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1773,7 +1782,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack av tretåig hackspett på Tall ( färska spår)</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1800,10 +1809,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128730571</v>
+        <v>128732276</v>
       </c>
       <c r="B13" t="n">
-        <v>91512</v>
+        <v>57716</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1811,34 +1820,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>569660</v>
+        <v>569841</v>
       </c>
       <c r="R13" t="n">
-        <v>6958074</v>
+        <v>6958102</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1871,6 +1885,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1897,10 +1916,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128732217</v>
+        <v>128732765</v>
       </c>
       <c r="B14" t="n">
-        <v>57876</v>
+        <v>91795</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1908,48 +1927,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>658</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>569777</v>
+        <v>569827</v>
       </c>
       <c r="R14" t="n">
-        <v>6958189</v>
+        <v>6958133</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1982,11 +1987,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>2 talltitor kommer flygandes väldigt närgånget och varnar</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2016,7 +2016,7 @@
         <v>128733181</v>
       </c>
       <c r="B15" t="n">
-        <v>98536</v>
+        <v>98542</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2110,45 +2110,50 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128728515</v>
+        <v>128731601</v>
       </c>
       <c r="B16" t="n">
-        <v>97490</v>
+        <v>57716</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>569608</v>
+        <v>569752</v>
       </c>
       <c r="R16" t="n">
-        <v>6958227</v>
+        <v>6958091</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2181,6 +2186,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2210,7 +2220,7 @@
         <v>128731490</v>
       </c>
       <c r="B17" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2311,7 +2321,7 @@
         <v>128730429</v>
       </c>
       <c r="B18" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2409,50 +2419,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128731601</v>
+        <v>128728515</v>
       </c>
       <c r="B19" t="n">
-        <v>57716</v>
+        <v>97496</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>569752</v>
+        <v>569608</v>
       </c>
       <c r="R19" t="n">
-        <v>6958091</v>
+        <v>6958227</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2485,11 +2490,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2516,10 +2516,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128732359</v>
+        <v>128743262</v>
       </c>
       <c r="B20" t="n">
-        <v>91494</v>
+        <v>79120</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2527,21 +2527,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2551,10 +2551,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>569820</v>
+        <v>569732</v>
       </c>
       <c r="R20" t="n">
-        <v>6958107</v>
+        <v>6957870</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2613,32 +2613,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128731612</v>
+        <v>128728022</v>
       </c>
       <c r="B21" t="n">
-        <v>91494</v>
+        <v>91464</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2648,10 +2648,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>569752</v>
+        <v>569583</v>
       </c>
       <c r="R21" t="n">
-        <v>6958091</v>
+        <v>6958204</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2710,10 +2710,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128743262</v>
+        <v>128732359</v>
       </c>
       <c r="B22" t="n">
-        <v>79116</v>
+        <v>91499</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2721,21 +2721,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2745,10 +2745,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>569732</v>
+        <v>569820</v>
       </c>
       <c r="R22" t="n">
-        <v>6957870</v>
+        <v>6958107</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2807,10 +2807,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128739020</v>
+        <v>128731612</v>
       </c>
       <c r="B23" t="n">
-        <v>57716</v>
+        <v>91499</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2818,39 +2818,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>569542</v>
+        <v>569752</v>
       </c>
       <c r="R23" t="n">
-        <v>6958049</v>
+        <v>6958091</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2883,11 +2878,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2914,37 +2904,38 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128730720</v>
+        <v>128739020</v>
       </c>
       <c r="B24" t="n">
-        <v>98619</v>
+        <v>57716</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>50</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -2953,10 +2944,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>569692</v>
+        <v>569542</v>
       </c>
       <c r="R24" t="n">
-        <v>6958094</v>
+        <v>6958049</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2993,7 +2984,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ca</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3020,10 +3011,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128743252</v>
+        <v>128730720</v>
       </c>
       <c r="B25" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3048,17 +3039,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>569610</v>
+        <v>569692</v>
       </c>
       <c r="R25" t="n">
-        <v>6958005</v>
+        <v>6958094</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3095,7 +3090,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>2 exemplar</t>
+          <t>Ca</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3122,32 +3117,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128728022</v>
+        <v>128743252</v>
       </c>
       <c r="B26" t="n">
-        <v>91459</v>
+        <v>98625</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3157,10 +3152,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>569583</v>
+        <v>569610</v>
       </c>
       <c r="R26" t="n">
-        <v>6958204</v>
+        <v>6958005</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3193,6 +3188,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>2 exemplar</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3321,45 +3321,49 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128729068</v>
+        <v>128731489</v>
       </c>
       <c r="B28" t="n">
-        <v>80250</v>
+        <v>98625</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>569604</v>
+        <v>569752</v>
       </c>
       <c r="R28" t="n">
-        <v>6958176</v>
+        <v>6958091</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3418,50 +3422,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128731291</v>
+        <v>128729068</v>
       </c>
       <c r="B29" t="n">
-        <v>57716</v>
+        <v>80254</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>569726</v>
+        <v>569604</v>
       </c>
       <c r="R29" t="n">
-        <v>6958097</v>
+        <v>6958176</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3494,11 +3493,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på tall</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3525,7 +3519,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128728019</v>
+        <v>128731291</v>
       </c>
       <c r="B30" t="n">
         <v>57716</v>
@@ -3565,10 +3559,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>569577</v>
+        <v>569726</v>
       </c>
       <c r="R30" t="n">
-        <v>6958213</v>
+        <v>6958097</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3605,7 +3599,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>Ringhack av tretåig hackspett på tall</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3632,37 +3626,38 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128731489</v>
+        <v>128728019</v>
       </c>
       <c r="B31" t="n">
-        <v>98619</v>
+        <v>57716</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>45</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -3671,10 +3666,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>569752</v>
+        <v>569577</v>
       </c>
       <c r="R31" t="n">
-        <v>6958091</v>
+        <v>6958213</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3707,6 +3702,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3736,7 +3736,7 @@
         <v>128728767</v>
       </c>
       <c r="B32" t="n">
-        <v>92784</v>
+        <v>92789</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3844,10 +3844,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128730513</v>
+        <v>128730603</v>
       </c>
       <c r="B33" t="n">
-        <v>80221</v>
+        <v>57716</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3855,34 +3855,39 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>569656</v>
+        <v>569738</v>
       </c>
       <c r="R33" t="n">
-        <v>6958093</v>
+        <v>6958117</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3915,6 +3920,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Äldre exemplar av ringhack på Tall från tretåig hackspett</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3941,10 +3951,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128730603</v>
+        <v>128730513</v>
       </c>
       <c r="B34" t="n">
-        <v>57716</v>
+        <v>80225</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3952,39 +3962,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>569738</v>
+        <v>569656</v>
       </c>
       <c r="R34" t="n">
-        <v>6958117</v>
+        <v>6958093</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4017,11 +4022,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Äldre exemplar av ringhack på Tall från tretåig hackspett</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4158,7 +4158,7 @@
         <v>128728318</v>
       </c>
       <c r="B36" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4255,7 +4255,7 @@
         <v>128731677</v>
       </c>
       <c r="B37" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4459,7 +4459,7 @@
         <v>128732677</v>
       </c>
       <c r="B39" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4560,7 +4560,7 @@
         <v>128743255</v>
       </c>
       <c r="B40" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4662,7 +4662,7 @@
         <v>128743254</v>
       </c>
       <c r="B41" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4761,10 +4761,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128729439</v>
+        <v>128729962</v>
       </c>
       <c r="B42" t="n">
-        <v>91494</v>
+        <v>80225</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4772,21 +4772,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4796,10 +4796,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>569703</v>
+        <v>569643</v>
       </c>
       <c r="R42" t="n">
-        <v>6958175</v>
+        <v>6958117</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4858,10 +4858,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128729962</v>
+        <v>128729439</v>
       </c>
       <c r="B43" t="n">
-        <v>80221</v>
+        <v>91499</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4869,21 +4869,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4893,10 +4893,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>569643</v>
+        <v>569703</v>
       </c>
       <c r="R43" t="n">
-        <v>6958117</v>
+        <v>6958175</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5164,7 +5164,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128732015</v>
+        <v>128731799</v>
       </c>
       <c r="B46" t="n">
         <v>57716</v>
@@ -5195,7 +5195,7 @@
       <c r="I46" t="inlineStr"/>
       <c r="M46" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -5204,10 +5204,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>569816</v>
+        <v>569774</v>
       </c>
       <c r="R46" t="n">
-        <v>6958081</v>
+        <v>6958163</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5244,7 +5244,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5271,37 +5271,38 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128732627</v>
+        <v>128732015</v>
       </c>
       <c r="B47" t="n">
-        <v>98619</v>
+        <v>57716</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>6</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -5310,10 +5311,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>569821</v>
+        <v>569816</v>
       </c>
       <c r="R47" t="n">
-        <v>6958151</v>
+        <v>6958081</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5350,7 +5351,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Kan finnas mer I blåbärsriset och mossan</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5377,37 +5378,38 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128728348</v>
+        <v>128738187</v>
       </c>
       <c r="B48" t="n">
-        <v>98619</v>
+        <v>57716</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>300</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -5416,10 +5418,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>569616</v>
+        <v>569681</v>
       </c>
       <c r="R48" t="n">
-        <v>6958208</v>
+        <v>6957939</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5452,6 +5454,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5478,7 +5485,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128731799</v>
+        <v>128728902</v>
       </c>
       <c r="B49" t="n">
         <v>57716</v>
@@ -5509,7 +5516,7 @@
       <c r="I49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -5518,10 +5525,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>569774</v>
+        <v>569673</v>
       </c>
       <c r="R49" t="n">
-        <v>6958163</v>
+        <v>6958225</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5585,38 +5592,37 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128738187</v>
+        <v>128732627</v>
       </c>
       <c r="B50" t="n">
-        <v>57716</v>
+        <v>98625</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>6</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -5625,10 +5631,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>569681</v>
+        <v>569821</v>
       </c>
       <c r="R50" t="n">
-        <v>6957939</v>
+        <v>6958151</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5665,7 +5671,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Kan finnas mer I blåbärsriset och mossan</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5692,38 +5698,37 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128728902</v>
+        <v>128728348</v>
       </c>
       <c r="B51" t="n">
-        <v>57716</v>
+        <v>98625</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>300</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -5732,10 +5737,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>569673</v>
+        <v>569616</v>
       </c>
       <c r="R51" t="n">
-        <v>6958225</v>
+        <v>6958208</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5768,11 +5773,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5799,45 +5799,49 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128731302</v>
+        <v>128729573</v>
       </c>
       <c r="B52" t="n">
-        <v>80181</v>
+        <v>98625</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>229497</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>569696</v>
+        <v>569706</v>
       </c>
       <c r="R52" t="n">
-        <v>6958031</v>
+        <v>6958159</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5896,49 +5900,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128729573</v>
+        <v>128731302</v>
       </c>
       <c r="B53" t="n">
-        <v>98619</v>
+        <v>80185</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>229497</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>569706</v>
+        <v>569696</v>
       </c>
       <c r="R53" t="n">
-        <v>6958159</v>
+        <v>6958031</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6318,10 +6318,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128732806</v>
+        <v>128732124</v>
       </c>
       <c r="B57" t="n">
-        <v>91505</v>
+        <v>80260</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6329,21 +6329,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1205</v>
+        <v>6463</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6353,10 +6353,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>569827</v>
+        <v>569816</v>
       </c>
       <c r="R57" t="n">
-        <v>6958133</v>
+        <v>6958081</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6415,32 +6415,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128732719</v>
+        <v>128730101</v>
       </c>
       <c r="B58" t="n">
-        <v>91948</v>
+        <v>80261</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1209</v>
+        <v>6464</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6450,10 +6450,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>569821</v>
+        <v>569630</v>
       </c>
       <c r="R58" t="n">
-        <v>6958151</v>
+        <v>6958139</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6512,45 +6512,50 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128728592</v>
+        <v>128739287</v>
       </c>
       <c r="B59" t="n">
-        <v>80256</v>
+        <v>57716</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>569604</v>
+        <v>569481</v>
       </c>
       <c r="R59" t="n">
-        <v>6958176</v>
+        <v>6958122</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6583,6 +6588,11 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6609,45 +6619,50 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128732124</v>
+        <v>128730490</v>
       </c>
       <c r="B60" t="n">
-        <v>80256</v>
+        <v>57716</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>569816</v>
+        <v>569707</v>
       </c>
       <c r="R60" t="n">
-        <v>6958081</v>
+        <v>6958131</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6680,6 +6695,11 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Både äldre och färska spår ( Ringhack av tretåig hackspett på tall)</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6706,45 +6726,50 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128730101</v>
+        <v>128730422</v>
       </c>
       <c r="B61" t="n">
-        <v>80257</v>
+        <v>57716</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>569630</v>
+        <v>569703</v>
       </c>
       <c r="R61" t="n">
-        <v>6958139</v>
+        <v>6958116</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6777,6 +6802,11 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6803,10 +6833,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128731387</v>
+        <v>128732806</v>
       </c>
       <c r="B62" t="n">
-        <v>80249</v>
+        <v>91510</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6814,21 +6844,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6461</v>
+        <v>1205</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6838,10 +6868,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>569740</v>
+        <v>569827</v>
       </c>
       <c r="R62" t="n">
-        <v>6958091</v>
+        <v>6958133</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6900,50 +6930,45 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128739287</v>
+        <v>128732719</v>
       </c>
       <c r="B63" t="n">
-        <v>57716</v>
+        <v>91953</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>569481</v>
+        <v>569821</v>
       </c>
       <c r="R63" t="n">
-        <v>6958122</v>
+        <v>6958151</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6976,11 +7001,6 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7007,50 +7027,45 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128730490</v>
+        <v>128730183</v>
       </c>
       <c r="B64" t="n">
-        <v>57716</v>
+        <v>80185</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>229497</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>569707</v>
+        <v>569630</v>
       </c>
       <c r="R64" t="n">
-        <v>6958131</v>
+        <v>6958129</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7083,11 +7098,6 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Både äldre och färska spår ( Ringhack av tretåig hackspett på tall)</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7114,50 +7124,45 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128730422</v>
+        <v>128731387</v>
       </c>
       <c r="B65" t="n">
-        <v>57716</v>
+        <v>80253</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>569703</v>
+        <v>569740</v>
       </c>
       <c r="R65" t="n">
-        <v>6958116</v>
+        <v>6958091</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7190,11 +7195,6 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7221,10 +7221,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128730183</v>
+        <v>128728592</v>
       </c>
       <c r="B66" t="n">
-        <v>80181</v>
+        <v>80260</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7232,21 +7232,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>229497</v>
+        <v>6463</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7256,10 +7256,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>569630</v>
+        <v>569604</v>
       </c>
       <c r="R66" t="n">
-        <v>6958129</v>
+        <v>6958176</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7321,7 +7321,7 @@
         <v>128729077</v>
       </c>
       <c r="B67" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7415,10 +7415,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128730273</v>
+        <v>128732112</v>
       </c>
       <c r="B68" t="n">
-        <v>79116</v>
+        <v>80225</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7426,21 +7426,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7450,10 +7450,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>569692</v>
+        <v>569824</v>
       </c>
       <c r="R68" t="n">
-        <v>6958127</v>
+        <v>6958091</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7512,10 +7512,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128732112</v>
+        <v>128730273</v>
       </c>
       <c r="B69" t="n">
-        <v>80221</v>
+        <v>79120</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7523,21 +7523,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7547,10 +7547,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>569824</v>
+        <v>569692</v>
       </c>
       <c r="R69" t="n">
-        <v>6958091</v>
+        <v>6958127</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7612,7 +7612,7 @@
         <v>128743263</v>
       </c>
       <c r="B70" t="n">
-        <v>92818</v>
+        <v>92823</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7711,10 +7711,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128732493</v>
+        <v>128731693</v>
       </c>
       <c r="B71" t="n">
-        <v>57716</v>
+        <v>91499</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7722,39 +7722,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>569795</v>
+        <v>569793</v>
       </c>
       <c r="R71" t="n">
-        <v>6958154</v>
+        <v>6958092</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7787,11 +7782,6 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7818,7 +7808,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128730928</v>
+        <v>128732493</v>
       </c>
       <c r="B72" t="n">
         <v>57716</v>
@@ -7847,24 +7837,21 @@
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
       <c r="M72" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N72" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>569673</v>
+        <v>569795</v>
       </c>
       <c r="R72" t="n">
-        <v>6958076</v>
+        <v>6958154</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7901,7 +7888,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Påbörjat bobygge av sannolikt tretåig hackspett. Ser ut att vara relativt färskt. 2 meter upp i död gran. Omkring 4,5 cm i diameter.</t>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7928,7 +7915,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128728149</v>
+        <v>128730928</v>
       </c>
       <c r="B73" t="n">
         <v>57716</v>
@@ -7957,21 +7944,24 @@
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
       <c r="M73" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>569585</v>
+        <v>569673</v>
       </c>
       <c r="R73" t="n">
-        <v>6958190</v>
+        <v>6958076</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8008,7 +7998,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Påbörjat bobygge av sannolikt tretåig hackspett. Ser ut att vara relativt färskt. 2 meter upp i död gran. Omkring 4,5 cm i diameter.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8035,7 +8025,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128730998</v>
+        <v>128728149</v>
       </c>
       <c r="B74" t="n">
         <v>57716</v>
@@ -8075,10 +8065,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>569670</v>
+        <v>569585</v>
       </c>
       <c r="R74" t="n">
-        <v>6958060</v>
+        <v>6958190</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8115,7 +8105,7 @@
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Ringhack på tall. Även äldre</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8142,10 +8132,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128731693</v>
+        <v>128730998</v>
       </c>
       <c r="B75" t="n">
-        <v>91494</v>
+        <v>57716</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8153,34 +8143,39 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>569793</v>
+        <v>569670</v>
       </c>
       <c r="R75" t="n">
-        <v>6958092</v>
+        <v>6958060</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8213,6 +8208,11 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Ringhack på tall. Även äldre</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8242,7 +8242,7 @@
         <v>128731100</v>
       </c>
       <c r="B76" t="n">
-        <v>91512</v>
+        <v>91517</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8336,10 +8336,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128732848</v>
+        <v>128731284</v>
       </c>
       <c r="B77" t="n">
-        <v>57716</v>
+        <v>57876</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8347,27 +8347,27 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="M77" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
@@ -8376,10 +8376,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>569873</v>
+        <v>569677</v>
       </c>
       <c r="R77" t="n">
-        <v>6958099</v>
+        <v>6958066</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8412,11 +8412,6 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8443,45 +8438,49 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128743247</v>
+        <v>128732718</v>
       </c>
       <c r="B78" t="n">
-        <v>57716</v>
+        <v>98625</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>569714</v>
+        <v>569834</v>
       </c>
       <c r="R78" t="n">
-        <v>6957901</v>
+        <v>6958143</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8514,11 +8513,6 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på gran ( färska spår)</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8545,38 +8539,37 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128731284</v>
+        <v>128733005</v>
       </c>
       <c r="B79" t="n">
-        <v>57876</v>
+        <v>98625</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>7</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
@@ -8585,10 +8578,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>569677</v>
+        <v>569882</v>
       </c>
       <c r="R79" t="n">
-        <v>6958066</v>
+        <v>6958106</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8647,37 +8640,38 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128732718</v>
+        <v>128732848</v>
       </c>
       <c r="B80" t="n">
-        <v>98619</v>
+        <v>57716</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>18</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
@@ -8686,10 +8680,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>569834</v>
+        <v>569873</v>
       </c>
       <c r="R80" t="n">
-        <v>6958143</v>
+        <v>6958099</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8722,6 +8716,11 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8748,49 +8747,45 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128733005</v>
+        <v>128743247</v>
       </c>
       <c r="B81" t="n">
-        <v>98619</v>
+        <v>57716</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>569882</v>
+        <v>569714</v>
       </c>
       <c r="R81" t="n">
-        <v>6958106</v>
+        <v>6957901</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8823,6 +8818,11 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på gran ( färska spår)</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8849,10 +8849,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128743244</v>
+        <v>128731226</v>
       </c>
       <c r="B82" t="n">
-        <v>91494</v>
+        <v>91517</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8860,21 +8860,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8884,10 +8884,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>569736</v>
+        <v>569705</v>
       </c>
       <c r="R82" t="n">
-        <v>6957867</v>
+        <v>6958098</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8946,10 +8946,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128731226</v>
+        <v>128743244</v>
       </c>
       <c r="B83" t="n">
-        <v>91512</v>
+        <v>91499</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8957,21 +8957,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8981,10 +8981,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>569705</v>
+        <v>569736</v>
       </c>
       <c r="R83" t="n">
-        <v>6958098</v>
+        <v>6957867</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9153,7 +9153,7 @@
         <v>128729895</v>
       </c>
       <c r="B85" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9254,7 +9254,7 @@
         <v>128743257</v>
       </c>
       <c r="B86" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9353,10 +9353,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128729069</v>
+        <v>128728419</v>
       </c>
       <c r="B87" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9388,10 +9388,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>569699</v>
+        <v>569608</v>
       </c>
       <c r="R87" t="n">
-        <v>6958200</v>
+        <v>6958227</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9424,6 +9424,11 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>Riklig förekomst inom området</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9450,10 +9455,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128728419</v>
+        <v>128743261</v>
       </c>
       <c r="B88" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9485,10 +9490,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>569608</v>
+        <v>569495</v>
       </c>
       <c r="R88" t="n">
-        <v>6958227</v>
+        <v>6958117</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9521,11 +9526,6 @@
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>Riklig förekomst inom området</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9552,10 +9552,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128743261</v>
+        <v>128729666</v>
       </c>
       <c r="B89" t="n">
-        <v>79116</v>
+        <v>57716</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9563,34 +9563,39 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P89" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>569495</v>
+        <v>569706</v>
       </c>
       <c r="R89" t="n">
-        <v>6958117</v>
+        <v>6958159</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9623,6 +9628,11 @@
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9649,7 +9659,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128729666</v>
+        <v>128727978</v>
       </c>
       <c r="B90" t="n">
         <v>57716</v>
@@ -9689,10 +9699,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>569706</v>
+        <v>569564</v>
       </c>
       <c r="R90" t="n">
-        <v>6958159</v>
+        <v>6958213</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9729,7 +9739,7 @@
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9756,50 +9766,45 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128727978</v>
+        <v>128738599</v>
       </c>
       <c r="B91" t="n">
-        <v>57716</v>
+        <v>80185</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>100109</v>
+        <v>229497</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P91" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>569564</v>
+        <v>569608</v>
       </c>
       <c r="R91" t="n">
-        <v>6958213</v>
+        <v>6958048</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9832,11 +9837,6 @@
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9863,32 +9863,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128738599</v>
+        <v>128729069</v>
       </c>
       <c r="B92" t="n">
-        <v>80181</v>
+        <v>79120</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9898,10 +9898,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>569608</v>
+        <v>569699</v>
       </c>
       <c r="R92" t="n">
-        <v>6958048</v>
+        <v>6958200</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9963,7 +9963,7 @@
         <v>128728152</v>
       </c>
       <c r="B93" t="n">
-        <v>91494</v>
+        <v>91499</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10167,7 +10167,7 @@
         <v>128731648</v>
       </c>
       <c r="B95" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10273,7 +10273,7 @@
         <v>128743253</v>
       </c>
       <c r="B96" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10375,7 +10375,7 @@
         <v>128743256</v>
       </c>
       <c r="B97" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>

--- a/artfynd/A 39666-2025 artfynd.xlsx
+++ b/artfynd/A 39666-2025 artfynd.xlsx
@@ -675,49 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128728896</v>
+        <v>128743246</v>
       </c>
       <c r="B2" t="n">
-        <v>98625</v>
+        <v>57716</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>569601</v>
+        <v>569648</v>
       </c>
       <c r="R2" t="n">
-        <v>6958191</v>
+        <v>6957944</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,6 +746,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall ( äldre och färska spår)</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,37 +777,38 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128732983</v>
+        <v>128728526</v>
       </c>
       <c r="B3" t="n">
-        <v>98625</v>
+        <v>57716</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>15</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -815,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>569873</v>
+        <v>569616</v>
       </c>
       <c r="R3" t="n">
-        <v>6958099</v>
+        <v>6958208</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -851,6 +853,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -877,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128732386</v>
+        <v>128739007</v>
       </c>
       <c r="B4" t="n">
-        <v>80225</v>
+        <v>57716</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -888,34 +895,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>569785</v>
+        <v>569542</v>
       </c>
       <c r="R4" t="n">
-        <v>6958124</v>
+        <v>6958069</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -948,6 +960,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -974,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128739007</v>
+        <v>128732386</v>
       </c>
       <c r="B5" t="n">
-        <v>57716</v>
+        <v>80225</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -985,39 +1002,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>569542</v>
+        <v>569785</v>
       </c>
       <c r="R5" t="n">
-        <v>6958069</v>
+        <v>6958124</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1050,11 +1062,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1081,38 +1088,37 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128728526</v>
+        <v>128728896</v>
       </c>
       <c r="B6" t="n">
-        <v>57716</v>
+        <v>98632</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>6</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1121,10 +1127,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>569616</v>
+        <v>569601</v>
       </c>
       <c r="R6" t="n">
-        <v>6958208</v>
+        <v>6958191</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1157,11 +1163,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1188,45 +1189,49 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128743246</v>
+        <v>128732983</v>
       </c>
       <c r="B7" t="n">
-        <v>57716</v>
+        <v>98632</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>569648</v>
+        <v>569873</v>
       </c>
       <c r="R7" t="n">
-        <v>6957944</v>
+        <v>6958099</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1259,11 +1264,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall ( äldre och färska spår)</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1290,10 +1290,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128729409</v>
+        <v>128730130</v>
       </c>
       <c r="B8" t="n">
-        <v>91499</v>
+        <v>57716</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1301,34 +1301,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>569700</v>
+        <v>569713</v>
       </c>
       <c r="R8" t="n">
-        <v>6958164</v>
+        <v>6958138</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1361,6 +1366,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1387,10 +1397,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128730130</v>
+        <v>128729409</v>
       </c>
       <c r="B9" t="n">
-        <v>57716</v>
+        <v>91504</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1398,39 +1408,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>569713</v>
+        <v>569700</v>
       </c>
       <c r="R9" t="n">
-        <v>6958138</v>
+        <v>6958164</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1463,11 +1468,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1610,32 +1610,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128730571</v>
+        <v>128733181</v>
       </c>
       <c r="B11" t="n">
-        <v>91517</v>
+        <v>98549</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>219790</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1645,10 +1645,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>569660</v>
+        <v>569900</v>
       </c>
       <c r="R11" t="n">
-        <v>6958074</v>
+        <v>6958101</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1707,10 +1707,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128743245</v>
+        <v>128732765</v>
       </c>
       <c r="B12" t="n">
-        <v>57716</v>
+        <v>91800</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1718,21 +1718,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1742,10 +1742,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>569590</v>
+        <v>569827</v>
       </c>
       <c r="R12" t="n">
-        <v>6958014</v>
+        <v>6958133</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1778,11 +1778,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall ( färska spår)</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1809,10 +1804,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128732276</v>
+        <v>128730571</v>
       </c>
       <c r="B13" t="n">
-        <v>57716</v>
+        <v>91522</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1820,39 +1815,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>569841</v>
+        <v>569660</v>
       </c>
       <c r="R13" t="n">
-        <v>6958102</v>
+        <v>6958074</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1885,11 +1875,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1916,10 +1901,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128732765</v>
+        <v>128732276</v>
       </c>
       <c r="B14" t="n">
-        <v>91795</v>
+        <v>57716</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1927,34 +1912,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>569827</v>
+        <v>569841</v>
       </c>
       <c r="R14" t="n">
-        <v>6958133</v>
+        <v>6958102</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1987,6 +1977,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2013,32 +2008,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128733181</v>
+        <v>128743245</v>
       </c>
       <c r="B15" t="n">
-        <v>98542</v>
+        <v>57716</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2048,10 +2043,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>569900</v>
+        <v>569590</v>
       </c>
       <c r="R15" t="n">
-        <v>6958101</v>
+        <v>6958014</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2084,6 +2079,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall ( färska spår)</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2110,50 +2110,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128731601</v>
+        <v>128728515</v>
       </c>
       <c r="B16" t="n">
-        <v>57716</v>
+        <v>97503</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>569752</v>
+        <v>569608</v>
       </c>
       <c r="R16" t="n">
-        <v>6958091</v>
+        <v>6958227</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2186,11 +2181,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2220,7 +2210,7 @@
         <v>128731490</v>
       </c>
       <c r="B17" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2321,7 +2311,7 @@
         <v>128730429</v>
       </c>
       <c r="B18" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2419,45 +2409,50 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128728515</v>
+        <v>128731601</v>
       </c>
       <c r="B19" t="n">
-        <v>97496</v>
+        <v>57716</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>569608</v>
+        <v>569752</v>
       </c>
       <c r="R19" t="n">
-        <v>6958227</v>
+        <v>6958091</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2490,6 +2485,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2613,45 +2613,50 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128728022</v>
+        <v>128731107</v>
       </c>
       <c r="B21" t="n">
-        <v>91464</v>
+        <v>57876</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5447</v>
+        <v>103021</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>569583</v>
+        <v>569705</v>
       </c>
       <c r="R21" t="n">
-        <v>6958204</v>
+        <v>6958098</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2713,7 +2718,7 @@
         <v>128732359</v>
       </c>
       <c r="B22" t="n">
-        <v>91499</v>
+        <v>91504</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2810,7 +2815,7 @@
         <v>128731612</v>
       </c>
       <c r="B23" t="n">
-        <v>91499</v>
+        <v>91504</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2904,50 +2909,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128739020</v>
+        <v>128728022</v>
       </c>
       <c r="B24" t="n">
-        <v>57716</v>
+        <v>91469</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>569542</v>
+        <v>569583</v>
       </c>
       <c r="R24" t="n">
-        <v>6958049</v>
+        <v>6958204</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2980,11 +2980,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3011,37 +3006,38 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128730720</v>
+        <v>128739020</v>
       </c>
       <c r="B25" t="n">
-        <v>98625</v>
+        <v>57716</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>50</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3050,10 +3046,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>569692</v>
+        <v>569542</v>
       </c>
       <c r="R25" t="n">
-        <v>6958094</v>
+        <v>6958049</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3090,7 +3086,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ca</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3117,10 +3113,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128743252</v>
+        <v>128730720</v>
       </c>
       <c r="B26" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3145,17 +3141,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>569610</v>
+        <v>569692</v>
       </c>
       <c r="R26" t="n">
-        <v>6958005</v>
+        <v>6958094</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3192,7 +3192,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>2 exemplar</t>
+          <t>Ca</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3219,50 +3219,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128731107</v>
+        <v>128743252</v>
       </c>
       <c r="B27" t="n">
-        <v>57876</v>
+        <v>98632</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>569705</v>
+        <v>569610</v>
       </c>
       <c r="R27" t="n">
-        <v>6958098</v>
+        <v>6958005</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3295,6 +3290,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>2 exemplar</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3321,49 +3321,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128731489</v>
+        <v>128729068</v>
       </c>
       <c r="B28" t="n">
-        <v>98625</v>
+        <v>80254</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>569752</v>
+        <v>569604</v>
       </c>
       <c r="R28" t="n">
-        <v>6958091</v>
+        <v>6958176</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3422,45 +3418,50 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128729068</v>
+        <v>128731291</v>
       </c>
       <c r="B29" t="n">
-        <v>80254</v>
+        <v>57716</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>569604</v>
+        <v>569726</v>
       </c>
       <c r="R29" t="n">
-        <v>6958176</v>
+        <v>6958097</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3493,6 +3494,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på tall</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3519,7 +3525,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128731291</v>
+        <v>128728019</v>
       </c>
       <c r="B30" t="n">
         <v>57716</v>
@@ -3559,10 +3565,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>569726</v>
+        <v>569577</v>
       </c>
       <c r="R30" t="n">
-        <v>6958097</v>
+        <v>6958213</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3599,7 +3605,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på tall</t>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3626,38 +3632,37 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128728019</v>
+        <v>128731489</v>
       </c>
       <c r="B31" t="n">
-        <v>57716</v>
+        <v>98632</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>45</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -3666,10 +3671,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>569577</v>
+        <v>569752</v>
       </c>
       <c r="R31" t="n">
-        <v>6958213</v>
+        <v>6958091</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3702,11 +3707,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3736,7 +3736,7 @@
         <v>128728767</v>
       </c>
       <c r="B32" t="n">
-        <v>92789</v>
+        <v>92794</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3844,38 +3844,38 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128730603</v>
+        <v>128728303</v>
       </c>
       <c r="B33" t="n">
-        <v>57716</v>
+        <v>57708</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>100110</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>J.F. Gmelin, 1788</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -3884,10 +3884,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>569738</v>
+        <v>569584</v>
       </c>
       <c r="R33" t="n">
-        <v>6958117</v>
+        <v>6958214</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3924,7 +3924,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Äldre exemplar av ringhack på Tall från tretåig hackspett</t>
+          <t>Hörs i närheten</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3951,10 +3951,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128730513</v>
+        <v>128730603</v>
       </c>
       <c r="B34" t="n">
-        <v>80225</v>
+        <v>57716</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3962,34 +3962,39 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>569656</v>
+        <v>569738</v>
       </c>
       <c r="R34" t="n">
-        <v>6958093</v>
+        <v>6958117</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4022,6 +4027,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Äldre exemplar av ringhack på Tall från tretåig hackspett</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4048,50 +4058,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128728303</v>
+        <v>128730513</v>
       </c>
       <c r="B35" t="n">
-        <v>57708</v>
+        <v>80225</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100110</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>569584</v>
+        <v>569656</v>
       </c>
       <c r="R35" t="n">
-        <v>6958214</v>
+        <v>6958093</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4124,11 +4129,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Hörs i närheten</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4155,10 +4155,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128728318</v>
+        <v>128729745</v>
       </c>
       <c r="B36" t="n">
-        <v>79120</v>
+        <v>57716</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4166,34 +4166,39 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>569616</v>
+        <v>569694</v>
       </c>
       <c r="R36" t="n">
-        <v>6958208</v>
+        <v>6958144</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4226,6 +4231,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4252,7 +4262,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128731677</v>
+        <v>128728318</v>
       </c>
       <c r="B37" t="n">
         <v>79120</v>
@@ -4287,10 +4297,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>569769</v>
+        <v>569616</v>
       </c>
       <c r="R37" t="n">
-        <v>6958153</v>
+        <v>6958208</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4349,10 +4359,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128729745</v>
+        <v>128731677</v>
       </c>
       <c r="B38" t="n">
-        <v>57716</v>
+        <v>79120</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4360,39 +4370,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>569694</v>
+        <v>569769</v>
       </c>
       <c r="R38" t="n">
-        <v>6958144</v>
+        <v>6958153</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4425,11 +4430,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4459,7 +4459,7 @@
         <v>128732677</v>
       </c>
       <c r="B39" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4560,7 +4560,7 @@
         <v>128743255</v>
       </c>
       <c r="B40" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4662,7 +4662,7 @@
         <v>128743254</v>
       </c>
       <c r="B41" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4761,10 +4761,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128729962</v>
+        <v>128729439</v>
       </c>
       <c r="B42" t="n">
-        <v>80225</v>
+        <v>91504</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4772,21 +4772,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4796,10 +4796,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>569643</v>
+        <v>569703</v>
       </c>
       <c r="R42" t="n">
-        <v>6958117</v>
+        <v>6958175</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4858,10 +4858,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128729439</v>
+        <v>128730475</v>
       </c>
       <c r="B43" t="n">
-        <v>91499</v>
+        <v>57716</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4869,34 +4869,39 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>569703</v>
+        <v>569675</v>
       </c>
       <c r="R43" t="n">
-        <v>6958175</v>
+        <v>6958098</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4929,6 +4934,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4955,10 +4965,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128730475</v>
+        <v>128728473</v>
       </c>
       <c r="B44" t="n">
-        <v>57716</v>
+        <v>57876</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4966,27 +4976,27 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -4995,10 +5005,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>569675</v>
+        <v>569608</v>
       </c>
       <c r="R44" t="n">
-        <v>6958098</v>
+        <v>6958227</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5031,11 +5041,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5062,10 +5067,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128728473</v>
+        <v>128729962</v>
       </c>
       <c r="B45" t="n">
-        <v>57876</v>
+        <v>80225</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5073,39 +5078,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>569608</v>
+        <v>569643</v>
       </c>
       <c r="R45" t="n">
-        <v>6958227</v>
+        <v>6958117</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5164,7 +5164,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128731799</v>
+        <v>128728902</v>
       </c>
       <c r="B46" t="n">
         <v>57716</v>
@@ -5195,7 +5195,7 @@
       <c r="I46" t="inlineStr"/>
       <c r="M46" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -5204,10 +5204,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>569774</v>
+        <v>569673</v>
       </c>
       <c r="R46" t="n">
-        <v>6958163</v>
+        <v>6958225</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5271,7 +5271,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128732015</v>
+        <v>128731799</v>
       </c>
       <c r="B47" t="n">
         <v>57716</v>
@@ -5302,7 +5302,7 @@
       <c r="I47" t="inlineStr"/>
       <c r="M47" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -5311,10 +5311,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>569816</v>
+        <v>569774</v>
       </c>
       <c r="R47" t="n">
-        <v>6958081</v>
+        <v>6958163</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5351,7 +5351,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5378,7 +5378,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128738187</v>
+        <v>128732015</v>
       </c>
       <c r="B48" t="n">
         <v>57716</v>
@@ -5418,10 +5418,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>569681</v>
+        <v>569816</v>
       </c>
       <c r="R48" t="n">
-        <v>6957939</v>
+        <v>6958081</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5485,7 +5485,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128728902</v>
+        <v>128738187</v>
       </c>
       <c r="B49" t="n">
         <v>57716</v>
@@ -5525,10 +5525,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>569673</v>
+        <v>569681</v>
       </c>
       <c r="R49" t="n">
-        <v>6958225</v>
+        <v>6957939</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5565,7 +5565,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5595,7 +5595,7 @@
         <v>128732627</v>
       </c>
       <c r="B50" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5701,7 +5701,7 @@
         <v>128728348</v>
       </c>
       <c r="B51" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5799,49 +5799,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128729573</v>
+        <v>128731302</v>
       </c>
       <c r="B52" t="n">
-        <v>98625</v>
+        <v>80185</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>229497</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>569706</v>
+        <v>569696</v>
       </c>
       <c r="R52" t="n">
-        <v>6958159</v>
+        <v>6958031</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5900,45 +5896,49 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128731302</v>
+        <v>128729573</v>
       </c>
       <c r="B53" t="n">
-        <v>80185</v>
+        <v>98632</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>229497</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>569696</v>
+        <v>569706</v>
       </c>
       <c r="R53" t="n">
-        <v>6958031</v>
+        <v>6958159</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5997,7 +5997,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128738306</v>
+        <v>128731037</v>
       </c>
       <c r="B54" t="n">
         <v>57716</v>
@@ -6028,7 +6028,7 @@
       <c r="I54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -6037,10 +6037,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>569644</v>
+        <v>569673</v>
       </c>
       <c r="R54" t="n">
-        <v>6957965</v>
+        <v>6958037</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6104,7 +6104,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128732183</v>
+        <v>128738306</v>
       </c>
       <c r="B55" t="n">
         <v>57716</v>
@@ -6144,10 +6144,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>569777</v>
+        <v>569644</v>
       </c>
       <c r="R55" t="n">
-        <v>6958189</v>
+        <v>6957965</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6184,7 +6184,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6211,7 +6211,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128731037</v>
+        <v>128732183</v>
       </c>
       <c r="B56" t="n">
         <v>57716</v>
@@ -6242,7 +6242,7 @@
       <c r="I56" t="inlineStr"/>
       <c r="M56" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -6251,10 +6251,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>569673</v>
+        <v>569777</v>
       </c>
       <c r="R56" t="n">
-        <v>6958037</v>
+        <v>6958189</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6291,7 +6291,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6318,10 +6318,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128732124</v>
+        <v>128732806</v>
       </c>
       <c r="B57" t="n">
-        <v>80260</v>
+        <v>91515</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6329,21 +6329,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6463</v>
+        <v>1205</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6353,10 +6353,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>569816</v>
+        <v>569827</v>
       </c>
       <c r="R57" t="n">
-        <v>6958081</v>
+        <v>6958133</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6415,32 +6415,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128730101</v>
+        <v>128732719</v>
       </c>
       <c r="B58" t="n">
-        <v>80261</v>
+        <v>91958</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6464</v>
+        <v>1209</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6450,10 +6450,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>569630</v>
+        <v>569821</v>
       </c>
       <c r="R58" t="n">
-        <v>6958139</v>
+        <v>6958151</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6512,50 +6512,45 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128739287</v>
+        <v>128730183</v>
       </c>
       <c r="B59" t="n">
-        <v>57716</v>
+        <v>80185</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>229497</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>569481</v>
+        <v>569630</v>
       </c>
       <c r="R59" t="n">
-        <v>6958122</v>
+        <v>6958129</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6588,11 +6583,6 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6619,50 +6609,45 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128730490</v>
+        <v>128728592</v>
       </c>
       <c r="B60" t="n">
-        <v>57716</v>
+        <v>80260</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>569707</v>
+        <v>569604</v>
       </c>
       <c r="R60" t="n">
-        <v>6958131</v>
+        <v>6958176</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6695,11 +6680,6 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Både äldre och färska spår ( Ringhack av tretåig hackspett på tall)</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6726,50 +6706,45 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128730422</v>
+        <v>128732124</v>
       </c>
       <c r="B61" t="n">
-        <v>57716</v>
+        <v>80260</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>569703</v>
+        <v>569816</v>
       </c>
       <c r="R61" t="n">
-        <v>6958116</v>
+        <v>6958081</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6802,11 +6777,6 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6833,10 +6803,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128732806</v>
+        <v>128730101</v>
       </c>
       <c r="B62" t="n">
-        <v>91510</v>
+        <v>80261</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6844,21 +6814,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1205</v>
+        <v>6464</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6868,10 +6838,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>569827</v>
+        <v>569630</v>
       </c>
       <c r="R62" t="n">
-        <v>6958133</v>
+        <v>6958139</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6930,32 +6900,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128732719</v>
+        <v>128731387</v>
       </c>
       <c r="B63" t="n">
-        <v>91953</v>
+        <v>80253</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1209</v>
+        <v>6461</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6965,10 +6935,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>569821</v>
+        <v>569740</v>
       </c>
       <c r="R63" t="n">
-        <v>6958151</v>
+        <v>6958091</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7027,45 +6997,50 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128730183</v>
+        <v>128730490</v>
       </c>
       <c r="B64" t="n">
-        <v>80185</v>
+        <v>57716</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>229497</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>569630</v>
+        <v>569707</v>
       </c>
       <c r="R64" t="n">
-        <v>6958129</v>
+        <v>6958131</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7098,6 +7073,11 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Både äldre och färska spår ( Ringhack av tretåig hackspett på tall)</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7124,45 +7104,50 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128731387</v>
+        <v>128730422</v>
       </c>
       <c r="B65" t="n">
-        <v>80253</v>
+        <v>57716</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6461</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>569740</v>
+        <v>569703</v>
       </c>
       <c r="R65" t="n">
-        <v>6958091</v>
+        <v>6958116</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7195,6 +7180,11 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7221,45 +7211,50 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128728592</v>
+        <v>128739287</v>
       </c>
       <c r="B66" t="n">
-        <v>80260</v>
+        <v>57716</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>569604</v>
+        <v>569481</v>
       </c>
       <c r="R66" t="n">
-        <v>6958176</v>
+        <v>6958122</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7292,6 +7287,11 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7318,10 +7318,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128729077</v>
+        <v>128730273</v>
       </c>
       <c r="B67" t="n">
-        <v>80225</v>
+        <v>79120</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7329,21 +7329,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7353,10 +7353,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>569604</v>
+        <v>569692</v>
       </c>
       <c r="R67" t="n">
-        <v>6958176</v>
+        <v>6958127</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7415,7 +7415,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128732112</v>
+        <v>128729077</v>
       </c>
       <c r="B68" t="n">
         <v>80225</v>
@@ -7450,10 +7450,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>569824</v>
+        <v>569604</v>
       </c>
       <c r="R68" t="n">
-        <v>6958091</v>
+        <v>6958176</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7512,10 +7512,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128730273</v>
+        <v>128732112</v>
       </c>
       <c r="B69" t="n">
-        <v>79120</v>
+        <v>80225</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7523,21 +7523,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7547,10 +7547,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>569692</v>
+        <v>569824</v>
       </c>
       <c r="R69" t="n">
-        <v>6958127</v>
+        <v>6958091</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7609,32 +7609,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128743263</v>
+        <v>128731693</v>
       </c>
       <c r="B70" t="n">
-        <v>92823</v>
+        <v>91504</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>5964</v>
+        <v>1202</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7644,10 +7644,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>569517</v>
+        <v>569793</v>
       </c>
       <c r="R70" t="n">
-        <v>6958123</v>
+        <v>6958092</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7680,11 +7680,6 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>3 exemplar</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7711,32 +7706,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128731693</v>
+        <v>128743263</v>
       </c>
       <c r="B71" t="n">
-        <v>91499</v>
+        <v>92830</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1202</v>
+        <v>5964</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7746,10 +7741,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>569793</v>
+        <v>569517</v>
       </c>
       <c r="R71" t="n">
-        <v>6958092</v>
+        <v>6958123</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7782,6 +7777,11 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>3 exemplar</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7808,7 +7808,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128732493</v>
+        <v>128728149</v>
       </c>
       <c r="B72" t="n">
         <v>57716</v>
@@ -7848,10 +7848,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>569795</v>
+        <v>569585</v>
       </c>
       <c r="R72" t="n">
-        <v>6958154</v>
+        <v>6958190</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7888,7 +7888,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7915,7 +7915,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128730928</v>
+        <v>128732493</v>
       </c>
       <c r="B73" t="n">
         <v>57716</v>
@@ -7944,24 +7944,21 @@
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
       <c r="M73" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N73" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>569673</v>
+        <v>569795</v>
       </c>
       <c r="R73" t="n">
-        <v>6958076</v>
+        <v>6958154</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7998,7 +7995,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Påbörjat bobygge av sannolikt tretåig hackspett. Ser ut att vara relativt färskt. 2 meter upp i död gran. Omkring 4,5 cm i diameter.</t>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8025,7 +8022,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128728149</v>
+        <v>128730998</v>
       </c>
       <c r="B74" t="n">
         <v>57716</v>
@@ -8065,10 +8062,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>569585</v>
+        <v>569670</v>
       </c>
       <c r="R74" t="n">
-        <v>6958190</v>
+        <v>6958060</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8105,7 +8102,7 @@
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på tall. Även äldre</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8132,7 +8129,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128730998</v>
+        <v>128730928</v>
       </c>
       <c r="B75" t="n">
         <v>57716</v>
@@ -8161,21 +8158,24 @@
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
       <c r="M75" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>569670</v>
+        <v>569673</v>
       </c>
       <c r="R75" t="n">
-        <v>6958060</v>
+        <v>6958076</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8212,7 +8212,7 @@
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>Ringhack på tall. Även äldre</t>
+          <t>Påbörjat bobygge av sannolikt tretåig hackspett. Ser ut att vara relativt färskt. 2 meter upp i död gran. Omkring 4,5 cm i diameter.</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8239,10 +8239,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128731100</v>
+        <v>128743247</v>
       </c>
       <c r="B76" t="n">
-        <v>91517</v>
+        <v>57716</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8250,21 +8250,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8274,10 +8274,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>569688</v>
+        <v>569714</v>
       </c>
       <c r="R76" t="n">
-        <v>6958069</v>
+        <v>6957901</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8310,6 +8310,11 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på gran ( färska spår)</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8336,10 +8341,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128731284</v>
+        <v>128732848</v>
       </c>
       <c r="B77" t="n">
-        <v>57876</v>
+        <v>57716</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8347,27 +8352,27 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="M77" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
@@ -8376,10 +8381,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>569677</v>
+        <v>569873</v>
       </c>
       <c r="R77" t="n">
-        <v>6958066</v>
+        <v>6958099</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8412,6 +8417,11 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8441,7 +8451,7 @@
         <v>128732718</v>
       </c>
       <c r="B78" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8542,7 +8552,7 @@
         <v>128733005</v>
       </c>
       <c r="B79" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8640,10 +8650,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128732848</v>
+        <v>128731100</v>
       </c>
       <c r="B80" t="n">
-        <v>57716</v>
+        <v>91522</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8651,39 +8661,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>569873</v>
+        <v>569688</v>
       </c>
       <c r="R80" t="n">
-        <v>6958099</v>
+        <v>6958069</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8716,11 +8721,6 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8747,10 +8747,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128743247</v>
+        <v>128731284</v>
       </c>
       <c r="B81" t="n">
-        <v>57716</v>
+        <v>57876</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8758,34 +8758,39 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>569714</v>
+        <v>569677</v>
       </c>
       <c r="R81" t="n">
-        <v>6957901</v>
+        <v>6958066</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8818,11 +8823,6 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på gran ( färska spår)</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8852,7 +8852,7 @@
         <v>128731226</v>
       </c>
       <c r="B82" t="n">
-        <v>91517</v>
+        <v>91522</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8946,10 +8946,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128743244</v>
+        <v>128728434</v>
       </c>
       <c r="B83" t="n">
-        <v>91499</v>
+        <v>57716</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8957,34 +8957,39 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>569736</v>
+        <v>569608</v>
       </c>
       <c r="R83" t="n">
-        <v>6957867</v>
+        <v>6958227</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9017,6 +9022,11 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9043,10 +9053,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128728434</v>
+        <v>128743244</v>
       </c>
       <c r="B84" t="n">
-        <v>57716</v>
+        <v>91504</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9054,39 +9064,34 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>569608</v>
+        <v>569736</v>
       </c>
       <c r="R84" t="n">
-        <v>6958227</v>
+        <v>6957867</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9119,11 +9124,6 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9150,10 +9150,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128729895</v>
+        <v>128743257</v>
       </c>
       <c r="B85" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9178,21 +9178,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
+      <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>569713</v>
+        <v>569656</v>
       </c>
       <c r="R85" t="n">
-        <v>6958138</v>
+        <v>6957942</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9225,6 +9221,11 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>23 exemplar (ca)</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9251,10 +9252,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128743257</v>
+        <v>128729895</v>
       </c>
       <c r="B86" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9279,17 +9280,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I86" t="inlineStr"/>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
       <c r="P86" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>569656</v>
+        <v>569713</v>
       </c>
       <c r="R86" t="n">
-        <v>6957942</v>
+        <v>6958138</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9322,11 +9327,6 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>23 exemplar (ca)</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9353,32 +9353,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128728419</v>
+        <v>128738599</v>
       </c>
       <c r="B87" t="n">
-        <v>79120</v>
+        <v>80185</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9391,7 +9391,7 @@
         <v>569608</v>
       </c>
       <c r="R87" t="n">
-        <v>6958227</v>
+        <v>6958048</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9424,11 +9424,6 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>Riklig förekomst inom området</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9455,7 +9450,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128743261</v>
+        <v>128729069</v>
       </c>
       <c r="B88" t="n">
         <v>79120</v>
@@ -9490,10 +9485,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>569495</v>
+        <v>569699</v>
       </c>
       <c r="R88" t="n">
-        <v>6958117</v>
+        <v>6958200</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9552,10 +9547,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128729666</v>
+        <v>128728419</v>
       </c>
       <c r="B89" t="n">
-        <v>57716</v>
+        <v>79120</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9563,39 +9558,34 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P89" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>569706</v>
+        <v>569608</v>
       </c>
       <c r="R89" t="n">
-        <v>6958159</v>
+        <v>6958227</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9632,7 +9622,7 @@
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Riklig förekomst inom området</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9659,10 +9649,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128727978</v>
+        <v>128743261</v>
       </c>
       <c r="B90" t="n">
-        <v>57716</v>
+        <v>79120</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9670,39 +9660,34 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P90" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>569564</v>
+        <v>569495</v>
       </c>
       <c r="R90" t="n">
-        <v>6958213</v>
+        <v>6958117</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9735,11 +9720,6 @@
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9766,45 +9746,50 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128738599</v>
+        <v>128727978</v>
       </c>
       <c r="B91" t="n">
-        <v>80185</v>
+        <v>57716</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>229497</v>
+        <v>100109</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P91" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>569608</v>
+        <v>569564</v>
       </c>
       <c r="R91" t="n">
-        <v>6958048</v>
+        <v>6958213</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9837,6 +9822,11 @@
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9863,10 +9853,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128729069</v>
+        <v>128729666</v>
       </c>
       <c r="B92" t="n">
-        <v>79120</v>
+        <v>57716</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9874,34 +9864,39 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>569699</v>
+        <v>569706</v>
       </c>
       <c r="R92" t="n">
-        <v>6958200</v>
+        <v>6958159</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9934,6 +9929,11 @@
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -9963,7 +9963,7 @@
         <v>128728152</v>
       </c>
       <c r="B93" t="n">
-        <v>91499</v>
+        <v>91504</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10167,7 +10167,7 @@
         <v>128731648</v>
       </c>
       <c r="B95" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10273,7 +10273,7 @@
         <v>128743253</v>
       </c>
       <c r="B96" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10375,7 +10375,7 @@
         <v>128743256</v>
       </c>
       <c r="B97" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>

--- a/artfynd/A 39666-2025 artfynd.xlsx
+++ b/artfynd/A 39666-2025 artfynd.xlsx
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128739007</v>
+        <v>128732386</v>
       </c>
       <c r="B4" t="n">
-        <v>57716</v>
+        <v>80225</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,39 +895,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>569542</v>
+        <v>569785</v>
       </c>
       <c r="R4" t="n">
-        <v>6958069</v>
+        <v>6958124</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -960,11 +955,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128732386</v>
+        <v>128739007</v>
       </c>
       <c r="B5" t="n">
-        <v>80225</v>
+        <v>57716</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1002,34 +992,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>569785</v>
+        <v>569542</v>
       </c>
       <c r="R5" t="n">
-        <v>6958124</v>
+        <v>6958069</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1062,6 +1057,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1290,10 +1290,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128730130</v>
+        <v>128729409</v>
       </c>
       <c r="B8" t="n">
-        <v>57716</v>
+        <v>91504</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1301,39 +1301,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>569713</v>
+        <v>569700</v>
       </c>
       <c r="R8" t="n">
-        <v>6958138</v>
+        <v>6958164</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1366,11 +1361,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1397,10 +1387,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128729409</v>
+        <v>128730130</v>
       </c>
       <c r="B9" t="n">
-        <v>91504</v>
+        <v>57716</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1408,34 +1398,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>569700</v>
+        <v>569713</v>
       </c>
       <c r="R9" t="n">
-        <v>6958164</v>
+        <v>6958138</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1468,6 +1463,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1494,10 +1494,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128732217</v>
+        <v>128730571</v>
       </c>
       <c r="B10" t="n">
-        <v>57876</v>
+        <v>91522</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1505,48 +1505,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>569777</v>
+        <v>569660</v>
       </c>
       <c r="R10" t="n">
-        <v>6958189</v>
+        <v>6958074</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1579,11 +1565,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>2 talltitor kommer flygandes väldigt närgånget och varnar</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1610,32 +1591,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128733181</v>
+        <v>128732765</v>
       </c>
       <c r="B11" t="n">
-        <v>98549</v>
+        <v>91800</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219790</v>
+        <v>658</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1645,10 +1626,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>569900</v>
+        <v>569827</v>
       </c>
       <c r="R11" t="n">
-        <v>6958101</v>
+        <v>6958133</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1707,10 +1688,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128732765</v>
+        <v>128732276</v>
       </c>
       <c r="B12" t="n">
-        <v>91800</v>
+        <v>57716</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1718,34 +1699,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>569827</v>
+        <v>569841</v>
       </c>
       <c r="R12" t="n">
-        <v>6958133</v>
+        <v>6958102</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1778,6 +1764,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1804,10 +1795,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128730571</v>
+        <v>128743245</v>
       </c>
       <c r="B13" t="n">
-        <v>91522</v>
+        <v>57716</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1815,21 +1806,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1839,10 +1830,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>569660</v>
+        <v>569590</v>
       </c>
       <c r="R13" t="n">
-        <v>6958074</v>
+        <v>6958014</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1875,6 +1866,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall ( färska spår)</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1901,50 +1897,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128732276</v>
+        <v>128733181</v>
       </c>
       <c r="B14" t="n">
-        <v>57716</v>
+        <v>98549</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>569841</v>
+        <v>569900</v>
       </c>
       <c r="R14" t="n">
-        <v>6958102</v>
+        <v>6958101</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1977,11 +1968,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2008,10 +1994,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128743245</v>
+        <v>128732217</v>
       </c>
       <c r="B15" t="n">
-        <v>57716</v>
+        <v>57876</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2019,34 +2005,48 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>569590</v>
+        <v>569777</v>
       </c>
       <c r="R15" t="n">
-        <v>6958014</v>
+        <v>6958189</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2083,7 +2083,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall ( färska spår)</t>
+          <t>2 talltitor kommer flygandes väldigt närgånget och varnar</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2110,45 +2110,50 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128728515</v>
+        <v>128731601</v>
       </c>
       <c r="B16" t="n">
-        <v>97503</v>
+        <v>57716</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>569608</v>
+        <v>569752</v>
       </c>
       <c r="R16" t="n">
-        <v>6958227</v>
+        <v>6958091</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2181,6 +2186,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2207,49 +2217,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128731490</v>
+        <v>128728515</v>
       </c>
       <c r="B17" t="n">
-        <v>98632</v>
+        <v>97503</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>569759</v>
+        <v>569608</v>
       </c>
       <c r="R17" t="n">
-        <v>6958118</v>
+        <v>6958227</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2308,7 +2314,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128730429</v>
+        <v>128731490</v>
       </c>
       <c r="B18" t="n">
         <v>98632</v>
@@ -2338,7 +2344,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2347,10 +2353,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>569683</v>
+        <v>569759</v>
       </c>
       <c r="R18" t="n">
-        <v>6958128</v>
+        <v>6958118</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2409,38 +2415,37 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128731601</v>
+        <v>128730429</v>
       </c>
       <c r="B19" t="n">
-        <v>57716</v>
+        <v>98632</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>80</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2449,10 +2454,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>569752</v>
+        <v>569683</v>
       </c>
       <c r="R19" t="n">
-        <v>6958091</v>
+        <v>6958128</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2485,11 +2490,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2613,50 +2613,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128731107</v>
+        <v>128728022</v>
       </c>
       <c r="B21" t="n">
-        <v>57876</v>
+        <v>91469</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103021</v>
+        <v>5447</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>569705</v>
+        <v>569583</v>
       </c>
       <c r="R21" t="n">
-        <v>6958098</v>
+        <v>6958204</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2715,10 +2710,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128732359</v>
+        <v>128739020</v>
       </c>
       <c r="B22" t="n">
-        <v>91504</v>
+        <v>57716</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2726,34 +2721,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>569820</v>
+        <v>569542</v>
       </c>
       <c r="R22" t="n">
-        <v>6958107</v>
+        <v>6958049</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2786,6 +2786,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2812,10 +2817,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128731612</v>
+        <v>128731107</v>
       </c>
       <c r="B23" t="n">
-        <v>91504</v>
+        <v>57876</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2823,34 +2828,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>569752</v>
+        <v>569705</v>
       </c>
       <c r="R23" t="n">
-        <v>6958091</v>
+        <v>6958098</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2909,32 +2919,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128728022</v>
+        <v>128732359</v>
       </c>
       <c r="B24" t="n">
-        <v>91469</v>
+        <v>91504</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2944,10 +2954,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>569583</v>
+        <v>569820</v>
       </c>
       <c r="R24" t="n">
-        <v>6958204</v>
+        <v>6958107</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3006,10 +3016,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128739020</v>
+        <v>128731612</v>
       </c>
       <c r="B25" t="n">
-        <v>57716</v>
+        <v>91504</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3017,39 +3027,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>569542</v>
+        <v>569752</v>
       </c>
       <c r="R25" t="n">
-        <v>6958049</v>
+        <v>6958091</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3082,11 +3087,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3418,7 +3418,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128731291</v>
+        <v>128728019</v>
       </c>
       <c r="B29" t="n">
         <v>57716</v>
@@ -3458,10 +3458,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>569726</v>
+        <v>569577</v>
       </c>
       <c r="R29" t="n">
-        <v>6958097</v>
+        <v>6958213</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3498,7 +3498,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på tall</t>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3525,38 +3525,37 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128728019</v>
+        <v>128731489</v>
       </c>
       <c r="B30" t="n">
-        <v>57716</v>
+        <v>98632</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>45</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3565,10 +3564,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>569577</v>
+        <v>569752</v>
       </c>
       <c r="R30" t="n">
-        <v>6958213</v>
+        <v>6958091</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3601,11 +3600,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3632,37 +3626,38 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128731489</v>
+        <v>128731291</v>
       </c>
       <c r="B31" t="n">
-        <v>98632</v>
+        <v>57716</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>45</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -3671,10 +3666,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>569752</v>
+        <v>569726</v>
       </c>
       <c r="R31" t="n">
-        <v>6958091</v>
+        <v>6958097</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3707,6 +3702,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på tall</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3844,50 +3844,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128728303</v>
+        <v>128730513</v>
       </c>
       <c r="B33" t="n">
-        <v>57708</v>
+        <v>80225</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100110</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>569584</v>
+        <v>569656</v>
       </c>
       <c r="R33" t="n">
-        <v>6958214</v>
+        <v>6958093</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3920,11 +3915,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Hörs i närheten</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4058,45 +4048,50 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128730513</v>
+        <v>128728303</v>
       </c>
       <c r="B35" t="n">
-        <v>80225</v>
+        <v>57708</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>100110</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>J.F. Gmelin, 1788</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>569656</v>
+        <v>569584</v>
       </c>
       <c r="R35" t="n">
-        <v>6958093</v>
+        <v>6958214</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4129,6 +4124,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Hörs i närheten</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4155,38 +4155,37 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128729745</v>
+        <v>128732677</v>
       </c>
       <c r="B36" t="n">
-        <v>57716</v>
+        <v>98632</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>12</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4195,10 +4194,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>569694</v>
+        <v>569817</v>
       </c>
       <c r="R36" t="n">
-        <v>6958144</v>
+        <v>6958134</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4231,11 +4230,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4262,32 +4256,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128728318</v>
+        <v>128743255</v>
       </c>
       <c r="B37" t="n">
-        <v>79120</v>
+        <v>98632</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4297,10 +4291,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>569616</v>
+        <v>569613</v>
       </c>
       <c r="R37" t="n">
-        <v>6958208</v>
+        <v>6957995</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4333,6 +4327,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>28 exemplar knärot</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4359,32 +4358,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128731677</v>
+        <v>128743254</v>
       </c>
       <c r="B38" t="n">
-        <v>79120</v>
+        <v>98632</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4394,10 +4393,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>569769</v>
+        <v>569547</v>
       </c>
       <c r="R38" t="n">
-        <v>6958153</v>
+        <v>6958078</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4430,6 +4429,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>20 (ca) exemplar</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4456,37 +4460,38 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128732677</v>
+        <v>128729745</v>
       </c>
       <c r="B39" t="n">
-        <v>98632</v>
+        <v>57716</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>12</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -4495,10 +4500,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>569817</v>
+        <v>569694</v>
       </c>
       <c r="R39" t="n">
-        <v>6958134</v>
+        <v>6958144</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4531,6 +4536,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4557,32 +4567,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128743255</v>
+        <v>128728318</v>
       </c>
       <c r="B40" t="n">
-        <v>98632</v>
+        <v>79120</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4592,10 +4602,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>569613</v>
+        <v>569616</v>
       </c>
       <c r="R40" t="n">
-        <v>6957995</v>
+        <v>6958208</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4628,11 +4638,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>28 exemplar knärot</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4659,32 +4664,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128743254</v>
+        <v>128731677</v>
       </c>
       <c r="B41" t="n">
-        <v>98632</v>
+        <v>79120</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4694,10 +4699,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>569547</v>
+        <v>569769</v>
       </c>
       <c r="R41" t="n">
-        <v>6958078</v>
+        <v>6958153</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4730,11 +4735,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>20 (ca) exemplar</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4761,10 +4761,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128729439</v>
+        <v>128728473</v>
       </c>
       <c r="B42" t="n">
-        <v>91504</v>
+        <v>57876</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4772,34 +4772,39 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>569703</v>
+        <v>569608</v>
       </c>
       <c r="R42" t="n">
-        <v>6958175</v>
+        <v>6958227</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4858,10 +4863,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128730475</v>
+        <v>128729439</v>
       </c>
       <c r="B43" t="n">
-        <v>57716</v>
+        <v>91504</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4869,39 +4874,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>569675</v>
+        <v>569703</v>
       </c>
       <c r="R43" t="n">
-        <v>6958098</v>
+        <v>6958175</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4934,11 +4934,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4965,10 +4960,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128728473</v>
+        <v>128729962</v>
       </c>
       <c r="B44" t="n">
-        <v>57876</v>
+        <v>80225</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4976,39 +4971,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>569608</v>
+        <v>569643</v>
       </c>
       <c r="R44" t="n">
-        <v>6958227</v>
+        <v>6958117</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5067,10 +5057,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128729962</v>
+        <v>128730475</v>
       </c>
       <c r="B45" t="n">
-        <v>80225</v>
+        <v>57716</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5078,34 +5068,39 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>569643</v>
+        <v>569675</v>
       </c>
       <c r="R45" t="n">
-        <v>6958117</v>
+        <v>6958098</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5138,6 +5133,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5164,38 +5164,37 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128728902</v>
+        <v>128732627</v>
       </c>
       <c r="B46" t="n">
-        <v>57716</v>
+        <v>98632</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>6</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -5204,10 +5203,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>569673</v>
+        <v>569821</v>
       </c>
       <c r="R46" t="n">
-        <v>6958225</v>
+        <v>6958151</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5244,7 +5243,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>Kan finnas mer I blåbärsriset och mossan</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5271,38 +5270,37 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128731799</v>
+        <v>128728348</v>
       </c>
       <c r="B47" t="n">
-        <v>57716</v>
+        <v>98632</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>300</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -5311,10 +5309,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>569774</v>
+        <v>569616</v>
       </c>
       <c r="R47" t="n">
-        <v>6958163</v>
+        <v>6958208</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5347,11 +5345,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5378,7 +5371,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128732015</v>
+        <v>128731799</v>
       </c>
       <c r="B48" t="n">
         <v>57716</v>
@@ -5409,7 +5402,7 @@
       <c r="I48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -5418,10 +5411,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>569816</v>
+        <v>569774</v>
       </c>
       <c r="R48" t="n">
-        <v>6958081</v>
+        <v>6958163</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5458,7 +5451,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5485,7 +5478,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128738187</v>
+        <v>128728902</v>
       </c>
       <c r="B49" t="n">
         <v>57716</v>
@@ -5525,10 +5518,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>569681</v>
+        <v>569673</v>
       </c>
       <c r="R49" t="n">
-        <v>6957939</v>
+        <v>6958225</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5565,7 +5558,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5592,37 +5585,38 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128732627</v>
+        <v>128732015</v>
       </c>
       <c r="B50" t="n">
-        <v>98632</v>
+        <v>57716</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>6</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -5631,10 +5625,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>569821</v>
+        <v>569816</v>
       </c>
       <c r="R50" t="n">
-        <v>6958151</v>
+        <v>6958081</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5671,7 +5665,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Kan finnas mer I blåbärsriset och mossan</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5698,37 +5692,38 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128728348</v>
+        <v>128738187</v>
       </c>
       <c r="B51" t="n">
-        <v>98632</v>
+        <v>57716</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>300</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -5737,10 +5732,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>569616</v>
+        <v>569681</v>
       </c>
       <c r="R51" t="n">
-        <v>6958208</v>
+        <v>6957939</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5773,6 +5768,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6318,10 +6318,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128732806</v>
+        <v>128728592</v>
       </c>
       <c r="B57" t="n">
-        <v>91515</v>
+        <v>80260</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6329,21 +6329,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1205</v>
+        <v>6463</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6353,10 +6353,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>569827</v>
+        <v>569604</v>
       </c>
       <c r="R57" t="n">
-        <v>6958133</v>
+        <v>6958176</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6415,32 +6415,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128732719</v>
+        <v>128732124</v>
       </c>
       <c r="B58" t="n">
-        <v>91958</v>
+        <v>80260</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1209</v>
+        <v>6463</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6450,10 +6450,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>569821</v>
+        <v>569816</v>
       </c>
       <c r="R58" t="n">
-        <v>6958151</v>
+        <v>6958081</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6512,10 +6512,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128730183</v>
+        <v>128730101</v>
       </c>
       <c r="B59" t="n">
-        <v>80185</v>
+        <v>80261</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6523,21 +6523,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>229497</v>
+        <v>6464</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6550,7 +6550,7 @@
         <v>569630</v>
       </c>
       <c r="R59" t="n">
-        <v>6958129</v>
+        <v>6958139</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6609,10 +6609,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128728592</v>
+        <v>128731387</v>
       </c>
       <c r="B60" t="n">
-        <v>80260</v>
+        <v>80253</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6620,21 +6620,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6463</v>
+        <v>6461</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6644,10 +6644,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>569604</v>
+        <v>569740</v>
       </c>
       <c r="R60" t="n">
-        <v>6958176</v>
+        <v>6958091</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6706,10 +6706,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128732124</v>
+        <v>128732806</v>
       </c>
       <c r="B61" t="n">
-        <v>80260</v>
+        <v>91515</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6717,21 +6717,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6463</v>
+        <v>1205</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6741,10 +6741,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>569816</v>
+        <v>569827</v>
       </c>
       <c r="R61" t="n">
-        <v>6958081</v>
+        <v>6958133</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6803,32 +6803,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128730101</v>
+        <v>128732719</v>
       </c>
       <c r="B62" t="n">
-        <v>80261</v>
+        <v>91958</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6464</v>
+        <v>1209</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6838,10 +6838,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>569630</v>
+        <v>569821</v>
       </c>
       <c r="R62" t="n">
-        <v>6958139</v>
+        <v>6958151</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6900,45 +6900,50 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128731387</v>
+        <v>128730490</v>
       </c>
       <c r="B63" t="n">
-        <v>80253</v>
+        <v>57716</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6461</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>569740</v>
+        <v>569707</v>
       </c>
       <c r="R63" t="n">
-        <v>6958091</v>
+        <v>6958131</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6971,6 +6976,11 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Både äldre och färska spår ( Ringhack av tretåig hackspett på tall)</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6997,7 +7007,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128730490</v>
+        <v>128730422</v>
       </c>
       <c r="B64" t="n">
         <v>57716</v>
@@ -7037,10 +7047,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>569707</v>
+        <v>569703</v>
       </c>
       <c r="R64" t="n">
-        <v>6958131</v>
+        <v>6958116</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7077,7 +7087,7 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Både äldre och färska spår ( Ringhack av tretåig hackspett på tall)</t>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7104,7 +7114,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128730422</v>
+        <v>128739287</v>
       </c>
       <c r="B65" t="n">
         <v>57716</v>
@@ -7144,10 +7154,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>569703</v>
+        <v>569481</v>
       </c>
       <c r="R65" t="n">
-        <v>6958116</v>
+        <v>6958122</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7184,7 +7194,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7211,50 +7221,45 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128739287</v>
+        <v>128730183</v>
       </c>
       <c r="B66" t="n">
-        <v>57716</v>
+        <v>80185</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>229497</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>569481</v>
+        <v>569630</v>
       </c>
       <c r="R66" t="n">
-        <v>6958122</v>
+        <v>6958129</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7287,11 +7292,6 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7318,10 +7318,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128730273</v>
+        <v>128729077</v>
       </c>
       <c r="B67" t="n">
-        <v>79120</v>
+        <v>80225</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7329,21 +7329,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7353,10 +7353,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>569692</v>
+        <v>569604</v>
       </c>
       <c r="R67" t="n">
-        <v>6958127</v>
+        <v>6958176</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7415,10 +7415,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128729077</v>
+        <v>128730273</v>
       </c>
       <c r="B68" t="n">
-        <v>80225</v>
+        <v>79120</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7426,21 +7426,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7450,10 +7450,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>569604</v>
+        <v>569692</v>
       </c>
       <c r="R68" t="n">
-        <v>6958176</v>
+        <v>6958127</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7609,10 +7609,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128731693</v>
+        <v>128732493</v>
       </c>
       <c r="B70" t="n">
-        <v>91504</v>
+        <v>57716</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7620,34 +7620,39 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>569793</v>
+        <v>569795</v>
       </c>
       <c r="R70" t="n">
-        <v>6958092</v>
+        <v>6958154</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7680,6 +7685,11 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7706,32 +7716,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128743263</v>
+        <v>128731693</v>
       </c>
       <c r="B71" t="n">
-        <v>92830</v>
+        <v>91504</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>5964</v>
+        <v>1202</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7741,10 +7751,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>569517</v>
+        <v>569793</v>
       </c>
       <c r="R71" t="n">
-        <v>6958123</v>
+        <v>6958092</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7777,11 +7787,6 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>3 exemplar</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7808,50 +7813,45 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128728149</v>
+        <v>128743263</v>
       </c>
       <c r="B72" t="n">
-        <v>57716</v>
+        <v>92830</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100109</v>
+        <v>5964</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>569585</v>
+        <v>569517</v>
       </c>
       <c r="R72" t="n">
-        <v>6958190</v>
+        <v>6958123</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7888,7 +7888,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>3 exemplar</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7915,7 +7915,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128732493</v>
+        <v>128728149</v>
       </c>
       <c r="B73" t="n">
         <v>57716</v>
@@ -7955,10 +7955,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>569795</v>
+        <v>569585</v>
       </c>
       <c r="R73" t="n">
-        <v>6958154</v>
+        <v>6958190</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7995,7 +7995,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8341,10 +8341,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128732848</v>
+        <v>128731100</v>
       </c>
       <c r="B77" t="n">
-        <v>57716</v>
+        <v>91522</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8352,39 +8352,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>569873</v>
+        <v>569688</v>
       </c>
       <c r="R77" t="n">
-        <v>6958099</v>
+        <v>6958069</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8417,11 +8412,6 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8448,37 +8438,38 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128732718</v>
+        <v>128732848</v>
       </c>
       <c r="B78" t="n">
-        <v>98632</v>
+        <v>57716</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>18</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
@@ -8487,10 +8478,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>569834</v>
+        <v>569873</v>
       </c>
       <c r="R78" t="n">
-        <v>6958143</v>
+        <v>6958099</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8523,6 +8514,11 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8549,37 +8545,38 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128733005</v>
+        <v>128731284</v>
       </c>
       <c r="B79" t="n">
-        <v>98632</v>
+        <v>57876</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>7</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
@@ -8588,10 +8585,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>569882</v>
+        <v>569677</v>
       </c>
       <c r="R79" t="n">
-        <v>6958106</v>
+        <v>6958066</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8650,45 +8647,49 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128731100</v>
+        <v>128732718</v>
       </c>
       <c r="B80" t="n">
-        <v>91522</v>
+        <v>98632</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>569688</v>
+        <v>569834</v>
       </c>
       <c r="R80" t="n">
-        <v>6958069</v>
+        <v>6958143</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8747,38 +8748,37 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128731284</v>
+        <v>128733005</v>
       </c>
       <c r="B81" t="n">
-        <v>57876</v>
+        <v>98632</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>7</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
@@ -8787,10 +8787,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>569677</v>
+        <v>569882</v>
       </c>
       <c r="R81" t="n">
-        <v>6958066</v>
+        <v>6958106</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8849,10 +8849,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128731226</v>
+        <v>128743244</v>
       </c>
       <c r="B82" t="n">
-        <v>91522</v>
+        <v>91504</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8860,21 +8860,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8884,10 +8884,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>569705</v>
+        <v>569736</v>
       </c>
       <c r="R82" t="n">
-        <v>6958098</v>
+        <v>6957867</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8946,10 +8946,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128728434</v>
+        <v>128731226</v>
       </c>
       <c r="B83" t="n">
-        <v>57716</v>
+        <v>91522</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8957,39 +8957,34 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>569608</v>
+        <v>569705</v>
       </c>
       <c r="R83" t="n">
-        <v>6958227</v>
+        <v>6958098</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9022,11 +9017,6 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9053,10 +9043,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128743244</v>
+        <v>128728434</v>
       </c>
       <c r="B84" t="n">
-        <v>91504</v>
+        <v>57716</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9064,34 +9054,39 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>569736</v>
+        <v>569608</v>
       </c>
       <c r="R84" t="n">
-        <v>6957867</v>
+        <v>6958227</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9124,6 +9119,11 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9150,7 +9150,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128743257</v>
+        <v>128729895</v>
       </c>
       <c r="B85" t="n">
         <v>98632</v>
@@ -9178,17 +9178,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I85" t="inlineStr"/>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>569656</v>
+        <v>569713</v>
       </c>
       <c r="R85" t="n">
-        <v>6957942</v>
+        <v>6958138</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9221,11 +9225,6 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>23 exemplar (ca)</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9252,7 +9251,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128729895</v>
+        <v>128743257</v>
       </c>
       <c r="B86" t="n">
         <v>98632</v>
@@ -9280,21 +9279,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
+      <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>569713</v>
+        <v>569656</v>
       </c>
       <c r="R86" t="n">
-        <v>6958138</v>
+        <v>6957942</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9327,6 +9322,11 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>23 exemplar (ca)</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9450,10 +9450,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128729069</v>
+        <v>128727978</v>
       </c>
       <c r="B88" t="n">
-        <v>79120</v>
+        <v>57716</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9461,34 +9461,39 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>569699</v>
+        <v>569564</v>
       </c>
       <c r="R88" t="n">
-        <v>6958200</v>
+        <v>6958213</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9521,6 +9526,11 @@
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9547,10 +9557,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128728419</v>
+        <v>128729666</v>
       </c>
       <c r="B89" t="n">
-        <v>79120</v>
+        <v>57716</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9558,34 +9568,39 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P89" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>569608</v>
+        <v>569706</v>
       </c>
       <c r="R89" t="n">
-        <v>6958227</v>
+        <v>6958159</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9622,7 +9637,7 @@
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>Riklig förekomst inom området</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9649,7 +9664,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128743261</v>
+        <v>128729069</v>
       </c>
       <c r="B90" t="n">
         <v>79120</v>
@@ -9684,10 +9699,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>569495</v>
+        <v>569699</v>
       </c>
       <c r="R90" t="n">
-        <v>6958117</v>
+        <v>6958200</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9746,10 +9761,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128727978</v>
+        <v>128728419</v>
       </c>
       <c r="B91" t="n">
-        <v>57716</v>
+        <v>79120</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9757,39 +9772,34 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P91" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>569564</v>
+        <v>569608</v>
       </c>
       <c r="R91" t="n">
-        <v>6958213</v>
+        <v>6958227</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9826,7 +9836,7 @@
       </c>
       <c r="AC91" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Riklig förekomst inom området</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9853,10 +9863,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128729666</v>
+        <v>128743261</v>
       </c>
       <c r="B92" t="n">
-        <v>57716</v>
+        <v>79120</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9864,39 +9874,34 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>569706</v>
+        <v>569495</v>
       </c>
       <c r="R92" t="n">
-        <v>6958159</v>
+        <v>6958117</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9929,11 +9934,6 @@
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC92" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD92" t="b">

--- a/artfynd/A 39666-2025 artfynd.xlsx
+++ b/artfynd/A 39666-2025 artfynd.xlsx
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128732386</v>
+        <v>128739007</v>
       </c>
       <c r="B4" t="n">
-        <v>80225</v>
+        <v>57716</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,34 +895,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>569785</v>
+        <v>569542</v>
       </c>
       <c r="R4" t="n">
-        <v>6958124</v>
+        <v>6958069</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -955,6 +960,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -981,38 +991,37 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128739007</v>
+        <v>128728896</v>
       </c>
       <c r="B5" t="n">
-        <v>57716</v>
+        <v>98632</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>6</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1021,10 +1030,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>569542</v>
+        <v>569601</v>
       </c>
       <c r="R5" t="n">
-        <v>6958069</v>
+        <v>6958191</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1057,11 +1066,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1088,7 +1092,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128728896</v>
+        <v>128732983</v>
       </c>
       <c r="B6" t="n">
         <v>98632</v>
@@ -1118,7 +1122,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1127,10 +1131,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>569601</v>
+        <v>569873</v>
       </c>
       <c r="R6" t="n">
-        <v>6958191</v>
+        <v>6958099</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1189,49 +1193,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128732983</v>
+        <v>128732386</v>
       </c>
       <c r="B7" t="n">
-        <v>98632</v>
+        <v>80225</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>569873</v>
+        <v>569785</v>
       </c>
       <c r="R7" t="n">
-        <v>6958099</v>
+        <v>6958124</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1494,10 +1494,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128730571</v>
+        <v>128732765</v>
       </c>
       <c r="B10" t="n">
-        <v>91522</v>
+        <v>91800</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1505,21 +1505,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1529,10 +1529,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>569660</v>
+        <v>569827</v>
       </c>
       <c r="R10" t="n">
-        <v>6958074</v>
+        <v>6958133</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1591,10 +1591,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128732765</v>
+        <v>128730571</v>
       </c>
       <c r="B11" t="n">
-        <v>91800</v>
+        <v>91522</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1602,21 +1602,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1626,10 +1626,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>569827</v>
+        <v>569660</v>
       </c>
       <c r="R11" t="n">
-        <v>6958133</v>
+        <v>6958074</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1897,45 +1897,59 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128733181</v>
+        <v>128732217</v>
       </c>
       <c r="B14" t="n">
-        <v>98549</v>
+        <v>57876</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219790</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>569900</v>
+        <v>569777</v>
       </c>
       <c r="R14" t="n">
-        <v>6958101</v>
+        <v>6958189</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1968,6 +1982,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>2 talltitor kommer flygandes väldigt närgånget och varnar</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1994,59 +2013,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128732217</v>
+        <v>128733181</v>
       </c>
       <c r="B15" t="n">
-        <v>57876</v>
+        <v>98549</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>219790</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>569777</v>
+        <v>569900</v>
       </c>
       <c r="R15" t="n">
-        <v>6958189</v>
+        <v>6958101</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2079,11 +2084,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>2 talltitor kommer flygandes väldigt närgånget och varnar</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2516,32 +2516,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128743262</v>
+        <v>128728022</v>
       </c>
       <c r="B20" t="n">
-        <v>79120</v>
+        <v>91469</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2551,10 +2551,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>569732</v>
+        <v>569583</v>
       </c>
       <c r="R20" t="n">
-        <v>6957870</v>
+        <v>6958204</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2613,32 +2613,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128728022</v>
+        <v>128743262</v>
       </c>
       <c r="B21" t="n">
-        <v>91469</v>
+        <v>79120</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2648,10 +2648,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>569583</v>
+        <v>569732</v>
       </c>
       <c r="R21" t="n">
-        <v>6958204</v>
+        <v>6957870</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2710,38 +2710,37 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128739020</v>
+        <v>128730720</v>
       </c>
       <c r="B22" t="n">
-        <v>57716</v>
+        <v>98632</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>50</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2750,10 +2749,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>569542</v>
+        <v>569692</v>
       </c>
       <c r="R22" t="n">
-        <v>6958049</v>
+        <v>6958094</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2790,7 +2789,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ca</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2817,50 +2816,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128731107</v>
+        <v>128743252</v>
       </c>
       <c r="B23" t="n">
-        <v>57876</v>
+        <v>98632</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>569705</v>
+        <v>569610</v>
       </c>
       <c r="R23" t="n">
-        <v>6958098</v>
+        <v>6958005</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2893,6 +2887,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>2 exemplar</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2919,10 +2918,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128732359</v>
+        <v>128731107</v>
       </c>
       <c r="B24" t="n">
-        <v>91504</v>
+        <v>57876</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2930,34 +2929,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>569820</v>
+        <v>569705</v>
       </c>
       <c r="R24" t="n">
-        <v>6958107</v>
+        <v>6958098</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3016,7 +3020,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128731612</v>
+        <v>128732359</v>
       </c>
       <c r="B25" t="n">
         <v>91504</v>
@@ -3051,10 +3055,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>569752</v>
+        <v>569820</v>
       </c>
       <c r="R25" t="n">
-        <v>6958091</v>
+        <v>6958107</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3113,49 +3117,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128730720</v>
+        <v>128731612</v>
       </c>
       <c r="B26" t="n">
-        <v>98632</v>
+        <v>91504</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>569692</v>
+        <v>569752</v>
       </c>
       <c r="R26" t="n">
-        <v>6958094</v>
+        <v>6958091</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3188,11 +3188,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ca</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3219,45 +3214,50 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128743252</v>
+        <v>128739020</v>
       </c>
       <c r="B27" t="n">
-        <v>98632</v>
+        <v>57716</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>569610</v>
+        <v>569542</v>
       </c>
       <c r="R27" t="n">
-        <v>6958005</v>
+        <v>6958049</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3294,7 +3294,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>2 exemplar</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3321,45 +3321,50 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128729068</v>
+        <v>128731291</v>
       </c>
       <c r="B28" t="n">
-        <v>80254</v>
+        <v>57716</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>569604</v>
+        <v>569726</v>
       </c>
       <c r="R28" t="n">
-        <v>6958176</v>
+        <v>6958097</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3392,6 +3397,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på tall</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3418,50 +3428,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128728019</v>
+        <v>128729068</v>
       </c>
       <c r="B29" t="n">
-        <v>57716</v>
+        <v>80254</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>569577</v>
+        <v>569604</v>
       </c>
       <c r="R29" t="n">
-        <v>6958213</v>
+        <v>6958176</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3494,11 +3499,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3525,37 +3525,38 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128731489</v>
+        <v>128728019</v>
       </c>
       <c r="B30" t="n">
-        <v>98632</v>
+        <v>57716</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>45</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3564,10 +3565,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>569752</v>
+        <v>569577</v>
       </c>
       <c r="R30" t="n">
-        <v>6958091</v>
+        <v>6958213</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3600,6 +3601,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3626,38 +3632,37 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128731291</v>
+        <v>128731489</v>
       </c>
       <c r="B31" t="n">
-        <v>57716</v>
+        <v>98632</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>45</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -3666,10 +3671,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>569726</v>
+        <v>569752</v>
       </c>
       <c r="R31" t="n">
-        <v>6958097</v>
+        <v>6958091</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3702,11 +3707,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på tall</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3733,54 +3733,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128728767</v>
+        <v>128730513</v>
       </c>
       <c r="B32" t="n">
-        <v>92794</v>
+        <v>80225</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>569639</v>
+        <v>569656</v>
       </c>
       <c r="R32" t="n">
-        <v>6958231</v>
+        <v>6958093</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3813,11 +3804,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>4 äldre ett färskt års exemplar</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3844,45 +3830,54 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128730513</v>
+        <v>128728767</v>
       </c>
       <c r="B33" t="n">
-        <v>80225</v>
+        <v>92794</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>569656</v>
+        <v>569639</v>
       </c>
       <c r="R33" t="n">
-        <v>6958093</v>
+        <v>6958231</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3915,6 +3910,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>4 äldre ett färskt års exemplar</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3941,38 +3941,38 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128730603</v>
+        <v>128728303</v>
       </c>
       <c r="B34" t="n">
-        <v>57716</v>
+        <v>57708</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>100110</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>J.F. Gmelin, 1788</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -3981,10 +3981,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>569738</v>
+        <v>569584</v>
       </c>
       <c r="R34" t="n">
-        <v>6958117</v>
+        <v>6958214</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4021,7 +4021,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Äldre exemplar av ringhack på Tall från tretåig hackspett</t>
+          <t>Hörs i närheten</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4048,38 +4048,38 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128728303</v>
+        <v>128730603</v>
       </c>
       <c r="B35" t="n">
-        <v>57708</v>
+        <v>57716</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100110</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4088,10 +4088,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>569584</v>
+        <v>569738</v>
       </c>
       <c r="R35" t="n">
-        <v>6958214</v>
+        <v>6958117</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Hörs i närheten</t>
+          <t>Äldre exemplar av ringhack på Tall från tretåig hackspett</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4155,37 +4155,38 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128732677</v>
+        <v>128729745</v>
       </c>
       <c r="B36" t="n">
-        <v>98632</v>
+        <v>57716</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>12</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4194,10 +4195,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>569817</v>
+        <v>569694</v>
       </c>
       <c r="R36" t="n">
-        <v>6958134</v>
+        <v>6958144</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4230,6 +4231,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4256,32 +4262,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128743255</v>
+        <v>128728318</v>
       </c>
       <c r="B37" t="n">
-        <v>98632</v>
+        <v>79120</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4291,10 +4297,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>569613</v>
+        <v>569616</v>
       </c>
       <c r="R37" t="n">
-        <v>6957995</v>
+        <v>6958208</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4327,11 +4333,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>28 exemplar knärot</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4358,32 +4359,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128743254</v>
+        <v>128731677</v>
       </c>
       <c r="B38" t="n">
-        <v>98632</v>
+        <v>79120</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4393,10 +4394,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>569547</v>
+        <v>569769</v>
       </c>
       <c r="R38" t="n">
-        <v>6958078</v>
+        <v>6958153</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4429,11 +4430,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>20 (ca) exemplar</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4460,50 +4456,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128729745</v>
+        <v>128743255</v>
       </c>
       <c r="B39" t="n">
-        <v>57716</v>
+        <v>98632</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>569694</v>
+        <v>569613</v>
       </c>
       <c r="R39" t="n">
-        <v>6958144</v>
+        <v>6957995</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4540,7 +4531,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>28 exemplar knärot</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4567,32 +4558,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128728318</v>
+        <v>128743254</v>
       </c>
       <c r="B40" t="n">
-        <v>79120</v>
+        <v>98632</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4602,10 +4593,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>569616</v>
+        <v>569547</v>
       </c>
       <c r="R40" t="n">
-        <v>6958208</v>
+        <v>6958078</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4638,6 +4629,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>20 (ca) exemplar</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4664,45 +4660,49 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128731677</v>
+        <v>128732677</v>
       </c>
       <c r="B41" t="n">
-        <v>79120</v>
+        <v>98632</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>569769</v>
+        <v>569817</v>
       </c>
       <c r="R41" t="n">
-        <v>6958153</v>
+        <v>6958134</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4761,10 +4761,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128728473</v>
+        <v>128729439</v>
       </c>
       <c r="B42" t="n">
-        <v>57876</v>
+        <v>91504</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4772,39 +4772,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>569608</v>
+        <v>569703</v>
       </c>
       <c r="R42" t="n">
-        <v>6958227</v>
+        <v>6958175</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4863,10 +4858,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128729439</v>
+        <v>128729962</v>
       </c>
       <c r="B43" t="n">
-        <v>91504</v>
+        <v>80225</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4874,21 +4869,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4898,10 +4893,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>569703</v>
+        <v>569643</v>
       </c>
       <c r="R43" t="n">
-        <v>6958175</v>
+        <v>6958117</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4960,10 +4955,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128729962</v>
+        <v>128730475</v>
       </c>
       <c r="B44" t="n">
-        <v>80225</v>
+        <v>57716</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4971,34 +4966,39 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>569643</v>
+        <v>569675</v>
       </c>
       <c r="R44" t="n">
-        <v>6958117</v>
+        <v>6958098</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5031,6 +5031,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5057,10 +5062,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128730475</v>
+        <v>128728473</v>
       </c>
       <c r="B45" t="n">
-        <v>57716</v>
+        <v>57876</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5068,27 +5073,27 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="M45" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -5097,10 +5102,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>569675</v>
+        <v>569608</v>
       </c>
       <c r="R45" t="n">
-        <v>6958098</v>
+        <v>6958227</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5133,11 +5138,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5164,37 +5164,38 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128732627</v>
+        <v>128728902</v>
       </c>
       <c r="B46" t="n">
-        <v>98632</v>
+        <v>57716</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>6</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -5203,10 +5204,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>569821</v>
+        <v>569673</v>
       </c>
       <c r="R46" t="n">
-        <v>6958151</v>
+        <v>6958225</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5243,7 +5244,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Kan finnas mer I blåbärsriset och mossan</t>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5270,37 +5271,38 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128728348</v>
+        <v>128731799</v>
       </c>
       <c r="B47" t="n">
-        <v>98632</v>
+        <v>57716</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>300</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -5309,10 +5311,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>569616</v>
+        <v>569774</v>
       </c>
       <c r="R47" t="n">
-        <v>6958208</v>
+        <v>6958163</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5345,6 +5347,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5371,7 +5378,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128731799</v>
+        <v>128732015</v>
       </c>
       <c r="B48" t="n">
         <v>57716</v>
@@ -5402,7 +5409,7 @@
       <c r="I48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -5411,10 +5418,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>569774</v>
+        <v>569816</v>
       </c>
       <c r="R48" t="n">
-        <v>6958163</v>
+        <v>6958081</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5451,7 +5458,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5478,7 +5485,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128728902</v>
+        <v>128738187</v>
       </c>
       <c r="B49" t="n">
         <v>57716</v>
@@ -5518,10 +5525,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>569673</v>
+        <v>569681</v>
       </c>
       <c r="R49" t="n">
-        <v>6958225</v>
+        <v>6957939</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5558,7 +5565,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5585,38 +5592,37 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128732015</v>
+        <v>128732627</v>
       </c>
       <c r="B50" t="n">
-        <v>57716</v>
+        <v>98632</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>6</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -5625,10 +5631,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>569816</v>
+        <v>569821</v>
       </c>
       <c r="R50" t="n">
-        <v>6958081</v>
+        <v>6958151</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5665,7 +5671,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Kan finnas mer I blåbärsriset och mossan</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5692,38 +5698,37 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128738187</v>
+        <v>128728348</v>
       </c>
       <c r="B51" t="n">
-        <v>57716</v>
+        <v>98632</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>300</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -5732,10 +5737,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>569681</v>
+        <v>569616</v>
       </c>
       <c r="R51" t="n">
-        <v>6957939</v>
+        <v>6958208</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5768,11 +5773,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6318,10 +6318,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128728592</v>
+        <v>128732806</v>
       </c>
       <c r="B57" t="n">
-        <v>80260</v>
+        <v>91515</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6329,21 +6329,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6463</v>
+        <v>1205</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6353,10 +6353,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>569604</v>
+        <v>569827</v>
       </c>
       <c r="R57" t="n">
-        <v>6958176</v>
+        <v>6958133</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6415,32 +6415,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128732124</v>
+        <v>128732719</v>
       </c>
       <c r="B58" t="n">
-        <v>80260</v>
+        <v>91958</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6463</v>
+        <v>1209</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6450,10 +6450,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>569816</v>
+        <v>569821</v>
       </c>
       <c r="R58" t="n">
-        <v>6958081</v>
+        <v>6958151</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6512,45 +6512,50 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128730101</v>
+        <v>128730490</v>
       </c>
       <c r="B59" t="n">
-        <v>80261</v>
+        <v>57716</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>569630</v>
+        <v>569707</v>
       </c>
       <c r="R59" t="n">
-        <v>6958139</v>
+        <v>6958131</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6583,6 +6588,11 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Både äldre och färska spår ( Ringhack av tretåig hackspett på tall)</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6609,45 +6619,50 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128731387</v>
+        <v>128730422</v>
       </c>
       <c r="B60" t="n">
-        <v>80253</v>
+        <v>57716</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6461</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>569740</v>
+        <v>569703</v>
       </c>
       <c r="R60" t="n">
-        <v>6958091</v>
+        <v>6958116</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6680,6 +6695,11 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6706,45 +6726,50 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128732806</v>
+        <v>128739287</v>
       </c>
       <c r="B61" t="n">
-        <v>91515</v>
+        <v>57716</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1205</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>569827</v>
+        <v>569481</v>
       </c>
       <c r="R61" t="n">
-        <v>6958133</v>
+        <v>6958122</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6777,6 +6802,11 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6803,32 +6833,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128732719</v>
+        <v>128728592</v>
       </c>
       <c r="B62" t="n">
-        <v>91958</v>
+        <v>80260</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1209</v>
+        <v>6463</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6838,10 +6868,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>569821</v>
+        <v>569604</v>
       </c>
       <c r="R62" t="n">
-        <v>6958151</v>
+        <v>6958176</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6900,50 +6930,45 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128730490</v>
+        <v>128732124</v>
       </c>
       <c r="B63" t="n">
-        <v>57716</v>
+        <v>80260</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>569707</v>
+        <v>569816</v>
       </c>
       <c r="R63" t="n">
-        <v>6958131</v>
+        <v>6958081</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6976,11 +7001,6 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Både äldre och färska spår ( Ringhack av tretåig hackspett på tall)</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7007,50 +7027,45 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128730422</v>
+        <v>128730101</v>
       </c>
       <c r="B64" t="n">
-        <v>57716</v>
+        <v>80261</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>569703</v>
+        <v>569630</v>
       </c>
       <c r="R64" t="n">
-        <v>6958116</v>
+        <v>6958139</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7083,11 +7098,6 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7114,50 +7124,45 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128739287</v>
+        <v>128731387</v>
       </c>
       <c r="B65" t="n">
-        <v>57716</v>
+        <v>80253</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>569481</v>
+        <v>569740</v>
       </c>
       <c r="R65" t="n">
-        <v>6958122</v>
+        <v>6958091</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7190,11 +7195,6 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7318,10 +7318,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128729077</v>
+        <v>128730273</v>
       </c>
       <c r="B67" t="n">
-        <v>80225</v>
+        <v>79120</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7329,21 +7329,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7353,10 +7353,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>569604</v>
+        <v>569692</v>
       </c>
       <c r="R67" t="n">
-        <v>6958176</v>
+        <v>6958127</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7415,10 +7415,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128730273</v>
+        <v>128729077</v>
       </c>
       <c r="B68" t="n">
-        <v>79120</v>
+        <v>80225</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7426,21 +7426,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7450,10 +7450,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>569692</v>
+        <v>569604</v>
       </c>
       <c r="R68" t="n">
-        <v>6958127</v>
+        <v>6958176</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7716,10 +7716,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128731693</v>
+        <v>128730998</v>
       </c>
       <c r="B71" t="n">
-        <v>91504</v>
+        <v>57716</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7727,34 +7727,39 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>569793</v>
+        <v>569670</v>
       </c>
       <c r="R71" t="n">
-        <v>6958092</v>
+        <v>6958060</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7787,6 +7792,11 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Ringhack på tall. Även äldre</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7813,45 +7823,53 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128743263</v>
+        <v>128730928</v>
       </c>
       <c r="B72" t="n">
-        <v>92830</v>
+        <v>57716</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>5964</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>569517</v>
+        <v>569673</v>
       </c>
       <c r="R72" t="n">
-        <v>6958123</v>
+        <v>6958076</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7888,7 +7906,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>3 exemplar</t>
+          <t>Påbörjat bobygge av sannolikt tretåig hackspett. Ser ut att vara relativt färskt. 2 meter upp i död gran. Omkring 4,5 cm i diameter.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7915,10 +7933,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128728149</v>
+        <v>128731693</v>
       </c>
       <c r="B73" t="n">
-        <v>57716</v>
+        <v>91504</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7926,39 +7944,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>569585</v>
+        <v>569793</v>
       </c>
       <c r="R73" t="n">
-        <v>6958190</v>
+        <v>6958092</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7991,11 +8004,6 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8022,50 +8030,45 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128730998</v>
+        <v>128743263</v>
       </c>
       <c r="B74" t="n">
-        <v>57716</v>
+        <v>92830</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100109</v>
+        <v>5964</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>569670</v>
+        <v>569517</v>
       </c>
       <c r="R74" t="n">
-        <v>6958060</v>
+        <v>6958123</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8102,7 +8105,7 @@
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Ringhack på tall. Även äldre</t>
+          <t>3 exemplar</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8129,7 +8132,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128730928</v>
+        <v>128728149</v>
       </c>
       <c r="B75" t="n">
         <v>57716</v>
@@ -8158,24 +8161,21 @@
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
       <c r="M75" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N75" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>569673</v>
+        <v>569585</v>
       </c>
       <c r="R75" t="n">
-        <v>6958076</v>
+        <v>6958190</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8212,7 +8212,7 @@
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>Påbörjat bobygge av sannolikt tretåig hackspett. Ser ut att vara relativt färskt. 2 meter upp i död gran. Omkring 4,5 cm i diameter.</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8239,10 +8239,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128743247</v>
+        <v>128731100</v>
       </c>
       <c r="B76" t="n">
-        <v>57716</v>
+        <v>91522</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8250,21 +8250,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8274,10 +8274,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>569714</v>
+        <v>569688</v>
       </c>
       <c r="R76" t="n">
-        <v>6957901</v>
+        <v>6958069</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8310,11 +8310,6 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på gran ( färska spår)</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8341,10 +8336,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128731100</v>
+        <v>128743247</v>
       </c>
       <c r="B77" t="n">
-        <v>91522</v>
+        <v>57716</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8352,21 +8347,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8376,10 +8371,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>569688</v>
+        <v>569714</v>
       </c>
       <c r="R77" t="n">
-        <v>6958069</v>
+        <v>6957901</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8412,6 +8407,11 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på gran ( färska spår)</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8647,7 +8647,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128732718</v>
+        <v>128733005</v>
       </c>
       <c r="B80" t="n">
         <v>98632</v>
@@ -8677,7 +8677,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
@@ -8686,10 +8686,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>569834</v>
+        <v>569882</v>
       </c>
       <c r="R80" t="n">
-        <v>6958143</v>
+        <v>6958106</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8748,7 +8748,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128733005</v>
+        <v>128732718</v>
       </c>
       <c r="B81" t="n">
         <v>98632</v>
@@ -8778,7 +8778,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>18</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
@@ -8787,10 +8787,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>569882</v>
+        <v>569834</v>
       </c>
       <c r="R81" t="n">
-        <v>6958106</v>
+        <v>6958143</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9150,7 +9150,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128729895</v>
+        <v>128743257</v>
       </c>
       <c r="B85" t="n">
         <v>98632</v>
@@ -9178,21 +9178,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
+      <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>569713</v>
+        <v>569656</v>
       </c>
       <c r="R85" t="n">
-        <v>6958138</v>
+        <v>6957942</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9225,6 +9221,11 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>23 exemplar (ca)</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9251,7 +9252,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128743257</v>
+        <v>128729895</v>
       </c>
       <c r="B86" t="n">
         <v>98632</v>
@@ -9279,17 +9280,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I86" t="inlineStr"/>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
       <c r="P86" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>569656</v>
+        <v>569713</v>
       </c>
       <c r="R86" t="n">
-        <v>6957942</v>
+        <v>6958138</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9322,11 +9327,6 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>23 exemplar (ca)</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9353,45 +9353,50 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128738599</v>
+        <v>128729666</v>
       </c>
       <c r="B87" t="n">
-        <v>80185</v>
+        <v>57716</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>229497</v>
+        <v>100109</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>569608</v>
+        <v>569706</v>
       </c>
       <c r="R87" t="n">
-        <v>6958048</v>
+        <v>6958159</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9424,6 +9429,11 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9450,10 +9460,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128727978</v>
+        <v>128728419</v>
       </c>
       <c r="B88" t="n">
-        <v>57716</v>
+        <v>79120</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9461,39 +9471,34 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>569564</v>
+        <v>569608</v>
       </c>
       <c r="R88" t="n">
-        <v>6958213</v>
+        <v>6958227</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9530,7 +9535,7 @@
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Riklig förekomst inom området</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9557,10 +9562,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128729666</v>
+        <v>128743261</v>
       </c>
       <c r="B89" t="n">
-        <v>57716</v>
+        <v>79120</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9568,39 +9573,34 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P89" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>569706</v>
+        <v>569495</v>
       </c>
       <c r="R89" t="n">
-        <v>6958159</v>
+        <v>6958117</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9633,11 +9633,6 @@
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9761,10 +9756,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128728419</v>
+        <v>128727978</v>
       </c>
       <c r="B91" t="n">
-        <v>79120</v>
+        <v>57716</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9772,34 +9767,39 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P91" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>569608</v>
+        <v>569564</v>
       </c>
       <c r="R91" t="n">
-        <v>6958227</v>
+        <v>6958213</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9836,7 +9836,7 @@
       </c>
       <c r="AC91" t="inlineStr">
         <is>
-          <t>Riklig förekomst inom området</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9863,32 +9863,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128743261</v>
+        <v>128738599</v>
       </c>
       <c r="B92" t="n">
-        <v>79120</v>
+        <v>80185</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9898,10 +9898,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>569495</v>
+        <v>569608</v>
       </c>
       <c r="R92" t="n">
-        <v>6958117</v>
+        <v>6958048</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10164,7 +10164,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128731648</v>
+        <v>128743256</v>
       </c>
       <c r="B95" t="n">
         <v>98632</v>
@@ -10192,21 +10192,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>119</t>
-        </is>
-      </c>
+      <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>569766</v>
+        <v>569647</v>
       </c>
       <c r="R95" t="n">
-        <v>6958144</v>
+        <v>6957950</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10243,7 +10239,7 @@
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>Ca ( möjligtvis fler)</t>
+          <t>23 exemplar</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10270,7 +10266,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128743253</v>
+        <v>128731648</v>
       </c>
       <c r="B96" t="n">
         <v>98632</v>
@@ -10298,17 +10294,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I96" t="inlineStr"/>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
       <c r="P96" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>569641</v>
+        <v>569766</v>
       </c>
       <c r="R96" t="n">
-        <v>6957953</v>
+        <v>6958144</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10345,7 +10345,7 @@
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>55 exemplar knärötter</t>
+          <t>Ca ( möjligtvis fler)</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10372,7 +10372,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128743256</v>
+        <v>128743253</v>
       </c>
       <c r="B97" t="n">
         <v>98632</v>
@@ -10407,10 +10407,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>569647</v>
+        <v>569641</v>
       </c>
       <c r="R97" t="n">
-        <v>6957950</v>
+        <v>6957953</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10447,7 +10447,7 @@
       </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>23 exemplar</t>
+          <t>55 exemplar knärötter</t>
         </is>
       </c>
       <c r="AD97" t="b">

--- a/artfynd/A 39666-2025 artfynd.xlsx
+++ b/artfynd/A 39666-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128743246</v>
+        <v>128732386</v>
       </c>
       <c r="B2" t="n">
-        <v>57716</v>
+        <v>80229</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>569648</v>
+        <v>569785</v>
       </c>
       <c r="R2" t="n">
-        <v>6957944</v>
+        <v>6958124</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall ( äldre och färska spår)</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128728526</v>
+        <v>128743246</v>
       </c>
       <c r="B3" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -806,21 +801,16 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>569616</v>
+        <v>569648</v>
       </c>
       <c r="R3" t="n">
-        <v>6958208</v>
+        <v>6957944</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +847,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack av tretåig hackspett på Tall ( äldre och färska spår)</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,10 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128739007</v>
+        <v>128728526</v>
       </c>
       <c r="B4" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -924,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>569542</v>
+        <v>569616</v>
       </c>
       <c r="R4" t="n">
-        <v>6958069</v>
+        <v>6958208</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -991,37 +981,38 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128728896</v>
+        <v>128739007</v>
       </c>
       <c r="B5" t="n">
-        <v>98632</v>
+        <v>57720</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>6</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1030,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>569601</v>
+        <v>569542</v>
       </c>
       <c r="R5" t="n">
-        <v>6958191</v>
+        <v>6958069</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,6 +1057,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1092,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128732983</v>
+        <v>128728896</v>
       </c>
       <c r="B6" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1122,7 +1118,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1131,10 +1127,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>569873</v>
+        <v>569601</v>
       </c>
       <c r="R6" t="n">
-        <v>6958099</v>
+        <v>6958191</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1193,45 +1189,49 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128732386</v>
+        <v>128732983</v>
       </c>
       <c r="B7" t="n">
-        <v>80225</v>
+        <v>98636</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>569785</v>
+        <v>569873</v>
       </c>
       <c r="R7" t="n">
-        <v>6958124</v>
+        <v>6958099</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1293,7 +1293,7 @@
         <v>128729409</v>
       </c>
       <c r="B8" t="n">
-        <v>91504</v>
+        <v>91508</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1390,7 +1390,7 @@
         <v>128730130</v>
       </c>
       <c r="B9" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1497,7 +1497,7 @@
         <v>128732765</v>
       </c>
       <c r="B10" t="n">
-        <v>91800</v>
+        <v>91804</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1594,7 +1594,7 @@
         <v>128730571</v>
       </c>
       <c r="B11" t="n">
-        <v>91522</v>
+        <v>91526</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>128732276</v>
       </c>
       <c r="B12" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
         <v>128743245</v>
       </c>
       <c r="B13" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1897,59 +1897,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128732217</v>
+        <v>128733181</v>
       </c>
       <c r="B14" t="n">
-        <v>57876</v>
+        <v>98553</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>219790</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>569777</v>
+        <v>569900</v>
       </c>
       <c r="R14" t="n">
-        <v>6958189</v>
+        <v>6958101</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1982,11 +1968,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>2 talltitor kommer flygandes väldigt närgånget och varnar</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2013,45 +1994,59 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128733181</v>
+        <v>128732217</v>
       </c>
       <c r="B15" t="n">
-        <v>98549</v>
+        <v>57880</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219790</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>569900</v>
+        <v>569777</v>
       </c>
       <c r="R15" t="n">
-        <v>6958101</v>
+        <v>6958189</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2084,6 +2079,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>2 talltitor kommer flygandes väldigt närgånget och varnar</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2113,7 +2113,7 @@
         <v>128731601</v>
       </c>
       <c r="B16" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2217,45 +2217,49 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128728515</v>
+        <v>128731490</v>
       </c>
       <c r="B17" t="n">
-        <v>97503</v>
+        <v>98636</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>569608</v>
+        <v>569759</v>
       </c>
       <c r="R17" t="n">
-        <v>6958227</v>
+        <v>6958118</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2314,10 +2318,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128731490</v>
+        <v>128730429</v>
       </c>
       <c r="B18" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2344,7 +2348,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>80</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2353,10 +2357,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>569759</v>
+        <v>569683</v>
       </c>
       <c r="R18" t="n">
-        <v>6958118</v>
+        <v>6958128</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2415,49 +2419,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128730429</v>
+        <v>128728515</v>
       </c>
       <c r="B19" t="n">
-        <v>98632</v>
+        <v>97507</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>569683</v>
+        <v>569608</v>
       </c>
       <c r="R19" t="n">
-        <v>6958128</v>
+        <v>6958227</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2519,7 +2519,7 @@
         <v>128728022</v>
       </c>
       <c r="B20" t="n">
-        <v>91469</v>
+        <v>91473</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2616,7 +2616,7 @@
         <v>128743262</v>
       </c>
       <c r="B21" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2710,37 +2710,38 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128730720</v>
+        <v>128739020</v>
       </c>
       <c r="B22" t="n">
-        <v>98632</v>
+        <v>57720</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>50</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2749,10 +2750,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>569692</v>
+        <v>569542</v>
       </c>
       <c r="R22" t="n">
-        <v>6958094</v>
+        <v>6958049</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2789,7 +2790,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ca</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2816,10 +2817,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128743252</v>
+        <v>128730720</v>
       </c>
       <c r="B23" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2844,17 +2845,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>569610</v>
+        <v>569692</v>
       </c>
       <c r="R23" t="n">
-        <v>6958005</v>
+        <v>6958094</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2891,7 +2896,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>2 exemplar</t>
+          <t>Ca</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2918,50 +2923,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128731107</v>
+        <v>128743252</v>
       </c>
       <c r="B24" t="n">
-        <v>57876</v>
+        <v>98636</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>569705</v>
+        <v>569610</v>
       </c>
       <c r="R24" t="n">
-        <v>6958098</v>
+        <v>6958005</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2994,6 +2994,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>2 exemplar</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3023,7 +3028,7 @@
         <v>128732359</v>
       </c>
       <c r="B25" t="n">
-        <v>91504</v>
+        <v>91508</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3120,7 +3125,7 @@
         <v>128731612</v>
       </c>
       <c r="B26" t="n">
-        <v>91504</v>
+        <v>91508</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3214,10 +3219,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128739020</v>
+        <v>128731107</v>
       </c>
       <c r="B27" t="n">
-        <v>57716</v>
+        <v>57880</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3225,27 +3230,27 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3254,10 +3259,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>569542</v>
+        <v>569705</v>
       </c>
       <c r="R27" t="n">
-        <v>6958049</v>
+        <v>6958098</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3290,11 +3295,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3321,50 +3321,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128731291</v>
+        <v>128729068</v>
       </c>
       <c r="B28" t="n">
-        <v>57716</v>
+        <v>80258</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>569726</v>
+        <v>569604</v>
       </c>
       <c r="R28" t="n">
-        <v>6958097</v>
+        <v>6958176</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3397,11 +3392,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på tall</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3428,45 +3418,50 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128729068</v>
+        <v>128731291</v>
       </c>
       <c r="B29" t="n">
-        <v>80254</v>
+        <v>57720</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>569604</v>
+        <v>569726</v>
       </c>
       <c r="R29" t="n">
-        <v>6958176</v>
+        <v>6958097</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3499,6 +3494,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på tall</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3525,38 +3525,37 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128728019</v>
+        <v>128731489</v>
       </c>
       <c r="B30" t="n">
-        <v>57716</v>
+        <v>98636</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>45</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3565,10 +3564,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>569577</v>
+        <v>569752</v>
       </c>
       <c r="R30" t="n">
-        <v>6958213</v>
+        <v>6958091</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3601,11 +3600,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3632,37 +3626,38 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128731489</v>
+        <v>128728019</v>
       </c>
       <c r="B31" t="n">
-        <v>98632</v>
+        <v>57720</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>45</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -3671,10 +3666,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>569752</v>
+        <v>569577</v>
       </c>
       <c r="R31" t="n">
-        <v>6958091</v>
+        <v>6958213</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3707,6 +3702,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3733,45 +3733,54 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128730513</v>
+        <v>128728767</v>
       </c>
       <c r="B32" t="n">
-        <v>80225</v>
+        <v>92798</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>569656</v>
+        <v>569639</v>
       </c>
       <c r="R32" t="n">
-        <v>6958093</v>
+        <v>6958231</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3804,6 +3813,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>4 äldre ett färskt års exemplar</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3830,10 +3844,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128728767</v>
+        <v>128728303</v>
       </c>
       <c r="B33" t="n">
-        <v>92794</v>
+        <v>57712</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3841,31 +3855,27 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4364</v>
+        <v>100110</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>J.F. Gmelin, 1788</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -3874,10 +3884,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>569639</v>
+        <v>569584</v>
       </c>
       <c r="R33" t="n">
-        <v>6958231</v>
+        <v>6958214</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3914,7 +3924,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>4 äldre ett färskt års exemplar</t>
+          <t>Hörs i närheten</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3941,38 +3951,38 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128728303</v>
+        <v>128730603</v>
       </c>
       <c r="B34" t="n">
-        <v>57708</v>
+        <v>57720</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100110</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -3981,10 +3991,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>569584</v>
+        <v>569738</v>
       </c>
       <c r="R34" t="n">
-        <v>6958214</v>
+        <v>6958117</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4021,7 +4031,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Hörs i närheten</t>
+          <t>Äldre exemplar av ringhack på Tall från tretåig hackspett</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4048,10 +4058,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128730603</v>
+        <v>128730513</v>
       </c>
       <c r="B35" t="n">
-        <v>57716</v>
+        <v>80229</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4059,39 +4069,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>569738</v>
+        <v>569656</v>
       </c>
       <c r="R35" t="n">
-        <v>6958117</v>
+        <v>6958093</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4124,11 +4129,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Äldre exemplar av ringhack på Tall från tretåig hackspett</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4155,10 +4155,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128729745</v>
+        <v>128728318</v>
       </c>
       <c r="B36" t="n">
-        <v>57716</v>
+        <v>79124</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4166,39 +4166,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>569694</v>
+        <v>569616</v>
       </c>
       <c r="R36" t="n">
-        <v>6958144</v>
+        <v>6958208</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4231,11 +4226,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4262,10 +4252,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128728318</v>
+        <v>128731677</v>
       </c>
       <c r="B37" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4297,10 +4287,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>569616</v>
+        <v>569769</v>
       </c>
       <c r="R37" t="n">
-        <v>6958208</v>
+        <v>6958153</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4359,10 +4349,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128731677</v>
+        <v>128729745</v>
       </c>
       <c r="B38" t="n">
-        <v>79120</v>
+        <v>57720</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4370,34 +4360,39 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>569769</v>
+        <v>569694</v>
       </c>
       <c r="R38" t="n">
-        <v>6958153</v>
+        <v>6958144</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4430,6 +4425,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4456,10 +4456,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128743255</v>
+        <v>128732677</v>
       </c>
       <c r="B39" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4484,17 +4484,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr"/>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>569613</v>
+        <v>569817</v>
       </c>
       <c r="R39" t="n">
-        <v>6957995</v>
+        <v>6958134</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4527,11 +4531,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>28 exemplar knärot</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4558,10 +4557,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128743254</v>
+        <v>128743255</v>
       </c>
       <c r="B40" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4593,10 +4592,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>569547</v>
+        <v>569613</v>
       </c>
       <c r="R40" t="n">
-        <v>6958078</v>
+        <v>6957995</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4633,7 +4632,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>20 (ca) exemplar</t>
+          <t>28 exemplar knärot</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4660,10 +4659,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128732677</v>
+        <v>128743254</v>
       </c>
       <c r="B41" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4688,21 +4687,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>569817</v>
+        <v>569547</v>
       </c>
       <c r="R41" t="n">
-        <v>6958134</v>
+        <v>6958078</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4735,6 +4730,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>20 (ca) exemplar</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4764,7 +4764,7 @@
         <v>128729439</v>
       </c>
       <c r="B42" t="n">
-        <v>91504</v>
+        <v>91508</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4861,7 +4861,7 @@
         <v>128729962</v>
       </c>
       <c r="B43" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4958,7 +4958,7 @@
         <v>128730475</v>
       </c>
       <c r="B44" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5065,7 +5065,7 @@
         <v>128728473</v>
       </c>
       <c r="B45" t="n">
-        <v>57876</v>
+        <v>57880</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5167,7 +5167,7 @@
         <v>128728902</v>
       </c>
       <c r="B46" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5274,7 +5274,7 @@
         <v>128731799</v>
       </c>
       <c r="B47" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5381,7 +5381,7 @@
         <v>128732015</v>
       </c>
       <c r="B48" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5488,7 +5488,7 @@
         <v>128738187</v>
       </c>
       <c r="B49" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
         <v>128732627</v>
       </c>
       <c r="B50" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5701,7 +5701,7 @@
         <v>128728348</v>
       </c>
       <c r="B51" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5799,45 +5799,49 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128731302</v>
+        <v>128729573</v>
       </c>
       <c r="B52" t="n">
-        <v>80185</v>
+        <v>98636</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>229497</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>569696</v>
+        <v>569706</v>
       </c>
       <c r="R52" t="n">
-        <v>6958031</v>
+        <v>6958159</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5896,49 +5900,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128729573</v>
+        <v>128731302</v>
       </c>
       <c r="B53" t="n">
-        <v>98632</v>
+        <v>80189</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>229497</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>569706</v>
+        <v>569696</v>
       </c>
       <c r="R53" t="n">
-        <v>6958159</v>
+        <v>6958031</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6000,7 +6000,7 @@
         <v>128731037</v>
       </c>
       <c r="B54" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6107,7 +6107,7 @@
         <v>128738306</v>
       </c>
       <c r="B55" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6214,7 +6214,7 @@
         <v>128732183</v>
       </c>
       <c r="B56" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6318,45 +6318,50 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128732806</v>
+        <v>128730490</v>
       </c>
       <c r="B57" t="n">
-        <v>91515</v>
+        <v>57720</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1205</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>569827</v>
+        <v>569707</v>
       </c>
       <c r="R57" t="n">
-        <v>6958133</v>
+        <v>6958131</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6389,6 +6394,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Både äldre och färska spår ( Ringhack av tretåig hackspett på tall)</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6415,32 +6425,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128732719</v>
+        <v>128732806</v>
       </c>
       <c r="B58" t="n">
-        <v>91958</v>
+        <v>91519</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1209</v>
+        <v>1205</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6450,10 +6460,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>569821</v>
+        <v>569827</v>
       </c>
       <c r="R58" t="n">
-        <v>6958151</v>
+        <v>6958133</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6512,50 +6522,45 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128730490</v>
+        <v>128732719</v>
       </c>
       <c r="B59" t="n">
-        <v>57716</v>
+        <v>91962</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>569707</v>
+        <v>569821</v>
       </c>
       <c r="R59" t="n">
-        <v>6958131</v>
+        <v>6958151</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6588,11 +6593,6 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Både äldre och färska spår ( Ringhack av tretåig hackspett på tall)</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6619,50 +6619,45 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128730422</v>
+        <v>128728592</v>
       </c>
       <c r="B60" t="n">
-        <v>57716</v>
+        <v>80264</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>569703</v>
+        <v>569604</v>
       </c>
       <c r="R60" t="n">
-        <v>6958116</v>
+        <v>6958176</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6695,11 +6690,6 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6726,50 +6716,45 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128739287</v>
+        <v>128732124</v>
       </c>
       <c r="B61" t="n">
-        <v>57716</v>
+        <v>80264</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>569481</v>
+        <v>569816</v>
       </c>
       <c r="R61" t="n">
-        <v>6958122</v>
+        <v>6958081</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6802,11 +6787,6 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6833,10 +6813,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128728592</v>
+        <v>128730101</v>
       </c>
       <c r="B62" t="n">
-        <v>80260</v>
+        <v>80265</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6844,21 +6824,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6463</v>
+        <v>6464</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6868,10 +6848,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>569604</v>
+        <v>569630</v>
       </c>
       <c r="R62" t="n">
-        <v>6958176</v>
+        <v>6958139</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6930,10 +6910,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128732124</v>
+        <v>128731387</v>
       </c>
       <c r="B63" t="n">
-        <v>80260</v>
+        <v>80257</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6941,21 +6921,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6463</v>
+        <v>6461</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6965,10 +6945,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>569816</v>
+        <v>569740</v>
       </c>
       <c r="R63" t="n">
-        <v>6958081</v>
+        <v>6958091</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7027,10 +7007,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128730101</v>
+        <v>128730183</v>
       </c>
       <c r="B64" t="n">
-        <v>80261</v>
+        <v>80189</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7038,21 +7018,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6464</v>
+        <v>229497</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7065,7 +7045,7 @@
         <v>569630</v>
       </c>
       <c r="R64" t="n">
-        <v>6958139</v>
+        <v>6958129</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7124,45 +7104,50 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128731387</v>
+        <v>128730422</v>
       </c>
       <c r="B65" t="n">
-        <v>80253</v>
+        <v>57720</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6461</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>569740</v>
+        <v>569703</v>
       </c>
       <c r="R65" t="n">
-        <v>6958091</v>
+        <v>6958116</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7195,6 +7180,11 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7221,45 +7211,50 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128730183</v>
+        <v>128739287</v>
       </c>
       <c r="B66" t="n">
-        <v>80185</v>
+        <v>57720</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>229497</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>569630</v>
+        <v>569481</v>
       </c>
       <c r="R66" t="n">
-        <v>6958129</v>
+        <v>6958122</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7292,6 +7287,11 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7318,10 +7318,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128730273</v>
+        <v>128729077</v>
       </c>
       <c r="B67" t="n">
-        <v>79120</v>
+        <v>80229</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7329,21 +7329,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7353,10 +7353,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>569692</v>
+        <v>569604</v>
       </c>
       <c r="R67" t="n">
-        <v>6958127</v>
+        <v>6958176</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7415,10 +7415,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128729077</v>
+        <v>128730273</v>
       </c>
       <c r="B68" t="n">
-        <v>80225</v>
+        <v>79124</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7426,21 +7426,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7450,10 +7450,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>569604</v>
+        <v>569692</v>
       </c>
       <c r="R68" t="n">
-        <v>6958176</v>
+        <v>6958127</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7515,7 +7515,7 @@
         <v>128732112</v>
       </c>
       <c r="B69" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7609,10 +7609,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128732493</v>
+        <v>128731693</v>
       </c>
       <c r="B70" t="n">
-        <v>57716</v>
+        <v>91508</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7620,39 +7620,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>569795</v>
+        <v>569793</v>
       </c>
       <c r="R70" t="n">
-        <v>6958154</v>
+        <v>6958092</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7685,11 +7680,6 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7716,50 +7706,45 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128730998</v>
+        <v>128743263</v>
       </c>
       <c r="B71" t="n">
-        <v>57716</v>
+        <v>92834</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100109</v>
+        <v>5964</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>569670</v>
+        <v>569517</v>
       </c>
       <c r="R71" t="n">
-        <v>6958060</v>
+        <v>6958123</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7796,7 +7781,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Ringhack på tall. Även äldre</t>
+          <t>3 exemplar</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7823,10 +7808,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128730928</v>
+        <v>128728149</v>
       </c>
       <c r="B72" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7852,24 +7837,21 @@
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
       <c r="M72" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N72" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>569673</v>
+        <v>569585</v>
       </c>
       <c r="R72" t="n">
-        <v>6958076</v>
+        <v>6958190</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7906,7 +7888,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Påbörjat bobygge av sannolikt tretåig hackspett. Ser ut att vara relativt färskt. 2 meter upp i död gran. Omkring 4,5 cm i diameter.</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7933,10 +7915,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128731693</v>
+        <v>128732493</v>
       </c>
       <c r="B73" t="n">
-        <v>91504</v>
+        <v>57720</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7944,34 +7926,39 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>569793</v>
+        <v>569795</v>
       </c>
       <c r="R73" t="n">
-        <v>6958092</v>
+        <v>6958154</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8004,6 +7991,11 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8030,45 +8022,50 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128743263</v>
+        <v>128730998</v>
       </c>
       <c r="B74" t="n">
-        <v>92830</v>
+        <v>57720</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>5964</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>569517</v>
+        <v>569670</v>
       </c>
       <c r="R74" t="n">
-        <v>6958123</v>
+        <v>6958060</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8105,7 +8102,7 @@
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>3 exemplar</t>
+          <t>Ringhack på tall. Även äldre</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8132,10 +8129,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128728149</v>
+        <v>128730928</v>
       </c>
       <c r="B75" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8161,21 +8158,24 @@
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
       <c r="M75" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>569585</v>
+        <v>569673</v>
       </c>
       <c r="R75" t="n">
-        <v>6958190</v>
+        <v>6958076</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8212,7 +8212,7 @@
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Påbörjat bobygge av sannolikt tretåig hackspett. Ser ut att vara relativt färskt. 2 meter upp i död gran. Omkring 4,5 cm i diameter.</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8242,7 +8242,7 @@
         <v>128731100</v>
       </c>
       <c r="B76" t="n">
-        <v>91522</v>
+        <v>91526</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8339,7 +8339,7 @@
         <v>128743247</v>
       </c>
       <c r="B77" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8441,7 +8441,7 @@
         <v>128732848</v>
       </c>
       <c r="B78" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8548,7 +8548,7 @@
         <v>128731284</v>
       </c>
       <c r="B79" t="n">
-        <v>57876</v>
+        <v>57880</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8647,10 +8647,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128733005</v>
+        <v>128732718</v>
       </c>
       <c r="B80" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8677,7 +8677,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>18</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
@@ -8686,10 +8686,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>569882</v>
+        <v>569834</v>
       </c>
       <c r="R80" t="n">
-        <v>6958106</v>
+        <v>6958143</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8748,10 +8748,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128732718</v>
+        <v>128733005</v>
       </c>
       <c r="B81" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8778,7 +8778,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
@@ -8787,10 +8787,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>569834</v>
+        <v>569882</v>
       </c>
       <c r="R81" t="n">
-        <v>6958143</v>
+        <v>6958106</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8849,10 +8849,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128743244</v>
+        <v>128731226</v>
       </c>
       <c r="B82" t="n">
-        <v>91504</v>
+        <v>91526</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8860,21 +8860,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8884,10 +8884,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>569736</v>
+        <v>569705</v>
       </c>
       <c r="R82" t="n">
-        <v>6957867</v>
+        <v>6958098</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8946,10 +8946,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128731226</v>
+        <v>128743244</v>
       </c>
       <c r="B83" t="n">
-        <v>91522</v>
+        <v>91508</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8957,21 +8957,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8981,10 +8981,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>569705</v>
+        <v>569736</v>
       </c>
       <c r="R83" t="n">
-        <v>6958098</v>
+        <v>6957867</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9046,7 +9046,7 @@
         <v>128728434</v>
       </c>
       <c r="B84" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9150,10 +9150,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128743257</v>
+        <v>128729895</v>
       </c>
       <c r="B85" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9178,17 +9178,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I85" t="inlineStr"/>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>569656</v>
+        <v>569713</v>
       </c>
       <c r="R85" t="n">
-        <v>6957942</v>
+        <v>6958138</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9221,11 +9225,6 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>23 exemplar (ca)</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9252,10 +9251,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128729895</v>
+        <v>128743257</v>
       </c>
       <c r="B86" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9280,21 +9279,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
+      <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>569713</v>
+        <v>569656</v>
       </c>
       <c r="R86" t="n">
-        <v>6958138</v>
+        <v>6957942</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9327,6 +9322,11 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>23 exemplar (ca)</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9353,10 +9353,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128729666</v>
+        <v>128729069</v>
       </c>
       <c r="B87" t="n">
-        <v>57716</v>
+        <v>79124</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9364,39 +9364,34 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>569706</v>
+        <v>569699</v>
       </c>
       <c r="R87" t="n">
-        <v>6958159</v>
+        <v>6958200</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9429,11 +9424,6 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9460,10 +9450,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128728419</v>
+        <v>128743261</v>
       </c>
       <c r="B88" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9495,10 +9485,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>569608</v>
+        <v>569495</v>
       </c>
       <c r="R88" t="n">
-        <v>6958227</v>
+        <v>6958117</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9531,11 +9521,6 @@
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>Riklig förekomst inom området</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9562,10 +9547,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128743261</v>
+        <v>128727978</v>
       </c>
       <c r="B89" t="n">
-        <v>79120</v>
+        <v>57720</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9573,34 +9558,39 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P89" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>569495</v>
+        <v>569564</v>
       </c>
       <c r="R89" t="n">
-        <v>6958117</v>
+        <v>6958213</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9633,6 +9623,11 @@
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9659,10 +9654,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128729069</v>
+        <v>128729666</v>
       </c>
       <c r="B90" t="n">
-        <v>79120</v>
+        <v>57720</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9670,34 +9665,39 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P90" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>569699</v>
+        <v>569706</v>
       </c>
       <c r="R90" t="n">
-        <v>6958200</v>
+        <v>6958159</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9730,6 +9730,11 @@
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9756,50 +9761,45 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128727978</v>
+        <v>128738599</v>
       </c>
       <c r="B91" t="n">
-        <v>57716</v>
+        <v>80189</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>100109</v>
+        <v>229497</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P91" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>569564</v>
+        <v>569608</v>
       </c>
       <c r="R91" t="n">
-        <v>6958213</v>
+        <v>6958048</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9832,11 +9832,6 @@
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9863,32 +9858,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128738599</v>
+        <v>128728419</v>
       </c>
       <c r="B92" t="n">
-        <v>80185</v>
+        <v>79124</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9901,7 +9896,7 @@
         <v>569608</v>
       </c>
       <c r="R92" t="n">
-        <v>6958048</v>
+        <v>6958227</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9934,6 +9929,11 @@
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>Riklig förekomst inom området</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -9963,7 +9963,7 @@
         <v>128728152</v>
       </c>
       <c r="B93" t="n">
-        <v>91504</v>
+        <v>91508</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10060,7 +10060,7 @@
         <v>128728274</v>
       </c>
       <c r="B94" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10164,10 +10164,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128743256</v>
+        <v>128731648</v>
       </c>
       <c r="B95" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10192,17 +10192,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I95" t="inlineStr"/>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
       <c r="P95" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>569647</v>
+        <v>569766</v>
       </c>
       <c r="R95" t="n">
-        <v>6957950</v>
+        <v>6958144</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10239,7 +10243,7 @@
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>23 exemplar</t>
+          <t>Ca ( möjligtvis fler)</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10266,10 +10270,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128731648</v>
+        <v>128743253</v>
       </c>
       <c r="B96" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10294,21 +10298,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>119</t>
-        </is>
-      </c>
+      <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>569766</v>
+        <v>569641</v>
       </c>
       <c r="R96" t="n">
-        <v>6958144</v>
+        <v>6957953</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10345,7 +10345,7 @@
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>Ca ( möjligtvis fler)</t>
+          <t>55 exemplar knärötter</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10372,10 +10372,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128743253</v>
+        <v>128743256</v>
       </c>
       <c r="B97" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10407,10 +10407,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>569641</v>
+        <v>569647</v>
       </c>
       <c r="R97" t="n">
-        <v>6957953</v>
+        <v>6957950</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10447,7 +10447,7 @@
       </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>55 exemplar knärötter</t>
+          <t>23 exemplar</t>
         </is>
       </c>
       <c r="AD97" t="b">

--- a/artfynd/A 39666-2025 artfynd.xlsx
+++ b/artfynd/A 39666-2025 artfynd.xlsx
@@ -1494,10 +1494,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128732765</v>
+        <v>128732217</v>
       </c>
       <c r="B10" t="n">
-        <v>91804</v>
+        <v>57880</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1505,34 +1505,48 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>658</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>569827</v>
+        <v>569777</v>
       </c>
       <c r="R10" t="n">
-        <v>6958133</v>
+        <v>6958189</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1565,6 +1579,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>2 talltitor kommer flygandes väldigt närgånget och varnar</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1688,50 +1707,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128732276</v>
+        <v>128733181</v>
       </c>
       <c r="B12" t="n">
-        <v>57720</v>
+        <v>98553</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>569841</v>
+        <v>569900</v>
       </c>
       <c r="R12" t="n">
-        <v>6958102</v>
+        <v>6958101</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1764,11 +1778,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1795,10 +1804,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128743245</v>
+        <v>128732765</v>
       </c>
       <c r="B13" t="n">
-        <v>57720</v>
+        <v>91804</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1806,21 +1815,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1830,10 +1839,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>569590</v>
+        <v>569827</v>
       </c>
       <c r="R13" t="n">
-        <v>6958014</v>
+        <v>6958133</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1866,11 +1875,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall ( färska spår)</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1897,45 +1901,50 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128733181</v>
+        <v>128732276</v>
       </c>
       <c r="B14" t="n">
-        <v>98553</v>
+        <v>57720</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>569900</v>
+        <v>569841</v>
       </c>
       <c r="R14" t="n">
-        <v>6958101</v>
+        <v>6958102</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1968,6 +1977,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1994,10 +2008,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128732217</v>
+        <v>128743245</v>
       </c>
       <c r="B15" t="n">
-        <v>57880</v>
+        <v>57720</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2005,48 +2019,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>569777</v>
+        <v>569590</v>
       </c>
       <c r="R15" t="n">
-        <v>6958189</v>
+        <v>6958014</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2083,7 +2083,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>2 talltitor kommer flygandes väldigt närgånget och varnar</t>
+          <t>Ringhack av tretåig hackspett på Tall ( färska spår)</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2217,49 +2217,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128731490</v>
+        <v>128728515</v>
       </c>
       <c r="B17" t="n">
-        <v>98636</v>
+        <v>97507</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>569759</v>
+        <v>569608</v>
       </c>
       <c r="R17" t="n">
-        <v>6958118</v>
+        <v>6958227</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2318,7 +2314,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128730429</v>
+        <v>128731490</v>
       </c>
       <c r="B18" t="n">
         <v>98636</v>
@@ -2348,7 +2344,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2357,10 +2353,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>569683</v>
+        <v>569759</v>
       </c>
       <c r="R18" t="n">
-        <v>6958128</v>
+        <v>6958118</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2419,45 +2415,49 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128728515</v>
+        <v>128730429</v>
       </c>
       <c r="B19" t="n">
-        <v>97507</v>
+        <v>98636</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>569608</v>
+        <v>569683</v>
       </c>
       <c r="R19" t="n">
-        <v>6958227</v>
+        <v>6958128</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2613,10 +2613,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128743262</v>
+        <v>128739020</v>
       </c>
       <c r="B21" t="n">
-        <v>79124</v>
+        <v>57720</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2624,34 +2624,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>569732</v>
+        <v>569542</v>
       </c>
       <c r="R21" t="n">
-        <v>6957870</v>
+        <v>6958049</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2684,6 +2689,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2710,38 +2720,37 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128739020</v>
+        <v>128730720</v>
       </c>
       <c r="B22" t="n">
-        <v>57720</v>
+        <v>98636</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>50</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2750,10 +2759,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>569542</v>
+        <v>569692</v>
       </c>
       <c r="R22" t="n">
-        <v>6958049</v>
+        <v>6958094</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2790,7 +2799,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ca</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2817,7 +2826,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128730720</v>
+        <v>128743252</v>
       </c>
       <c r="B23" t="n">
         <v>98636</v>
@@ -2845,21 +2854,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>569692</v>
+        <v>569610</v>
       </c>
       <c r="R23" t="n">
-        <v>6958094</v>
+        <v>6958005</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2896,7 +2901,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ca</t>
+          <t>2 exemplar</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2923,32 +2928,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128743252</v>
+        <v>128732359</v>
       </c>
       <c r="B24" t="n">
-        <v>98636</v>
+        <v>91508</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2958,10 +2963,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>569610</v>
+        <v>569820</v>
       </c>
       <c r="R24" t="n">
-        <v>6958005</v>
+        <v>6958107</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2994,11 +2999,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>2 exemplar</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3025,7 +3025,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128732359</v>
+        <v>128731612</v>
       </c>
       <c r="B25" t="n">
         <v>91508</v>
@@ -3060,10 +3060,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>569820</v>
+        <v>569752</v>
       </c>
       <c r="R25" t="n">
-        <v>6958107</v>
+        <v>6958091</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3122,10 +3122,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128731612</v>
+        <v>128743262</v>
       </c>
       <c r="B26" t="n">
-        <v>91508</v>
+        <v>79124</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3133,21 +3133,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3157,10 +3157,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>569752</v>
+        <v>569732</v>
       </c>
       <c r="R26" t="n">
-        <v>6958091</v>
+        <v>6957870</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3525,37 +3525,38 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128731489</v>
+        <v>128728019</v>
       </c>
       <c r="B30" t="n">
-        <v>98636</v>
+        <v>57720</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>45</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3564,10 +3565,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>569752</v>
+        <v>569577</v>
       </c>
       <c r="R30" t="n">
-        <v>6958091</v>
+        <v>6958213</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3600,6 +3601,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3626,38 +3632,37 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128728019</v>
+        <v>128731489</v>
       </c>
       <c r="B31" t="n">
-        <v>57720</v>
+        <v>98636</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>45</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -3666,10 +3671,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>569577</v>
+        <v>569752</v>
       </c>
       <c r="R31" t="n">
-        <v>6958213</v>
+        <v>6958091</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3702,11 +3707,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4955,10 +4955,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128730475</v>
+        <v>128728473</v>
       </c>
       <c r="B44" t="n">
-        <v>57720</v>
+        <v>57880</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4966,27 +4966,27 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -4995,10 +4995,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>569675</v>
+        <v>569608</v>
       </c>
       <c r="R44" t="n">
-        <v>6958098</v>
+        <v>6958227</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5031,11 +5031,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5062,10 +5057,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128728473</v>
+        <v>128730475</v>
       </c>
       <c r="B45" t="n">
-        <v>57880</v>
+        <v>57720</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5073,27 +5068,27 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="M45" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -5102,10 +5097,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>569608</v>
+        <v>569675</v>
       </c>
       <c r="R45" t="n">
-        <v>6958227</v>
+        <v>6958098</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5138,6 +5133,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6318,50 +6318,45 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128730490</v>
+        <v>128732806</v>
       </c>
       <c r="B57" t="n">
-        <v>57720</v>
+        <v>91519</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>1205</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>569707</v>
+        <v>569827</v>
       </c>
       <c r="R57" t="n">
-        <v>6958131</v>
+        <v>6958133</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6394,11 +6389,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Både äldre och färska spår ( Ringhack av tretåig hackspett på tall)</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6425,32 +6415,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128732806</v>
+        <v>128732719</v>
       </c>
       <c r="B58" t="n">
-        <v>91519</v>
+        <v>91962</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1205</v>
+        <v>1209</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6460,10 +6450,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>569827</v>
+        <v>569821</v>
       </c>
       <c r="R58" t="n">
-        <v>6958133</v>
+        <v>6958151</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6522,32 +6512,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128732719</v>
+        <v>128728592</v>
       </c>
       <c r="B59" t="n">
-        <v>91962</v>
+        <v>80264</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1209</v>
+        <v>6463</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6557,10 +6547,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>569821</v>
+        <v>569604</v>
       </c>
       <c r="R59" t="n">
-        <v>6958151</v>
+        <v>6958176</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6619,7 +6609,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128728592</v>
+        <v>128732124</v>
       </c>
       <c r="B60" t="n">
         <v>80264</v>
@@ -6654,10 +6644,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>569604</v>
+        <v>569816</v>
       </c>
       <c r="R60" t="n">
-        <v>6958176</v>
+        <v>6958081</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6716,10 +6706,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128732124</v>
+        <v>128730101</v>
       </c>
       <c r="B61" t="n">
-        <v>80264</v>
+        <v>80265</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6727,21 +6717,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6463</v>
+        <v>6464</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6751,10 +6741,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>569816</v>
+        <v>569630</v>
       </c>
       <c r="R61" t="n">
-        <v>6958081</v>
+        <v>6958139</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6813,10 +6803,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128730101</v>
+        <v>128731387</v>
       </c>
       <c r="B62" t="n">
-        <v>80265</v>
+        <v>80257</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6824,21 +6814,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6464</v>
+        <v>6461</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6848,10 +6838,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>569630</v>
+        <v>569740</v>
       </c>
       <c r="R62" t="n">
-        <v>6958139</v>
+        <v>6958091</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6910,45 +6900,50 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128731387</v>
+        <v>128730490</v>
       </c>
       <c r="B63" t="n">
-        <v>80257</v>
+        <v>57720</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6461</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>569740</v>
+        <v>569707</v>
       </c>
       <c r="R63" t="n">
-        <v>6958091</v>
+        <v>6958131</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6981,6 +6976,11 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Både äldre och färska spår ( Ringhack av tretåig hackspett på tall)</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7007,45 +7007,50 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128730183</v>
+        <v>128730422</v>
       </c>
       <c r="B64" t="n">
-        <v>80189</v>
+        <v>57720</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>229497</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>569630</v>
+        <v>569703</v>
       </c>
       <c r="R64" t="n">
-        <v>6958129</v>
+        <v>6958116</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7078,6 +7083,11 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7104,7 +7114,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128730422</v>
+        <v>128739287</v>
       </c>
       <c r="B65" t="n">
         <v>57720</v>
@@ -7144,10 +7154,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>569703</v>
+        <v>569481</v>
       </c>
       <c r="R65" t="n">
-        <v>6958116</v>
+        <v>6958122</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7184,7 +7194,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7211,50 +7221,45 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128739287</v>
+        <v>128730183</v>
       </c>
       <c r="B66" t="n">
-        <v>57720</v>
+        <v>80189</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>229497</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>569481</v>
+        <v>569630</v>
       </c>
       <c r="R66" t="n">
-        <v>6958122</v>
+        <v>6958129</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7287,11 +7292,6 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7609,32 +7609,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128731693</v>
+        <v>128743263</v>
       </c>
       <c r="B70" t="n">
-        <v>91508</v>
+        <v>92834</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1202</v>
+        <v>5964</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7644,10 +7644,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>569793</v>
+        <v>569517</v>
       </c>
       <c r="R70" t="n">
-        <v>6958092</v>
+        <v>6958123</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7680,6 +7680,11 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>3 exemplar</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7706,45 +7711,50 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128743263</v>
+        <v>128728149</v>
       </c>
       <c r="B71" t="n">
-        <v>92834</v>
+        <v>57720</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>5964</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>569517</v>
+        <v>569585</v>
       </c>
       <c r="R71" t="n">
-        <v>6958123</v>
+        <v>6958190</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7781,7 +7791,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>3 exemplar</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7808,7 +7818,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128728149</v>
+        <v>128732493</v>
       </c>
       <c r="B72" t="n">
         <v>57720</v>
@@ -7848,10 +7858,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>569585</v>
+        <v>569795</v>
       </c>
       <c r="R72" t="n">
-        <v>6958190</v>
+        <v>6958154</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7888,7 +7898,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7915,7 +7925,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128732493</v>
+        <v>128730998</v>
       </c>
       <c r="B73" t="n">
         <v>57720</v>
@@ -7955,10 +7965,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>569795</v>
+        <v>569670</v>
       </c>
       <c r="R73" t="n">
-        <v>6958154</v>
+        <v>6958060</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7995,7 +8005,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>Ringhack på tall. Även äldre</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8022,7 +8032,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128730998</v>
+        <v>128730928</v>
       </c>
       <c r="B74" t="n">
         <v>57720</v>
@@ -8051,21 +8061,24 @@
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
       <c r="M74" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>569670</v>
+        <v>569673</v>
       </c>
       <c r="R74" t="n">
-        <v>6958060</v>
+        <v>6958076</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8102,7 +8115,7 @@
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Ringhack på tall. Även äldre</t>
+          <t>Påbörjat bobygge av sannolikt tretåig hackspett. Ser ut att vara relativt färskt. 2 meter upp i död gran. Omkring 4,5 cm i diameter.</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8129,10 +8142,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128730928</v>
+        <v>128731693</v>
       </c>
       <c r="B75" t="n">
-        <v>57720</v>
+        <v>91508</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8140,42 +8153,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>569673</v>
+        <v>569793</v>
       </c>
       <c r="R75" t="n">
-        <v>6958076</v>
+        <v>6958092</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8208,11 +8213,6 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Påbörjat bobygge av sannolikt tretåig hackspett. Ser ut att vara relativt färskt. 2 meter upp i död gran. Omkring 4,5 cm i diameter.</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8336,10 +8336,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128743247</v>
+        <v>128731284</v>
       </c>
       <c r="B77" t="n">
-        <v>57720</v>
+        <v>57880</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8347,34 +8347,39 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>569714</v>
+        <v>569677</v>
       </c>
       <c r="R77" t="n">
-        <v>6957901</v>
+        <v>6958066</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8407,11 +8412,6 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på gran ( färska spår)</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8438,38 +8438,37 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128732848</v>
+        <v>128732718</v>
       </c>
       <c r="B78" t="n">
-        <v>57720</v>
+        <v>98636</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>18</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
@@ -8478,10 +8477,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>569873</v>
+        <v>569834</v>
       </c>
       <c r="R78" t="n">
-        <v>6958099</v>
+        <v>6958143</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8514,11 +8513,6 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8545,38 +8539,37 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128731284</v>
+        <v>128733005</v>
       </c>
       <c r="B79" t="n">
-        <v>57880</v>
+        <v>98636</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>7</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
@@ -8585,10 +8578,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>569677</v>
+        <v>569882</v>
       </c>
       <c r="R79" t="n">
-        <v>6958066</v>
+        <v>6958106</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8647,49 +8640,45 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128732718</v>
+        <v>128743247</v>
       </c>
       <c r="B80" t="n">
-        <v>98636</v>
+        <v>57720</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>569834</v>
+        <v>569714</v>
       </c>
       <c r="R80" t="n">
-        <v>6958143</v>
+        <v>6957901</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8722,6 +8711,11 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på gran ( färska spår)</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8748,37 +8742,38 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128733005</v>
+        <v>128732848</v>
       </c>
       <c r="B81" t="n">
-        <v>98636</v>
+        <v>57720</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>7</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
@@ -8787,10 +8782,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>569882</v>
+        <v>569873</v>
       </c>
       <c r="R81" t="n">
-        <v>6958106</v>
+        <v>6958099</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8823,6 +8818,11 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8946,10 +8946,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128743244</v>
+        <v>128728434</v>
       </c>
       <c r="B83" t="n">
-        <v>91508</v>
+        <v>57720</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8957,34 +8957,39 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>569736</v>
+        <v>569608</v>
       </c>
       <c r="R83" t="n">
-        <v>6957867</v>
+        <v>6958227</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9017,6 +9022,11 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9043,38 +9053,37 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128728434</v>
+        <v>128729895</v>
       </c>
       <c r="B84" t="n">
-        <v>57720</v>
+        <v>98636</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>26</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
@@ -9083,10 +9092,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>569608</v>
+        <v>569713</v>
       </c>
       <c r="R84" t="n">
-        <v>6958227</v>
+        <v>6958138</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9119,11 +9128,6 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9150,7 +9154,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128729895</v>
+        <v>128743257</v>
       </c>
       <c r="B85" t="n">
         <v>98636</v>
@@ -9178,21 +9182,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
+      <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>569713</v>
+        <v>569656</v>
       </c>
       <c r="R85" t="n">
-        <v>6958138</v>
+        <v>6957942</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9225,6 +9225,11 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>23 exemplar (ca)</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9251,32 +9256,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128743257</v>
+        <v>128743244</v>
       </c>
       <c r="B86" t="n">
-        <v>98636</v>
+        <v>91508</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9286,10 +9291,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>569656</v>
+        <v>569736</v>
       </c>
       <c r="R86" t="n">
-        <v>6957942</v>
+        <v>6957867</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9322,11 +9327,6 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>23 exemplar (ca)</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9450,7 +9450,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128743261</v>
+        <v>128728419</v>
       </c>
       <c r="B88" t="n">
         <v>79124</v>
@@ -9485,10 +9485,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>569495</v>
+        <v>569608</v>
       </c>
       <c r="R88" t="n">
-        <v>6958117</v>
+        <v>6958227</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9521,6 +9521,11 @@
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>Riklig förekomst inom området</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9547,10 +9552,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128727978</v>
+        <v>128743261</v>
       </c>
       <c r="B89" t="n">
-        <v>57720</v>
+        <v>79124</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9558,39 +9563,34 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P89" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>569564</v>
+        <v>569495</v>
       </c>
       <c r="R89" t="n">
-        <v>6958213</v>
+        <v>6958117</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9623,11 +9623,6 @@
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9654,7 +9649,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128729666</v>
+        <v>128727978</v>
       </c>
       <c r="B90" t="n">
         <v>57720</v>
@@ -9694,10 +9689,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>569706</v>
+        <v>569564</v>
       </c>
       <c r="R90" t="n">
-        <v>6958159</v>
+        <v>6958213</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9734,7 +9729,7 @@
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9761,45 +9756,50 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128738599</v>
+        <v>128729666</v>
       </c>
       <c r="B91" t="n">
-        <v>80189</v>
+        <v>57720</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>229497</v>
+        <v>100109</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P91" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>569608</v>
+        <v>569706</v>
       </c>
       <c r="R91" t="n">
-        <v>6958048</v>
+        <v>6958159</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9832,6 +9832,11 @@
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9858,32 +9863,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128728419</v>
+        <v>128738599</v>
       </c>
       <c r="B92" t="n">
-        <v>79124</v>
+        <v>80189</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9896,7 +9901,7 @@
         <v>569608</v>
       </c>
       <c r="R92" t="n">
-        <v>6958227</v>
+        <v>6958048</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9929,11 +9934,6 @@
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC92" t="inlineStr">
-        <is>
-          <t>Riklig förekomst inom området</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -9960,32 +9960,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128728152</v>
+        <v>128743253</v>
       </c>
       <c r="B93" t="n">
-        <v>91508</v>
+        <v>98636</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9995,10 +9995,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>569577</v>
+        <v>569641</v>
       </c>
       <c r="R93" t="n">
-        <v>6958213</v>
+        <v>6957953</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10031,6 +10031,11 @@
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>55 exemplar knärötter</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10057,10 +10062,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128728274</v>
+        <v>128728152</v>
       </c>
       <c r="B94" t="n">
-        <v>57720</v>
+        <v>91508</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10068,39 +10073,34 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P94" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>569599</v>
+        <v>569577</v>
       </c>
       <c r="R94" t="n">
-        <v>6958201</v>
+        <v>6958213</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10133,11 +10133,6 @@
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>Både äldre och färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10164,37 +10159,38 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128731648</v>
+        <v>128728274</v>
       </c>
       <c r="B95" t="n">
-        <v>98636</v>
+        <v>57720</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>119</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P95" t="inlineStr">
@@ -10203,10 +10199,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>569766</v>
+        <v>569599</v>
       </c>
       <c r="R95" t="n">
-        <v>6958144</v>
+        <v>6958201</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10243,7 +10239,7 @@
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>Ca ( möjligtvis fler)</t>
+          <t>Både äldre och färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10270,7 +10266,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128743253</v>
+        <v>128731648</v>
       </c>
       <c r="B96" t="n">
         <v>98636</v>
@@ -10298,17 +10294,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I96" t="inlineStr"/>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
       <c r="P96" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>569641</v>
+        <v>569766</v>
       </c>
       <c r="R96" t="n">
-        <v>6957953</v>
+        <v>6958144</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10345,7 +10345,7 @@
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>55 exemplar knärötter</t>
+          <t>Ca ( möjligtvis fler)</t>
         </is>
       </c>
       <c r="AD96" t="b">

--- a/artfynd/A 39666-2025 artfynd.xlsx
+++ b/artfynd/A 39666-2025 artfynd.xlsx
@@ -772,45 +772,49 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128743246</v>
+        <v>128728896</v>
       </c>
       <c r="B3" t="n">
-        <v>57720</v>
+        <v>98636</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>569648</v>
+        <v>569601</v>
       </c>
       <c r="R3" t="n">
-        <v>6957944</v>
+        <v>6958191</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -843,11 +847,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall ( äldre och färska spår)</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -874,38 +873,37 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128728526</v>
+        <v>128732983</v>
       </c>
       <c r="B4" t="n">
-        <v>57720</v>
+        <v>98636</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>15</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -914,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>569616</v>
+        <v>569873</v>
       </c>
       <c r="R4" t="n">
-        <v>6958208</v>
+        <v>6958099</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -950,11 +948,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -981,7 +974,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128739007</v>
+        <v>128743246</v>
       </c>
       <c r="B5" t="n">
         <v>57720</v>
@@ -1010,21 +1003,16 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>569542</v>
+        <v>569648</v>
       </c>
       <c r="R5" t="n">
-        <v>6958069</v>
+        <v>6957944</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1061,7 +1049,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack av tretåig hackspett på Tall ( äldre och färska spår)</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1088,37 +1076,38 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128728896</v>
+        <v>128728526</v>
       </c>
       <c r="B6" t="n">
-        <v>98636</v>
+        <v>57720</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>6</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1127,10 +1116,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>569601</v>
+        <v>569616</v>
       </c>
       <c r="R6" t="n">
-        <v>6958191</v>
+        <v>6958208</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1163,6 +1152,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1189,37 +1183,38 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128732983</v>
+        <v>128739007</v>
       </c>
       <c r="B7" t="n">
-        <v>98636</v>
+        <v>57720</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>15</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1228,10 +1223,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>569873</v>
+        <v>569542</v>
       </c>
       <c r="R7" t="n">
-        <v>6958099</v>
+        <v>6958069</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1264,6 +1259,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1494,10 +1494,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128732217</v>
+        <v>128730571</v>
       </c>
       <c r="B10" t="n">
-        <v>57880</v>
+        <v>91526</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1505,48 +1505,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>569777</v>
+        <v>569660</v>
       </c>
       <c r="R10" t="n">
-        <v>6958189</v>
+        <v>6958074</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1579,11 +1565,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>2 talltitor kommer flygandes väldigt närgånget och varnar</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1610,10 +1591,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128730571</v>
+        <v>128732765</v>
       </c>
       <c r="B11" t="n">
-        <v>91526</v>
+        <v>91804</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1621,21 +1602,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1645,10 +1626,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>569660</v>
+        <v>569827</v>
       </c>
       <c r="R11" t="n">
-        <v>6958074</v>
+        <v>6958133</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1707,45 +1688,50 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128733181</v>
+        <v>128732276</v>
       </c>
       <c r="B12" t="n">
-        <v>98553</v>
+        <v>57720</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>569900</v>
+        <v>569841</v>
       </c>
       <c r="R12" t="n">
-        <v>6958101</v>
+        <v>6958102</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1778,6 +1764,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1804,10 +1795,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128732765</v>
+        <v>128743245</v>
       </c>
       <c r="B13" t="n">
-        <v>91804</v>
+        <v>57720</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1815,21 +1806,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1839,10 +1830,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>569827</v>
+        <v>569590</v>
       </c>
       <c r="R13" t="n">
-        <v>6958133</v>
+        <v>6958014</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1875,6 +1866,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall ( färska spår)</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1901,10 +1897,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128732276</v>
+        <v>128732217</v>
       </c>
       <c r="B14" t="n">
-        <v>57720</v>
+        <v>57880</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1912,27 +1908,36 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -1941,10 +1946,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>569841</v>
+        <v>569777</v>
       </c>
       <c r="R14" t="n">
-        <v>6958102</v>
+        <v>6958189</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1981,7 +1986,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>2 talltitor kommer flygandes väldigt närgånget och varnar</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2008,32 +2013,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128743245</v>
+        <v>128733181</v>
       </c>
       <c r="B15" t="n">
-        <v>57720</v>
+        <v>98553</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2043,10 +2048,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>569590</v>
+        <v>569900</v>
       </c>
       <c r="R15" t="n">
-        <v>6958014</v>
+        <v>6958101</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2079,11 +2084,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall ( färska spår)</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2516,32 +2516,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128728022</v>
+        <v>128732359</v>
       </c>
       <c r="B20" t="n">
-        <v>91473</v>
+        <v>91508</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2551,10 +2551,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>569583</v>
+        <v>569820</v>
       </c>
       <c r="R20" t="n">
-        <v>6958204</v>
+        <v>6958107</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2613,10 +2613,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128739020</v>
+        <v>128731612</v>
       </c>
       <c r="B21" t="n">
-        <v>57720</v>
+        <v>91508</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2624,39 +2624,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>569542</v>
+        <v>569752</v>
       </c>
       <c r="R21" t="n">
-        <v>6958049</v>
+        <v>6958091</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2689,11 +2684,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2720,49 +2710,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128730720</v>
+        <v>128743262</v>
       </c>
       <c r="B22" t="n">
-        <v>98636</v>
+        <v>79124</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>569692</v>
+        <v>569732</v>
       </c>
       <c r="R22" t="n">
-        <v>6958094</v>
+        <v>6957870</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2795,11 +2781,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ca</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2826,45 +2807,50 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128743252</v>
+        <v>128739020</v>
       </c>
       <c r="B23" t="n">
-        <v>98636</v>
+        <v>57720</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>569610</v>
+        <v>569542</v>
       </c>
       <c r="R23" t="n">
-        <v>6958005</v>
+        <v>6958049</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2901,7 +2887,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>2 exemplar</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2928,45 +2914,49 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128732359</v>
+        <v>128730720</v>
       </c>
       <c r="B24" t="n">
-        <v>91508</v>
+        <v>98636</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>569820</v>
+        <v>569692</v>
       </c>
       <c r="R24" t="n">
-        <v>6958107</v>
+        <v>6958094</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2999,6 +2989,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ca</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3025,32 +3020,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128731612</v>
+        <v>128743252</v>
       </c>
       <c r="B25" t="n">
-        <v>91508</v>
+        <v>98636</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3060,10 +3055,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>569752</v>
+        <v>569610</v>
       </c>
       <c r="R25" t="n">
-        <v>6958091</v>
+        <v>6958005</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3096,6 +3091,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>2 exemplar</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3122,32 +3122,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128743262</v>
+        <v>128728022</v>
       </c>
       <c r="B26" t="n">
-        <v>79124</v>
+        <v>91473</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3157,10 +3157,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>569732</v>
+        <v>569583</v>
       </c>
       <c r="R26" t="n">
-        <v>6957870</v>
+        <v>6958204</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3733,10 +3733,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128728767</v>
+        <v>128728303</v>
       </c>
       <c r="B32" t="n">
-        <v>92798</v>
+        <v>57712</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3744,31 +3744,27 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4364</v>
+        <v>100110</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>J.F. Gmelin, 1788</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -3777,10 +3773,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>569639</v>
+        <v>569584</v>
       </c>
       <c r="R32" t="n">
-        <v>6958231</v>
+        <v>6958214</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3817,7 +3813,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>4 äldre ett färskt års exemplar</t>
+          <t>Hörs i närheten</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3844,38 +3840,38 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128728303</v>
+        <v>128730603</v>
       </c>
       <c r="B33" t="n">
-        <v>57712</v>
+        <v>57720</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100110</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -3884,10 +3880,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>569584</v>
+        <v>569738</v>
       </c>
       <c r="R33" t="n">
-        <v>6958214</v>
+        <v>6958117</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3924,7 +3920,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Hörs i närheten</t>
+          <t>Äldre exemplar av ringhack på Tall från tretåig hackspett</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3951,10 +3947,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128730603</v>
+        <v>128730513</v>
       </c>
       <c r="B34" t="n">
-        <v>57720</v>
+        <v>80229</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3962,39 +3958,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>569738</v>
+        <v>569656</v>
       </c>
       <c r="R34" t="n">
-        <v>6958117</v>
+        <v>6958093</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4027,11 +4018,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Äldre exemplar av ringhack på Tall från tretåig hackspett</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4058,45 +4044,54 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128730513</v>
+        <v>128728767</v>
       </c>
       <c r="B35" t="n">
-        <v>80229</v>
+        <v>92798</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>569656</v>
+        <v>569639</v>
       </c>
       <c r="R35" t="n">
-        <v>6958093</v>
+        <v>6958231</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4129,6 +4124,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>4 äldre ett färskt års exemplar</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4155,7 +4155,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128728318</v>
+        <v>128731677</v>
       </c>
       <c r="B36" t="n">
         <v>79124</v>
@@ -4190,10 +4190,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>569616</v>
+        <v>569769</v>
       </c>
       <c r="R36" t="n">
-        <v>6958208</v>
+        <v>6958153</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4252,7 +4252,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128731677</v>
+        <v>128728318</v>
       </c>
       <c r="B37" t="n">
         <v>79124</v>
@@ -4287,10 +4287,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>569769</v>
+        <v>569616</v>
       </c>
       <c r="R37" t="n">
-        <v>6958153</v>
+        <v>6958208</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4955,10 +4955,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128728473</v>
+        <v>128730475</v>
       </c>
       <c r="B44" t="n">
-        <v>57880</v>
+        <v>57720</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4966,27 +4966,27 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -4995,10 +4995,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>569608</v>
+        <v>569675</v>
       </c>
       <c r="R44" t="n">
-        <v>6958227</v>
+        <v>6958098</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5031,6 +5031,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5057,10 +5062,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128730475</v>
+        <v>128728473</v>
       </c>
       <c r="B45" t="n">
-        <v>57720</v>
+        <v>57880</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5068,27 +5073,27 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="M45" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -5097,10 +5102,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>569675</v>
+        <v>569608</v>
       </c>
       <c r="R45" t="n">
-        <v>6958098</v>
+        <v>6958227</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5133,11 +5138,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5164,38 +5164,37 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128728902</v>
+        <v>128732627</v>
       </c>
       <c r="B46" t="n">
-        <v>57720</v>
+        <v>98636</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>6</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -5204,10 +5203,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>569673</v>
+        <v>569821</v>
       </c>
       <c r="R46" t="n">
-        <v>6958225</v>
+        <v>6958151</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5244,7 +5243,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>Kan finnas mer I blåbärsriset och mossan</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5271,38 +5270,37 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128731799</v>
+        <v>128728348</v>
       </c>
       <c r="B47" t="n">
-        <v>57720</v>
+        <v>98636</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>300</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -5311,10 +5309,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>569774</v>
+        <v>569616</v>
       </c>
       <c r="R47" t="n">
-        <v>6958163</v>
+        <v>6958208</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5347,11 +5345,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5378,7 +5371,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128732015</v>
+        <v>128728902</v>
       </c>
       <c r="B48" t="n">
         <v>57720</v>
@@ -5418,10 +5411,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>569816</v>
+        <v>569673</v>
       </c>
       <c r="R48" t="n">
-        <v>6958081</v>
+        <v>6958225</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5458,7 +5451,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5485,7 +5478,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128738187</v>
+        <v>128731799</v>
       </c>
       <c r="B49" t="n">
         <v>57720</v>
@@ -5516,7 +5509,7 @@
       <c r="I49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -5525,10 +5518,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>569681</v>
+        <v>569774</v>
       </c>
       <c r="R49" t="n">
-        <v>6957939</v>
+        <v>6958163</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5565,7 +5558,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5592,37 +5585,38 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128732627</v>
+        <v>128732015</v>
       </c>
       <c r="B50" t="n">
-        <v>98636</v>
+        <v>57720</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>6</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -5631,10 +5625,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>569821</v>
+        <v>569816</v>
       </c>
       <c r="R50" t="n">
-        <v>6958151</v>
+        <v>6958081</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5671,7 +5665,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Kan finnas mer I blåbärsriset och mossan</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5698,37 +5692,38 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128728348</v>
+        <v>128738187</v>
       </c>
       <c r="B51" t="n">
-        <v>98636</v>
+        <v>57720</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>300</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -5737,10 +5732,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>569616</v>
+        <v>569681</v>
       </c>
       <c r="R51" t="n">
-        <v>6958208</v>
+        <v>6957939</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5773,6 +5768,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6318,10 +6318,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128732806</v>
+        <v>128730183</v>
       </c>
       <c r="B57" t="n">
-        <v>91519</v>
+        <v>80189</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6329,21 +6329,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1205</v>
+        <v>229497</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6353,10 +6353,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>569827</v>
+        <v>569630</v>
       </c>
       <c r="R57" t="n">
-        <v>6958133</v>
+        <v>6958129</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6415,32 +6415,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128732719</v>
+        <v>128732806</v>
       </c>
       <c r="B58" t="n">
-        <v>91962</v>
+        <v>91519</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1209</v>
+        <v>1205</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6450,10 +6450,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>569821</v>
+        <v>569827</v>
       </c>
       <c r="R58" t="n">
-        <v>6958151</v>
+        <v>6958133</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6512,32 +6512,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128728592</v>
+        <v>128732719</v>
       </c>
       <c r="B59" t="n">
-        <v>80264</v>
+        <v>91962</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6463</v>
+        <v>1209</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6547,10 +6547,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>569604</v>
+        <v>569821</v>
       </c>
       <c r="R59" t="n">
-        <v>6958176</v>
+        <v>6958151</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6609,10 +6609,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128732124</v>
+        <v>128731387</v>
       </c>
       <c r="B60" t="n">
-        <v>80264</v>
+        <v>80257</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6620,21 +6620,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6463</v>
+        <v>6461</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6644,10 +6644,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>569816</v>
+        <v>569740</v>
       </c>
       <c r="R60" t="n">
-        <v>6958081</v>
+        <v>6958091</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6706,10 +6706,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128730101</v>
+        <v>128728592</v>
       </c>
       <c r="B61" t="n">
-        <v>80265</v>
+        <v>80264</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6717,21 +6717,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6464</v>
+        <v>6463</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6741,10 +6741,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>569630</v>
+        <v>569604</v>
       </c>
       <c r="R61" t="n">
-        <v>6958139</v>
+        <v>6958176</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6803,10 +6803,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128731387</v>
+        <v>128730101</v>
       </c>
       <c r="B62" t="n">
-        <v>80257</v>
+        <v>80265</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6814,21 +6814,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6461</v>
+        <v>6464</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6838,10 +6838,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>569740</v>
+        <v>569630</v>
       </c>
       <c r="R62" t="n">
-        <v>6958091</v>
+        <v>6958139</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6900,50 +6900,45 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128730490</v>
+        <v>128732124</v>
       </c>
       <c r="B63" t="n">
-        <v>57720</v>
+        <v>80264</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>569707</v>
+        <v>569816</v>
       </c>
       <c r="R63" t="n">
-        <v>6958131</v>
+        <v>6958081</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6976,11 +6971,6 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Både äldre och färska spår ( Ringhack av tretåig hackspett på tall)</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7007,7 +6997,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128730422</v>
+        <v>128730490</v>
       </c>
       <c r="B64" t="n">
         <v>57720</v>
@@ -7047,10 +7037,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>569703</v>
+        <v>569707</v>
       </c>
       <c r="R64" t="n">
-        <v>6958116</v>
+        <v>6958131</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7087,7 +7077,7 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>Både äldre och färska spår ( Ringhack av tretåig hackspett på tall)</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7114,7 +7104,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128739287</v>
+        <v>128730422</v>
       </c>
       <c r="B65" t="n">
         <v>57720</v>
@@ -7154,10 +7144,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>569481</v>
+        <v>569703</v>
       </c>
       <c r="R65" t="n">
-        <v>6958122</v>
+        <v>6958116</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7194,7 +7184,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7221,45 +7211,50 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128730183</v>
+        <v>128739287</v>
       </c>
       <c r="B66" t="n">
-        <v>80189</v>
+        <v>57720</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>229497</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>569630</v>
+        <v>569481</v>
       </c>
       <c r="R66" t="n">
-        <v>6958129</v>
+        <v>6958122</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7292,6 +7287,11 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7415,10 +7415,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128730273</v>
+        <v>128732112</v>
       </c>
       <c r="B68" t="n">
-        <v>79124</v>
+        <v>80229</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7426,21 +7426,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7450,10 +7450,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>569692</v>
+        <v>569824</v>
       </c>
       <c r="R68" t="n">
-        <v>6958127</v>
+        <v>6958091</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7512,10 +7512,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128732112</v>
+        <v>128730273</v>
       </c>
       <c r="B69" t="n">
-        <v>80229</v>
+        <v>79124</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7523,21 +7523,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7547,10 +7547,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>569824</v>
+        <v>569692</v>
       </c>
       <c r="R69" t="n">
-        <v>6958091</v>
+        <v>6958127</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7711,10 +7711,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128728149</v>
+        <v>128731693</v>
       </c>
       <c r="B71" t="n">
-        <v>57720</v>
+        <v>91508</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7722,39 +7722,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>569585</v>
+        <v>569793</v>
       </c>
       <c r="R71" t="n">
-        <v>6958190</v>
+        <v>6958092</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7787,11 +7782,6 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7818,7 +7808,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128732493</v>
+        <v>128728149</v>
       </c>
       <c r="B72" t="n">
         <v>57720</v>
@@ -7858,10 +7848,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>569795</v>
+        <v>569585</v>
       </c>
       <c r="R72" t="n">
-        <v>6958154</v>
+        <v>6958190</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7898,7 +7888,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7925,7 +7915,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128730998</v>
+        <v>128732493</v>
       </c>
       <c r="B73" t="n">
         <v>57720</v>
@@ -7965,10 +7955,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>569670</v>
+        <v>569795</v>
       </c>
       <c r="R73" t="n">
-        <v>6958060</v>
+        <v>6958154</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8005,7 +7995,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Ringhack på tall. Även äldre</t>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8032,7 +8022,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128730928</v>
+        <v>128730998</v>
       </c>
       <c r="B74" t="n">
         <v>57720</v>
@@ -8061,24 +8051,21 @@
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
       <c r="M74" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N74" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>569673</v>
+        <v>569670</v>
       </c>
       <c r="R74" t="n">
-        <v>6958076</v>
+        <v>6958060</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8115,7 +8102,7 @@
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Påbörjat bobygge av sannolikt tretåig hackspett. Ser ut att vara relativt färskt. 2 meter upp i död gran. Omkring 4,5 cm i diameter.</t>
+          <t>Ringhack på tall. Även äldre</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8142,10 +8129,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128731693</v>
+        <v>128730928</v>
       </c>
       <c r="B75" t="n">
-        <v>91508</v>
+        <v>57720</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8153,34 +8140,42 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>569793</v>
+        <v>569673</v>
       </c>
       <c r="R75" t="n">
-        <v>6958092</v>
+        <v>6958076</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8213,6 +8208,11 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Påbörjat bobygge av sannolikt tretåig hackspett. Ser ut att vara relativt färskt. 2 meter upp i död gran. Omkring 4,5 cm i diameter.</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8336,10 +8336,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128731284</v>
+        <v>128743247</v>
       </c>
       <c r="B77" t="n">
-        <v>57880</v>
+        <v>57720</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8347,39 +8347,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>569677</v>
+        <v>569714</v>
       </c>
       <c r="R77" t="n">
-        <v>6958066</v>
+        <v>6957901</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8412,6 +8407,11 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på gran ( färska spår)</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8438,37 +8438,38 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128732718</v>
+        <v>128732848</v>
       </c>
       <c r="B78" t="n">
-        <v>98636</v>
+        <v>57720</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>18</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
@@ -8477,10 +8478,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>569834</v>
+        <v>569873</v>
       </c>
       <c r="R78" t="n">
-        <v>6958143</v>
+        <v>6958099</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8513,6 +8514,11 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8539,7 +8545,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128733005</v>
+        <v>128732718</v>
       </c>
       <c r="B79" t="n">
         <v>98636</v>
@@ -8569,7 +8575,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>18</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
@@ -8578,10 +8584,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>569882</v>
+        <v>569834</v>
       </c>
       <c r="R79" t="n">
-        <v>6958106</v>
+        <v>6958143</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8640,45 +8646,49 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128743247</v>
+        <v>128733005</v>
       </c>
       <c r="B80" t="n">
-        <v>57720</v>
+        <v>98636</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>569714</v>
+        <v>569882</v>
       </c>
       <c r="R80" t="n">
-        <v>6957901</v>
+        <v>6958106</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8711,11 +8721,6 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på gran ( färska spår)</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8742,10 +8747,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128732848</v>
+        <v>128731284</v>
       </c>
       <c r="B81" t="n">
-        <v>57720</v>
+        <v>57880</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8753,27 +8758,27 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="M81" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
@@ -8782,10 +8787,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>569873</v>
+        <v>569677</v>
       </c>
       <c r="R81" t="n">
-        <v>6958099</v>
+        <v>6958066</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8818,11 +8823,6 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8849,10 +8849,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128731226</v>
+        <v>128743244</v>
       </c>
       <c r="B82" t="n">
-        <v>91526</v>
+        <v>91508</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8860,21 +8860,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8884,10 +8884,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>569705</v>
+        <v>569736</v>
       </c>
       <c r="R82" t="n">
-        <v>6958098</v>
+        <v>6957867</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8946,10 +8946,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128728434</v>
+        <v>128731226</v>
       </c>
       <c r="B83" t="n">
-        <v>57720</v>
+        <v>91526</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8957,39 +8957,34 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>569608</v>
+        <v>569705</v>
       </c>
       <c r="R83" t="n">
-        <v>6958227</v>
+        <v>6958098</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9022,11 +9017,6 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9053,37 +9043,38 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128729895</v>
+        <v>128728434</v>
       </c>
       <c r="B84" t="n">
-        <v>98636</v>
+        <v>57720</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>26</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
@@ -9092,10 +9083,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>569713</v>
+        <v>569608</v>
       </c>
       <c r="R84" t="n">
-        <v>6958138</v>
+        <v>6958227</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9128,6 +9119,11 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9154,7 +9150,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128743257</v>
+        <v>128729895</v>
       </c>
       <c r="B85" t="n">
         <v>98636</v>
@@ -9182,17 +9178,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I85" t="inlineStr"/>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>569656</v>
+        <v>569713</v>
       </c>
       <c r="R85" t="n">
-        <v>6957942</v>
+        <v>6958138</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9225,11 +9225,6 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>23 exemplar (ca)</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9256,32 +9251,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128743244</v>
+        <v>128743257</v>
       </c>
       <c r="B86" t="n">
-        <v>91508</v>
+        <v>98636</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9291,10 +9286,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>569736</v>
+        <v>569656</v>
       </c>
       <c r="R86" t="n">
-        <v>6957867</v>
+        <v>6957942</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9327,6 +9322,11 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>23 exemplar (ca)</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9353,7 +9353,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128729069</v>
+        <v>128728419</v>
       </c>
       <c r="B87" t="n">
         <v>79124</v>
@@ -9388,10 +9388,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>569699</v>
+        <v>569608</v>
       </c>
       <c r="R87" t="n">
-        <v>6958200</v>
+        <v>6958227</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9424,6 +9424,11 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>Riklig förekomst inom området</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9450,7 +9455,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128728419</v>
+        <v>128729069</v>
       </c>
       <c r="B88" t="n">
         <v>79124</v>
@@ -9485,10 +9490,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>569608</v>
+        <v>569699</v>
       </c>
       <c r="R88" t="n">
-        <v>6958227</v>
+        <v>6958200</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9521,11 +9526,6 @@
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>Riklig förekomst inom området</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9960,32 +9960,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128743253</v>
+        <v>128728152</v>
       </c>
       <c r="B93" t="n">
-        <v>98636</v>
+        <v>91508</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9995,10 +9995,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>569641</v>
+        <v>569577</v>
       </c>
       <c r="R93" t="n">
-        <v>6957953</v>
+        <v>6958213</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10031,11 +10031,6 @@
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC93" t="inlineStr">
-        <is>
-          <t>55 exemplar knärötter</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10062,10 +10057,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128728152</v>
+        <v>128728274</v>
       </c>
       <c r="B94" t="n">
-        <v>91508</v>
+        <v>57720</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10073,34 +10068,39 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P94" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>569577</v>
+        <v>569599</v>
       </c>
       <c r="R94" t="n">
-        <v>6958213</v>
+        <v>6958201</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10133,6 +10133,11 @@
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>Både äldre och färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10159,38 +10164,37 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128728274</v>
+        <v>128731648</v>
       </c>
       <c r="B95" t="n">
-        <v>57720</v>
+        <v>98636</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr"/>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>119</t>
         </is>
       </c>
       <c r="P95" t="inlineStr">
@@ -10199,10 +10203,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>569599</v>
+        <v>569766</v>
       </c>
       <c r="R95" t="n">
-        <v>6958201</v>
+        <v>6958144</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10239,7 +10243,7 @@
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>Både äldre och färska ringhack på tall</t>
+          <t>Ca ( möjligtvis fler)</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10266,7 +10270,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128731648</v>
+        <v>128743253</v>
       </c>
       <c r="B96" t="n">
         <v>98636</v>
@@ -10294,21 +10298,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>119</t>
-        </is>
-      </c>
+      <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>569766</v>
+        <v>569641</v>
       </c>
       <c r="R96" t="n">
-        <v>6958144</v>
+        <v>6957953</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10345,7 +10345,7 @@
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>Ca ( möjligtvis fler)</t>
+          <t>55 exemplar knärötter</t>
         </is>
       </c>
       <c r="AD96" t="b">

--- a/artfynd/A 39666-2025 artfynd.xlsx
+++ b/artfynd/A 39666-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128732386</v>
       </c>
       <c r="B2" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,49 +772,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128728896</v>
+        <v>128743246</v>
       </c>
       <c r="B3" t="n">
-        <v>98636</v>
+        <v>57723</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>569601</v>
+        <v>569648</v>
       </c>
       <c r="R3" t="n">
-        <v>6958191</v>
+        <v>6957944</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -847,6 +843,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall ( äldre och färska spår)</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -873,37 +874,38 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128732983</v>
+        <v>128728526</v>
       </c>
       <c r="B4" t="n">
-        <v>98636</v>
+        <v>57723</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>15</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -912,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>569873</v>
+        <v>569616</v>
       </c>
       <c r="R4" t="n">
-        <v>6958099</v>
+        <v>6958208</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -948,6 +950,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -974,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128743246</v>
+        <v>128739007</v>
       </c>
       <c r="B5" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1003,16 +1010,21 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>569648</v>
+        <v>569542</v>
       </c>
       <c r="R5" t="n">
-        <v>6957944</v>
+        <v>6958069</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1049,7 +1061,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall ( äldre och färska spår)</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1076,38 +1088,37 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128728526</v>
+        <v>128732983</v>
       </c>
       <c r="B6" t="n">
-        <v>57720</v>
+        <v>98643</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>15</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1116,10 +1127,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>569616</v>
+        <v>569873</v>
       </c>
       <c r="R6" t="n">
-        <v>6958208</v>
+        <v>6958099</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1152,11 +1163,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1183,38 +1189,37 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128739007</v>
+        <v>128728896</v>
       </c>
       <c r="B7" t="n">
-        <v>57720</v>
+        <v>98643</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>6</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1223,10 +1228,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>569542</v>
+        <v>569601</v>
       </c>
       <c r="R7" t="n">
-        <v>6958069</v>
+        <v>6958191</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1259,11 +1264,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1293,7 +1293,7 @@
         <v>128729409</v>
       </c>
       <c r="B8" t="n">
-        <v>91508</v>
+        <v>91513</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1390,7 +1390,7 @@
         <v>128730130</v>
       </c>
       <c r="B9" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1494,10 +1494,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128730571</v>
+        <v>128732765</v>
       </c>
       <c r="B10" t="n">
-        <v>91526</v>
+        <v>91809</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1505,21 +1505,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1529,10 +1529,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>569660</v>
+        <v>569827</v>
       </c>
       <c r="R10" t="n">
-        <v>6958074</v>
+        <v>6958133</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1591,10 +1591,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128732765</v>
+        <v>128730571</v>
       </c>
       <c r="B11" t="n">
-        <v>91804</v>
+        <v>91531</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1602,21 +1602,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1626,10 +1626,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>569827</v>
+        <v>569660</v>
       </c>
       <c r="R11" t="n">
-        <v>6958133</v>
+        <v>6958074</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1691,7 +1691,7 @@
         <v>128732276</v>
       </c>
       <c r="B12" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
         <v>128743245</v>
       </c>
       <c r="B13" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
         <v>128732217</v>
       </c>
       <c r="B14" t="n">
-        <v>57880</v>
+        <v>57883</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2016,7 +2016,7 @@
         <v>128733181</v>
       </c>
       <c r="B15" t="n">
-        <v>98553</v>
+        <v>98560</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2113,7 +2113,7 @@
         <v>128731601</v>
       </c>
       <c r="B16" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2217,45 +2217,49 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128728515</v>
+        <v>128731490</v>
       </c>
       <c r="B17" t="n">
-        <v>97507</v>
+        <v>98643</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>569608</v>
+        <v>569759</v>
       </c>
       <c r="R17" t="n">
-        <v>6958227</v>
+        <v>6958118</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2314,10 +2318,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128731490</v>
+        <v>128730429</v>
       </c>
       <c r="B18" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2344,7 +2348,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>80</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2353,10 +2357,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>569759</v>
+        <v>569683</v>
       </c>
       <c r="R18" t="n">
-        <v>6958118</v>
+        <v>6958128</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2415,49 +2419,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128730429</v>
+        <v>128728515</v>
       </c>
       <c r="B19" t="n">
-        <v>98636</v>
+        <v>97514</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>569683</v>
+        <v>569608</v>
       </c>
       <c r="R19" t="n">
-        <v>6958128</v>
+        <v>6958227</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2516,10 +2516,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128732359</v>
+        <v>128739020</v>
       </c>
       <c r="B20" t="n">
-        <v>91508</v>
+        <v>57723</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2527,34 +2527,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>569820</v>
+        <v>569542</v>
       </c>
       <c r="R20" t="n">
-        <v>6958107</v>
+        <v>6958049</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2587,6 +2592,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2613,10 +2623,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128731612</v>
+        <v>128732359</v>
       </c>
       <c r="B21" t="n">
-        <v>91508</v>
+        <v>91513</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2648,10 +2658,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>569752</v>
+        <v>569820</v>
       </c>
       <c r="R21" t="n">
-        <v>6958091</v>
+        <v>6958107</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2710,10 +2720,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128743262</v>
+        <v>128731612</v>
       </c>
       <c r="B22" t="n">
-        <v>79124</v>
+        <v>91513</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2721,21 +2731,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2745,10 +2755,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>569732</v>
+        <v>569752</v>
       </c>
       <c r="R22" t="n">
-        <v>6957870</v>
+        <v>6958091</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2807,50 +2817,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128739020</v>
+        <v>128728022</v>
       </c>
       <c r="B23" t="n">
-        <v>57720</v>
+        <v>91478</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>569542</v>
+        <v>569583</v>
       </c>
       <c r="R23" t="n">
-        <v>6958049</v>
+        <v>6958204</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2883,11 +2888,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2914,49 +2914,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128730720</v>
+        <v>128743262</v>
       </c>
       <c r="B24" t="n">
-        <v>98636</v>
+        <v>79029</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>569692</v>
+        <v>569732</v>
       </c>
       <c r="R24" t="n">
-        <v>6958094</v>
+        <v>6957870</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2989,11 +2985,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ca</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3020,10 +3011,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128743252</v>
+        <v>128730720</v>
       </c>
       <c r="B25" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3048,17 +3039,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>569610</v>
+        <v>569692</v>
       </c>
       <c r="R25" t="n">
-        <v>6958005</v>
+        <v>6958094</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3095,7 +3090,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>2 exemplar</t>
+          <t>Ca</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3122,32 +3117,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128728022</v>
+        <v>128743252</v>
       </c>
       <c r="B26" t="n">
-        <v>91473</v>
+        <v>98643</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3157,10 +3152,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>569583</v>
+        <v>569610</v>
       </c>
       <c r="R26" t="n">
-        <v>6958204</v>
+        <v>6958005</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3193,6 +3188,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>2 exemplar</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3222,7 +3222,7 @@
         <v>128731107</v>
       </c>
       <c r="B27" t="n">
-        <v>57880</v>
+        <v>57883</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3324,7 +3324,7 @@
         <v>128729068</v>
       </c>
       <c r="B28" t="n">
-        <v>80258</v>
+        <v>80163</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3421,7 +3421,7 @@
         <v>128731291</v>
       </c>
       <c r="B29" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3528,7 +3528,7 @@
         <v>128728019</v>
       </c>
       <c r="B30" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3635,7 +3635,7 @@
         <v>128731489</v>
       </c>
       <c r="B31" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3733,10 +3733,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128728303</v>
+        <v>128728767</v>
       </c>
       <c r="B32" t="n">
-        <v>57712</v>
+        <v>92803</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3744,27 +3744,31 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100110</v>
+        <v>4364</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -3773,10 +3777,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>569584</v>
+        <v>569639</v>
       </c>
       <c r="R32" t="n">
-        <v>6958214</v>
+        <v>6958231</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3813,7 +3817,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Hörs i närheten</t>
+          <t>4 äldre ett färskt års exemplar</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3840,10 +3844,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128730603</v>
+        <v>128730513</v>
       </c>
       <c r="B33" t="n">
-        <v>57720</v>
+        <v>80134</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3851,39 +3855,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>569738</v>
+        <v>569656</v>
       </c>
       <c r="R33" t="n">
-        <v>6958117</v>
+        <v>6958093</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3916,11 +3915,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Äldre exemplar av ringhack på Tall från tretåig hackspett</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3947,45 +3941,50 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128730513</v>
+        <v>128728303</v>
       </c>
       <c r="B34" t="n">
-        <v>80229</v>
+        <v>57715</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>100110</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>J.F. Gmelin, 1788</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>569656</v>
+        <v>569584</v>
       </c>
       <c r="R34" t="n">
-        <v>6958093</v>
+        <v>6958214</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4018,6 +4017,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Hörs i närheten</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4044,42 +4048,38 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128728767</v>
+        <v>128730603</v>
       </c>
       <c r="B35" t="n">
-        <v>92798</v>
+        <v>57723</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4088,10 +4088,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>569639</v>
+        <v>569738</v>
       </c>
       <c r="R35" t="n">
-        <v>6958231</v>
+        <v>6958117</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>4 äldre ett färskt års exemplar</t>
+          <t>Äldre exemplar av ringhack på Tall från tretåig hackspett</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4155,10 +4155,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128731677</v>
+        <v>128729745</v>
       </c>
       <c r="B36" t="n">
-        <v>79124</v>
+        <v>57723</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4166,34 +4166,39 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>569769</v>
+        <v>569694</v>
       </c>
       <c r="R36" t="n">
-        <v>6958153</v>
+        <v>6958144</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4226,6 +4231,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4255,7 +4265,7 @@
         <v>128728318</v>
       </c>
       <c r="B37" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4349,10 +4359,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128729745</v>
+        <v>128731677</v>
       </c>
       <c r="B38" t="n">
-        <v>57720</v>
+        <v>79029</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4360,39 +4370,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>569694</v>
+        <v>569769</v>
       </c>
       <c r="R38" t="n">
-        <v>6958144</v>
+        <v>6958153</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4425,11 +4430,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4459,7 +4459,7 @@
         <v>128732677</v>
       </c>
       <c r="B39" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4560,7 +4560,7 @@
         <v>128743255</v>
       </c>
       <c r="B40" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4662,7 +4662,7 @@
         <v>128743254</v>
       </c>
       <c r="B41" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4761,10 +4761,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128729439</v>
+        <v>128729962</v>
       </c>
       <c r="B42" t="n">
-        <v>91508</v>
+        <v>80134</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4772,21 +4772,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4796,10 +4796,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>569703</v>
+        <v>569643</v>
       </c>
       <c r="R42" t="n">
-        <v>6958175</v>
+        <v>6958117</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4858,10 +4858,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128729962</v>
+        <v>128729439</v>
       </c>
       <c r="B43" t="n">
-        <v>80229</v>
+        <v>91513</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4869,21 +4869,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4893,10 +4893,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>569643</v>
+        <v>569703</v>
       </c>
       <c r="R43" t="n">
-        <v>6958117</v>
+        <v>6958175</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4958,7 +4958,7 @@
         <v>128730475</v>
       </c>
       <c r="B44" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5065,7 +5065,7 @@
         <v>128728473</v>
       </c>
       <c r="B45" t="n">
-        <v>57880</v>
+        <v>57883</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5164,37 +5164,38 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128732627</v>
+        <v>128728902</v>
       </c>
       <c r="B46" t="n">
-        <v>98636</v>
+        <v>57723</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>6</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -5203,10 +5204,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>569821</v>
+        <v>569673</v>
       </c>
       <c r="R46" t="n">
-        <v>6958151</v>
+        <v>6958225</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5243,7 +5244,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Kan finnas mer I blåbärsriset och mossan</t>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5270,37 +5271,38 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128728348</v>
+        <v>128731799</v>
       </c>
       <c r="B47" t="n">
-        <v>98636</v>
+        <v>57723</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>300</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -5309,10 +5311,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>569616</v>
+        <v>569774</v>
       </c>
       <c r="R47" t="n">
-        <v>6958208</v>
+        <v>6958163</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5345,6 +5347,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5371,10 +5378,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128728902</v>
+        <v>128732015</v>
       </c>
       <c r="B48" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5411,10 +5418,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>569673</v>
+        <v>569816</v>
       </c>
       <c r="R48" t="n">
-        <v>6958225</v>
+        <v>6958081</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5451,7 +5458,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5478,10 +5485,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128731799</v>
+        <v>128738187</v>
       </c>
       <c r="B49" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5509,7 +5516,7 @@
       <c r="I49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -5518,10 +5525,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>569774</v>
+        <v>569681</v>
       </c>
       <c r="R49" t="n">
-        <v>6958163</v>
+        <v>6957939</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5558,7 +5565,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5585,38 +5592,37 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128732015</v>
+        <v>128732627</v>
       </c>
       <c r="B50" t="n">
-        <v>57720</v>
+        <v>98643</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>6</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -5625,10 +5631,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>569816</v>
+        <v>569821</v>
       </c>
       <c r="R50" t="n">
-        <v>6958081</v>
+        <v>6958151</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5665,7 +5671,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Kan finnas mer I blåbärsriset och mossan</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5692,38 +5698,37 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128738187</v>
+        <v>128728348</v>
       </c>
       <c r="B51" t="n">
-        <v>57720</v>
+        <v>98643</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>300</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -5732,10 +5737,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>569681</v>
+        <v>569616</v>
       </c>
       <c r="R51" t="n">
-        <v>6957939</v>
+        <v>6958208</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5768,11 +5773,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5799,49 +5799,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128729573</v>
+        <v>128731302</v>
       </c>
       <c r="B52" t="n">
-        <v>98636</v>
+        <v>80094</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>229497</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>569706</v>
+        <v>569696</v>
       </c>
       <c r="R52" t="n">
-        <v>6958159</v>
+        <v>6958031</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5900,45 +5896,49 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128731302</v>
+        <v>128729573</v>
       </c>
       <c r="B53" t="n">
-        <v>80189</v>
+        <v>98643</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>229497</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>569696</v>
+        <v>569706</v>
       </c>
       <c r="R53" t="n">
-        <v>6958031</v>
+        <v>6958159</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5997,10 +5997,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128731037</v>
+        <v>128738306</v>
       </c>
       <c r="B54" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6028,7 +6028,7 @@
       <c r="I54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -6037,10 +6037,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>569673</v>
+        <v>569644</v>
       </c>
       <c r="R54" t="n">
-        <v>6958037</v>
+        <v>6957965</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6104,10 +6104,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128738306</v>
+        <v>128732183</v>
       </c>
       <c r="B55" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6144,10 +6144,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>569644</v>
+        <v>569777</v>
       </c>
       <c r="R55" t="n">
-        <v>6957965</v>
+        <v>6958189</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6184,7 +6184,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6211,10 +6211,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128732183</v>
+        <v>128731037</v>
       </c>
       <c r="B56" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6242,7 +6242,7 @@
       <c r="I56" t="inlineStr"/>
       <c r="M56" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -6251,10 +6251,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>569777</v>
+        <v>569673</v>
       </c>
       <c r="R56" t="n">
-        <v>6958189</v>
+        <v>6958037</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6291,7 +6291,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6321,7 +6321,7 @@
         <v>128730183</v>
       </c>
       <c r="B57" t="n">
-        <v>80189</v>
+        <v>80094</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6418,7 +6418,7 @@
         <v>128732806</v>
       </c>
       <c r="B58" t="n">
-        <v>91519</v>
+        <v>91524</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6515,7 +6515,7 @@
         <v>128732719</v>
       </c>
       <c r="B59" t="n">
-        <v>91962</v>
+        <v>91967</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6609,10 +6609,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128731387</v>
+        <v>128728592</v>
       </c>
       <c r="B60" t="n">
-        <v>80257</v>
+        <v>80169</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6620,21 +6620,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6461</v>
+        <v>6463</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6644,10 +6644,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>569740</v>
+        <v>569604</v>
       </c>
       <c r="R60" t="n">
-        <v>6958091</v>
+        <v>6958176</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6706,10 +6706,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128728592</v>
+        <v>128732124</v>
       </c>
       <c r="B61" t="n">
-        <v>80264</v>
+        <v>80169</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6741,10 +6741,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>569604</v>
+        <v>569816</v>
       </c>
       <c r="R61" t="n">
-        <v>6958176</v>
+        <v>6958081</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6806,7 +6806,7 @@
         <v>128730101</v>
       </c>
       <c r="B62" t="n">
-        <v>80265</v>
+        <v>80170</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6900,10 +6900,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128732124</v>
+        <v>128731387</v>
       </c>
       <c r="B63" t="n">
-        <v>80264</v>
+        <v>80162</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6911,21 +6911,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6463</v>
+        <v>6461</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6935,10 +6935,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>569816</v>
+        <v>569740</v>
       </c>
       <c r="R63" t="n">
-        <v>6958081</v>
+        <v>6958091</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7000,7 +7000,7 @@
         <v>128730490</v>
       </c>
       <c r="B64" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7107,7 +7107,7 @@
         <v>128730422</v>
       </c>
       <c r="B65" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7214,7 +7214,7 @@
         <v>128739287</v>
       </c>
       <c r="B66" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7318,10 +7318,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128729077</v>
+        <v>128730273</v>
       </c>
       <c r="B67" t="n">
-        <v>80229</v>
+        <v>79029</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7329,21 +7329,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7353,10 +7353,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>569604</v>
+        <v>569692</v>
       </c>
       <c r="R67" t="n">
-        <v>6958176</v>
+        <v>6958127</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7415,10 +7415,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128732112</v>
+        <v>128729077</v>
       </c>
       <c r="B68" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7450,10 +7450,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>569824</v>
+        <v>569604</v>
       </c>
       <c r="R68" t="n">
-        <v>6958091</v>
+        <v>6958176</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7512,10 +7512,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128730273</v>
+        <v>128732112</v>
       </c>
       <c r="B69" t="n">
-        <v>79124</v>
+        <v>80134</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7523,21 +7523,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7547,10 +7547,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>569692</v>
+        <v>569824</v>
       </c>
       <c r="R69" t="n">
-        <v>6958127</v>
+        <v>6958091</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7612,7 +7612,7 @@
         <v>128743263</v>
       </c>
       <c r="B70" t="n">
-        <v>92834</v>
+        <v>92839</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7711,10 +7711,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128731693</v>
+        <v>128728149</v>
       </c>
       <c r="B71" t="n">
-        <v>91508</v>
+        <v>57723</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7722,34 +7722,39 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>569793</v>
+        <v>569585</v>
       </c>
       <c r="R71" t="n">
-        <v>6958092</v>
+        <v>6958190</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7782,6 +7787,11 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7808,10 +7818,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128728149</v>
+        <v>128732493</v>
       </c>
       <c r="B72" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7848,10 +7858,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>569585</v>
+        <v>569795</v>
       </c>
       <c r="R72" t="n">
-        <v>6958190</v>
+        <v>6958154</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7888,7 +7898,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7915,10 +7925,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128732493</v>
+        <v>128730998</v>
       </c>
       <c r="B73" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7955,10 +7965,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>569795</v>
+        <v>569670</v>
       </c>
       <c r="R73" t="n">
-        <v>6958154</v>
+        <v>6958060</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7995,7 +8005,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>Ringhack på tall. Även äldre</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8022,10 +8032,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128730998</v>
+        <v>128730928</v>
       </c>
       <c r="B74" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8051,21 +8061,24 @@
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
       <c r="M74" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>569670</v>
+        <v>569673</v>
       </c>
       <c r="R74" t="n">
-        <v>6958060</v>
+        <v>6958076</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8102,7 +8115,7 @@
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Ringhack på tall. Även äldre</t>
+          <t>Påbörjat bobygge av sannolikt tretåig hackspett. Ser ut att vara relativt färskt. 2 meter upp i död gran. Omkring 4,5 cm i diameter.</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8129,10 +8142,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128730928</v>
+        <v>128731693</v>
       </c>
       <c r="B75" t="n">
-        <v>57720</v>
+        <v>91513</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8140,42 +8153,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>569673</v>
+        <v>569793</v>
       </c>
       <c r="R75" t="n">
-        <v>6958076</v>
+        <v>6958092</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8208,11 +8213,6 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Påbörjat bobygge av sannolikt tretåig hackspett. Ser ut att vara relativt färskt. 2 meter upp i död gran. Omkring 4,5 cm i diameter.</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8242,7 +8242,7 @@
         <v>128731100</v>
       </c>
       <c r="B76" t="n">
-        <v>91526</v>
+        <v>91531</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8336,45 +8336,49 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128743247</v>
+        <v>128732718</v>
       </c>
       <c r="B77" t="n">
-        <v>57720</v>
+        <v>98643</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>569714</v>
+        <v>569834</v>
       </c>
       <c r="R77" t="n">
-        <v>6957901</v>
+        <v>6958143</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8407,11 +8411,6 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på gran ( färska spår)</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8438,38 +8437,37 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128732848</v>
+        <v>128733005</v>
       </c>
       <c r="B78" t="n">
-        <v>57720</v>
+        <v>98643</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>7</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
@@ -8478,10 +8476,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>569873</v>
+        <v>569882</v>
       </c>
       <c r="R78" t="n">
-        <v>6958099</v>
+        <v>6958106</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8514,11 +8512,6 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8545,37 +8538,38 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128732718</v>
+        <v>128731284</v>
       </c>
       <c r="B79" t="n">
-        <v>98636</v>
+        <v>57883</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>18</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
@@ -8584,10 +8578,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>569834</v>
+        <v>569677</v>
       </c>
       <c r="R79" t="n">
-        <v>6958143</v>
+        <v>6958066</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8646,49 +8640,45 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128733005</v>
+        <v>128743247</v>
       </c>
       <c r="B80" t="n">
-        <v>98636</v>
+        <v>57723</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>569882</v>
+        <v>569714</v>
       </c>
       <c r="R80" t="n">
-        <v>6958106</v>
+        <v>6957901</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8721,6 +8711,11 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på gran ( färska spår)</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8747,10 +8742,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128731284</v>
+        <v>128732848</v>
       </c>
       <c r="B81" t="n">
-        <v>57880</v>
+        <v>57723</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8758,27 +8753,27 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="M81" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
@@ -8787,10 +8782,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>569677</v>
+        <v>569873</v>
       </c>
       <c r="R81" t="n">
-        <v>6958066</v>
+        <v>6958099</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8823,6 +8818,11 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8852,7 +8852,7 @@
         <v>128743244</v>
       </c>
       <c r="B82" t="n">
-        <v>91508</v>
+        <v>91513</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8949,7 +8949,7 @@
         <v>128731226</v>
       </c>
       <c r="B83" t="n">
-        <v>91526</v>
+        <v>91531</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9043,38 +9043,37 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128728434</v>
+        <v>128729895</v>
       </c>
       <c r="B84" t="n">
-        <v>57720</v>
+        <v>98643</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>26</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
@@ -9083,10 +9082,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>569608</v>
+        <v>569713</v>
       </c>
       <c r="R84" t="n">
-        <v>6958227</v>
+        <v>6958138</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9119,11 +9118,6 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9150,10 +9144,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128729895</v>
+        <v>128743257</v>
       </c>
       <c r="B85" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9178,21 +9172,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
+      <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>569713</v>
+        <v>569656</v>
       </c>
       <c r="R85" t="n">
-        <v>6958138</v>
+        <v>6957942</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9225,6 +9215,11 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>23 exemplar (ca)</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9251,45 +9246,50 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128743257</v>
+        <v>128728434</v>
       </c>
       <c r="B86" t="n">
-        <v>98636</v>
+        <v>57723</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P86" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>569656</v>
+        <v>569608</v>
       </c>
       <c r="R86" t="n">
-        <v>6957942</v>
+        <v>6958227</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9326,7 +9326,7 @@
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>23 exemplar (ca)</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9353,10 +9353,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128728419</v>
+        <v>128729069</v>
       </c>
       <c r="B87" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9388,10 +9388,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>569608</v>
+        <v>569699</v>
       </c>
       <c r="R87" t="n">
-        <v>6958227</v>
+        <v>6958200</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9424,11 +9424,6 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>Riklig förekomst inom området</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9455,10 +9450,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128729069</v>
+        <v>128728419</v>
       </c>
       <c r="B88" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9490,10 +9485,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>569699</v>
+        <v>569608</v>
       </c>
       <c r="R88" t="n">
-        <v>6958200</v>
+        <v>6958227</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9526,6 +9521,11 @@
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>Riklig förekomst inom området</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9555,7 +9555,7 @@
         <v>128743261</v>
       </c>
       <c r="B89" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9652,7 +9652,7 @@
         <v>128727978</v>
       </c>
       <c r="B90" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9759,7 +9759,7 @@
         <v>128729666</v>
       </c>
       <c r="B91" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9866,7 +9866,7 @@
         <v>128738599</v>
       </c>
       <c r="B92" t="n">
-        <v>80189</v>
+        <v>80094</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9963,7 +9963,7 @@
         <v>128728152</v>
       </c>
       <c r="B93" t="n">
-        <v>91508</v>
+        <v>91513</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10057,38 +10057,37 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128728274</v>
+        <v>128731648</v>
       </c>
       <c r="B94" t="n">
-        <v>57720</v>
+        <v>98643</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr"/>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>119</t>
         </is>
       </c>
       <c r="P94" t="inlineStr">
@@ -10097,10 +10096,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>569599</v>
+        <v>569766</v>
       </c>
       <c r="R94" t="n">
-        <v>6958201</v>
+        <v>6958144</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10137,7 +10136,7 @@
       </c>
       <c r="AC94" t="inlineStr">
         <is>
-          <t>Både äldre och färska ringhack på tall</t>
+          <t>Ca ( möjligtvis fler)</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10164,10 +10163,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128731648</v>
+        <v>128743253</v>
       </c>
       <c r="B95" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10192,21 +10191,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>119</t>
-        </is>
-      </c>
+      <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>569766</v>
+        <v>569641</v>
       </c>
       <c r="R95" t="n">
-        <v>6958144</v>
+        <v>6957953</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10243,7 +10238,7 @@
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>Ca ( möjligtvis fler)</t>
+          <t>55 exemplar knärötter</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10270,10 +10265,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128743253</v>
+        <v>128743256</v>
       </c>
       <c r="B96" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10305,10 +10300,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>569641</v>
+        <v>569647</v>
       </c>
       <c r="R96" t="n">
-        <v>6957953</v>
+        <v>6957950</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10345,7 +10340,7 @@
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>55 exemplar knärötter</t>
+          <t>23 exemplar</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10372,45 +10367,50 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128743256</v>
+        <v>128728274</v>
       </c>
       <c r="B97" t="n">
-        <v>98636</v>
+        <v>57723</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P97" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>569647</v>
+        <v>569599</v>
       </c>
       <c r="R97" t="n">
-        <v>6957950</v>
+        <v>6958201</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10447,7 +10447,7 @@
       </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>23 exemplar</t>
+          <t>Både äldre och färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD97" t="b">

--- a/artfynd/A 39666-2025 artfynd.xlsx
+++ b/artfynd/A 39666-2025 artfynd.xlsx
@@ -1290,10 +1290,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128730130</v>
+        <v>128729409</v>
       </c>
       <c r="B8" t="n">
-        <v>57723</v>
+        <v>91520</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1301,39 +1301,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>569713</v>
+        <v>569700</v>
       </c>
       <c r="R8" t="n">
-        <v>6958138</v>
+        <v>6958164</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1366,11 +1361,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1397,10 +1387,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128729409</v>
+        <v>128730130</v>
       </c>
       <c r="B9" t="n">
-        <v>91520</v>
+        <v>57723</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1408,34 +1398,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>569700</v>
+        <v>569713</v>
       </c>
       <c r="R9" t="n">
-        <v>6958164</v>
+        <v>6958138</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1468,6 +1463,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -2217,45 +2217,49 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128728515</v>
+        <v>128731490</v>
       </c>
       <c r="B17" t="n">
-        <v>97522</v>
+        <v>98651</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>569608</v>
+        <v>569759</v>
       </c>
       <c r="R17" t="n">
-        <v>6958227</v>
+        <v>6958118</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2314,7 +2318,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128731490</v>
+        <v>128730429</v>
       </c>
       <c r="B18" t="n">
         <v>98651</v>
@@ -2344,7 +2348,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>80</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2353,10 +2357,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>569759</v>
+        <v>569683</v>
       </c>
       <c r="R18" t="n">
-        <v>6958118</v>
+        <v>6958128</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2415,49 +2419,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128730429</v>
+        <v>128728515</v>
       </c>
       <c r="B19" t="n">
-        <v>98651</v>
+        <v>97522</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>569683</v>
+        <v>569608</v>
       </c>
       <c r="R19" t="n">
-        <v>6958128</v>
+        <v>6958227</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2516,10 +2516,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128743262</v>
+        <v>128732359</v>
       </c>
       <c r="B20" t="n">
-        <v>79034</v>
+        <v>91520</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2527,21 +2527,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2551,10 +2551,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>569732</v>
+        <v>569820</v>
       </c>
       <c r="R20" t="n">
-        <v>6957870</v>
+        <v>6958107</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2613,32 +2613,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128728022</v>
+        <v>128731612</v>
       </c>
       <c r="B21" t="n">
-        <v>91485</v>
+        <v>91520</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2648,10 +2648,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>569583</v>
+        <v>569752</v>
       </c>
       <c r="R21" t="n">
-        <v>6958204</v>
+        <v>6958091</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2919,49 +2919,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128730720</v>
+        <v>128743262</v>
       </c>
       <c r="B24" t="n">
-        <v>98651</v>
+        <v>79034</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>569692</v>
+        <v>569732</v>
       </c>
       <c r="R24" t="n">
-        <v>6958094</v>
+        <v>6957870</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2994,11 +2990,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ca</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3025,32 +3016,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128743252</v>
+        <v>128728022</v>
       </c>
       <c r="B25" t="n">
-        <v>98651</v>
+        <v>91485</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3060,10 +3051,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>569610</v>
+        <v>569583</v>
       </c>
       <c r="R25" t="n">
-        <v>6958005</v>
+        <v>6958204</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3096,11 +3087,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>2 exemplar</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3127,45 +3113,49 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128732359</v>
+        <v>128730720</v>
       </c>
       <c r="B26" t="n">
-        <v>91520</v>
+        <v>98651</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>569820</v>
+        <v>569692</v>
       </c>
       <c r="R26" t="n">
-        <v>6958107</v>
+        <v>6958094</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3198,6 +3188,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ca</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3224,32 +3219,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128731612</v>
+        <v>128743252</v>
       </c>
       <c r="B27" t="n">
-        <v>91520</v>
+        <v>98651</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3259,10 +3254,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>569752</v>
+        <v>569610</v>
       </c>
       <c r="R27" t="n">
-        <v>6958091</v>
+        <v>6958005</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3295,6 +3290,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>2 exemplar</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4654,10 +4654,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128729439</v>
+        <v>128729962</v>
       </c>
       <c r="B41" t="n">
-        <v>91520</v>
+        <v>80139</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4665,21 +4665,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4689,10 +4689,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>569703</v>
+        <v>569643</v>
       </c>
       <c r="R41" t="n">
-        <v>6958175</v>
+        <v>6958117</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4751,10 +4751,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128728473</v>
+        <v>128730475</v>
       </c>
       <c r="B42" t="n">
-        <v>57883</v>
+        <v>57723</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4762,27 +4762,27 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -4791,10 +4791,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>569608</v>
+        <v>569675</v>
       </c>
       <c r="R42" t="n">
-        <v>6958227</v>
+        <v>6958098</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4827,6 +4827,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4853,10 +4858,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128729962</v>
+        <v>128729439</v>
       </c>
       <c r="B43" t="n">
-        <v>80139</v>
+        <v>91520</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4864,21 +4869,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4888,10 +4893,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>569643</v>
+        <v>569703</v>
       </c>
       <c r="R43" t="n">
-        <v>6958117</v>
+        <v>6958175</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4950,10 +4955,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128730475</v>
+        <v>128728473</v>
       </c>
       <c r="B44" t="n">
-        <v>57723</v>
+        <v>57883</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4961,27 +4966,27 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -4990,10 +4995,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>569675</v>
+        <v>569608</v>
       </c>
       <c r="R44" t="n">
-        <v>6958098</v>
+        <v>6958227</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5026,11 +5031,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6211,50 +6211,45 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128739287</v>
+        <v>128732806</v>
       </c>
       <c r="B56" t="n">
-        <v>57723</v>
+        <v>91531</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>1205</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>569481</v>
+        <v>569827</v>
       </c>
       <c r="R56" t="n">
-        <v>6958122</v>
+        <v>6958133</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6287,11 +6282,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6318,50 +6308,45 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128730490</v>
+        <v>128732719</v>
       </c>
       <c r="B57" t="n">
-        <v>57723</v>
+        <v>91975</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>569707</v>
+        <v>569821</v>
       </c>
       <c r="R57" t="n">
-        <v>6958131</v>
+        <v>6958151</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6394,11 +6379,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Både äldre och färska spår ( Ringhack av tretåig hackspett på tall)</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6425,50 +6405,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128730422</v>
+        <v>128728592</v>
       </c>
       <c r="B58" t="n">
-        <v>57723</v>
+        <v>80174</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>569703</v>
+        <v>569604</v>
       </c>
       <c r="R58" t="n">
-        <v>6958116</v>
+        <v>6958176</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6501,11 +6476,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6532,10 +6502,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128732806</v>
+        <v>128732124</v>
       </c>
       <c r="B59" t="n">
-        <v>91531</v>
+        <v>80174</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6543,21 +6513,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1205</v>
+        <v>6463</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6567,10 +6537,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>569827</v>
+        <v>569816</v>
       </c>
       <c r="R59" t="n">
-        <v>6958133</v>
+        <v>6958081</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6629,32 +6599,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128732719</v>
+        <v>128730101</v>
       </c>
       <c r="B60" t="n">
-        <v>91975</v>
+        <v>80175</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1209</v>
+        <v>6464</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6664,10 +6634,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>569821</v>
+        <v>569630</v>
       </c>
       <c r="R60" t="n">
-        <v>6958151</v>
+        <v>6958139</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6726,10 +6696,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128728592</v>
+        <v>128731387</v>
       </c>
       <c r="B61" t="n">
-        <v>80174</v>
+        <v>80167</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6737,21 +6707,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6463</v>
+        <v>6461</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6761,10 +6731,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>569604</v>
+        <v>569740</v>
       </c>
       <c r="R61" t="n">
-        <v>6958176</v>
+        <v>6958091</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6823,10 +6793,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128732124</v>
+        <v>128730183</v>
       </c>
       <c r="B62" t="n">
-        <v>80174</v>
+        <v>80099</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6834,21 +6804,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6463</v>
+        <v>229497</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6858,10 +6828,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>569816</v>
+        <v>569630</v>
       </c>
       <c r="R62" t="n">
-        <v>6958081</v>
+        <v>6958129</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6920,45 +6890,50 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128730101</v>
+        <v>128739287</v>
       </c>
       <c r="B63" t="n">
-        <v>80175</v>
+        <v>57723</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>569630</v>
+        <v>569481</v>
       </c>
       <c r="R63" t="n">
-        <v>6958139</v>
+        <v>6958122</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6991,6 +6966,11 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7017,45 +6997,50 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128731387</v>
+        <v>128730490</v>
       </c>
       <c r="B64" t="n">
-        <v>80167</v>
+        <v>57723</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6461</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>569740</v>
+        <v>569707</v>
       </c>
       <c r="R64" t="n">
-        <v>6958091</v>
+        <v>6958131</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7088,6 +7073,11 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Både äldre och färska spår ( Ringhack av tretåig hackspett på tall)</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7114,45 +7104,50 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128730183</v>
+        <v>128730422</v>
       </c>
       <c r="B65" t="n">
-        <v>80099</v>
+        <v>57723</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>229497</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>569630</v>
+        <v>569703</v>
       </c>
       <c r="R65" t="n">
-        <v>6958129</v>
+        <v>6958116</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7185,6 +7180,11 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7502,32 +7502,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128731693</v>
+        <v>128743263</v>
       </c>
       <c r="B69" t="n">
-        <v>91520</v>
+        <v>92847</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1202</v>
+        <v>5964</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7537,10 +7537,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>569793</v>
+        <v>569517</v>
       </c>
       <c r="R69" t="n">
-        <v>6958092</v>
+        <v>6958123</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7573,6 +7573,11 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>3 exemplar</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7599,45 +7604,50 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128743263</v>
+        <v>128732493</v>
       </c>
       <c r="B70" t="n">
-        <v>92847</v>
+        <v>57723</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>5964</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>569517</v>
+        <v>569795</v>
       </c>
       <c r="R70" t="n">
-        <v>6958123</v>
+        <v>6958154</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7674,7 +7684,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>3 exemplar</t>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7701,7 +7711,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128732493</v>
+        <v>128730928</v>
       </c>
       <c r="B71" t="n">
         <v>57723</v>
@@ -7730,21 +7740,24 @@
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
       <c r="M71" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>569795</v>
+        <v>569673</v>
       </c>
       <c r="R71" t="n">
-        <v>6958154</v>
+        <v>6958076</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7781,7 +7794,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>Påbörjat bobygge av sannolikt tretåig hackspett. Ser ut att vara relativt färskt. 2 meter upp i död gran. Omkring 4,5 cm i diameter.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7808,7 +7821,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128730928</v>
+        <v>128728149</v>
       </c>
       <c r="B72" t="n">
         <v>57723</v>
@@ -7837,24 +7850,21 @@
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
       <c r="M72" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N72" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>569673</v>
+        <v>569585</v>
       </c>
       <c r="R72" t="n">
-        <v>6958076</v>
+        <v>6958190</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7891,7 +7901,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Påbörjat bobygge av sannolikt tretåig hackspett. Ser ut att vara relativt färskt. 2 meter upp i död gran. Omkring 4,5 cm i diameter.</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7918,7 +7928,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128728149</v>
+        <v>128730998</v>
       </c>
       <c r="B73" t="n">
         <v>57723</v>
@@ -7958,10 +7968,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>569585</v>
+        <v>569670</v>
       </c>
       <c r="R73" t="n">
-        <v>6958190</v>
+        <v>6958060</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7998,7 +8008,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på tall. Även äldre</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8025,10 +8035,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128730998</v>
+        <v>128731693</v>
       </c>
       <c r="B74" t="n">
-        <v>57723</v>
+        <v>91520</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8036,39 +8046,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>569670</v>
+        <v>569793</v>
       </c>
       <c r="R74" t="n">
-        <v>6958060</v>
+        <v>6958092</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8101,11 +8106,6 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Ringhack på tall. Även äldre</t>
         </is>
       </c>
       <c r="AD74" t="b">

--- a/artfynd/A 39666-2025 artfynd.xlsx
+++ b/artfynd/A 39666-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128732386</v>
+        <v>128743246</v>
       </c>
       <c r="B2" t="n">
-        <v>80139</v>
+        <v>57723</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>569785</v>
+        <v>569648</v>
       </c>
       <c r="R2" t="n">
-        <v>6958124</v>
+        <v>6957944</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,6 +746,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall ( äldre och färska spår)</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128739007</v>
+        <v>128728526</v>
       </c>
       <c r="B3" t="n">
         <v>57723</v>
@@ -812,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>569542</v>
+        <v>569616</v>
       </c>
       <c r="R3" t="n">
-        <v>6958069</v>
+        <v>6958208</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,7 +884,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128728526</v>
+        <v>128739007</v>
       </c>
       <c r="B4" t="n">
         <v>57723</v>
@@ -919,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>569616</v>
+        <v>569542</v>
       </c>
       <c r="R4" t="n">
-        <v>6958208</v>
+        <v>6958069</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128743246</v>
+        <v>128732386</v>
       </c>
       <c r="B5" t="n">
-        <v>57723</v>
+        <v>80139</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -997,21 +1002,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>569648</v>
+        <v>569785</v>
       </c>
       <c r="R5" t="n">
-        <v>6957944</v>
+        <v>6958124</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1057,11 +1062,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall ( äldre och färska spår)</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1091,7 +1091,7 @@
         <v>128728896</v>
       </c>
       <c r="B6" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
         <v>128732983</v>
       </c>
       <c r="B7" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         <v>128729409</v>
       </c>
       <c r="B8" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1497,7 +1497,7 @@
         <v>128732765</v>
       </c>
       <c r="B10" t="n">
-        <v>91805</v>
+        <v>91808</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1591,10 +1591,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128743245</v>
+        <v>128730571</v>
       </c>
       <c r="B11" t="n">
-        <v>57723</v>
+        <v>91541</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1602,21 +1602,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1626,10 +1626,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>569590</v>
+        <v>569660</v>
       </c>
       <c r="R11" t="n">
-        <v>6958014</v>
+        <v>6958074</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1662,11 +1662,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall ( färska spår)</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1800,32 +1795,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128733181</v>
+        <v>128743245</v>
       </c>
       <c r="B13" t="n">
-        <v>98568</v>
+        <v>57723</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1835,10 +1830,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>569900</v>
+        <v>569590</v>
       </c>
       <c r="R13" t="n">
-        <v>6958101</v>
+        <v>6958014</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1871,6 +1866,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall ( färska spår)</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1897,10 +1897,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128730571</v>
+        <v>128732217</v>
       </c>
       <c r="B14" t="n">
-        <v>91538</v>
+        <v>57883</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1908,34 +1908,48 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>569660</v>
+        <v>569777</v>
       </c>
       <c r="R14" t="n">
-        <v>6958074</v>
+        <v>6958189</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1968,6 +1982,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>2 talltitor kommer flygandes väldigt närgånget och varnar</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1994,59 +2013,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128732217</v>
+        <v>128733181</v>
       </c>
       <c r="B15" t="n">
-        <v>57883</v>
+        <v>98573</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>219790</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>569777</v>
+        <v>569900</v>
       </c>
       <c r="R15" t="n">
-        <v>6958189</v>
+        <v>6958101</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2079,11 +2084,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>2 talltitor kommer flygandes väldigt närgånget och varnar</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2110,50 +2110,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128731601</v>
+        <v>128728515</v>
       </c>
       <c r="B16" t="n">
-        <v>57723</v>
+        <v>97527</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>569752</v>
+        <v>569608</v>
       </c>
       <c r="R16" t="n">
-        <v>6958091</v>
+        <v>6958227</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2186,11 +2181,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2220,7 +2210,7 @@
         <v>128731490</v>
       </c>
       <c r="B17" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2321,7 +2311,7 @@
         <v>128730429</v>
       </c>
       <c r="B18" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2419,45 +2409,50 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128728515</v>
+        <v>128731601</v>
       </c>
       <c r="B19" t="n">
-        <v>97522</v>
+        <v>57723</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>569608</v>
+        <v>569752</v>
       </c>
       <c r="R19" t="n">
-        <v>6958227</v>
+        <v>6958091</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2490,6 +2485,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2516,45 +2516,49 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128732359</v>
+        <v>128730720</v>
       </c>
       <c r="B20" t="n">
-        <v>91520</v>
+        <v>98656</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>569820</v>
+        <v>569692</v>
       </c>
       <c r="R20" t="n">
-        <v>6958107</v>
+        <v>6958094</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2587,6 +2591,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ca</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2613,32 +2622,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128731612</v>
+        <v>128743252</v>
       </c>
       <c r="B21" t="n">
-        <v>91520</v>
+        <v>98656</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2648,10 +2657,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>569752</v>
+        <v>569610</v>
       </c>
       <c r="R21" t="n">
-        <v>6958091</v>
+        <v>6958005</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2684,6 +2693,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>2 exemplar</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2710,10 +2724,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128739020</v>
+        <v>128731107</v>
       </c>
       <c r="B22" t="n">
-        <v>57723</v>
+        <v>57883</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2721,27 +2735,27 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2750,10 +2764,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>569542</v>
+        <v>569705</v>
       </c>
       <c r="R22" t="n">
-        <v>6958049</v>
+        <v>6958098</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2786,11 +2800,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2817,10 +2826,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128731107</v>
+        <v>128732359</v>
       </c>
       <c r="B23" t="n">
-        <v>57883</v>
+        <v>91523</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2828,39 +2837,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>569705</v>
+        <v>569820</v>
       </c>
       <c r="R23" t="n">
-        <v>6958098</v>
+        <v>6958107</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2919,10 +2923,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128743262</v>
+        <v>128731612</v>
       </c>
       <c r="B24" t="n">
-        <v>79034</v>
+        <v>91523</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2930,21 +2934,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2954,10 +2958,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>569732</v>
+        <v>569752</v>
       </c>
       <c r="R24" t="n">
-        <v>6957870</v>
+        <v>6958091</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3019,7 +3023,7 @@
         <v>128728022</v>
       </c>
       <c r="B25" t="n">
-        <v>91485</v>
+        <v>91488</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3113,49 +3117,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128730720</v>
+        <v>128743262</v>
       </c>
       <c r="B26" t="n">
-        <v>98651</v>
+        <v>79034</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>569692</v>
+        <v>569732</v>
       </c>
       <c r="R26" t="n">
-        <v>6958094</v>
+        <v>6957870</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3188,11 +3188,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ca</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3219,45 +3214,50 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128743252</v>
+        <v>128739020</v>
       </c>
       <c r="B27" t="n">
-        <v>98651</v>
+        <v>57723</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>569610</v>
+        <v>569542</v>
       </c>
       <c r="R27" t="n">
-        <v>6958005</v>
+        <v>6958049</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3294,7 +3294,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>2 exemplar</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3321,45 +3321,50 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128729068</v>
+        <v>128731291</v>
       </c>
       <c r="B28" t="n">
-        <v>80168</v>
+        <v>57723</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>569604</v>
+        <v>569726</v>
       </c>
       <c r="R28" t="n">
-        <v>6958176</v>
+        <v>6958097</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3392,6 +3397,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på tall</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3418,7 +3428,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128731291</v>
+        <v>128728019</v>
       </c>
       <c r="B29" t="n">
         <v>57723</v>
@@ -3458,10 +3468,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>569726</v>
+        <v>569577</v>
       </c>
       <c r="R29" t="n">
-        <v>6958097</v>
+        <v>6958213</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3498,7 +3508,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på tall</t>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3525,50 +3535,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128728019</v>
+        <v>128729068</v>
       </c>
       <c r="B30" t="n">
-        <v>57723</v>
+        <v>80168</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>569577</v>
+        <v>569604</v>
       </c>
       <c r="R30" t="n">
-        <v>6958213</v>
+        <v>6958176</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3601,11 +3606,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3635,7 +3635,7 @@
         <v>128731489</v>
       </c>
       <c r="B31" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3736,7 +3736,7 @@
         <v>128728767</v>
       </c>
       <c r="B32" t="n">
-        <v>92811</v>
+        <v>92816</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3844,10 +3844,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128730603</v>
+        <v>128730513</v>
       </c>
       <c r="B33" t="n">
-        <v>57723</v>
+        <v>80139</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3855,39 +3855,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>569738</v>
+        <v>569656</v>
       </c>
       <c r="R33" t="n">
-        <v>6958117</v>
+        <v>6958093</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3920,11 +3915,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Äldre exemplar av ringhack på Tall från tretåig hackspett</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3951,10 +3941,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128730513</v>
+        <v>128730603</v>
       </c>
       <c r="B34" t="n">
-        <v>80139</v>
+        <v>57723</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3962,34 +3952,39 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>569656</v>
+        <v>569738</v>
       </c>
       <c r="R34" t="n">
-        <v>6958093</v>
+        <v>6958117</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4022,6 +4017,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Äldre exemplar av ringhack på Tall från tretåig hackspett</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4048,10 +4048,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128728318</v>
+        <v>128729745</v>
       </c>
       <c r="B35" t="n">
-        <v>79034</v>
+        <v>57723</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4059,34 +4059,39 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>569616</v>
+        <v>569694</v>
       </c>
       <c r="R35" t="n">
-        <v>6958208</v>
+        <v>6958144</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4119,6 +4124,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4145,45 +4155,49 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128731677</v>
+        <v>128732677</v>
       </c>
       <c r="B36" t="n">
-        <v>79034</v>
+        <v>98656</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>569769</v>
+        <v>569817</v>
       </c>
       <c r="R36" t="n">
-        <v>6958153</v>
+        <v>6958134</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4242,10 +4256,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128732677</v>
+        <v>128743255</v>
       </c>
       <c r="B37" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4270,21 +4284,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>569817</v>
+        <v>569613</v>
       </c>
       <c r="R37" t="n">
-        <v>6958134</v>
+        <v>6957995</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4317,6 +4327,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>28 exemplar knärot</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4343,32 +4358,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128743255</v>
+        <v>128728318</v>
       </c>
       <c r="B38" t="n">
-        <v>98651</v>
+        <v>79034</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4378,10 +4393,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>569613</v>
+        <v>569616</v>
       </c>
       <c r="R38" t="n">
-        <v>6957995</v>
+        <v>6958208</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4414,11 +4429,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>28 exemplar knärot</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4445,32 +4455,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128743254</v>
+        <v>128731677</v>
       </c>
       <c r="B39" t="n">
-        <v>98651</v>
+        <v>79034</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4480,10 +4490,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>569547</v>
+        <v>569769</v>
       </c>
       <c r="R39" t="n">
-        <v>6958078</v>
+        <v>6958153</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4516,11 +4526,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>20 (ca) exemplar</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4547,50 +4552,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128729745</v>
+        <v>128743254</v>
       </c>
       <c r="B40" t="n">
-        <v>57723</v>
+        <v>98656</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>569694</v>
+        <v>569547</v>
       </c>
       <c r="R40" t="n">
-        <v>6958144</v>
+        <v>6958078</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4627,7 +4627,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>20 (ca) exemplar</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4654,10 +4654,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128729962</v>
+        <v>128728473</v>
       </c>
       <c r="B41" t="n">
-        <v>80139</v>
+        <v>57883</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4665,34 +4665,39 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>569643</v>
+        <v>569608</v>
       </c>
       <c r="R41" t="n">
-        <v>6958117</v>
+        <v>6958227</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4751,10 +4756,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128730475</v>
+        <v>128729439</v>
       </c>
       <c r="B42" t="n">
-        <v>57723</v>
+        <v>91523</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4762,39 +4767,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>569675</v>
+        <v>569703</v>
       </c>
       <c r="R42" t="n">
-        <v>6958098</v>
+        <v>6958175</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4827,11 +4827,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4858,10 +4853,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128729439</v>
+        <v>128730475</v>
       </c>
       <c r="B43" t="n">
-        <v>91520</v>
+        <v>57723</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4869,34 +4864,39 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>569703</v>
+        <v>569675</v>
       </c>
       <c r="R43" t="n">
-        <v>6958175</v>
+        <v>6958098</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4929,6 +4929,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4955,10 +4960,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128728473</v>
+        <v>128729962</v>
       </c>
       <c r="B44" t="n">
-        <v>57883</v>
+        <v>80139</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4966,39 +4971,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>569608</v>
+        <v>569643</v>
       </c>
       <c r="R44" t="n">
-        <v>6958227</v>
+        <v>6958117</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5057,7 +5057,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128731799</v>
+        <v>128728902</v>
       </c>
       <c r="B45" t="n">
         <v>57723</v>
@@ -5088,7 +5088,7 @@
       <c r="I45" t="inlineStr"/>
       <c r="M45" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -5097,10 +5097,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>569774</v>
+        <v>569673</v>
       </c>
       <c r="R45" t="n">
-        <v>6958163</v>
+        <v>6958225</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5164,7 +5164,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128732015</v>
+        <v>128731799</v>
       </c>
       <c r="B46" t="n">
         <v>57723</v>
@@ -5195,7 +5195,7 @@
       <c r="I46" t="inlineStr"/>
       <c r="M46" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -5204,10 +5204,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>569816</v>
+        <v>569774</v>
       </c>
       <c r="R46" t="n">
-        <v>6958081</v>
+        <v>6958163</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5244,7 +5244,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5271,7 +5271,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128738187</v>
+        <v>128732015</v>
       </c>
       <c r="B47" t="n">
         <v>57723</v>
@@ -5311,10 +5311,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>569681</v>
+        <v>569816</v>
       </c>
       <c r="R47" t="n">
-        <v>6957939</v>
+        <v>6958081</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5378,7 +5378,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128728902</v>
+        <v>128738187</v>
       </c>
       <c r="B48" t="n">
         <v>57723</v>
@@ -5418,10 +5418,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>569673</v>
+        <v>569681</v>
       </c>
       <c r="R48" t="n">
-        <v>6958225</v>
+        <v>6957939</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5458,7 +5458,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5488,7 +5488,7 @@
         <v>128732627</v>
       </c>
       <c r="B49" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5594,7 +5594,7 @@
         <v>128728348</v>
       </c>
       <c r="B50" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5695,7 +5695,7 @@
         <v>128729573</v>
       </c>
       <c r="B51" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5890,7 +5890,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128738306</v>
+        <v>128731037</v>
       </c>
       <c r="B53" t="n">
         <v>57723</v>
@@ -5921,7 +5921,7 @@
       <c r="I53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -5930,10 +5930,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>569644</v>
+        <v>569673</v>
       </c>
       <c r="R53" t="n">
-        <v>6957965</v>
+        <v>6958037</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5997,7 +5997,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128732183</v>
+        <v>128738306</v>
       </c>
       <c r="B54" t="n">
         <v>57723</v>
@@ -6037,10 +6037,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>569777</v>
+        <v>569644</v>
       </c>
       <c r="R54" t="n">
-        <v>6958189</v>
+        <v>6957965</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6077,7 +6077,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6104,7 +6104,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128731037</v>
+        <v>128732183</v>
       </c>
       <c r="B55" t="n">
         <v>57723</v>
@@ -6135,7 +6135,7 @@
       <c r="I55" t="inlineStr"/>
       <c r="M55" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -6144,10 +6144,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>569673</v>
+        <v>569777</v>
       </c>
       <c r="R55" t="n">
-        <v>6958037</v>
+        <v>6958189</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6184,7 +6184,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6214,7 +6214,7 @@
         <v>128732806</v>
       </c>
       <c r="B56" t="n">
-        <v>91531</v>
+        <v>91534</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6311,7 +6311,7 @@
         <v>128732719</v>
       </c>
       <c r="B57" t="n">
-        <v>91975</v>
+        <v>91978</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6793,45 +6793,50 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128730183</v>
+        <v>128730490</v>
       </c>
       <c r="B62" t="n">
-        <v>80099</v>
+        <v>57723</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>229497</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>569630</v>
+        <v>569707</v>
       </c>
       <c r="R62" t="n">
-        <v>6958129</v>
+        <v>6958131</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6864,6 +6869,11 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Både äldre och färska spår ( Ringhack av tretåig hackspett på tall)</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6890,7 +6900,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128739287</v>
+        <v>128730422</v>
       </c>
       <c r="B63" t="n">
         <v>57723</v>
@@ -6930,10 +6940,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>569481</v>
+        <v>569703</v>
       </c>
       <c r="R63" t="n">
-        <v>6958122</v>
+        <v>6958116</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6970,7 +6980,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6997,7 +7007,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128730490</v>
+        <v>128739287</v>
       </c>
       <c r="B64" t="n">
         <v>57723</v>
@@ -7037,10 +7047,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>569707</v>
+        <v>569481</v>
       </c>
       <c r="R64" t="n">
-        <v>6958131</v>
+        <v>6958122</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7077,7 +7087,7 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Både äldre och färska spår ( Ringhack av tretåig hackspett på tall)</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7104,50 +7114,45 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128730422</v>
+        <v>128730183</v>
       </c>
       <c r="B65" t="n">
-        <v>57723</v>
+        <v>80099</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>229497</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>569703</v>
+        <v>569630</v>
       </c>
       <c r="R65" t="n">
-        <v>6958116</v>
+        <v>6958129</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7180,11 +7185,6 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7211,10 +7211,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128730273</v>
+        <v>128729077</v>
       </c>
       <c r="B66" t="n">
-        <v>79034</v>
+        <v>80139</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7222,21 +7222,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7246,10 +7246,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>569692</v>
+        <v>569604</v>
       </c>
       <c r="R66" t="n">
-        <v>6958127</v>
+        <v>6958176</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7308,10 +7308,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128732112</v>
+        <v>128730273</v>
       </c>
       <c r="B67" t="n">
-        <v>80139</v>
+        <v>79034</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7319,21 +7319,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7343,10 +7343,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>569824</v>
+        <v>569692</v>
       </c>
       <c r="R67" t="n">
-        <v>6958091</v>
+        <v>6958127</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7405,7 +7405,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128729077</v>
+        <v>128732112</v>
       </c>
       <c r="B68" t="n">
         <v>80139</v>
@@ -7440,10 +7440,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>569604</v>
+        <v>569824</v>
       </c>
       <c r="R68" t="n">
-        <v>6958176</v>
+        <v>6958091</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7502,32 +7502,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128743263</v>
+        <v>128731693</v>
       </c>
       <c r="B69" t="n">
-        <v>92847</v>
+        <v>91523</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>5964</v>
+        <v>1202</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7537,10 +7537,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>569517</v>
+        <v>569793</v>
       </c>
       <c r="R69" t="n">
-        <v>6958123</v>
+        <v>6958092</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7573,11 +7573,6 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>3 exemplar</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7604,50 +7599,45 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128732493</v>
+        <v>128743263</v>
       </c>
       <c r="B70" t="n">
-        <v>57723</v>
+        <v>92852</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>5964</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>569795</v>
+        <v>569517</v>
       </c>
       <c r="R70" t="n">
-        <v>6958154</v>
+        <v>6958123</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7684,7 +7674,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>3 exemplar</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7711,7 +7701,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128730928</v>
+        <v>128728149</v>
       </c>
       <c r="B71" t="n">
         <v>57723</v>
@@ -7740,24 +7730,21 @@
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
       <c r="M71" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N71" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>569673</v>
+        <v>569585</v>
       </c>
       <c r="R71" t="n">
-        <v>6958076</v>
+        <v>6958190</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7794,7 +7781,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Påbörjat bobygge av sannolikt tretåig hackspett. Ser ut att vara relativt färskt. 2 meter upp i död gran. Omkring 4,5 cm i diameter.</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7821,7 +7808,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128728149</v>
+        <v>128732493</v>
       </c>
       <c r="B72" t="n">
         <v>57723</v>
@@ -7861,10 +7848,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>569585</v>
+        <v>569795</v>
       </c>
       <c r="R72" t="n">
-        <v>6958190</v>
+        <v>6958154</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7901,7 +7888,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8035,10 +8022,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128731693</v>
+        <v>128730928</v>
       </c>
       <c r="B74" t="n">
-        <v>91520</v>
+        <v>57723</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8046,34 +8033,42 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>569793</v>
+        <v>569673</v>
       </c>
       <c r="R74" t="n">
-        <v>6958092</v>
+        <v>6958076</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8106,6 +8101,11 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Påbörjat bobygge av sannolikt tretåig hackspett. Ser ut att vara relativt färskt. 2 meter upp i död gran. Omkring 4,5 cm i diameter.</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8132,49 +8132,45 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128732718</v>
+        <v>128743247</v>
       </c>
       <c r="B75" t="n">
-        <v>98651</v>
+        <v>57723</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>569834</v>
+        <v>569714</v>
       </c>
       <c r="R75" t="n">
-        <v>6958143</v>
+        <v>6957901</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8207,6 +8203,11 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på gran ( färska spår)</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8233,37 +8234,38 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128733005</v>
+        <v>128732848</v>
       </c>
       <c r="B76" t="n">
-        <v>98651</v>
+        <v>57723</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>7</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
@@ -8272,10 +8274,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>569882</v>
+        <v>569873</v>
       </c>
       <c r="R76" t="n">
-        <v>6958106</v>
+        <v>6958099</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8308,6 +8310,11 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8337,7 +8344,7 @@
         <v>128731100</v>
       </c>
       <c r="B77" t="n">
-        <v>91538</v>
+        <v>91541</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8431,10 +8438,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128732848</v>
+        <v>128731284</v>
       </c>
       <c r="B78" t="n">
-        <v>57723</v>
+        <v>57883</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8442,27 +8449,27 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="M78" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
@@ -8471,10 +8478,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>569873</v>
+        <v>569677</v>
       </c>
       <c r="R78" t="n">
-        <v>6958099</v>
+        <v>6958066</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8507,11 +8514,6 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8538,45 +8540,49 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128743247</v>
+        <v>128732718</v>
       </c>
       <c r="B79" t="n">
-        <v>57723</v>
+        <v>98656</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>569714</v>
+        <v>569834</v>
       </c>
       <c r="R79" t="n">
-        <v>6957901</v>
+        <v>6958143</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8609,11 +8615,6 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på gran ( färska spår)</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8640,38 +8641,37 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128731284</v>
+        <v>128733005</v>
       </c>
       <c r="B80" t="n">
-        <v>57883</v>
+        <v>98656</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>7</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
@@ -8680,10 +8680,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>569677</v>
+        <v>569882</v>
       </c>
       <c r="R80" t="n">
-        <v>6958066</v>
+        <v>6958106</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8742,10 +8742,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128743244</v>
+        <v>128731226</v>
       </c>
       <c r="B81" t="n">
-        <v>91520</v>
+        <v>91541</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8753,21 +8753,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8777,10 +8777,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>569736</v>
+        <v>569705</v>
       </c>
       <c r="R81" t="n">
-        <v>6957867</v>
+        <v>6958098</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8839,10 +8839,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128731226</v>
+        <v>128743244</v>
       </c>
       <c r="B82" t="n">
-        <v>91538</v>
+        <v>91523</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8850,21 +8850,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8874,10 +8874,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>569705</v>
+        <v>569736</v>
       </c>
       <c r="R82" t="n">
-        <v>6958098</v>
+        <v>6957867</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9046,7 +9046,7 @@
         <v>128729895</v>
       </c>
       <c r="B84" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9147,7 +9147,7 @@
         <v>128743257</v>
       </c>
       <c r="B85" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9246,7 +9246,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128729069</v>
+        <v>128728419</v>
       </c>
       <c r="B86" t="n">
         <v>79034</v>
@@ -9281,10 +9281,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>569699</v>
+        <v>569608</v>
       </c>
       <c r="R86" t="n">
-        <v>6958200</v>
+        <v>6958227</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9317,6 +9317,11 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>Riklig förekomst inom området</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9343,10 +9348,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128728419</v>
+        <v>128727978</v>
       </c>
       <c r="B87" t="n">
-        <v>79034</v>
+        <v>57723</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9354,34 +9359,39 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>569608</v>
+        <v>569564</v>
       </c>
       <c r="R87" t="n">
-        <v>6958227</v>
+        <v>6958213</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9418,7 +9428,7 @@
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>Riklig förekomst inom området</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9445,10 +9455,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128743261</v>
+        <v>128729666</v>
       </c>
       <c r="B88" t="n">
-        <v>79034</v>
+        <v>57723</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9456,34 +9466,39 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>569495</v>
+        <v>569706</v>
       </c>
       <c r="R88" t="n">
-        <v>6958117</v>
+        <v>6958159</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9516,6 +9531,11 @@
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9542,10 +9562,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128729666</v>
+        <v>128729069</v>
       </c>
       <c r="B89" t="n">
-        <v>57723</v>
+        <v>79034</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9553,39 +9573,34 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P89" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>569706</v>
+        <v>569699</v>
       </c>
       <c r="R89" t="n">
-        <v>6958159</v>
+        <v>6958200</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9618,11 +9633,6 @@
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9649,10 +9659,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128727978</v>
+        <v>128743261</v>
       </c>
       <c r="B90" t="n">
-        <v>57723</v>
+        <v>79034</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9660,39 +9670,34 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P90" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>569564</v>
+        <v>569495</v>
       </c>
       <c r="R90" t="n">
-        <v>6958213</v>
+        <v>6958117</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9725,11 +9730,6 @@
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9853,45 +9853,49 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128728152</v>
+        <v>128731648</v>
       </c>
       <c r="B92" t="n">
-        <v>91520</v>
+        <v>98656</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>569577</v>
+        <v>569766</v>
       </c>
       <c r="R92" t="n">
-        <v>6958213</v>
+        <v>6958144</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9924,6 +9928,11 @@
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>Ca ( möjligtvis fler)</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -9950,10 +9959,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128731648</v>
+        <v>128743253</v>
       </c>
       <c r="B93" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9978,21 +9987,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>119</t>
-        </is>
-      </c>
+      <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>569766</v>
+        <v>569641</v>
       </c>
       <c r="R93" t="n">
-        <v>6958144</v>
+        <v>6957953</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10029,7 +10034,7 @@
       </c>
       <c r="AC93" t="inlineStr">
         <is>
-          <t>Ca ( möjligtvis fler)</t>
+          <t>55 exemplar knärötter</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10056,10 +10061,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128743253</v>
+        <v>128743256</v>
       </c>
       <c r="B94" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10091,10 +10096,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>569641</v>
+        <v>569647</v>
       </c>
       <c r="R94" t="n">
-        <v>6957953</v>
+        <v>6957950</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10131,7 +10136,7 @@
       </c>
       <c r="AC94" t="inlineStr">
         <is>
-          <t>55 exemplar knärötter</t>
+          <t>23 exemplar</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10158,32 +10163,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128743256</v>
+        <v>128728152</v>
       </c>
       <c r="B95" t="n">
-        <v>98651</v>
+        <v>91523</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10193,10 +10198,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>569647</v>
+        <v>569577</v>
       </c>
       <c r="R95" t="n">
-        <v>6957950</v>
+        <v>6958213</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10229,11 +10234,6 @@
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>23 exemplar</t>
         </is>
       </c>
       <c r="AD95" t="b">

--- a/artfynd/A 39666-2025 artfynd.xlsx
+++ b/artfynd/A 39666-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128743246</v>
+        <v>128732386</v>
       </c>
       <c r="B2" t="n">
-        <v>57723</v>
+        <v>80140</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>569648</v>
+        <v>569785</v>
       </c>
       <c r="R2" t="n">
-        <v>6957944</v>
+        <v>6958124</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall ( äldre och färska spår)</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -991,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128732386</v>
+        <v>128743246</v>
       </c>
       <c r="B5" t="n">
-        <v>80139</v>
+        <v>57723</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1002,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>569785</v>
+        <v>569648</v>
       </c>
       <c r="R5" t="n">
-        <v>6958124</v>
+        <v>6957944</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1062,6 +1057,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall ( äldre och färska spår)</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1091,7 +1091,7 @@
         <v>128728896</v>
       </c>
       <c r="B6" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
         <v>128732983</v>
       </c>
       <c r="B7" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1290,10 +1290,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128729409</v>
+        <v>128730130</v>
       </c>
       <c r="B8" t="n">
-        <v>91523</v>
+        <v>57723</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1301,34 +1301,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>569700</v>
+        <v>569713</v>
       </c>
       <c r="R8" t="n">
-        <v>6958164</v>
+        <v>6958138</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1361,6 +1366,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1387,10 +1397,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128730130</v>
+        <v>128729409</v>
       </c>
       <c r="B9" t="n">
-        <v>57723</v>
+        <v>91526</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1398,39 +1408,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>569713</v>
+        <v>569700</v>
       </c>
       <c r="R9" t="n">
-        <v>6958138</v>
+        <v>6958164</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1463,11 +1468,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1497,7 +1497,7 @@
         <v>128732765</v>
       </c>
       <c r="B10" t="n">
-        <v>91808</v>
+        <v>91811</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1594,7 +1594,7 @@
         <v>128730571</v>
       </c>
       <c r="B11" t="n">
-        <v>91541</v>
+        <v>91544</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2016,7 +2016,7 @@
         <v>128733181</v>
       </c>
       <c r="B15" t="n">
-        <v>98573</v>
+        <v>98576</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2110,45 +2110,49 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128728515</v>
+        <v>128731490</v>
       </c>
       <c r="B16" t="n">
-        <v>97527</v>
+        <v>98659</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>569608</v>
+        <v>569759</v>
       </c>
       <c r="R16" t="n">
-        <v>6958227</v>
+        <v>6958118</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2207,10 +2211,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128731490</v>
+        <v>128730429</v>
       </c>
       <c r="B17" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2237,7 +2241,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>80</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2246,10 +2250,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>569759</v>
+        <v>569683</v>
       </c>
       <c r="R17" t="n">
-        <v>6958118</v>
+        <v>6958128</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2308,37 +2312,38 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128730429</v>
+        <v>128731601</v>
       </c>
       <c r="B18" t="n">
-        <v>98656</v>
+        <v>57723</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>80</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2347,10 +2352,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>569683</v>
+        <v>569752</v>
       </c>
       <c r="R18" t="n">
-        <v>6958128</v>
+        <v>6958091</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2383,6 +2388,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2409,50 +2419,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128731601</v>
+        <v>128728515</v>
       </c>
       <c r="B19" t="n">
-        <v>57723</v>
+        <v>97530</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>569752</v>
+        <v>569608</v>
       </c>
       <c r="R19" t="n">
-        <v>6958091</v>
+        <v>6958227</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2485,11 +2490,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2519,7 +2519,7 @@
         <v>128730720</v>
       </c>
       <c r="B20" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2625,7 +2625,7 @@
         <v>128743252</v>
       </c>
       <c r="B21" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2724,50 +2724,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128731107</v>
+        <v>128728022</v>
       </c>
       <c r="B22" t="n">
-        <v>57883</v>
+        <v>91491</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103021</v>
+        <v>5447</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>569705</v>
+        <v>569583</v>
       </c>
       <c r="R22" t="n">
-        <v>6958098</v>
+        <v>6958204</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2826,10 +2821,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128732359</v>
+        <v>128739020</v>
       </c>
       <c r="B23" t="n">
-        <v>91523</v>
+        <v>57723</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2837,34 +2832,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>569820</v>
+        <v>569542</v>
       </c>
       <c r="R23" t="n">
-        <v>6958107</v>
+        <v>6958049</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2897,6 +2897,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2923,10 +2928,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128731612</v>
+        <v>128732359</v>
       </c>
       <c r="B24" t="n">
-        <v>91523</v>
+        <v>91526</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2958,10 +2963,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>569752</v>
+        <v>569820</v>
       </c>
       <c r="R24" t="n">
-        <v>6958091</v>
+        <v>6958107</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3020,32 +3025,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128728022</v>
+        <v>128731612</v>
       </c>
       <c r="B25" t="n">
-        <v>91488</v>
+        <v>91526</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3055,10 +3060,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>569583</v>
+        <v>569752</v>
       </c>
       <c r="R25" t="n">
-        <v>6958204</v>
+        <v>6958091</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3120,7 +3125,7 @@
         <v>128743262</v>
       </c>
       <c r="B26" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3214,10 +3219,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128739020</v>
+        <v>128731107</v>
       </c>
       <c r="B27" t="n">
-        <v>57723</v>
+        <v>57883</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3225,27 +3230,27 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3254,10 +3259,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>569542</v>
+        <v>569705</v>
       </c>
       <c r="R27" t="n">
-        <v>6958049</v>
+        <v>6958098</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3290,11 +3295,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3321,38 +3321,37 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128731291</v>
+        <v>128731489</v>
       </c>
       <c r="B28" t="n">
-        <v>57723</v>
+        <v>98659</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>45</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3361,10 +3360,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>569726</v>
+        <v>569752</v>
       </c>
       <c r="R28" t="n">
-        <v>6958097</v>
+        <v>6958091</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3397,11 +3396,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på tall</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3428,50 +3422,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128728019</v>
+        <v>128729068</v>
       </c>
       <c r="B29" t="n">
-        <v>57723</v>
+        <v>80169</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>569577</v>
+        <v>569604</v>
       </c>
       <c r="R29" t="n">
-        <v>6958213</v>
+        <v>6958176</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3504,11 +3493,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3535,45 +3519,50 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128729068</v>
+        <v>128731291</v>
       </c>
       <c r="B30" t="n">
-        <v>80168</v>
+        <v>57723</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>569604</v>
+        <v>569726</v>
       </c>
       <c r="R30" t="n">
-        <v>6958176</v>
+        <v>6958097</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3606,6 +3595,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på tall</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3632,37 +3626,38 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128731489</v>
+        <v>128728019</v>
       </c>
       <c r="B31" t="n">
-        <v>98656</v>
+        <v>57723</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>45</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -3671,10 +3666,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>569752</v>
+        <v>569577</v>
       </c>
       <c r="R31" t="n">
-        <v>6958091</v>
+        <v>6958213</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3707,6 +3702,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3733,54 +3733,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128728767</v>
+        <v>128730513</v>
       </c>
       <c r="B32" t="n">
-        <v>92816</v>
+        <v>80140</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>569639</v>
+        <v>569656</v>
       </c>
       <c r="R32" t="n">
-        <v>6958231</v>
+        <v>6958093</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3813,11 +3804,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>4 äldre ett färskt års exemplar</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3844,10 +3830,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128730513</v>
+        <v>128730603</v>
       </c>
       <c r="B33" t="n">
-        <v>80139</v>
+        <v>57723</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3855,34 +3841,39 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>569656</v>
+        <v>569738</v>
       </c>
       <c r="R33" t="n">
-        <v>6958093</v>
+        <v>6958117</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3915,6 +3906,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Äldre exemplar av ringhack på Tall från tretåig hackspett</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3941,38 +3937,42 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128730603</v>
+        <v>128728767</v>
       </c>
       <c r="B34" t="n">
-        <v>57723</v>
+        <v>92819</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -3981,10 +3981,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>569738</v>
+        <v>569639</v>
       </c>
       <c r="R34" t="n">
-        <v>6958117</v>
+        <v>6958231</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4021,7 +4021,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Äldre exemplar av ringhack på Tall från tretåig hackspett</t>
+          <t>4 äldre ett färskt års exemplar</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4048,38 +4048,37 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128729745</v>
+        <v>128732677</v>
       </c>
       <c r="B35" t="n">
-        <v>57723</v>
+        <v>98659</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>12</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4088,10 +4087,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>569694</v>
+        <v>569817</v>
       </c>
       <c r="R35" t="n">
-        <v>6958144</v>
+        <v>6958134</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4124,11 +4123,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4155,10 +4149,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128732677</v>
+        <v>128743255</v>
       </c>
       <c r="B36" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4183,21 +4177,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>569817</v>
+        <v>569613</v>
       </c>
       <c r="R36" t="n">
-        <v>6958134</v>
+        <v>6957995</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4230,6 +4220,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>28 exemplar knärot</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4256,10 +4251,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128743255</v>
+        <v>128743254</v>
       </c>
       <c r="B37" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4291,10 +4286,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>569613</v>
+        <v>569547</v>
       </c>
       <c r="R37" t="n">
-        <v>6957995</v>
+        <v>6958078</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4331,7 +4326,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>28 exemplar knärot</t>
+          <t>20 (ca) exemplar</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4361,7 +4356,7 @@
         <v>128728318</v>
       </c>
       <c r="B38" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4458,7 +4453,7 @@
         <v>128731677</v>
       </c>
       <c r="B39" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4552,45 +4547,50 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128743254</v>
+        <v>128729745</v>
       </c>
       <c r="B40" t="n">
-        <v>98656</v>
+        <v>57723</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>569547</v>
+        <v>569694</v>
       </c>
       <c r="R40" t="n">
-        <v>6958078</v>
+        <v>6958144</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4627,7 +4627,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>20 (ca) exemplar</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4654,10 +4654,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128728473</v>
+        <v>128729439</v>
       </c>
       <c r="B41" t="n">
-        <v>57883</v>
+        <v>91526</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4665,39 +4665,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>569608</v>
+        <v>569703</v>
       </c>
       <c r="R41" t="n">
-        <v>6958227</v>
+        <v>6958175</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4756,10 +4751,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128729439</v>
+        <v>128729962</v>
       </c>
       <c r="B42" t="n">
-        <v>91523</v>
+        <v>80140</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4767,21 +4762,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4791,10 +4786,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>569703</v>
+        <v>569643</v>
       </c>
       <c r="R42" t="n">
-        <v>6958175</v>
+        <v>6958117</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4960,10 +4955,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128729962</v>
+        <v>128728473</v>
       </c>
       <c r="B44" t="n">
-        <v>80139</v>
+        <v>57883</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4971,34 +4966,39 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>569643</v>
+        <v>569608</v>
       </c>
       <c r="R44" t="n">
-        <v>6958117</v>
+        <v>6958227</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5057,38 +5057,37 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128728902</v>
+        <v>128732627</v>
       </c>
       <c r="B45" t="n">
-        <v>57723</v>
+        <v>98659</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>6</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -5097,10 +5096,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>569673</v>
+        <v>569821</v>
       </c>
       <c r="R45" t="n">
-        <v>6958225</v>
+        <v>6958151</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5137,7 +5136,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>Kan finnas mer I blåbärsriset och mossan</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5164,38 +5163,37 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128731799</v>
+        <v>128728348</v>
       </c>
       <c r="B46" t="n">
-        <v>57723</v>
+        <v>98659</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>300</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -5204,10 +5202,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>569774</v>
+        <v>569616</v>
       </c>
       <c r="R46" t="n">
-        <v>6958163</v>
+        <v>6958208</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5240,11 +5238,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5271,7 +5264,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128732015</v>
+        <v>128728902</v>
       </c>
       <c r="B47" t="n">
         <v>57723</v>
@@ -5311,10 +5304,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>569816</v>
+        <v>569673</v>
       </c>
       <c r="R47" t="n">
-        <v>6958081</v>
+        <v>6958225</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5351,7 +5344,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5378,7 +5371,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128738187</v>
+        <v>128731799</v>
       </c>
       <c r="B48" t="n">
         <v>57723</v>
@@ -5409,7 +5402,7 @@
       <c r="I48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -5418,10 +5411,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>569681</v>
+        <v>569774</v>
       </c>
       <c r="R48" t="n">
-        <v>6957939</v>
+        <v>6958163</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5458,7 +5451,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5485,37 +5478,38 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128732627</v>
+        <v>128732015</v>
       </c>
       <c r="B49" t="n">
-        <v>98656</v>
+        <v>57723</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>6</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -5524,10 +5518,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>569821</v>
+        <v>569816</v>
       </c>
       <c r="R49" t="n">
-        <v>6958151</v>
+        <v>6958081</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5564,7 +5558,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Kan finnas mer I blåbärsriset och mossan</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5591,37 +5585,38 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128728348</v>
+        <v>128738187</v>
       </c>
       <c r="B50" t="n">
-        <v>98656</v>
+        <v>57723</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>300</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -5630,10 +5625,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>569616</v>
+        <v>569681</v>
       </c>
       <c r="R50" t="n">
-        <v>6958208</v>
+        <v>6957939</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5666,6 +5661,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5695,7 +5695,7 @@
         <v>128729573</v>
       </c>
       <c r="B51" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5796,7 +5796,7 @@
         <v>128731302</v>
       </c>
       <c r="B52" t="n">
-        <v>80099</v>
+        <v>80100</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6211,10 +6211,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128732806</v>
+        <v>128728592</v>
       </c>
       <c r="B56" t="n">
-        <v>91534</v>
+        <v>80175</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6222,21 +6222,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1205</v>
+        <v>6463</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6246,10 +6246,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>569827</v>
+        <v>569604</v>
       </c>
       <c r="R56" t="n">
-        <v>6958133</v>
+        <v>6958176</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6308,32 +6308,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128732719</v>
+        <v>128732124</v>
       </c>
       <c r="B57" t="n">
-        <v>91978</v>
+        <v>80175</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1209</v>
+        <v>6463</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6343,10 +6343,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>569821</v>
+        <v>569816</v>
       </c>
       <c r="R57" t="n">
-        <v>6958151</v>
+        <v>6958081</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6405,10 +6405,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128728592</v>
+        <v>128730101</v>
       </c>
       <c r="B58" t="n">
-        <v>80174</v>
+        <v>80176</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6416,21 +6416,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6463</v>
+        <v>6464</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6440,10 +6440,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>569604</v>
+        <v>569630</v>
       </c>
       <c r="R58" t="n">
-        <v>6958176</v>
+        <v>6958139</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6502,10 +6502,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128732124</v>
+        <v>128731387</v>
       </c>
       <c r="B59" t="n">
-        <v>80174</v>
+        <v>80168</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6513,21 +6513,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6463</v>
+        <v>6461</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6537,10 +6537,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>569816</v>
+        <v>569740</v>
       </c>
       <c r="R59" t="n">
-        <v>6958081</v>
+        <v>6958091</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6599,45 +6599,50 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128730101</v>
+        <v>128730490</v>
       </c>
       <c r="B60" t="n">
-        <v>80175</v>
+        <v>57723</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>569630</v>
+        <v>569707</v>
       </c>
       <c r="R60" t="n">
-        <v>6958139</v>
+        <v>6958131</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6670,6 +6675,11 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Både äldre och färska spår ( Ringhack av tretåig hackspett på tall)</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6696,45 +6706,50 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128731387</v>
+        <v>128730422</v>
       </c>
       <c r="B61" t="n">
-        <v>80167</v>
+        <v>57723</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6461</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>569740</v>
+        <v>569703</v>
       </c>
       <c r="R61" t="n">
-        <v>6958091</v>
+        <v>6958116</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6767,6 +6782,11 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6793,7 +6813,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128730490</v>
+        <v>128739287</v>
       </c>
       <c r="B62" t="n">
         <v>57723</v>
@@ -6833,10 +6853,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>569707</v>
+        <v>569481</v>
       </c>
       <c r="R62" t="n">
-        <v>6958131</v>
+        <v>6958122</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6873,7 +6893,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Både äldre och färska spår ( Ringhack av tretåig hackspett på tall)</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6900,50 +6920,45 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128730422</v>
+        <v>128732806</v>
       </c>
       <c r="B63" t="n">
-        <v>57723</v>
+        <v>91537</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>1205</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>569703</v>
+        <v>569827</v>
       </c>
       <c r="R63" t="n">
-        <v>6958116</v>
+        <v>6958133</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6976,11 +6991,6 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7007,50 +7017,45 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128739287</v>
+        <v>128732719</v>
       </c>
       <c r="B64" t="n">
-        <v>57723</v>
+        <v>91981</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>569481</v>
+        <v>569821</v>
       </c>
       <c r="R64" t="n">
-        <v>6958122</v>
+        <v>6958151</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7083,11 +7088,6 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7117,7 +7117,7 @@
         <v>128730183</v>
       </c>
       <c r="B65" t="n">
-        <v>80099</v>
+        <v>80100</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7214,7 +7214,7 @@
         <v>128729077</v>
       </c>
       <c r="B66" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         <v>128730273</v>
       </c>
       <c r="B67" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7408,7 +7408,7 @@
         <v>128732112</v>
       </c>
       <c r="B68" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7505,7 +7505,7 @@
         <v>128731693</v>
       </c>
       <c r="B69" t="n">
-        <v>91523</v>
+        <v>91526</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7602,7 +7602,7 @@
         <v>128743263</v>
       </c>
       <c r="B70" t="n">
-        <v>92852</v>
+        <v>92855</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8341,45 +8341,49 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128731100</v>
+        <v>128732718</v>
       </c>
       <c r="B77" t="n">
-        <v>91541</v>
+        <v>98659</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>569688</v>
+        <v>569834</v>
       </c>
       <c r="R77" t="n">
-        <v>6958069</v>
+        <v>6958143</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8438,38 +8442,37 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128731284</v>
+        <v>128733005</v>
       </c>
       <c r="B78" t="n">
-        <v>57883</v>
+        <v>98659</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>7</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
@@ -8478,10 +8481,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>569677</v>
+        <v>569882</v>
       </c>
       <c r="R78" t="n">
-        <v>6958066</v>
+        <v>6958106</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8540,49 +8543,45 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128732718</v>
+        <v>128731100</v>
       </c>
       <c r="B79" t="n">
-        <v>98656</v>
+        <v>91544</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>569834</v>
+        <v>569688</v>
       </c>
       <c r="R79" t="n">
-        <v>6958143</v>
+        <v>6958069</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8641,37 +8640,38 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128733005</v>
+        <v>128731284</v>
       </c>
       <c r="B80" t="n">
-        <v>98656</v>
+        <v>57883</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>7</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
@@ -8680,10 +8680,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>569882</v>
+        <v>569677</v>
       </c>
       <c r="R80" t="n">
-        <v>6958106</v>
+        <v>6958066</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8742,10 +8742,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128731226</v>
+        <v>128743244</v>
       </c>
       <c r="B81" t="n">
-        <v>91541</v>
+        <v>91526</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8753,21 +8753,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8777,10 +8777,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>569705</v>
+        <v>569736</v>
       </c>
       <c r="R81" t="n">
-        <v>6958098</v>
+        <v>6957867</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8839,10 +8839,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128743244</v>
+        <v>128728434</v>
       </c>
       <c r="B82" t="n">
-        <v>91523</v>
+        <v>57723</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8850,34 +8850,39 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>569736</v>
+        <v>569608</v>
       </c>
       <c r="R82" t="n">
-        <v>6957867</v>
+        <v>6958227</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8910,6 +8915,11 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8936,10 +8946,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128728434</v>
+        <v>128731226</v>
       </c>
       <c r="B83" t="n">
-        <v>57723</v>
+        <v>91544</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8947,39 +8957,34 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>569608</v>
+        <v>569705</v>
       </c>
       <c r="R83" t="n">
-        <v>6958227</v>
+        <v>6958098</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9012,11 +9017,6 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9046,7 +9046,7 @@
         <v>128729895</v>
       </c>
       <c r="B84" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9147,7 +9147,7 @@
         <v>128743257</v>
       </c>
       <c r="B85" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9246,10 +9246,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128728419</v>
+        <v>128729069</v>
       </c>
       <c r="B86" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9281,10 +9281,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>569608</v>
+        <v>569699</v>
       </c>
       <c r="R86" t="n">
-        <v>6958227</v>
+        <v>6958200</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9317,11 +9317,6 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>Riklig förekomst inom området</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9348,10 +9343,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128727978</v>
+        <v>128728419</v>
       </c>
       <c r="B87" t="n">
-        <v>57723</v>
+        <v>79035</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9359,39 +9354,34 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>569564</v>
+        <v>569608</v>
       </c>
       <c r="R87" t="n">
-        <v>6958213</v>
+        <v>6958227</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9428,7 +9418,7 @@
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Riklig förekomst inom området</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9455,10 +9445,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128729666</v>
+        <v>128743261</v>
       </c>
       <c r="B88" t="n">
-        <v>57723</v>
+        <v>79035</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9466,39 +9456,34 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>569706</v>
+        <v>569495</v>
       </c>
       <c r="R88" t="n">
-        <v>6958159</v>
+        <v>6958117</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9531,11 +9516,6 @@
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9562,10 +9542,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128729069</v>
+        <v>128727978</v>
       </c>
       <c r="B89" t="n">
-        <v>79034</v>
+        <v>57723</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9573,34 +9553,39 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P89" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>569699</v>
+        <v>569564</v>
       </c>
       <c r="R89" t="n">
-        <v>6958200</v>
+        <v>6958213</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9633,6 +9618,11 @@
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9659,10 +9649,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128743261</v>
+        <v>128729666</v>
       </c>
       <c r="B90" t="n">
-        <v>79034</v>
+        <v>57723</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9670,34 +9660,39 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P90" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>569495</v>
+        <v>569706</v>
       </c>
       <c r="R90" t="n">
-        <v>6958117</v>
+        <v>6958159</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9730,6 +9725,11 @@
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9759,7 +9759,7 @@
         <v>128738599</v>
       </c>
       <c r="B91" t="n">
-        <v>80099</v>
+        <v>80100</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9853,49 +9853,45 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128731648</v>
+        <v>128728152</v>
       </c>
       <c r="B92" t="n">
-        <v>98656</v>
+        <v>91526</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>119</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>569766</v>
+        <v>569577</v>
       </c>
       <c r="R92" t="n">
-        <v>6958144</v>
+        <v>6958213</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9928,11 +9924,6 @@
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC92" t="inlineStr">
-        <is>
-          <t>Ca ( möjligtvis fler)</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -9959,10 +9950,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128743253</v>
+        <v>128731648</v>
       </c>
       <c r="B93" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9987,17 +9978,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I93" t="inlineStr"/>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>569641</v>
+        <v>569766</v>
       </c>
       <c r="R93" t="n">
-        <v>6957953</v>
+        <v>6958144</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10034,7 +10029,7 @@
       </c>
       <c r="AC93" t="inlineStr">
         <is>
-          <t>55 exemplar knärötter</t>
+          <t>Ca ( möjligtvis fler)</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10061,10 +10056,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128743256</v>
+        <v>128743253</v>
       </c>
       <c r="B94" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10096,10 +10091,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>569647</v>
+        <v>569641</v>
       </c>
       <c r="R94" t="n">
-        <v>6957950</v>
+        <v>6957953</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10136,7 +10131,7 @@
       </c>
       <c r="AC94" t="inlineStr">
         <is>
-          <t>23 exemplar</t>
+          <t>55 exemplar knärötter</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10163,32 +10158,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128728152</v>
+        <v>128743256</v>
       </c>
       <c r="B95" t="n">
-        <v>91523</v>
+        <v>98659</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10198,10 +10193,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>569577</v>
+        <v>569647</v>
       </c>
       <c r="R95" t="n">
-        <v>6958213</v>
+        <v>6957950</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10234,6 +10229,11 @@
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>23 exemplar</t>
         </is>
       </c>
       <c r="AD95" t="b">

--- a/artfynd/A 39666-2025 artfynd.xlsx
+++ b/artfynd/A 39666-2025 artfynd.xlsx
@@ -772,7 +772,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128728526</v>
+        <v>128743246</v>
       </c>
       <c r="B3" t="n">
         <v>57723</v>
@@ -801,21 +801,16 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>569616</v>
+        <v>569648</v>
       </c>
       <c r="R3" t="n">
-        <v>6958208</v>
+        <v>6957944</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +847,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack av tretåig hackspett på Tall ( äldre och färska spår)</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,7 +874,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128739007</v>
+        <v>128728526</v>
       </c>
       <c r="B4" t="n">
         <v>57723</v>
@@ -919,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>569542</v>
+        <v>569616</v>
       </c>
       <c r="R4" t="n">
-        <v>6958069</v>
+        <v>6958208</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128743246</v>
+        <v>128739007</v>
       </c>
       <c r="B5" t="n">
         <v>57723</v>
@@ -1015,16 +1010,21 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>569648</v>
+        <v>569542</v>
       </c>
       <c r="R5" t="n">
-        <v>6957944</v>
+        <v>6958069</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1061,7 +1061,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall ( äldre och färska spår)</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1494,10 +1494,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128732765</v>
+        <v>128732276</v>
       </c>
       <c r="B10" t="n">
-        <v>91811</v>
+        <v>57723</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1505,34 +1505,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>569827</v>
+        <v>569841</v>
       </c>
       <c r="R10" t="n">
-        <v>6958133</v>
+        <v>6958102</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1565,6 +1570,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1591,10 +1601,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128730571</v>
+        <v>128743245</v>
       </c>
       <c r="B11" t="n">
-        <v>91544</v>
+        <v>57723</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1602,21 +1612,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1626,10 +1636,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>569660</v>
+        <v>569590</v>
       </c>
       <c r="R11" t="n">
-        <v>6958074</v>
+        <v>6958014</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1662,6 +1672,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall ( färska spår)</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1688,10 +1703,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128732276</v>
+        <v>128732217</v>
       </c>
       <c r="B12" t="n">
-        <v>57723</v>
+        <v>57883</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1699,27 +1714,36 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1728,10 +1752,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>569841</v>
+        <v>569777</v>
       </c>
       <c r="R12" t="n">
-        <v>6958102</v>
+        <v>6958189</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1768,7 +1792,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>2 talltitor kommer flygandes väldigt närgånget och varnar</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1795,32 +1819,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128743245</v>
+        <v>128733181</v>
       </c>
       <c r="B13" t="n">
-        <v>57723</v>
+        <v>98576</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1830,10 +1854,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>569590</v>
+        <v>569900</v>
       </c>
       <c r="R13" t="n">
-        <v>6958014</v>
+        <v>6958101</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1866,11 +1890,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall ( färska spår)</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1897,10 +1916,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128732217</v>
+        <v>128732765</v>
       </c>
       <c r="B14" t="n">
-        <v>57883</v>
+        <v>91811</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1908,48 +1927,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>658</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>569777</v>
+        <v>569827</v>
       </c>
       <c r="R14" t="n">
-        <v>6958189</v>
+        <v>6958133</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1982,11 +1987,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>2 talltitor kommer flygandes väldigt närgånget och varnar</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2013,32 +2013,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128733181</v>
+        <v>128730571</v>
       </c>
       <c r="B15" t="n">
-        <v>98576</v>
+        <v>91544</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219790</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2048,10 +2048,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>569900</v>
+        <v>569660</v>
       </c>
       <c r="R15" t="n">
-        <v>6958101</v>
+        <v>6958074</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2516,49 +2516,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128730720</v>
+        <v>128728022</v>
       </c>
       <c r="B20" t="n">
-        <v>98659</v>
+        <v>91491</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>569692</v>
+        <v>569583</v>
       </c>
       <c r="R20" t="n">
-        <v>6958094</v>
+        <v>6958204</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2591,11 +2587,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ca</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2622,32 +2613,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128743252</v>
+        <v>128743262</v>
       </c>
       <c r="B21" t="n">
-        <v>98659</v>
+        <v>79035</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2657,10 +2648,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>569610</v>
+        <v>569732</v>
       </c>
       <c r="R21" t="n">
-        <v>6958005</v>
+        <v>6957870</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2693,11 +2684,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>2 exemplar</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2724,32 +2710,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128728022</v>
+        <v>128732359</v>
       </c>
       <c r="B22" t="n">
-        <v>91491</v>
+        <v>91526</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2759,10 +2745,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>569583</v>
+        <v>569820</v>
       </c>
       <c r="R22" t="n">
-        <v>6958204</v>
+        <v>6958107</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2821,10 +2807,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128739020</v>
+        <v>128731612</v>
       </c>
       <c r="B23" t="n">
-        <v>57723</v>
+        <v>91526</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2832,39 +2818,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>569542</v>
+        <v>569752</v>
       </c>
       <c r="R23" t="n">
-        <v>6958049</v>
+        <v>6958091</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2897,11 +2878,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2928,10 +2904,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128732359</v>
+        <v>128739020</v>
       </c>
       <c r="B24" t="n">
-        <v>91526</v>
+        <v>57723</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2939,34 +2915,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>569820</v>
+        <v>569542</v>
       </c>
       <c r="R24" t="n">
-        <v>6958107</v>
+        <v>6958049</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2999,6 +2980,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3025,10 +3011,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128731612</v>
+        <v>128731107</v>
       </c>
       <c r="B25" t="n">
-        <v>91526</v>
+        <v>57883</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3036,34 +3022,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>569752</v>
+        <v>569705</v>
       </c>
       <c r="R25" t="n">
-        <v>6958091</v>
+        <v>6958098</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3122,45 +3113,49 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128743262</v>
+        <v>128730720</v>
       </c>
       <c r="B26" t="n">
-        <v>79035</v>
+        <v>98659</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>569732</v>
+        <v>569692</v>
       </c>
       <c r="R26" t="n">
-        <v>6957870</v>
+        <v>6958094</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3193,6 +3188,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ca</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3219,50 +3219,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128731107</v>
+        <v>128743252</v>
       </c>
       <c r="B27" t="n">
-        <v>57883</v>
+        <v>98659</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>569705</v>
+        <v>569610</v>
       </c>
       <c r="R27" t="n">
-        <v>6958098</v>
+        <v>6958005</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3295,6 +3290,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>2 exemplar</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3321,49 +3321,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128731489</v>
+        <v>128729068</v>
       </c>
       <c r="B28" t="n">
-        <v>98659</v>
+        <v>80169</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>569752</v>
+        <v>569604</v>
       </c>
       <c r="R28" t="n">
-        <v>6958091</v>
+        <v>6958176</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3422,45 +3418,50 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128729068</v>
+        <v>128731291</v>
       </c>
       <c r="B29" t="n">
-        <v>80169</v>
+        <v>57723</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>569604</v>
+        <v>569726</v>
       </c>
       <c r="R29" t="n">
-        <v>6958176</v>
+        <v>6958097</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3493,6 +3494,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på tall</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3519,7 +3525,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128731291</v>
+        <v>128728019</v>
       </c>
       <c r="B30" t="n">
         <v>57723</v>
@@ -3559,10 +3565,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>569726</v>
+        <v>569577</v>
       </c>
       <c r="R30" t="n">
-        <v>6958097</v>
+        <v>6958213</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3599,7 +3605,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på tall</t>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3626,38 +3632,37 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128728019</v>
+        <v>128731489</v>
       </c>
       <c r="B31" t="n">
-        <v>57723</v>
+        <v>98659</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>45</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -3666,10 +3671,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>569577</v>
+        <v>569752</v>
       </c>
       <c r="R31" t="n">
-        <v>6958213</v>
+        <v>6958091</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3702,11 +3707,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3733,45 +3733,54 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128730513</v>
+        <v>128728767</v>
       </c>
       <c r="B32" t="n">
-        <v>80140</v>
+        <v>92819</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>569656</v>
+        <v>569639</v>
       </c>
       <c r="R32" t="n">
-        <v>6958093</v>
+        <v>6958231</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3804,6 +3813,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>4 äldre ett färskt års exemplar</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3830,10 +3844,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128730603</v>
+        <v>128730513</v>
       </c>
       <c r="B33" t="n">
-        <v>57723</v>
+        <v>80140</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3841,39 +3855,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>569738</v>
+        <v>569656</v>
       </c>
       <c r="R33" t="n">
-        <v>6958117</v>
+        <v>6958093</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3906,11 +3915,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Äldre exemplar av ringhack på Tall från tretåig hackspett</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3937,42 +3941,38 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128728767</v>
+        <v>128730603</v>
       </c>
       <c r="B34" t="n">
-        <v>92819</v>
+        <v>57723</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -3981,10 +3981,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>569639</v>
+        <v>569738</v>
       </c>
       <c r="R34" t="n">
-        <v>6958231</v>
+        <v>6958117</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4021,7 +4021,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>4 äldre ett färskt års exemplar</t>
+          <t>Äldre exemplar av ringhack på Tall från tretåig hackspett</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -5057,37 +5057,38 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128732627</v>
+        <v>128728902</v>
       </c>
       <c r="B45" t="n">
-        <v>98659</v>
+        <v>57723</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>6</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -5096,10 +5097,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>569821</v>
+        <v>569673</v>
       </c>
       <c r="R45" t="n">
-        <v>6958151</v>
+        <v>6958225</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5136,7 +5137,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Kan finnas mer I blåbärsriset och mossan</t>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5163,37 +5164,38 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128728348</v>
+        <v>128731799</v>
       </c>
       <c r="B46" t="n">
-        <v>98659</v>
+        <v>57723</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>300</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -5202,10 +5204,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>569616</v>
+        <v>569774</v>
       </c>
       <c r="R46" t="n">
-        <v>6958208</v>
+        <v>6958163</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5238,6 +5240,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5264,7 +5271,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128728902</v>
+        <v>128732015</v>
       </c>
       <c r="B47" t="n">
         <v>57723</v>
@@ -5304,10 +5311,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>569673</v>
+        <v>569816</v>
       </c>
       <c r="R47" t="n">
-        <v>6958225</v>
+        <v>6958081</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5344,7 +5351,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5371,7 +5378,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128731799</v>
+        <v>128738187</v>
       </c>
       <c r="B48" t="n">
         <v>57723</v>
@@ -5402,7 +5409,7 @@
       <c r="I48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -5411,10 +5418,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>569774</v>
+        <v>569681</v>
       </c>
       <c r="R48" t="n">
-        <v>6958163</v>
+        <v>6957939</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5451,7 +5458,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5478,38 +5485,37 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128732015</v>
+        <v>128732627</v>
       </c>
       <c r="B49" t="n">
-        <v>57723</v>
+        <v>98659</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>6</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -5518,10 +5524,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>569816</v>
+        <v>569821</v>
       </c>
       <c r="R49" t="n">
-        <v>6958081</v>
+        <v>6958151</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5558,7 +5564,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Kan finnas mer I blåbärsriset och mossan</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5585,38 +5591,37 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128738187</v>
+        <v>128728348</v>
       </c>
       <c r="B50" t="n">
-        <v>57723</v>
+        <v>98659</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>300</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -5625,10 +5630,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>569681</v>
+        <v>569616</v>
       </c>
       <c r="R50" t="n">
-        <v>6957939</v>
+        <v>6958208</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5661,11 +5666,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6211,45 +6211,50 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128728592</v>
+        <v>128730490</v>
       </c>
       <c r="B56" t="n">
-        <v>80175</v>
+        <v>57723</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>569604</v>
+        <v>569707</v>
       </c>
       <c r="R56" t="n">
-        <v>6958176</v>
+        <v>6958131</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6282,6 +6287,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Både äldre och färska spår ( Ringhack av tretåig hackspett på tall)</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6308,45 +6318,50 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128732124</v>
+        <v>128730422</v>
       </c>
       <c r="B57" t="n">
-        <v>80175</v>
+        <v>57723</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>569816</v>
+        <v>569703</v>
       </c>
       <c r="R57" t="n">
-        <v>6958081</v>
+        <v>6958116</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6379,6 +6394,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6405,45 +6425,50 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128730101</v>
+        <v>128739287</v>
       </c>
       <c r="B58" t="n">
-        <v>80176</v>
+        <v>57723</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>569630</v>
+        <v>569481</v>
       </c>
       <c r="R58" t="n">
-        <v>6958139</v>
+        <v>6958122</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6476,6 +6501,11 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6502,10 +6532,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128731387</v>
+        <v>128730183</v>
       </c>
       <c r="B59" t="n">
-        <v>80168</v>
+        <v>80100</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6513,21 +6543,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6461</v>
+        <v>229497</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6537,10 +6567,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>569740</v>
+        <v>569630</v>
       </c>
       <c r="R59" t="n">
-        <v>6958091</v>
+        <v>6958129</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6599,50 +6629,45 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128730490</v>
+        <v>128728592</v>
       </c>
       <c r="B60" t="n">
-        <v>57723</v>
+        <v>80175</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>569707</v>
+        <v>569604</v>
       </c>
       <c r="R60" t="n">
-        <v>6958131</v>
+        <v>6958176</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6675,11 +6700,6 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Både äldre och färska spår ( Ringhack av tretåig hackspett på tall)</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6706,50 +6726,45 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128730422</v>
+        <v>128732124</v>
       </c>
       <c r="B61" t="n">
-        <v>57723</v>
+        <v>80175</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>569703</v>
+        <v>569816</v>
       </c>
       <c r="R61" t="n">
-        <v>6958116</v>
+        <v>6958081</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6782,11 +6797,6 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6813,50 +6823,45 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128739287</v>
+        <v>128730101</v>
       </c>
       <c r="B62" t="n">
-        <v>57723</v>
+        <v>80176</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>569481</v>
+        <v>569630</v>
       </c>
       <c r="R62" t="n">
-        <v>6958122</v>
+        <v>6958139</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6889,11 +6894,6 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6920,10 +6920,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128732806</v>
+        <v>128731387</v>
       </c>
       <c r="B63" t="n">
-        <v>91537</v>
+        <v>80168</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6931,21 +6931,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1205</v>
+        <v>6461</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6955,10 +6955,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>569827</v>
+        <v>569740</v>
       </c>
       <c r="R63" t="n">
-        <v>6958133</v>
+        <v>6958091</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7017,32 +7017,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128732719</v>
+        <v>128732806</v>
       </c>
       <c r="B64" t="n">
-        <v>91981</v>
+        <v>91537</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1209</v>
+        <v>1205</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7052,10 +7052,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>569821</v>
+        <v>569827</v>
       </c>
       <c r="R64" t="n">
-        <v>6958151</v>
+        <v>6958133</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7114,32 +7114,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128730183</v>
+        <v>128732719</v>
       </c>
       <c r="B65" t="n">
-        <v>80100</v>
+        <v>91981</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>229497</v>
+        <v>1209</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7149,10 +7149,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>569630</v>
+        <v>569821</v>
       </c>
       <c r="R65" t="n">
-        <v>6958129</v>
+        <v>6958151</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7502,32 +7502,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128731693</v>
+        <v>128743263</v>
       </c>
       <c r="B69" t="n">
-        <v>91526</v>
+        <v>92855</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1202</v>
+        <v>5964</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7537,10 +7537,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>569793</v>
+        <v>569517</v>
       </c>
       <c r="R69" t="n">
-        <v>6958092</v>
+        <v>6958123</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7573,6 +7573,11 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>3 exemplar</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7599,45 +7604,50 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128743263</v>
+        <v>128732493</v>
       </c>
       <c r="B70" t="n">
-        <v>92855</v>
+        <v>57723</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>5964</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>569517</v>
+        <v>569795</v>
       </c>
       <c r="R70" t="n">
-        <v>6958123</v>
+        <v>6958154</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7674,7 +7684,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>3 exemplar</t>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7701,7 +7711,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128728149</v>
+        <v>128730998</v>
       </c>
       <c r="B71" t="n">
         <v>57723</v>
@@ -7741,10 +7751,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>569585</v>
+        <v>569670</v>
       </c>
       <c r="R71" t="n">
-        <v>6958190</v>
+        <v>6958060</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7781,7 +7791,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på tall. Även äldre</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7808,10 +7818,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128732493</v>
+        <v>128731693</v>
       </c>
       <c r="B72" t="n">
-        <v>57723</v>
+        <v>91526</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7819,39 +7829,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>569795</v>
+        <v>569793</v>
       </c>
       <c r="R72" t="n">
-        <v>6958154</v>
+        <v>6958092</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7884,11 +7889,6 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7915,7 +7915,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128730998</v>
+        <v>128728149</v>
       </c>
       <c r="B73" t="n">
         <v>57723</v>
@@ -7955,10 +7955,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>569670</v>
+        <v>569585</v>
       </c>
       <c r="R73" t="n">
-        <v>6958060</v>
+        <v>6958190</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7995,7 +7995,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Ringhack på tall. Även äldre</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8132,10 +8132,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128743247</v>
+        <v>128731100</v>
       </c>
       <c r="B75" t="n">
-        <v>57723</v>
+        <v>91544</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8143,21 +8143,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8167,10 +8167,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>569714</v>
+        <v>569688</v>
       </c>
       <c r="R75" t="n">
-        <v>6957901</v>
+        <v>6958069</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8203,11 +8203,6 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på gran ( färska spår)</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8234,7 +8229,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128732848</v>
+        <v>128743247</v>
       </c>
       <c r="B76" t="n">
         <v>57723</v>
@@ -8263,21 +8258,16 @@
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>569873</v>
+        <v>569714</v>
       </c>
       <c r="R76" t="n">
-        <v>6958099</v>
+        <v>6957901</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8314,7 +8304,7 @@
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack av tretåig hackspett på gran ( färska spår)</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8341,37 +8331,38 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128732718</v>
+        <v>128732848</v>
       </c>
       <c r="B77" t="n">
-        <v>98659</v>
+        <v>57723</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>18</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
@@ -8380,10 +8371,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>569834</v>
+        <v>569873</v>
       </c>
       <c r="R77" t="n">
-        <v>6958143</v>
+        <v>6958099</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8416,6 +8407,11 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8442,7 +8438,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128733005</v>
+        <v>128732718</v>
       </c>
       <c r="B78" t="n">
         <v>98659</v>
@@ -8472,7 +8468,7 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>18</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
@@ -8481,10 +8477,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>569882</v>
+        <v>569834</v>
       </c>
       <c r="R78" t="n">
-        <v>6958106</v>
+        <v>6958143</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8543,45 +8539,49 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128731100</v>
+        <v>128733005</v>
       </c>
       <c r="B79" t="n">
-        <v>91544</v>
+        <v>98659</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>569688</v>
+        <v>569882</v>
       </c>
       <c r="R79" t="n">
-        <v>6958069</v>
+        <v>6958106</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8742,10 +8742,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128743244</v>
+        <v>128728434</v>
       </c>
       <c r="B81" t="n">
-        <v>91526</v>
+        <v>57723</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8753,34 +8753,39 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>569736</v>
+        <v>569608</v>
       </c>
       <c r="R81" t="n">
-        <v>6957867</v>
+        <v>6958227</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8813,6 +8818,11 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8839,10 +8849,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128728434</v>
+        <v>128743244</v>
       </c>
       <c r="B82" t="n">
-        <v>57723</v>
+        <v>91526</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8850,39 +8860,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>569608</v>
+        <v>569736</v>
       </c>
       <c r="R82" t="n">
-        <v>6958227</v>
+        <v>6957867</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8915,11 +8920,6 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9950,37 +9950,38 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128731648</v>
+        <v>128728274</v>
       </c>
       <c r="B93" t="n">
-        <v>98659</v>
+        <v>57723</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>119</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P93" t="inlineStr">
@@ -9989,10 +9990,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>569766</v>
+        <v>569599</v>
       </c>
       <c r="R93" t="n">
-        <v>6958144</v>
+        <v>6958201</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10029,7 +10030,7 @@
       </c>
       <c r="AC93" t="inlineStr">
         <is>
-          <t>Ca ( möjligtvis fler)</t>
+          <t>Både äldre och färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10056,7 +10057,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128743253</v>
+        <v>128731648</v>
       </c>
       <c r="B94" t="n">
         <v>98659</v>
@@ -10084,17 +10085,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I94" t="inlineStr"/>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
       <c r="P94" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>569641</v>
+        <v>569766</v>
       </c>
       <c r="R94" t="n">
-        <v>6957953</v>
+        <v>6958144</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10131,7 +10136,7 @@
       </c>
       <c r="AC94" t="inlineStr">
         <is>
-          <t>55 exemplar knärötter</t>
+          <t>Ca ( möjligtvis fler)</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10158,7 +10163,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128743256</v>
+        <v>128743253</v>
       </c>
       <c r="B95" t="n">
         <v>98659</v>
@@ -10193,10 +10198,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>569647</v>
+        <v>569641</v>
       </c>
       <c r="R95" t="n">
-        <v>6957950</v>
+        <v>6957953</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10233,7 +10238,7 @@
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>23 exemplar</t>
+          <t>55 exemplar knärötter</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10260,50 +10265,45 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128728274</v>
+        <v>128743256</v>
       </c>
       <c r="B96" t="n">
-        <v>57723</v>
+        <v>98659</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P96" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>569599</v>
+        <v>569647</v>
       </c>
       <c r="R96" t="n">
-        <v>6958201</v>
+        <v>6957950</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10340,7 +10340,7 @@
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>Både äldre och färska ringhack på tall</t>
+          <t>23 exemplar</t>
         </is>
       </c>
       <c r="AD96" t="b">

--- a/artfynd/A 39666-2025 artfynd.xlsx
+++ b/artfynd/A 39666-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128732386</v>
+        <v>128739007</v>
       </c>
       <c r="B2" t="n">
-        <v>80140</v>
+        <v>57723</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>569785</v>
+        <v>569542</v>
       </c>
       <c r="R2" t="n">
-        <v>6958124</v>
+        <v>6958069</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128743246</v>
+        <v>128728526</v>
       </c>
       <c r="B3" t="n">
         <v>57723</v>
@@ -801,16 +811,21 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>569648</v>
+        <v>569616</v>
       </c>
       <c r="R3" t="n">
-        <v>6957944</v>
+        <v>6958208</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -847,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall ( äldre och färska spår)</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -874,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128728526</v>
+        <v>128743246</v>
       </c>
       <c r="B4" t="n">
         <v>57723</v>
@@ -903,21 +918,16 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>569616</v>
+        <v>569648</v>
       </c>
       <c r="R4" t="n">
-        <v>6958208</v>
+        <v>6957944</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -954,7 +964,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack av tretåig hackspett på Tall ( äldre och färska spår)</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -981,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128739007</v>
+        <v>128732386</v>
       </c>
       <c r="B5" t="n">
-        <v>57723</v>
+        <v>80140</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -992,39 +1002,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>569542</v>
+        <v>569785</v>
       </c>
       <c r="R5" t="n">
-        <v>6958069</v>
+        <v>6958124</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1057,11 +1062,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1290,10 +1290,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128730130</v>
+        <v>128729409</v>
       </c>
       <c r="B8" t="n">
-        <v>57723</v>
+        <v>91526</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1301,39 +1301,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>569713</v>
+        <v>569700</v>
       </c>
       <c r="R8" t="n">
-        <v>6958138</v>
+        <v>6958164</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1366,11 +1361,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1397,10 +1387,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128729409</v>
+        <v>128730130</v>
       </c>
       <c r="B9" t="n">
-        <v>91526</v>
+        <v>57723</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1408,34 +1398,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>569700</v>
+        <v>569713</v>
       </c>
       <c r="R9" t="n">
-        <v>6958164</v>
+        <v>6958138</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1468,6 +1463,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1494,10 +1494,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128732276</v>
+        <v>128730571</v>
       </c>
       <c r="B10" t="n">
-        <v>57723</v>
+        <v>91544</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1505,39 +1505,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>569841</v>
+        <v>569660</v>
       </c>
       <c r="R10" t="n">
-        <v>6958102</v>
+        <v>6958074</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1570,11 +1565,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1601,10 +1591,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128743245</v>
+        <v>128732765</v>
       </c>
       <c r="B11" t="n">
-        <v>57723</v>
+        <v>91811</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1612,21 +1602,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1636,10 +1626,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>569590</v>
+        <v>569827</v>
       </c>
       <c r="R11" t="n">
-        <v>6958014</v>
+        <v>6958133</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1672,11 +1662,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall ( färska spår)</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1703,10 +1688,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128732217</v>
+        <v>128743245</v>
       </c>
       <c r="B12" t="n">
-        <v>57883</v>
+        <v>57723</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1714,48 +1699,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>569777</v>
+        <v>569590</v>
       </c>
       <c r="R12" t="n">
-        <v>6958189</v>
+        <v>6958014</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1792,7 +1763,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>2 talltitor kommer flygandes väldigt närgånget och varnar</t>
+          <t>Ringhack av tretåig hackspett på Tall ( färska spår)</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1819,45 +1790,50 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128733181</v>
+        <v>128732276</v>
       </c>
       <c r="B13" t="n">
-        <v>98576</v>
+        <v>57723</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>569900</v>
+        <v>569841</v>
       </c>
       <c r="R13" t="n">
-        <v>6958101</v>
+        <v>6958102</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1890,6 +1866,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1916,10 +1897,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128732765</v>
+        <v>128732217</v>
       </c>
       <c r="B14" t="n">
-        <v>91811</v>
+        <v>57883</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1927,34 +1908,48 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>658</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>569827</v>
+        <v>569777</v>
       </c>
       <c r="R14" t="n">
-        <v>6958133</v>
+        <v>6958189</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1987,6 +1982,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>2 talltitor kommer flygandes väldigt närgånget och varnar</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2013,32 +2013,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128730571</v>
+        <v>128733181</v>
       </c>
       <c r="B15" t="n">
-        <v>91544</v>
+        <v>98576</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>219790</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2048,10 +2048,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>569660</v>
+        <v>569900</v>
       </c>
       <c r="R15" t="n">
-        <v>6958074</v>
+        <v>6958101</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2110,37 +2110,38 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128731490</v>
+        <v>128731601</v>
       </c>
       <c r="B16" t="n">
-        <v>98659</v>
+        <v>57723</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>20</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2149,10 +2150,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>569759</v>
+        <v>569752</v>
       </c>
       <c r="R16" t="n">
-        <v>6958118</v>
+        <v>6958091</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2185,6 +2186,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2211,49 +2217,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128730429</v>
+        <v>128728515</v>
       </c>
       <c r="B17" t="n">
-        <v>98659</v>
+        <v>97530</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>569683</v>
+        <v>569608</v>
       </c>
       <c r="R17" t="n">
-        <v>6958128</v>
+        <v>6958227</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2312,38 +2314,37 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128731601</v>
+        <v>128731490</v>
       </c>
       <c r="B18" t="n">
-        <v>57723</v>
+        <v>98659</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>20</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2352,10 +2353,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>569752</v>
+        <v>569759</v>
       </c>
       <c r="R18" t="n">
-        <v>6958091</v>
+        <v>6958118</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2388,11 +2389,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2419,45 +2415,49 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128728515</v>
+        <v>128730429</v>
       </c>
       <c r="B19" t="n">
-        <v>97530</v>
+        <v>98659</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>569608</v>
+        <v>569683</v>
       </c>
       <c r="R19" t="n">
-        <v>6958227</v>
+        <v>6958128</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2516,32 +2516,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128728022</v>
+        <v>128732359</v>
       </c>
       <c r="B20" t="n">
-        <v>91491</v>
+        <v>91526</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2551,10 +2551,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>569583</v>
+        <v>569820</v>
       </c>
       <c r="R20" t="n">
-        <v>6958204</v>
+        <v>6958107</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2613,10 +2613,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128743262</v>
+        <v>128731612</v>
       </c>
       <c r="B21" t="n">
-        <v>79035</v>
+        <v>91526</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2624,21 +2624,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2648,10 +2648,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>569732</v>
+        <v>569752</v>
       </c>
       <c r="R21" t="n">
-        <v>6957870</v>
+        <v>6958091</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2710,45 +2710,49 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128732359</v>
+        <v>128730720</v>
       </c>
       <c r="B22" t="n">
-        <v>91526</v>
+        <v>98659</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>569820</v>
+        <v>569692</v>
       </c>
       <c r="R22" t="n">
-        <v>6958107</v>
+        <v>6958094</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2781,6 +2785,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ca</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2807,32 +2816,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128731612</v>
+        <v>128743252</v>
       </c>
       <c r="B23" t="n">
-        <v>91526</v>
+        <v>98659</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2842,10 +2851,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>569752</v>
+        <v>569610</v>
       </c>
       <c r="R23" t="n">
-        <v>6958091</v>
+        <v>6958005</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2878,6 +2887,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>2 exemplar</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2904,50 +2918,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128739020</v>
+        <v>128728022</v>
       </c>
       <c r="B24" t="n">
-        <v>57723</v>
+        <v>91491</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>569542</v>
+        <v>569583</v>
       </c>
       <c r="R24" t="n">
-        <v>6958049</v>
+        <v>6958204</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2980,11 +2989,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3011,10 +3015,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128731107</v>
+        <v>128743262</v>
       </c>
       <c r="B25" t="n">
-        <v>57883</v>
+        <v>79035</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3022,39 +3026,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>569705</v>
+        <v>569732</v>
       </c>
       <c r="R25" t="n">
-        <v>6958098</v>
+        <v>6957870</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3113,37 +3112,38 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128730720</v>
+        <v>128739020</v>
       </c>
       <c r="B26" t="n">
-        <v>98659</v>
+        <v>57723</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>50</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3152,10 +3152,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>569692</v>
+        <v>569542</v>
       </c>
       <c r="R26" t="n">
-        <v>6958094</v>
+        <v>6958049</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3192,7 +3192,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ca</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3219,45 +3219,50 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128743252</v>
+        <v>128731107</v>
       </c>
       <c r="B27" t="n">
-        <v>98659</v>
+        <v>57883</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>569610</v>
+        <v>569705</v>
       </c>
       <c r="R27" t="n">
-        <v>6958005</v>
+        <v>6958098</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3290,11 +3295,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>2 exemplar</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3321,45 +3321,50 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128729068</v>
+        <v>128731291</v>
       </c>
       <c r="B28" t="n">
-        <v>80169</v>
+        <v>57723</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>569604</v>
+        <v>569726</v>
       </c>
       <c r="R28" t="n">
-        <v>6958176</v>
+        <v>6958097</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3392,6 +3397,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på tall</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3418,7 +3428,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128731291</v>
+        <v>128728019</v>
       </c>
       <c r="B29" t="n">
         <v>57723</v>
@@ -3458,10 +3468,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>569726</v>
+        <v>569577</v>
       </c>
       <c r="R29" t="n">
-        <v>6958097</v>
+        <v>6958213</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3498,7 +3508,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på tall</t>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3525,38 +3535,37 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128728019</v>
+        <v>128731489</v>
       </c>
       <c r="B30" t="n">
-        <v>57723</v>
+        <v>98659</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>45</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3565,10 +3574,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>569577</v>
+        <v>569752</v>
       </c>
       <c r="R30" t="n">
-        <v>6958213</v>
+        <v>6958091</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3601,11 +3610,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3632,49 +3636,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128731489</v>
+        <v>128729068</v>
       </c>
       <c r="B31" t="n">
-        <v>98659</v>
+        <v>80169</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>569752</v>
+        <v>569604</v>
       </c>
       <c r="R31" t="n">
-        <v>6958091</v>
+        <v>6958176</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3844,10 +3844,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128730513</v>
+        <v>128730603</v>
       </c>
       <c r="B33" t="n">
-        <v>80140</v>
+        <v>57723</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3855,34 +3855,39 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>569656</v>
+        <v>569738</v>
       </c>
       <c r="R33" t="n">
-        <v>6958093</v>
+        <v>6958117</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3915,6 +3920,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Äldre exemplar av ringhack på Tall från tretåig hackspett</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3941,10 +3951,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128730603</v>
+        <v>128730513</v>
       </c>
       <c r="B34" t="n">
-        <v>57723</v>
+        <v>80140</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3952,39 +3962,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>569738</v>
+        <v>569656</v>
       </c>
       <c r="R34" t="n">
-        <v>6958117</v>
+        <v>6958093</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4017,11 +4022,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Äldre exemplar av ringhack på Tall från tretåig hackspett</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4048,49 +4048,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128732677</v>
+        <v>128728318</v>
       </c>
       <c r="B35" t="n">
-        <v>98659</v>
+        <v>79035</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>569817</v>
+        <v>569616</v>
       </c>
       <c r="R35" t="n">
-        <v>6958134</v>
+        <v>6958208</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4149,32 +4145,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128743255</v>
+        <v>128731677</v>
       </c>
       <c r="B36" t="n">
-        <v>98659</v>
+        <v>79035</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4184,10 +4180,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>569613</v>
+        <v>569769</v>
       </c>
       <c r="R36" t="n">
-        <v>6957995</v>
+        <v>6958153</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4220,11 +4216,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>28 exemplar knärot</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4251,45 +4242,50 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128743254</v>
+        <v>128729745</v>
       </c>
       <c r="B37" t="n">
-        <v>98659</v>
+        <v>57723</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>569547</v>
+        <v>569694</v>
       </c>
       <c r="R37" t="n">
-        <v>6958078</v>
+        <v>6958144</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4326,7 +4322,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>20 (ca) exemplar</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4353,45 +4349,49 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128728318</v>
+        <v>128732677</v>
       </c>
       <c r="B38" t="n">
-        <v>79035</v>
+        <v>98659</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>569616</v>
+        <v>569817</v>
       </c>
       <c r="R38" t="n">
-        <v>6958208</v>
+        <v>6958134</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4450,32 +4450,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128731677</v>
+        <v>128743255</v>
       </c>
       <c r="B39" t="n">
-        <v>79035</v>
+        <v>98659</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4485,10 +4485,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>569769</v>
+        <v>569613</v>
       </c>
       <c r="R39" t="n">
-        <v>6958153</v>
+        <v>6957995</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4521,6 +4521,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>28 exemplar knärot</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4547,50 +4552,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128729745</v>
+        <v>128743254</v>
       </c>
       <c r="B40" t="n">
-        <v>57723</v>
+        <v>98659</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>569694</v>
+        <v>569547</v>
       </c>
       <c r="R40" t="n">
-        <v>6958144</v>
+        <v>6958078</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4627,7 +4627,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>20 (ca) exemplar</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4654,10 +4654,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128729439</v>
+        <v>128729962</v>
       </c>
       <c r="B41" t="n">
-        <v>91526</v>
+        <v>80140</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4665,21 +4665,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4689,10 +4689,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>569703</v>
+        <v>569643</v>
       </c>
       <c r="R41" t="n">
-        <v>6958175</v>
+        <v>6958117</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4751,10 +4751,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128729962</v>
+        <v>128730475</v>
       </c>
       <c r="B42" t="n">
-        <v>80140</v>
+        <v>57723</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4762,34 +4762,39 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>569643</v>
+        <v>569675</v>
       </c>
       <c r="R42" t="n">
-        <v>6958117</v>
+        <v>6958098</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4822,6 +4827,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4848,10 +4858,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128730475</v>
+        <v>128728473</v>
       </c>
       <c r="B43" t="n">
-        <v>57723</v>
+        <v>57883</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4859,27 +4869,27 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -4888,10 +4898,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>569675</v>
+        <v>569608</v>
       </c>
       <c r="R43" t="n">
-        <v>6958098</v>
+        <v>6958227</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4924,11 +4934,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4955,10 +4960,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128728473</v>
+        <v>128729439</v>
       </c>
       <c r="B44" t="n">
-        <v>57883</v>
+        <v>91526</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4966,39 +4971,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>569608</v>
+        <v>569703</v>
       </c>
       <c r="R44" t="n">
-        <v>6958227</v>
+        <v>6958175</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5057,38 +5057,37 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128728902</v>
+        <v>128732627</v>
       </c>
       <c r="B45" t="n">
-        <v>57723</v>
+        <v>98659</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>6</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -5097,10 +5096,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>569673</v>
+        <v>569821</v>
       </c>
       <c r="R45" t="n">
-        <v>6958225</v>
+        <v>6958151</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5137,7 +5136,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>Kan finnas mer I blåbärsriset och mossan</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5164,38 +5163,37 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128731799</v>
+        <v>128728348</v>
       </c>
       <c r="B46" t="n">
-        <v>57723</v>
+        <v>98659</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>300</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -5204,10 +5202,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>569774</v>
+        <v>569616</v>
       </c>
       <c r="R46" t="n">
-        <v>6958163</v>
+        <v>6958208</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5240,11 +5238,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5271,7 +5264,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128732015</v>
+        <v>128731799</v>
       </c>
       <c r="B47" t="n">
         <v>57723</v>
@@ -5302,7 +5295,7 @@
       <c r="I47" t="inlineStr"/>
       <c r="M47" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -5311,10 +5304,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>569816</v>
+        <v>569774</v>
       </c>
       <c r="R47" t="n">
-        <v>6958081</v>
+        <v>6958163</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5351,7 +5344,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5378,7 +5371,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128738187</v>
+        <v>128732015</v>
       </c>
       <c r="B48" t="n">
         <v>57723</v>
@@ -5418,10 +5411,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>569681</v>
+        <v>569816</v>
       </c>
       <c r="R48" t="n">
-        <v>6957939</v>
+        <v>6958081</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5485,37 +5478,38 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128732627</v>
+        <v>128738187</v>
       </c>
       <c r="B49" t="n">
-        <v>98659</v>
+        <v>57723</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>6</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -5524,10 +5518,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>569821</v>
+        <v>569681</v>
       </c>
       <c r="R49" t="n">
-        <v>6958151</v>
+        <v>6957939</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5564,7 +5558,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Kan finnas mer I blåbärsriset och mossan</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5591,37 +5585,38 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128728348</v>
+        <v>128728902</v>
       </c>
       <c r="B50" t="n">
-        <v>98659</v>
+        <v>57723</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>300</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -5630,10 +5625,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>569616</v>
+        <v>569673</v>
       </c>
       <c r="R50" t="n">
-        <v>6958208</v>
+        <v>6958225</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5666,6 +5661,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5692,49 +5692,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128729573</v>
+        <v>128731302</v>
       </c>
       <c r="B51" t="n">
-        <v>98659</v>
+        <v>80100</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>229497</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>569706</v>
+        <v>569696</v>
       </c>
       <c r="R51" t="n">
-        <v>6958159</v>
+        <v>6958031</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5793,45 +5789,49 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128731302</v>
+        <v>128729573</v>
       </c>
       <c r="B52" t="n">
-        <v>80100</v>
+        <v>98659</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>229497</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>569696</v>
+        <v>569706</v>
       </c>
       <c r="R52" t="n">
-        <v>6958031</v>
+        <v>6958159</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5890,7 +5890,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128731037</v>
+        <v>128738306</v>
       </c>
       <c r="B53" t="n">
         <v>57723</v>
@@ -5921,7 +5921,7 @@
       <c r="I53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -5930,10 +5930,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>569673</v>
+        <v>569644</v>
       </c>
       <c r="R53" t="n">
-        <v>6958037</v>
+        <v>6957965</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5997,7 +5997,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128738306</v>
+        <v>128732183</v>
       </c>
       <c r="B54" t="n">
         <v>57723</v>
@@ -6037,10 +6037,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>569644</v>
+        <v>569777</v>
       </c>
       <c r="R54" t="n">
-        <v>6957965</v>
+        <v>6958189</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6077,7 +6077,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6104,7 +6104,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128732183</v>
+        <v>128731037</v>
       </c>
       <c r="B55" t="n">
         <v>57723</v>
@@ -6135,7 +6135,7 @@
       <c r="I55" t="inlineStr"/>
       <c r="M55" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -6144,10 +6144,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>569777</v>
+        <v>569673</v>
       </c>
       <c r="R55" t="n">
-        <v>6958189</v>
+        <v>6958037</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6184,7 +6184,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6211,50 +6211,45 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128730490</v>
+        <v>128728592</v>
       </c>
       <c r="B56" t="n">
-        <v>57723</v>
+        <v>80175</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>569707</v>
+        <v>569604</v>
       </c>
       <c r="R56" t="n">
-        <v>6958131</v>
+        <v>6958176</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6287,11 +6282,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Både äldre och färska spår ( Ringhack av tretåig hackspett på tall)</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6318,50 +6308,45 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128730422</v>
+        <v>128732124</v>
       </c>
       <c r="B57" t="n">
-        <v>57723</v>
+        <v>80175</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>569703</v>
+        <v>569816</v>
       </c>
       <c r="R57" t="n">
-        <v>6958116</v>
+        <v>6958081</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6394,11 +6379,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6425,50 +6405,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128739287</v>
+        <v>128730101</v>
       </c>
       <c r="B58" t="n">
-        <v>57723</v>
+        <v>80176</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>569481</v>
+        <v>569630</v>
       </c>
       <c r="R58" t="n">
-        <v>6958122</v>
+        <v>6958139</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6501,11 +6476,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6532,10 +6502,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128730183</v>
+        <v>128731387</v>
       </c>
       <c r="B59" t="n">
-        <v>80100</v>
+        <v>80168</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6543,21 +6513,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>229497</v>
+        <v>6461</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6567,10 +6537,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>569630</v>
+        <v>569740</v>
       </c>
       <c r="R59" t="n">
-        <v>6958129</v>
+        <v>6958091</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6629,10 +6599,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128728592</v>
+        <v>128732806</v>
       </c>
       <c r="B60" t="n">
-        <v>80175</v>
+        <v>91537</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6640,21 +6610,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6463</v>
+        <v>1205</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6664,10 +6634,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>569604</v>
+        <v>569827</v>
       </c>
       <c r="R60" t="n">
-        <v>6958176</v>
+        <v>6958133</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6726,32 +6696,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128732124</v>
+        <v>128732719</v>
       </c>
       <c r="B61" t="n">
-        <v>80175</v>
+        <v>91981</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6463</v>
+        <v>1209</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6761,10 +6731,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>569816</v>
+        <v>569821</v>
       </c>
       <c r="R61" t="n">
-        <v>6958081</v>
+        <v>6958151</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6823,45 +6793,50 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128730101</v>
+        <v>128739287</v>
       </c>
       <c r="B62" t="n">
-        <v>80176</v>
+        <v>57723</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>569630</v>
+        <v>569481</v>
       </c>
       <c r="R62" t="n">
-        <v>6958139</v>
+        <v>6958122</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6894,6 +6869,11 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6920,45 +6900,50 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128731387</v>
+        <v>128730490</v>
       </c>
       <c r="B63" t="n">
-        <v>80168</v>
+        <v>57723</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6461</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>569740</v>
+        <v>569707</v>
       </c>
       <c r="R63" t="n">
-        <v>6958091</v>
+        <v>6958131</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6991,6 +6976,11 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Både äldre och färska spår ( Ringhack av tretåig hackspett på tall)</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7017,45 +7007,50 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128732806</v>
+        <v>128730422</v>
       </c>
       <c r="B64" t="n">
-        <v>91537</v>
+        <v>57723</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1205</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>569827</v>
+        <v>569703</v>
       </c>
       <c r="R64" t="n">
-        <v>6958133</v>
+        <v>6958116</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7088,6 +7083,11 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7114,32 +7114,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128732719</v>
+        <v>128730183</v>
       </c>
       <c r="B65" t="n">
-        <v>91981</v>
+        <v>80100</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1209</v>
+        <v>229497</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7149,10 +7149,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>569821</v>
+        <v>569630</v>
       </c>
       <c r="R65" t="n">
-        <v>6958151</v>
+        <v>6958129</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7502,32 +7502,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128743263</v>
+        <v>128731693</v>
       </c>
       <c r="B69" t="n">
-        <v>92855</v>
+        <v>91526</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>5964</v>
+        <v>1202</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7537,10 +7537,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>569517</v>
+        <v>569793</v>
       </c>
       <c r="R69" t="n">
-        <v>6958123</v>
+        <v>6958092</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7573,11 +7573,6 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>3 exemplar</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7604,50 +7599,45 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128732493</v>
+        <v>128743263</v>
       </c>
       <c r="B70" t="n">
-        <v>57723</v>
+        <v>92855</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>5964</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>569795</v>
+        <v>569517</v>
       </c>
       <c r="R70" t="n">
-        <v>6958154</v>
+        <v>6958123</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7684,7 +7674,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>3 exemplar</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7711,7 +7701,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128730998</v>
+        <v>128732493</v>
       </c>
       <c r="B71" t="n">
         <v>57723</v>
@@ -7751,10 +7741,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>569670</v>
+        <v>569795</v>
       </c>
       <c r="R71" t="n">
-        <v>6958060</v>
+        <v>6958154</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7791,7 +7781,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Ringhack på tall. Även äldre</t>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7818,10 +7808,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128731693</v>
+        <v>128730928</v>
       </c>
       <c r="B72" t="n">
-        <v>91526</v>
+        <v>57723</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7829,34 +7819,42 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>569793</v>
+        <v>569673</v>
       </c>
       <c r="R72" t="n">
-        <v>6958092</v>
+        <v>6958076</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7889,6 +7887,11 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Påbörjat bobygge av sannolikt tretåig hackspett. Ser ut att vara relativt färskt. 2 meter upp i död gran. Omkring 4,5 cm i diameter.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8022,7 +8025,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128730928</v>
+        <v>128730998</v>
       </c>
       <c r="B74" t="n">
         <v>57723</v>
@@ -8051,24 +8054,21 @@
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
       <c r="M74" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N74" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>569673</v>
+        <v>569670</v>
       </c>
       <c r="R74" t="n">
-        <v>6958076</v>
+        <v>6958060</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8105,7 +8105,7 @@
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Påbörjat bobygge av sannolikt tretåig hackspett. Ser ut att vara relativt färskt. 2 meter upp i död gran. Omkring 4,5 cm i diameter.</t>
+          <t>Ringhack på tall. Även äldre</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8229,7 +8229,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128743247</v>
+        <v>128732848</v>
       </c>
       <c r="B76" t="n">
         <v>57723</v>
@@ -8258,16 +8258,21 @@
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>569714</v>
+        <v>569873</v>
       </c>
       <c r="R76" t="n">
-        <v>6957901</v>
+        <v>6958099</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8304,7 +8309,7 @@
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på gran ( färska spår)</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8331,7 +8336,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128732848</v>
+        <v>128743247</v>
       </c>
       <c r="B77" t="n">
         <v>57723</v>
@@ -8360,21 +8365,16 @@
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>569873</v>
+        <v>569714</v>
       </c>
       <c r="R77" t="n">
-        <v>6958099</v>
+        <v>6957901</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8411,7 +8411,7 @@
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack av tretåig hackspett på gran ( färska spår)</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8438,37 +8438,38 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128732718</v>
+        <v>128731284</v>
       </c>
       <c r="B78" t="n">
-        <v>98659</v>
+        <v>57883</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>18</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
@@ -8477,10 +8478,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>569834</v>
+        <v>569677</v>
       </c>
       <c r="R78" t="n">
-        <v>6958143</v>
+        <v>6958066</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8539,7 +8540,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128733005</v>
+        <v>128732718</v>
       </c>
       <c r="B79" t="n">
         <v>98659</v>
@@ -8569,7 +8570,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>18</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
@@ -8578,10 +8579,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>569882</v>
+        <v>569834</v>
       </c>
       <c r="R79" t="n">
-        <v>6958106</v>
+        <v>6958143</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8640,38 +8641,37 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128731284</v>
+        <v>128733005</v>
       </c>
       <c r="B80" t="n">
-        <v>57883</v>
+        <v>98659</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>7</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
@@ -8680,10 +8680,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>569677</v>
+        <v>569882</v>
       </c>
       <c r="R80" t="n">
-        <v>6958066</v>
+        <v>6958106</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8742,10 +8742,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128728434</v>
+        <v>128731226</v>
       </c>
       <c r="B81" t="n">
-        <v>57723</v>
+        <v>91544</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8753,39 +8753,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>569608</v>
+        <v>569705</v>
       </c>
       <c r="R81" t="n">
-        <v>6958227</v>
+        <v>6958098</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8818,11 +8813,6 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8946,10 +8936,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128731226</v>
+        <v>128728434</v>
       </c>
       <c r="B83" t="n">
-        <v>91544</v>
+        <v>57723</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8957,34 +8947,39 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>569705</v>
+        <v>569608</v>
       </c>
       <c r="R83" t="n">
-        <v>6958098</v>
+        <v>6958227</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9017,6 +9012,11 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9542,7 +9542,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128727978</v>
+        <v>128729666</v>
       </c>
       <c r="B89" t="n">
         <v>57723</v>
@@ -9582,10 +9582,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>569564</v>
+        <v>569706</v>
       </c>
       <c r="R89" t="n">
-        <v>6958213</v>
+        <v>6958159</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9622,7 +9622,7 @@
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9649,7 +9649,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128729666</v>
+        <v>128727978</v>
       </c>
       <c r="B90" t="n">
         <v>57723</v>
@@ -9689,10 +9689,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>569706</v>
+        <v>569564</v>
       </c>
       <c r="R90" t="n">
-        <v>6958159</v>
+        <v>6958213</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9729,7 +9729,7 @@
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9853,45 +9853,49 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128728152</v>
+        <v>128731648</v>
       </c>
       <c r="B92" t="n">
-        <v>91526</v>
+        <v>98659</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>569577</v>
+        <v>569766</v>
       </c>
       <c r="R92" t="n">
-        <v>6958213</v>
+        <v>6958144</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9924,6 +9928,11 @@
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>Ca ( möjligtvis fler)</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -9950,50 +9959,45 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128728274</v>
+        <v>128743253</v>
       </c>
       <c r="B93" t="n">
-        <v>57723</v>
+        <v>98659</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>569599</v>
+        <v>569641</v>
       </c>
       <c r="R93" t="n">
-        <v>6958201</v>
+        <v>6957953</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10030,7 +10034,7 @@
       </c>
       <c r="AC93" t="inlineStr">
         <is>
-          <t>Både äldre och färska ringhack på tall</t>
+          <t>55 exemplar knärötter</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10057,7 +10061,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128731648</v>
+        <v>128743256</v>
       </c>
       <c r="B94" t="n">
         <v>98659</v>
@@ -10085,21 +10089,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>119</t>
-        </is>
-      </c>
+      <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>569766</v>
+        <v>569647</v>
       </c>
       <c r="R94" t="n">
-        <v>6958144</v>
+        <v>6957950</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10136,7 +10136,7 @@
       </c>
       <c r="AC94" t="inlineStr">
         <is>
-          <t>Ca ( möjligtvis fler)</t>
+          <t>23 exemplar</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10163,32 +10163,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128743253</v>
+        <v>128728152</v>
       </c>
       <c r="B95" t="n">
-        <v>98659</v>
+        <v>91526</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10198,10 +10198,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>569641</v>
+        <v>569577</v>
       </c>
       <c r="R95" t="n">
-        <v>6957953</v>
+        <v>6958213</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10234,11 +10234,6 @@
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>55 exemplar knärötter</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10265,45 +10260,50 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128743256</v>
+        <v>128728274</v>
       </c>
       <c r="B96" t="n">
-        <v>98659</v>
+        <v>57723</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P96" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>569647</v>
+        <v>569599</v>
       </c>
       <c r="R96" t="n">
-        <v>6957950</v>
+        <v>6958201</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10340,7 +10340,7 @@
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>23 exemplar</t>
+          <t>Både äldre och färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD96" t="b">

--- a/artfynd/A 39666-2025 artfynd.xlsx
+++ b/artfynd/A 39666-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128739007</v>
+        <v>128743246</v>
       </c>
       <c r="B2" t="n">
         <v>57723</v>
@@ -704,21 +704,16 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>569542</v>
+        <v>569648</v>
       </c>
       <c r="R2" t="n">
-        <v>6958069</v>
+        <v>6957944</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +750,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack av tretåig hackspett på Tall ( äldre och färska spår)</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -889,7 +884,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128743246</v>
+        <v>128739007</v>
       </c>
       <c r="B4" t="n">
         <v>57723</v>
@@ -918,16 +913,21 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>569648</v>
+        <v>569542</v>
       </c>
       <c r="R4" t="n">
-        <v>6957944</v>
+        <v>6958069</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,7 +964,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall ( äldre och färska spår)</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1290,10 +1290,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128729409</v>
+        <v>128730130</v>
       </c>
       <c r="B8" t="n">
-        <v>91526</v>
+        <v>57723</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1301,34 +1301,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>569700</v>
+        <v>569713</v>
       </c>
       <c r="R8" t="n">
-        <v>6958164</v>
+        <v>6958138</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1361,6 +1366,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1387,10 +1397,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128730130</v>
+        <v>128729409</v>
       </c>
       <c r="B9" t="n">
-        <v>57723</v>
+        <v>91526</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1398,39 +1408,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>569713</v>
+        <v>569700</v>
       </c>
       <c r="R9" t="n">
-        <v>6958138</v>
+        <v>6958164</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1463,11 +1468,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1494,32 +1494,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128730571</v>
+        <v>128733181</v>
       </c>
       <c r="B10" t="n">
-        <v>91544</v>
+        <v>98576</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>219790</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1529,10 +1529,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>569660</v>
+        <v>569900</v>
       </c>
       <c r="R10" t="n">
-        <v>6958074</v>
+        <v>6958101</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1688,10 +1688,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128743245</v>
+        <v>128730571</v>
       </c>
       <c r="B12" t="n">
-        <v>57723</v>
+        <v>91544</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1699,21 +1699,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1723,10 +1723,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>569590</v>
+        <v>569660</v>
       </c>
       <c r="R12" t="n">
-        <v>6958014</v>
+        <v>6958074</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1759,11 +1759,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall ( färska spår)</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1790,7 +1785,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128732276</v>
+        <v>128743245</v>
       </c>
       <c r="B13" t="n">
         <v>57723</v>
@@ -1819,21 +1814,16 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>569841</v>
+        <v>569590</v>
       </c>
       <c r="R13" t="n">
-        <v>6958102</v>
+        <v>6958014</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1870,7 +1860,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack av tretåig hackspett på Tall ( färska spår)</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1897,10 +1887,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128732217</v>
+        <v>128732276</v>
       </c>
       <c r="B14" t="n">
-        <v>57883</v>
+        <v>57723</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1908,36 +1898,27 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -1946,10 +1927,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>569777</v>
+        <v>569841</v>
       </c>
       <c r="R14" t="n">
-        <v>6958189</v>
+        <v>6958102</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1986,7 +1967,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>2 talltitor kommer flygandes väldigt närgånget och varnar</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2013,45 +1994,59 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128733181</v>
+        <v>128732217</v>
       </c>
       <c r="B15" t="n">
-        <v>98576</v>
+        <v>57883</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219790</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>569900</v>
+        <v>569777</v>
       </c>
       <c r="R15" t="n">
-        <v>6958101</v>
+        <v>6958189</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2084,6 +2079,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>2 talltitor kommer flygandes väldigt närgånget och varnar</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2217,45 +2217,49 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128728515</v>
+        <v>128731490</v>
       </c>
       <c r="B17" t="n">
-        <v>97530</v>
+        <v>98659</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>569608</v>
+        <v>569759</v>
       </c>
       <c r="R17" t="n">
-        <v>6958227</v>
+        <v>6958118</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2314,7 +2318,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128731490</v>
+        <v>128730429</v>
       </c>
       <c r="B18" t="n">
         <v>98659</v>
@@ -2344,7 +2348,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>80</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2353,10 +2357,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>569759</v>
+        <v>569683</v>
       </c>
       <c r="R18" t="n">
-        <v>6958118</v>
+        <v>6958128</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2415,49 +2419,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128730429</v>
+        <v>128728515</v>
       </c>
       <c r="B19" t="n">
-        <v>98659</v>
+        <v>97530</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>569683</v>
+        <v>569608</v>
       </c>
       <c r="R19" t="n">
-        <v>6958128</v>
+        <v>6958227</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2710,49 +2710,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128730720</v>
+        <v>128728022</v>
       </c>
       <c r="B22" t="n">
-        <v>98659</v>
+        <v>91491</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>569692</v>
+        <v>569583</v>
       </c>
       <c r="R22" t="n">
-        <v>6958094</v>
+        <v>6958204</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2785,11 +2781,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ca</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2816,32 +2807,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128743252</v>
+        <v>128743262</v>
       </c>
       <c r="B23" t="n">
-        <v>98659</v>
+        <v>79035</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2851,10 +2842,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>569610</v>
+        <v>569732</v>
       </c>
       <c r="R23" t="n">
-        <v>6958005</v>
+        <v>6957870</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2887,11 +2878,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>2 exemplar</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2918,45 +2904,50 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128728022</v>
+        <v>128731107</v>
       </c>
       <c r="B24" t="n">
-        <v>91491</v>
+        <v>57883</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5447</v>
+        <v>103021</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>569583</v>
+        <v>569705</v>
       </c>
       <c r="R24" t="n">
-        <v>6958204</v>
+        <v>6958098</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3015,10 +3006,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128743262</v>
+        <v>128739020</v>
       </c>
       <c r="B25" t="n">
-        <v>79035</v>
+        <v>57723</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3026,34 +3017,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>569732</v>
+        <v>569542</v>
       </c>
       <c r="R25" t="n">
-        <v>6957870</v>
+        <v>6958049</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3086,6 +3082,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3112,38 +3113,37 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128739020</v>
+        <v>128730720</v>
       </c>
       <c r="B26" t="n">
-        <v>57723</v>
+        <v>98659</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>50</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3152,10 +3152,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>569542</v>
+        <v>569692</v>
       </c>
       <c r="R26" t="n">
-        <v>6958049</v>
+        <v>6958094</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3192,7 +3192,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ca</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3219,50 +3219,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128731107</v>
+        <v>128743252</v>
       </c>
       <c r="B27" t="n">
-        <v>57883</v>
+        <v>98659</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>569705</v>
+        <v>569610</v>
       </c>
       <c r="R27" t="n">
-        <v>6958098</v>
+        <v>6958005</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3295,6 +3290,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>2 exemplar</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3321,50 +3321,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128731291</v>
+        <v>128729068</v>
       </c>
       <c r="B28" t="n">
-        <v>57723</v>
+        <v>80169</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>569726</v>
+        <v>569604</v>
       </c>
       <c r="R28" t="n">
-        <v>6958097</v>
+        <v>6958176</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3397,11 +3392,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på tall</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3428,7 +3418,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128728019</v>
+        <v>128731291</v>
       </c>
       <c r="B29" t="n">
         <v>57723</v>
@@ -3468,10 +3458,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>569577</v>
+        <v>569726</v>
       </c>
       <c r="R29" t="n">
-        <v>6958213</v>
+        <v>6958097</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3508,7 +3498,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>Ringhack av tretåig hackspett på tall</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3535,37 +3525,38 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128731489</v>
+        <v>128728019</v>
       </c>
       <c r="B30" t="n">
-        <v>98659</v>
+        <v>57723</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>45</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3574,10 +3565,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>569752</v>
+        <v>569577</v>
       </c>
       <c r="R30" t="n">
-        <v>6958091</v>
+        <v>6958213</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3610,6 +3601,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3636,45 +3632,49 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128729068</v>
+        <v>128731489</v>
       </c>
       <c r="B31" t="n">
-        <v>80169</v>
+        <v>98659</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>569604</v>
+        <v>569752</v>
       </c>
       <c r="R31" t="n">
-        <v>6958176</v>
+        <v>6958091</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3844,10 +3844,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128730603</v>
+        <v>128730513</v>
       </c>
       <c r="B33" t="n">
-        <v>57723</v>
+        <v>80140</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3855,39 +3855,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>569738</v>
+        <v>569656</v>
       </c>
       <c r="R33" t="n">
-        <v>6958117</v>
+        <v>6958093</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3920,11 +3915,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Äldre exemplar av ringhack på Tall från tretåig hackspett</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3951,10 +3941,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128730513</v>
+        <v>128730603</v>
       </c>
       <c r="B34" t="n">
-        <v>80140</v>
+        <v>57723</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3962,34 +3952,39 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>569656</v>
+        <v>569738</v>
       </c>
       <c r="R34" t="n">
-        <v>6958093</v>
+        <v>6958117</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4022,6 +4017,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Äldre exemplar av ringhack på Tall från tretåig hackspett</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4751,10 +4751,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128730475</v>
+        <v>128728473</v>
       </c>
       <c r="B42" t="n">
-        <v>57723</v>
+        <v>57883</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4762,27 +4762,27 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -4791,10 +4791,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>569675</v>
+        <v>569608</v>
       </c>
       <c r="R42" t="n">
-        <v>6958098</v>
+        <v>6958227</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4827,11 +4827,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4858,10 +4853,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128728473</v>
+        <v>128730475</v>
       </c>
       <c r="B43" t="n">
-        <v>57883</v>
+        <v>57723</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4869,27 +4864,27 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -4898,10 +4893,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>569608</v>
+        <v>569675</v>
       </c>
       <c r="R43" t="n">
-        <v>6958227</v>
+        <v>6958098</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4934,6 +4929,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5371,7 +5371,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128732015</v>
+        <v>128738187</v>
       </c>
       <c r="B48" t="n">
         <v>57723</v>
@@ -5411,10 +5411,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>569816</v>
+        <v>569681</v>
       </c>
       <c r="R48" t="n">
-        <v>6958081</v>
+        <v>6957939</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5478,7 +5478,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128738187</v>
+        <v>128728902</v>
       </c>
       <c r="B49" t="n">
         <v>57723</v>
@@ -5518,10 +5518,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>569681</v>
+        <v>569673</v>
       </c>
       <c r="R49" t="n">
-        <v>6957939</v>
+        <v>6958225</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5558,7 +5558,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5585,7 +5585,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128728902</v>
+        <v>128732015</v>
       </c>
       <c r="B50" t="n">
         <v>57723</v>
@@ -5625,10 +5625,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>569673</v>
+        <v>569816</v>
       </c>
       <c r="R50" t="n">
-        <v>6958225</v>
+        <v>6958081</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5665,7 +5665,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5692,45 +5692,49 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128731302</v>
+        <v>128729573</v>
       </c>
       <c r="B51" t="n">
-        <v>80100</v>
+        <v>98659</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>229497</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>569696</v>
+        <v>569706</v>
       </c>
       <c r="R51" t="n">
-        <v>6958031</v>
+        <v>6958159</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5789,49 +5793,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128729573</v>
+        <v>128731302</v>
       </c>
       <c r="B52" t="n">
-        <v>98659</v>
+        <v>80100</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>229497</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>569706</v>
+        <v>569696</v>
       </c>
       <c r="R52" t="n">
-        <v>6958159</v>
+        <v>6958031</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5997,7 +5997,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128732183</v>
+        <v>128731037</v>
       </c>
       <c r="B54" t="n">
         <v>57723</v>
@@ -6028,7 +6028,7 @@
       <c r="I54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -6037,10 +6037,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>569777</v>
+        <v>569673</v>
       </c>
       <c r="R54" t="n">
-        <v>6958189</v>
+        <v>6958037</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6077,7 +6077,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6104,7 +6104,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128731037</v>
+        <v>128732183</v>
       </c>
       <c r="B55" t="n">
         <v>57723</v>
@@ -6135,7 +6135,7 @@
       <c r="I55" t="inlineStr"/>
       <c r="M55" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -6144,10 +6144,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>569673</v>
+        <v>569777</v>
       </c>
       <c r="R55" t="n">
-        <v>6958037</v>
+        <v>6958189</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6184,7 +6184,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6211,45 +6211,50 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128728592</v>
+        <v>128739287</v>
       </c>
       <c r="B56" t="n">
-        <v>80175</v>
+        <v>57723</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>569604</v>
+        <v>569481</v>
       </c>
       <c r="R56" t="n">
-        <v>6958176</v>
+        <v>6958122</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6282,6 +6287,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6308,45 +6318,50 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128732124</v>
+        <v>128730490</v>
       </c>
       <c r="B57" t="n">
-        <v>80175</v>
+        <v>57723</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>569816</v>
+        <v>569707</v>
       </c>
       <c r="R57" t="n">
-        <v>6958081</v>
+        <v>6958131</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6379,6 +6394,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Både äldre och färska spår ( Ringhack av tretåig hackspett på tall)</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6405,10 +6425,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128730101</v>
+        <v>128730183</v>
       </c>
       <c r="B58" t="n">
-        <v>80176</v>
+        <v>80100</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6416,21 +6436,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6464</v>
+        <v>229497</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6443,7 +6463,7 @@
         <v>569630</v>
       </c>
       <c r="R58" t="n">
-        <v>6958139</v>
+        <v>6958129</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6502,10 +6522,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128731387</v>
+        <v>128732806</v>
       </c>
       <c r="B59" t="n">
-        <v>80168</v>
+        <v>91537</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6513,21 +6533,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6461</v>
+        <v>1205</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6537,10 +6557,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>569740</v>
+        <v>569827</v>
       </c>
       <c r="R59" t="n">
-        <v>6958091</v>
+        <v>6958133</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6599,32 +6619,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128732806</v>
+        <v>128732719</v>
       </c>
       <c r="B60" t="n">
-        <v>91537</v>
+        <v>91981</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1205</v>
+        <v>1209</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6634,10 +6654,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>569827</v>
+        <v>569821</v>
       </c>
       <c r="R60" t="n">
-        <v>6958133</v>
+        <v>6958151</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6696,32 +6716,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128732719</v>
+        <v>128728592</v>
       </c>
       <c r="B61" t="n">
-        <v>91981</v>
+        <v>80175</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1209</v>
+        <v>6463</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6731,10 +6751,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>569821</v>
+        <v>569604</v>
       </c>
       <c r="R61" t="n">
-        <v>6958151</v>
+        <v>6958176</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6793,50 +6813,45 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128739287</v>
+        <v>128732124</v>
       </c>
       <c r="B62" t="n">
-        <v>57723</v>
+        <v>80175</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>569481</v>
+        <v>569816</v>
       </c>
       <c r="R62" t="n">
-        <v>6958122</v>
+        <v>6958081</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6869,11 +6884,6 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6900,50 +6910,45 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128730490</v>
+        <v>128730101</v>
       </c>
       <c r="B63" t="n">
-        <v>57723</v>
+        <v>80176</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>569707</v>
+        <v>569630</v>
       </c>
       <c r="R63" t="n">
-        <v>6958131</v>
+        <v>6958139</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6976,11 +6981,6 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Både äldre och färska spår ( Ringhack av tretåig hackspett på tall)</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7007,50 +7007,45 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128730422</v>
+        <v>128731387</v>
       </c>
       <c r="B64" t="n">
-        <v>57723</v>
+        <v>80168</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>569703</v>
+        <v>569740</v>
       </c>
       <c r="R64" t="n">
-        <v>6958116</v>
+        <v>6958091</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7083,11 +7078,6 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7114,45 +7104,50 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128730183</v>
+        <v>128730422</v>
       </c>
       <c r="B65" t="n">
-        <v>80100</v>
+        <v>57723</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>229497</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>569630</v>
+        <v>569703</v>
       </c>
       <c r="R65" t="n">
-        <v>6958129</v>
+        <v>6958116</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7185,6 +7180,11 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7211,7 +7211,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128729077</v>
+        <v>128732112</v>
       </c>
       <c r="B66" t="n">
         <v>80140</v>
@@ -7246,10 +7246,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>569604</v>
+        <v>569824</v>
       </c>
       <c r="R66" t="n">
-        <v>6958176</v>
+        <v>6958091</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7405,7 +7405,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128732112</v>
+        <v>128729077</v>
       </c>
       <c r="B68" t="n">
         <v>80140</v>
@@ -7440,10 +7440,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>569824</v>
+        <v>569604</v>
       </c>
       <c r="R68" t="n">
-        <v>6958091</v>
+        <v>6958176</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7701,7 +7701,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128732493</v>
+        <v>128728149</v>
       </c>
       <c r="B71" t="n">
         <v>57723</v>
@@ -7741,10 +7741,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>569795</v>
+        <v>569585</v>
       </c>
       <c r="R71" t="n">
-        <v>6958154</v>
+        <v>6958190</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7781,7 +7781,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7808,7 +7808,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128730928</v>
+        <v>128732493</v>
       </c>
       <c r="B72" t="n">
         <v>57723</v>
@@ -7837,24 +7837,21 @@
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
       <c r="M72" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N72" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>569673</v>
+        <v>569795</v>
       </c>
       <c r="R72" t="n">
-        <v>6958076</v>
+        <v>6958154</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7891,7 +7888,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Påbörjat bobygge av sannolikt tretåig hackspett. Ser ut att vara relativt färskt. 2 meter upp i död gran. Omkring 4,5 cm i diameter.</t>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7918,7 +7915,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128728149</v>
+        <v>128730998</v>
       </c>
       <c r="B73" t="n">
         <v>57723</v>
@@ -7958,10 +7955,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>569585</v>
+        <v>569670</v>
       </c>
       <c r="R73" t="n">
-        <v>6958190</v>
+        <v>6958060</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7998,7 +7995,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på tall. Även äldre</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8025,7 +8022,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128730998</v>
+        <v>128730928</v>
       </c>
       <c r="B74" t="n">
         <v>57723</v>
@@ -8054,21 +8051,24 @@
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
       <c r="M74" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>569670</v>
+        <v>569673</v>
       </c>
       <c r="R74" t="n">
-        <v>6958060</v>
+        <v>6958076</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8105,7 +8105,7 @@
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Ringhack på tall. Även äldre</t>
+          <t>Påbörjat bobygge av sannolikt tretåig hackspett. Ser ut att vara relativt färskt. 2 meter upp i död gran. Omkring 4,5 cm i diameter.</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8132,45 +8132,49 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128731100</v>
+        <v>128732718</v>
       </c>
       <c r="B75" t="n">
-        <v>91544</v>
+        <v>98659</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>569688</v>
+        <v>569834</v>
       </c>
       <c r="R75" t="n">
-        <v>6958069</v>
+        <v>6958143</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8229,38 +8233,37 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128732848</v>
+        <v>128733005</v>
       </c>
       <c r="B76" t="n">
-        <v>57723</v>
+        <v>98659</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>7</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
@@ -8269,10 +8272,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>569873</v>
+        <v>569882</v>
       </c>
       <c r="R76" t="n">
-        <v>6958099</v>
+        <v>6958106</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8305,11 +8308,6 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8336,10 +8334,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128743247</v>
+        <v>128731100</v>
       </c>
       <c r="B77" t="n">
-        <v>57723</v>
+        <v>91544</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8347,21 +8345,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8371,10 +8369,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>569714</v>
+        <v>569688</v>
       </c>
       <c r="R77" t="n">
-        <v>6957901</v>
+        <v>6958069</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8407,11 +8405,6 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på gran ( färska spår)</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8438,10 +8431,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128731284</v>
+        <v>128743247</v>
       </c>
       <c r="B78" t="n">
-        <v>57883</v>
+        <v>57723</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8449,39 +8442,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>569677</v>
+        <v>569714</v>
       </c>
       <c r="R78" t="n">
-        <v>6958066</v>
+        <v>6957901</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8514,6 +8502,11 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på gran ( färska spår)</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8540,37 +8533,38 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128732718</v>
+        <v>128732848</v>
       </c>
       <c r="B79" t="n">
-        <v>98659</v>
+        <v>57723</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>18</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
@@ -8579,10 +8573,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>569834</v>
+        <v>569873</v>
       </c>
       <c r="R79" t="n">
-        <v>6958143</v>
+        <v>6958099</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8615,6 +8609,11 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8641,37 +8640,38 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128733005</v>
+        <v>128731284</v>
       </c>
       <c r="B80" t="n">
-        <v>98659</v>
+        <v>57883</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>7</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
@@ -8680,10 +8680,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>569882</v>
+        <v>569677</v>
       </c>
       <c r="R80" t="n">
-        <v>6958106</v>
+        <v>6958066</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8936,38 +8936,37 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128728434</v>
+        <v>128729895</v>
       </c>
       <c r="B83" t="n">
-        <v>57723</v>
+        <v>98659</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>26</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
@@ -8976,10 +8975,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>569608</v>
+        <v>569713</v>
       </c>
       <c r="R83" t="n">
-        <v>6958227</v>
+        <v>6958138</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9012,11 +9011,6 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9043,7 +9037,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128729895</v>
+        <v>128743257</v>
       </c>
       <c r="B84" t="n">
         <v>98659</v>
@@ -9071,21 +9065,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
+      <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>569713</v>
+        <v>569656</v>
       </c>
       <c r="R84" t="n">
-        <v>6958138</v>
+        <v>6957942</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9118,6 +9108,11 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>23 exemplar (ca)</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9144,45 +9139,50 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128743257</v>
+        <v>128728434</v>
       </c>
       <c r="B85" t="n">
-        <v>98659</v>
+        <v>57723</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>569656</v>
+        <v>569608</v>
       </c>
       <c r="R85" t="n">
-        <v>6957942</v>
+        <v>6958227</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9219,7 +9219,7 @@
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>23 exemplar (ca)</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9542,7 +9542,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128729666</v>
+        <v>128727978</v>
       </c>
       <c r="B89" t="n">
         <v>57723</v>
@@ -9582,10 +9582,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>569706</v>
+        <v>569564</v>
       </c>
       <c r="R89" t="n">
-        <v>6958159</v>
+        <v>6958213</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9622,7 +9622,7 @@
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9649,7 +9649,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128727978</v>
+        <v>128729666</v>
       </c>
       <c r="B90" t="n">
         <v>57723</v>
@@ -9689,10 +9689,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>569564</v>
+        <v>569706</v>
       </c>
       <c r="R90" t="n">
-        <v>6958213</v>
+        <v>6958159</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9729,7 +9729,7 @@
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9853,49 +9853,45 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128731648</v>
+        <v>128728152</v>
       </c>
       <c r="B92" t="n">
-        <v>98659</v>
+        <v>91526</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>119</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>569766</v>
+        <v>569577</v>
       </c>
       <c r="R92" t="n">
-        <v>6958144</v>
+        <v>6958213</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9928,11 +9924,6 @@
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC92" t="inlineStr">
-        <is>
-          <t>Ca ( möjligtvis fler)</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -9959,45 +9950,50 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128743253</v>
+        <v>128728274</v>
       </c>
       <c r="B93" t="n">
-        <v>98659</v>
+        <v>57723</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>569641</v>
+        <v>569599</v>
       </c>
       <c r="R93" t="n">
-        <v>6957953</v>
+        <v>6958201</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10034,7 +10030,7 @@
       </c>
       <c r="AC93" t="inlineStr">
         <is>
-          <t>55 exemplar knärötter</t>
+          <t>Både äldre och färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10061,7 +10057,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128743256</v>
+        <v>128731648</v>
       </c>
       <c r="B94" t="n">
         <v>98659</v>
@@ -10089,17 +10085,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I94" t="inlineStr"/>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
       <c r="P94" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>569647</v>
+        <v>569766</v>
       </c>
       <c r="R94" t="n">
-        <v>6957950</v>
+        <v>6958144</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10136,7 +10136,7 @@
       </c>
       <c r="AC94" t="inlineStr">
         <is>
-          <t>23 exemplar</t>
+          <t>Ca ( möjligtvis fler)</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10163,32 +10163,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128728152</v>
+        <v>128743253</v>
       </c>
       <c r="B95" t="n">
-        <v>91526</v>
+        <v>98659</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10198,10 +10198,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>569577</v>
+        <v>569641</v>
       </c>
       <c r="R95" t="n">
-        <v>6958213</v>
+        <v>6957953</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10234,6 +10234,11 @@
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>55 exemplar knärötter</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10260,50 +10265,45 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128728274</v>
+        <v>128743256</v>
       </c>
       <c r="B96" t="n">
-        <v>57723</v>
+        <v>98659</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P96" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>569599</v>
+        <v>569647</v>
       </c>
       <c r="R96" t="n">
-        <v>6958201</v>
+        <v>6957950</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10340,7 +10340,7 @@
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>Både äldre och färska ringhack på tall</t>
+          <t>23 exemplar</t>
         </is>
       </c>
       <c r="AD96" t="b">

--- a/artfynd/A 39666-2025 artfynd.xlsx
+++ b/artfynd/A 39666-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128743246</v>
+        <v>128732386</v>
       </c>
       <c r="B2" t="n">
-        <v>57723</v>
+        <v>80144</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>569648</v>
+        <v>569785</v>
       </c>
       <c r="R2" t="n">
-        <v>6957944</v>
+        <v>6958124</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall ( äldre och färska spår)</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128728526</v>
+        <v>128743246</v>
       </c>
       <c r="B3" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -806,21 +801,16 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>569616</v>
+        <v>569648</v>
       </c>
       <c r="R3" t="n">
-        <v>6958208</v>
+        <v>6957944</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +847,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack av tretåig hackspett på Tall ( äldre och färska spår)</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,10 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128739007</v>
+        <v>128728526</v>
       </c>
       <c r="B4" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -924,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>569542</v>
+        <v>569616</v>
       </c>
       <c r="R4" t="n">
-        <v>6958069</v>
+        <v>6958208</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -991,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128732386</v>
+        <v>128739007</v>
       </c>
       <c r="B5" t="n">
-        <v>80140</v>
+        <v>57725</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1002,34 +992,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>569785</v>
+        <v>569542</v>
       </c>
       <c r="R5" t="n">
-        <v>6958124</v>
+        <v>6958069</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1062,6 +1057,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1091,7 +1091,7 @@
         <v>128728896</v>
       </c>
       <c r="B6" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
         <v>128732983</v>
       </c>
       <c r="B7" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         <v>128730130</v>
       </c>
       <c r="B8" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1400,7 +1400,7 @@
         <v>128729409</v>
       </c>
       <c r="B9" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1494,32 +1494,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128733181</v>
+        <v>128730571</v>
       </c>
       <c r="B10" t="n">
-        <v>98576</v>
+        <v>91551</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219790</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1529,10 +1529,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>569900</v>
+        <v>569660</v>
       </c>
       <c r="R10" t="n">
-        <v>6958101</v>
+        <v>6958074</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1594,7 +1594,7 @@
         <v>128732765</v>
       </c>
       <c r="B11" t="n">
-        <v>91811</v>
+        <v>91818</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1688,10 +1688,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128730571</v>
+        <v>128732276</v>
       </c>
       <c r="B12" t="n">
-        <v>91544</v>
+        <v>57725</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1699,34 +1699,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>569660</v>
+        <v>569841</v>
       </c>
       <c r="R12" t="n">
-        <v>6958074</v>
+        <v>6958102</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1759,6 +1764,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1788,7 +1798,7 @@
         <v>128743245</v>
       </c>
       <c r="B13" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1887,10 +1897,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128732276</v>
+        <v>128732217</v>
       </c>
       <c r="B14" t="n">
-        <v>57723</v>
+        <v>57885</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1898,27 +1908,36 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -1927,10 +1946,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>569841</v>
+        <v>569777</v>
       </c>
       <c r="R14" t="n">
-        <v>6958102</v>
+        <v>6958189</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1967,7 +1986,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>2 talltitor kommer flygandes väldigt närgånget och varnar</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1994,59 +2013,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128732217</v>
+        <v>128733181</v>
       </c>
       <c r="B15" t="n">
-        <v>57883</v>
+        <v>98586</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>219790</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>569777</v>
+        <v>569900</v>
       </c>
       <c r="R15" t="n">
-        <v>6958189</v>
+        <v>6958101</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2079,11 +2084,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>2 talltitor kommer flygandes väldigt närgånget och varnar</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2110,38 +2110,37 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128731601</v>
+        <v>128731490</v>
       </c>
       <c r="B16" t="n">
-        <v>57723</v>
+        <v>98669</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>20</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2150,10 +2149,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>569752</v>
+        <v>569759</v>
       </c>
       <c r="R16" t="n">
-        <v>6958091</v>
+        <v>6958118</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2186,11 +2185,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2217,10 +2211,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128731490</v>
+        <v>128730429</v>
       </c>
       <c r="B17" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2247,7 +2241,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>80</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2256,10 +2250,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>569759</v>
+        <v>569683</v>
       </c>
       <c r="R17" t="n">
-        <v>6958118</v>
+        <v>6958128</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2318,49 +2312,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128730429</v>
+        <v>128728515</v>
       </c>
       <c r="B18" t="n">
-        <v>98659</v>
+        <v>97540</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>569683</v>
+        <v>569608</v>
       </c>
       <c r="R18" t="n">
-        <v>6958128</v>
+        <v>6958227</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2419,45 +2409,50 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128728515</v>
+        <v>128731601</v>
       </c>
       <c r="B19" t="n">
-        <v>97530</v>
+        <v>57725</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>569608</v>
+        <v>569752</v>
       </c>
       <c r="R19" t="n">
-        <v>6958227</v>
+        <v>6958091</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2490,6 +2485,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2516,10 +2516,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128732359</v>
+        <v>128731107</v>
       </c>
       <c r="B20" t="n">
-        <v>91526</v>
+        <v>57885</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2527,34 +2527,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>569820</v>
+        <v>569705</v>
       </c>
       <c r="R20" t="n">
-        <v>6958107</v>
+        <v>6958098</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2613,45 +2618,49 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128731612</v>
+        <v>128730720</v>
       </c>
       <c r="B21" t="n">
-        <v>91526</v>
+        <v>98669</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>569752</v>
+        <v>569692</v>
       </c>
       <c r="R21" t="n">
-        <v>6958091</v>
+        <v>6958094</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2684,6 +2693,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ca</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2710,32 +2724,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128728022</v>
+        <v>128743252</v>
       </c>
       <c r="B22" t="n">
-        <v>91491</v>
+        <v>98669</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2745,10 +2759,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>569583</v>
+        <v>569610</v>
       </c>
       <c r="R22" t="n">
-        <v>6958204</v>
+        <v>6958005</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2781,6 +2795,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>2 exemplar</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2807,10 +2826,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128743262</v>
+        <v>128731612</v>
       </c>
       <c r="B23" t="n">
-        <v>79035</v>
+        <v>91533</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2818,21 +2837,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2842,10 +2861,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>569732</v>
+        <v>569752</v>
       </c>
       <c r="R23" t="n">
-        <v>6957870</v>
+        <v>6958091</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2904,50 +2923,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128731107</v>
+        <v>128728022</v>
       </c>
       <c r="B24" t="n">
-        <v>57883</v>
+        <v>91497</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103021</v>
+        <v>5447</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>569705</v>
+        <v>569583</v>
       </c>
       <c r="R24" t="n">
-        <v>6958098</v>
+        <v>6958204</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3006,10 +3020,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128739020</v>
+        <v>128743262</v>
       </c>
       <c r="B25" t="n">
-        <v>57723</v>
+        <v>79039</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3017,39 +3031,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>569542</v>
+        <v>569732</v>
       </c>
       <c r="R25" t="n">
-        <v>6958049</v>
+        <v>6957870</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3082,11 +3091,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3113,37 +3117,38 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128730720</v>
+        <v>128739020</v>
       </c>
       <c r="B26" t="n">
-        <v>98659</v>
+        <v>57725</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>50</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3152,10 +3157,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>569692</v>
+        <v>569542</v>
       </c>
       <c r="R26" t="n">
-        <v>6958094</v>
+        <v>6958049</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3192,7 +3197,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ca</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3219,32 +3224,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128743252</v>
+        <v>128732359</v>
       </c>
       <c r="B27" t="n">
-        <v>98659</v>
+        <v>91533</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3254,10 +3259,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>569610</v>
+        <v>569820</v>
       </c>
       <c r="R27" t="n">
-        <v>6958005</v>
+        <v>6958107</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3290,11 +3295,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>2 exemplar</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3324,7 +3324,7 @@
         <v>128729068</v>
       </c>
       <c r="B28" t="n">
-        <v>80169</v>
+        <v>80173</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3421,7 +3421,7 @@
         <v>128731291</v>
       </c>
       <c r="B29" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3528,7 +3528,7 @@
         <v>128728019</v>
       </c>
       <c r="B30" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3635,7 +3635,7 @@
         <v>128731489</v>
       </c>
       <c r="B31" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3736,7 +3736,7 @@
         <v>128728767</v>
       </c>
       <c r="B32" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3847,7 +3847,7 @@
         <v>128730513</v>
       </c>
       <c r="B33" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3944,7 +3944,7 @@
         <v>128730603</v>
       </c>
       <c r="B34" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4051,7 +4051,7 @@
         <v>128728318</v>
       </c>
       <c r="B35" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4148,7 +4148,7 @@
         <v>128731677</v>
       </c>
       <c r="B36" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4242,38 +4242,37 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128729745</v>
+        <v>128732677</v>
       </c>
       <c r="B37" t="n">
-        <v>57723</v>
+        <v>98669</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>12</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4282,10 +4281,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>569694</v>
+        <v>569817</v>
       </c>
       <c r="R37" t="n">
-        <v>6958144</v>
+        <v>6958134</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4318,11 +4317,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4349,10 +4343,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128732677</v>
+        <v>128743255</v>
       </c>
       <c r="B38" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4377,21 +4371,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>569817</v>
+        <v>569613</v>
       </c>
       <c r="R38" t="n">
-        <v>6958134</v>
+        <v>6957995</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4424,6 +4414,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>28 exemplar knärot</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4450,45 +4445,50 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128743255</v>
+        <v>128729745</v>
       </c>
       <c r="B39" t="n">
-        <v>98659</v>
+        <v>57725</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>569613</v>
+        <v>569694</v>
       </c>
       <c r="R39" t="n">
-        <v>6957995</v>
+        <v>6958144</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4525,7 +4525,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>28 exemplar knärot</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4555,7 +4555,7 @@
         <v>128743254</v>
       </c>
       <c r="B40" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4654,10 +4654,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128729962</v>
+        <v>128729439</v>
       </c>
       <c r="B41" t="n">
-        <v>80140</v>
+        <v>91533</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4665,21 +4665,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4689,10 +4689,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>569643</v>
+        <v>569703</v>
       </c>
       <c r="R41" t="n">
-        <v>6958117</v>
+        <v>6958175</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4751,10 +4751,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128728473</v>
+        <v>128729962</v>
       </c>
       <c r="B42" t="n">
-        <v>57883</v>
+        <v>80144</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4762,39 +4762,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>569608</v>
+        <v>569643</v>
       </c>
       <c r="R42" t="n">
-        <v>6958227</v>
+        <v>6958117</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4856,7 +4851,7 @@
         <v>128730475</v>
       </c>
       <c r="B43" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4960,10 +4955,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128729439</v>
+        <v>128728473</v>
       </c>
       <c r="B44" t="n">
-        <v>91526</v>
+        <v>57885</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4971,34 +4966,39 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>569703</v>
+        <v>569608</v>
       </c>
       <c r="R44" t="n">
-        <v>6958175</v>
+        <v>6958227</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5060,7 +5060,7 @@
         <v>128732627</v>
       </c>
       <c r="B45" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5166,7 +5166,7 @@
         <v>128728348</v>
       </c>
       <c r="B46" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5264,10 +5264,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128731799</v>
+        <v>128728902</v>
       </c>
       <c r="B47" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5295,7 +5295,7 @@
       <c r="I47" t="inlineStr"/>
       <c r="M47" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -5304,10 +5304,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>569774</v>
+        <v>569673</v>
       </c>
       <c r="R47" t="n">
-        <v>6958163</v>
+        <v>6958225</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5371,10 +5371,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128738187</v>
+        <v>128731799</v>
       </c>
       <c r="B48" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5402,7 +5402,7 @@
       <c r="I48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -5411,10 +5411,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>569681</v>
+        <v>569774</v>
       </c>
       <c r="R48" t="n">
-        <v>6957939</v>
+        <v>6958163</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5451,7 +5451,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5478,10 +5478,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128728902</v>
+        <v>128732015</v>
       </c>
       <c r="B49" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5518,10 +5518,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>569673</v>
+        <v>569816</v>
       </c>
       <c r="R49" t="n">
-        <v>6958225</v>
+        <v>6958081</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5558,7 +5558,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5585,10 +5585,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128732015</v>
+        <v>128738187</v>
       </c>
       <c r="B50" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5625,10 +5625,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>569816</v>
+        <v>569681</v>
       </c>
       <c r="R50" t="n">
-        <v>6958081</v>
+        <v>6957939</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5695,7 +5695,7 @@
         <v>128729573</v>
       </c>
       <c r="B51" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5796,7 +5796,7 @@
         <v>128731302</v>
       </c>
       <c r="B52" t="n">
-        <v>80100</v>
+        <v>80104</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5890,10 +5890,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128738306</v>
+        <v>128731037</v>
       </c>
       <c r="B53" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5921,7 +5921,7 @@
       <c r="I53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -5930,10 +5930,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>569644</v>
+        <v>569673</v>
       </c>
       <c r="R53" t="n">
-        <v>6957965</v>
+        <v>6958037</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5997,10 +5997,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128731037</v>
+        <v>128738306</v>
       </c>
       <c r="B54" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6028,7 +6028,7 @@
       <c r="I54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -6037,10 +6037,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>569673</v>
+        <v>569644</v>
       </c>
       <c r="R54" t="n">
-        <v>6958037</v>
+        <v>6957965</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6107,7 +6107,7 @@
         <v>128732183</v>
       </c>
       <c r="B55" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6211,50 +6211,45 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128739287</v>
+        <v>128728592</v>
       </c>
       <c r="B56" t="n">
-        <v>57723</v>
+        <v>80179</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>569481</v>
+        <v>569604</v>
       </c>
       <c r="R56" t="n">
-        <v>6958122</v>
+        <v>6958176</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6287,11 +6282,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6318,50 +6308,45 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128730490</v>
+        <v>128730101</v>
       </c>
       <c r="B57" t="n">
-        <v>57723</v>
+        <v>80180</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>569707</v>
+        <v>569630</v>
       </c>
       <c r="R57" t="n">
-        <v>6958131</v>
+        <v>6958139</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6394,11 +6379,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Både äldre och färska spår ( Ringhack av tretåig hackspett på tall)</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6428,7 +6408,7 @@
         <v>128730183</v>
       </c>
       <c r="B58" t="n">
-        <v>80100</v>
+        <v>80104</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6525,7 +6505,7 @@
         <v>128732806</v>
       </c>
       <c r="B59" t="n">
-        <v>91537</v>
+        <v>91544</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6622,7 +6602,7 @@
         <v>128732719</v>
       </c>
       <c r="B60" t="n">
-        <v>91981</v>
+        <v>91988</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6716,10 +6696,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128728592</v>
+        <v>128732124</v>
       </c>
       <c r="B61" t="n">
-        <v>80175</v>
+        <v>80179</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6751,10 +6731,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>569604</v>
+        <v>569816</v>
       </c>
       <c r="R61" t="n">
-        <v>6958176</v>
+        <v>6958081</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6813,10 +6793,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128732124</v>
+        <v>128731387</v>
       </c>
       <c r="B62" t="n">
-        <v>80175</v>
+        <v>80172</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6824,21 +6804,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6463</v>
+        <v>6461</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6848,10 +6828,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>569816</v>
+        <v>569740</v>
       </c>
       <c r="R62" t="n">
-        <v>6958081</v>
+        <v>6958091</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6910,45 +6890,50 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128730101</v>
+        <v>128730490</v>
       </c>
       <c r="B63" t="n">
-        <v>80176</v>
+        <v>57725</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>569630</v>
+        <v>569707</v>
       </c>
       <c r="R63" t="n">
-        <v>6958139</v>
+        <v>6958131</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6981,6 +6966,11 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Både äldre och färska spår ( Ringhack av tretåig hackspett på tall)</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7007,45 +6997,50 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128731387</v>
+        <v>128730422</v>
       </c>
       <c r="B64" t="n">
-        <v>80168</v>
+        <v>57725</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6461</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>569740</v>
+        <v>569703</v>
       </c>
       <c r="R64" t="n">
-        <v>6958091</v>
+        <v>6958116</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7078,6 +7073,11 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7104,10 +7104,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128730422</v>
+        <v>128739287</v>
       </c>
       <c r="B65" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7144,10 +7144,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>569703</v>
+        <v>569481</v>
       </c>
       <c r="R65" t="n">
-        <v>6958116</v>
+        <v>6958122</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7184,7 +7184,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7211,10 +7211,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128732112</v>
+        <v>128729077</v>
       </c>
       <c r="B66" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7246,10 +7246,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>569824</v>
+        <v>569604</v>
       </c>
       <c r="R66" t="n">
-        <v>6958091</v>
+        <v>6958176</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7308,10 +7308,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128730273</v>
+        <v>128732112</v>
       </c>
       <c r="B67" t="n">
-        <v>79035</v>
+        <v>80144</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7319,21 +7319,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7343,10 +7343,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>569692</v>
+        <v>569824</v>
       </c>
       <c r="R67" t="n">
-        <v>6958127</v>
+        <v>6958091</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7405,10 +7405,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128729077</v>
+        <v>128730273</v>
       </c>
       <c r="B68" t="n">
-        <v>80140</v>
+        <v>79039</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7416,21 +7416,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7440,10 +7440,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>569604</v>
+        <v>569692</v>
       </c>
       <c r="R68" t="n">
-        <v>6958176</v>
+        <v>6958127</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7505,7 +7505,7 @@
         <v>128731693</v>
       </c>
       <c r="B69" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7602,7 +7602,7 @@
         <v>128743263</v>
       </c>
       <c r="B70" t="n">
-        <v>92855</v>
+        <v>92862</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7704,7 +7704,7 @@
         <v>128728149</v>
       </c>
       <c r="B71" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7811,7 +7811,7 @@
         <v>128732493</v>
       </c>
       <c r="B72" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7918,7 +7918,7 @@
         <v>128730998</v>
       </c>
       <c r="B73" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8025,7 +8025,7 @@
         <v>128730928</v>
       </c>
       <c r="B74" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8132,49 +8132,45 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128732718</v>
+        <v>128731100</v>
       </c>
       <c r="B75" t="n">
-        <v>98659</v>
+        <v>91551</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>569834</v>
+        <v>569688</v>
       </c>
       <c r="R75" t="n">
-        <v>6958143</v>
+        <v>6958069</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8233,10 +8229,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128733005</v>
+        <v>128732718</v>
       </c>
       <c r="B76" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8263,7 +8259,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>18</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
@@ -8272,10 +8268,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>569882</v>
+        <v>569834</v>
       </c>
       <c r="R76" t="n">
-        <v>6958106</v>
+        <v>6958143</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8334,45 +8330,49 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128731100</v>
+        <v>128733005</v>
       </c>
       <c r="B77" t="n">
-        <v>91544</v>
+        <v>98669</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>569688</v>
+        <v>569882</v>
       </c>
       <c r="R77" t="n">
-        <v>6958069</v>
+        <v>6958106</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8434,7 +8434,7 @@
         <v>128743247</v>
       </c>
       <c r="B78" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8536,7 +8536,7 @@
         <v>128732848</v>
       </c>
       <c r="B79" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8643,7 +8643,7 @@
         <v>128731284</v>
       </c>
       <c r="B80" t="n">
-        <v>57883</v>
+        <v>57885</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8742,10 +8742,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128731226</v>
+        <v>128728434</v>
       </c>
       <c r="B81" t="n">
-        <v>91544</v>
+        <v>57725</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8753,34 +8753,39 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>569705</v>
+        <v>569608</v>
       </c>
       <c r="R81" t="n">
-        <v>6958098</v>
+        <v>6958227</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8813,6 +8818,11 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8839,10 +8849,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128743244</v>
+        <v>128731226</v>
       </c>
       <c r="B82" t="n">
-        <v>91526</v>
+        <v>91551</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8850,21 +8860,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8874,10 +8884,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>569736</v>
+        <v>569705</v>
       </c>
       <c r="R82" t="n">
-        <v>6957867</v>
+        <v>6958098</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8936,49 +8946,45 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128729895</v>
+        <v>128743244</v>
       </c>
       <c r="B83" t="n">
-        <v>98659</v>
+        <v>91533</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>569713</v>
+        <v>569736</v>
       </c>
       <c r="R83" t="n">
-        <v>6958138</v>
+        <v>6957867</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9037,10 +9043,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128743257</v>
+        <v>128729895</v>
       </c>
       <c r="B84" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9065,17 +9071,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I84" t="inlineStr"/>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>569656</v>
+        <v>569713</v>
       </c>
       <c r="R84" t="n">
-        <v>6957942</v>
+        <v>6958138</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9108,11 +9118,6 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>23 exemplar (ca)</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9139,50 +9144,45 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128728434</v>
+        <v>128743257</v>
       </c>
       <c r="B85" t="n">
-        <v>57723</v>
+        <v>98669</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>569608</v>
+        <v>569656</v>
       </c>
       <c r="R85" t="n">
-        <v>6958227</v>
+        <v>6957942</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9219,7 +9219,7 @@
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>23 exemplar (ca)</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9246,32 +9246,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128729069</v>
+        <v>128738599</v>
       </c>
       <c r="B86" t="n">
-        <v>79035</v>
+        <v>80104</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9281,10 +9281,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>569699</v>
+        <v>569608</v>
       </c>
       <c r="R86" t="n">
-        <v>6958200</v>
+        <v>6958048</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9343,10 +9343,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128728419</v>
+        <v>128729069</v>
       </c>
       <c r="B87" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9378,10 +9378,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>569608</v>
+        <v>569699</v>
       </c>
       <c r="R87" t="n">
-        <v>6958227</v>
+        <v>6958200</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9414,11 +9414,6 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>Riklig förekomst inom området</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9445,10 +9440,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128743261</v>
+        <v>128728419</v>
       </c>
       <c r="B88" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9480,10 +9475,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>569495</v>
+        <v>569608</v>
       </c>
       <c r="R88" t="n">
-        <v>6958117</v>
+        <v>6958227</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9516,6 +9511,11 @@
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>Riklig förekomst inom området</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9542,10 +9542,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128727978</v>
+        <v>128743261</v>
       </c>
       <c r="B89" t="n">
-        <v>57723</v>
+        <v>79039</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9553,39 +9553,34 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P89" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>569564</v>
+        <v>569495</v>
       </c>
       <c r="R89" t="n">
-        <v>6958213</v>
+        <v>6958117</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9618,11 +9613,6 @@
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9649,10 +9639,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128729666</v>
+        <v>128727978</v>
       </c>
       <c r="B90" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9689,10 +9679,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>569706</v>
+        <v>569564</v>
       </c>
       <c r="R90" t="n">
-        <v>6958159</v>
+        <v>6958213</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9729,7 +9719,7 @@
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9756,45 +9746,50 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128738599</v>
+        <v>128729666</v>
       </c>
       <c r="B91" t="n">
-        <v>80100</v>
+        <v>57725</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>229497</v>
+        <v>100109</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P91" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>569608</v>
+        <v>569706</v>
       </c>
       <c r="R91" t="n">
-        <v>6958048</v>
+        <v>6958159</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9827,6 +9822,11 @@
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9856,7 +9856,7 @@
         <v>128728152</v>
       </c>
       <c r="B92" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9953,7 +9953,7 @@
         <v>128728274</v>
       </c>
       <c r="B93" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10060,7 +10060,7 @@
         <v>128731648</v>
       </c>
       <c r="B94" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10166,7 +10166,7 @@
         <v>128743253</v>
       </c>
       <c r="B95" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10268,7 +10268,7 @@
         <v>128743256</v>
       </c>
       <c r="B96" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10370,7 +10370,7 @@
         <v>128728303</v>
       </c>
       <c r="B97" t="n">
-        <v>57715</v>
+        <v>57717</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>

--- a/artfynd/A 39666-2025 artfynd.xlsx
+++ b/artfynd/A 39666-2025 artfynd.xlsx
@@ -1494,10 +1494,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128730571</v>
+        <v>128732276</v>
       </c>
       <c r="B10" t="n">
-        <v>91551</v>
+        <v>57725</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1505,34 +1505,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>569660</v>
+        <v>569841</v>
       </c>
       <c r="R10" t="n">
-        <v>6958074</v>
+        <v>6958102</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1565,6 +1570,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1591,10 +1601,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128732765</v>
+        <v>128743245</v>
       </c>
       <c r="B11" t="n">
-        <v>91818</v>
+        <v>57725</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1602,21 +1612,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1626,10 +1636,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>569827</v>
+        <v>569590</v>
       </c>
       <c r="R11" t="n">
-        <v>6958133</v>
+        <v>6958014</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1662,6 +1672,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall ( färska spår)</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1688,10 +1703,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128732276</v>
+        <v>128732217</v>
       </c>
       <c r="B12" t="n">
-        <v>57725</v>
+        <v>57885</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1699,27 +1714,36 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1728,10 +1752,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>569841</v>
+        <v>569777</v>
       </c>
       <c r="R12" t="n">
-        <v>6958102</v>
+        <v>6958189</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1768,7 +1792,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>2 talltitor kommer flygandes väldigt närgånget och varnar</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1795,10 +1819,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128743245</v>
+        <v>128730571</v>
       </c>
       <c r="B13" t="n">
-        <v>57725</v>
+        <v>91551</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1806,21 +1830,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1830,10 +1854,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>569590</v>
+        <v>569660</v>
       </c>
       <c r="R13" t="n">
-        <v>6958014</v>
+        <v>6958074</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1866,11 +1890,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall ( färska spår)</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1897,10 +1916,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128732217</v>
+        <v>128732765</v>
       </c>
       <c r="B14" t="n">
-        <v>57885</v>
+        <v>91818</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1908,48 +1927,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>658</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>569777</v>
+        <v>569827</v>
       </c>
       <c r="R14" t="n">
-        <v>6958189</v>
+        <v>6958133</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1982,11 +1987,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>2 talltitor kommer flygandes väldigt närgånget och varnar</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2110,37 +2110,38 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128731490</v>
+        <v>128731601</v>
       </c>
       <c r="B16" t="n">
-        <v>98669</v>
+        <v>57725</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>20</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2149,10 +2150,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>569759</v>
+        <v>569752</v>
       </c>
       <c r="R16" t="n">
-        <v>6958118</v>
+        <v>6958091</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2185,6 +2186,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2211,7 +2217,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128730429</v>
+        <v>128731490</v>
       </c>
       <c r="B17" t="n">
         <v>98669</v>
@@ -2241,7 +2247,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2250,10 +2256,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>569683</v>
+        <v>569759</v>
       </c>
       <c r="R17" t="n">
-        <v>6958128</v>
+        <v>6958118</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2312,45 +2318,49 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128728515</v>
+        <v>128730429</v>
       </c>
       <c r="B18" t="n">
-        <v>97540</v>
+        <v>98669</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>569608</v>
+        <v>569683</v>
       </c>
       <c r="R18" t="n">
-        <v>6958227</v>
+        <v>6958128</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2409,50 +2419,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128731601</v>
+        <v>128728515</v>
       </c>
       <c r="B19" t="n">
-        <v>57725</v>
+        <v>97540</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>569752</v>
+        <v>569608</v>
       </c>
       <c r="R19" t="n">
-        <v>6958091</v>
+        <v>6958227</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2485,11 +2490,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2516,10 +2516,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128731107</v>
+        <v>128732359</v>
       </c>
       <c r="B20" t="n">
-        <v>57885</v>
+        <v>91533</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2527,39 +2527,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>569705</v>
+        <v>569820</v>
       </c>
       <c r="R20" t="n">
-        <v>6958098</v>
+        <v>6958107</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2618,49 +2613,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128730720</v>
+        <v>128731612</v>
       </c>
       <c r="B21" t="n">
-        <v>98669</v>
+        <v>91533</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>569692</v>
+        <v>569752</v>
       </c>
       <c r="R21" t="n">
-        <v>6958094</v>
+        <v>6958091</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2693,11 +2684,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ca</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2724,45 +2710,50 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128743252</v>
+        <v>128731107</v>
       </c>
       <c r="B22" t="n">
-        <v>98669</v>
+        <v>57885</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>569610</v>
+        <v>569705</v>
       </c>
       <c r="R22" t="n">
-        <v>6958005</v>
+        <v>6958098</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2795,11 +2786,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>2 exemplar</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2826,45 +2812,49 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128731612</v>
+        <v>128730720</v>
       </c>
       <c r="B23" t="n">
-        <v>91533</v>
+        <v>98669</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>569752</v>
+        <v>569692</v>
       </c>
       <c r="R23" t="n">
-        <v>6958091</v>
+        <v>6958094</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2897,6 +2887,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ca</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2923,32 +2918,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128728022</v>
+        <v>128743252</v>
       </c>
       <c r="B24" t="n">
-        <v>91497</v>
+        <v>98669</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2958,10 +2953,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>569583</v>
+        <v>569610</v>
       </c>
       <c r="R24" t="n">
-        <v>6958204</v>
+        <v>6958005</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2994,6 +2989,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>2 exemplar</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3020,32 +3020,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128743262</v>
+        <v>128728022</v>
       </c>
       <c r="B25" t="n">
-        <v>79039</v>
+        <v>91497</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3055,10 +3055,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>569732</v>
+        <v>569583</v>
       </c>
       <c r="R25" t="n">
-        <v>6957870</v>
+        <v>6958204</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3117,10 +3117,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128739020</v>
+        <v>128743262</v>
       </c>
       <c r="B26" t="n">
-        <v>57725</v>
+        <v>79039</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3128,39 +3128,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>569542</v>
+        <v>569732</v>
       </c>
       <c r="R26" t="n">
-        <v>6958049</v>
+        <v>6957870</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3193,11 +3188,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3224,10 +3214,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128732359</v>
+        <v>128739020</v>
       </c>
       <c r="B27" t="n">
-        <v>91533</v>
+        <v>57725</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3235,34 +3225,39 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>569820</v>
+        <v>569542</v>
       </c>
       <c r="R27" t="n">
-        <v>6958107</v>
+        <v>6958049</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3295,6 +3290,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4242,37 +4242,38 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128732677</v>
+        <v>128729745</v>
       </c>
       <c r="B37" t="n">
-        <v>98669</v>
+        <v>57725</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>12</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4281,10 +4282,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>569817</v>
+        <v>569694</v>
       </c>
       <c r="R37" t="n">
-        <v>6958134</v>
+        <v>6958144</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4317,6 +4318,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4343,7 +4349,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128743255</v>
+        <v>128732677</v>
       </c>
       <c r="B38" t="n">
         <v>98669</v>
@@ -4371,17 +4377,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr"/>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>569613</v>
+        <v>569817</v>
       </c>
       <c r="R38" t="n">
-        <v>6957995</v>
+        <v>6958134</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4414,11 +4424,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>28 exemplar knärot</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4445,50 +4450,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128729745</v>
+        <v>128743255</v>
       </c>
       <c r="B39" t="n">
-        <v>57725</v>
+        <v>98669</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>569694</v>
+        <v>569613</v>
       </c>
       <c r="R39" t="n">
-        <v>6958144</v>
+        <v>6957995</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4525,7 +4525,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>28 exemplar knärot</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -6211,10 +6211,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128728592</v>
+        <v>128732806</v>
       </c>
       <c r="B56" t="n">
-        <v>80179</v>
+        <v>91544</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6222,21 +6222,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6463</v>
+        <v>1205</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6246,10 +6246,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>569604</v>
+        <v>569827</v>
       </c>
       <c r="R56" t="n">
-        <v>6958176</v>
+        <v>6958133</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6308,32 +6308,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128730101</v>
+        <v>128732719</v>
       </c>
       <c r="B57" t="n">
-        <v>80180</v>
+        <v>91988</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6464</v>
+        <v>1209</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6343,10 +6343,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>569630</v>
+        <v>569821</v>
       </c>
       <c r="R57" t="n">
-        <v>6958139</v>
+        <v>6958151</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6405,10 +6405,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128730183</v>
+        <v>128728592</v>
       </c>
       <c r="B58" t="n">
-        <v>80104</v>
+        <v>80179</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6416,21 +6416,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>229497</v>
+        <v>6463</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6440,10 +6440,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>569630</v>
+        <v>569604</v>
       </c>
       <c r="R58" t="n">
-        <v>6958129</v>
+        <v>6958176</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6502,10 +6502,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128732806</v>
+        <v>128732124</v>
       </c>
       <c r="B59" t="n">
-        <v>91544</v>
+        <v>80179</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6513,21 +6513,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1205</v>
+        <v>6463</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6537,10 +6537,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>569827</v>
+        <v>569816</v>
       </c>
       <c r="R59" t="n">
-        <v>6958133</v>
+        <v>6958081</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6599,32 +6599,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128732719</v>
+        <v>128730101</v>
       </c>
       <c r="B60" t="n">
-        <v>91988</v>
+        <v>80180</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1209</v>
+        <v>6464</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6634,10 +6634,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>569821</v>
+        <v>569630</v>
       </c>
       <c r="R60" t="n">
-        <v>6958151</v>
+        <v>6958139</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6696,10 +6696,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128732124</v>
+        <v>128731387</v>
       </c>
       <c r="B61" t="n">
-        <v>80179</v>
+        <v>80172</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6707,21 +6707,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6463</v>
+        <v>6461</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6731,10 +6731,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>569816</v>
+        <v>569740</v>
       </c>
       <c r="R61" t="n">
-        <v>6958081</v>
+        <v>6958091</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6793,45 +6793,50 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128731387</v>
+        <v>128730490</v>
       </c>
       <c r="B62" t="n">
-        <v>80172</v>
+        <v>57725</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6461</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>569740</v>
+        <v>569707</v>
       </c>
       <c r="R62" t="n">
-        <v>6958091</v>
+        <v>6958131</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6864,6 +6869,11 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Både äldre och färska spår ( Ringhack av tretåig hackspett på tall)</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6890,7 +6900,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128730490</v>
+        <v>128730422</v>
       </c>
       <c r="B63" t="n">
         <v>57725</v>
@@ -6930,10 +6940,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>569707</v>
+        <v>569703</v>
       </c>
       <c r="R63" t="n">
-        <v>6958131</v>
+        <v>6958116</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6970,7 +6980,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Både äldre och färska spår ( Ringhack av tretåig hackspett på tall)</t>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6997,7 +7007,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128730422</v>
+        <v>128739287</v>
       </c>
       <c r="B64" t="n">
         <v>57725</v>
@@ -7037,10 +7047,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>569703</v>
+        <v>569481</v>
       </c>
       <c r="R64" t="n">
-        <v>6958116</v>
+        <v>6958122</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7077,7 +7087,7 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7104,50 +7114,45 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128739287</v>
+        <v>128730183</v>
       </c>
       <c r="B65" t="n">
-        <v>57725</v>
+        <v>80104</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>229497</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>569481</v>
+        <v>569630</v>
       </c>
       <c r="R65" t="n">
-        <v>6958122</v>
+        <v>6958129</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7180,11 +7185,6 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8132,10 +8132,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128731100</v>
+        <v>128731284</v>
       </c>
       <c r="B75" t="n">
-        <v>91551</v>
+        <v>57885</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8143,34 +8143,39 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>569688</v>
+        <v>569677</v>
       </c>
       <c r="R75" t="n">
-        <v>6958069</v>
+        <v>6958066</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8229,49 +8234,45 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128732718</v>
+        <v>128731100</v>
       </c>
       <c r="B76" t="n">
-        <v>98669</v>
+        <v>91551</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>569834</v>
+        <v>569688</v>
       </c>
       <c r="R76" t="n">
-        <v>6958143</v>
+        <v>6958069</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8330,49 +8331,45 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128733005</v>
+        <v>128743247</v>
       </c>
       <c r="B77" t="n">
-        <v>98669</v>
+        <v>57725</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>569882</v>
+        <v>569714</v>
       </c>
       <c r="R77" t="n">
-        <v>6958106</v>
+        <v>6957901</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8405,6 +8402,11 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på gran ( färska spår)</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8431,7 +8433,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128743247</v>
+        <v>128732848</v>
       </c>
       <c r="B78" t="n">
         <v>57725</v>
@@ -8460,16 +8462,21 @@
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>569714</v>
+        <v>569873</v>
       </c>
       <c r="R78" t="n">
-        <v>6957901</v>
+        <v>6958099</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8506,7 +8513,7 @@
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på gran ( färska spår)</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8533,38 +8540,37 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128732848</v>
+        <v>128732718</v>
       </c>
       <c r="B79" t="n">
-        <v>57725</v>
+        <v>98669</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>18</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
@@ -8573,10 +8579,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>569873</v>
+        <v>569834</v>
       </c>
       <c r="R79" t="n">
-        <v>6958099</v>
+        <v>6958143</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8609,11 +8615,6 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8640,38 +8641,37 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128731284</v>
+        <v>128733005</v>
       </c>
       <c r="B80" t="n">
-        <v>57885</v>
+        <v>98669</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>7</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
@@ -8680,10 +8680,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>569677</v>
+        <v>569882</v>
       </c>
       <c r="R80" t="n">
-        <v>6958066</v>
+        <v>6958106</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>

--- a/artfynd/A 39666-2025 artfynd.xlsx
+++ b/artfynd/A 39666-2025 artfynd.xlsx
@@ -1494,10 +1494,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128732276</v>
+        <v>128730571</v>
       </c>
       <c r="B10" t="n">
-        <v>57725</v>
+        <v>91551</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1505,39 +1505,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>569841</v>
+        <v>569660</v>
       </c>
       <c r="R10" t="n">
-        <v>6958102</v>
+        <v>6958074</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1570,11 +1565,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1601,10 +1591,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128743245</v>
+        <v>128732765</v>
       </c>
       <c r="B11" t="n">
-        <v>57725</v>
+        <v>91818</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1612,21 +1602,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1636,10 +1626,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>569590</v>
+        <v>569827</v>
       </c>
       <c r="R11" t="n">
-        <v>6958014</v>
+        <v>6958133</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1672,11 +1662,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall ( färska spår)</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1703,10 +1688,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128732217</v>
+        <v>128732276</v>
       </c>
       <c r="B12" t="n">
-        <v>57885</v>
+        <v>57725</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1714,36 +1699,27 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1752,10 +1728,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>569777</v>
+        <v>569841</v>
       </c>
       <c r="R12" t="n">
-        <v>6958189</v>
+        <v>6958102</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1792,7 +1768,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>2 talltitor kommer flygandes väldigt närgånget och varnar</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1819,10 +1795,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128730571</v>
+        <v>128743245</v>
       </c>
       <c r="B13" t="n">
-        <v>91551</v>
+        <v>57725</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1830,21 +1806,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1854,10 +1830,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>569660</v>
+        <v>569590</v>
       </c>
       <c r="R13" t="n">
-        <v>6958074</v>
+        <v>6958014</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1890,6 +1866,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall ( färska spår)</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1916,10 +1897,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128732765</v>
+        <v>128732217</v>
       </c>
       <c r="B14" t="n">
-        <v>91818</v>
+        <v>57885</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1927,34 +1908,48 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>658</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>569827</v>
+        <v>569777</v>
       </c>
       <c r="R14" t="n">
-        <v>6958133</v>
+        <v>6958189</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1987,6 +1982,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>2 talltitor kommer flygandes väldigt närgånget och varnar</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2110,38 +2110,37 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128731601</v>
+        <v>128731490</v>
       </c>
       <c r="B16" t="n">
-        <v>57725</v>
+        <v>98669</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>20</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2150,10 +2149,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>569752</v>
+        <v>569759</v>
       </c>
       <c r="R16" t="n">
-        <v>6958091</v>
+        <v>6958118</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2186,11 +2185,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2217,7 +2211,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128731490</v>
+        <v>128730429</v>
       </c>
       <c r="B17" t="n">
         <v>98669</v>
@@ -2247,7 +2241,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>80</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2256,10 +2250,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>569759</v>
+        <v>569683</v>
       </c>
       <c r="R17" t="n">
-        <v>6958118</v>
+        <v>6958128</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2318,49 +2312,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128730429</v>
+        <v>128728515</v>
       </c>
       <c r="B18" t="n">
-        <v>98669</v>
+        <v>97540</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>569683</v>
+        <v>569608</v>
       </c>
       <c r="R18" t="n">
-        <v>6958128</v>
+        <v>6958227</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2419,45 +2409,50 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128728515</v>
+        <v>128731601</v>
       </c>
       <c r="B19" t="n">
-        <v>97540</v>
+        <v>57725</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>569608</v>
+        <v>569752</v>
       </c>
       <c r="R19" t="n">
-        <v>6958227</v>
+        <v>6958091</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2490,6 +2485,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2516,10 +2516,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128732359</v>
+        <v>128731107</v>
       </c>
       <c r="B20" t="n">
-        <v>91533</v>
+        <v>57885</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2527,34 +2527,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>569820</v>
+        <v>569705</v>
       </c>
       <c r="R20" t="n">
-        <v>6958107</v>
+        <v>6958098</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2613,45 +2618,49 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128731612</v>
+        <v>128730720</v>
       </c>
       <c r="B21" t="n">
-        <v>91533</v>
+        <v>98669</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>569752</v>
+        <v>569692</v>
       </c>
       <c r="R21" t="n">
-        <v>6958091</v>
+        <v>6958094</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2684,6 +2693,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ca</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2710,50 +2724,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128731107</v>
+        <v>128743252</v>
       </c>
       <c r="B22" t="n">
-        <v>57885</v>
+        <v>98669</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>569705</v>
+        <v>569610</v>
       </c>
       <c r="R22" t="n">
-        <v>6958098</v>
+        <v>6958005</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2786,6 +2795,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>2 exemplar</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2812,49 +2826,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128730720</v>
+        <v>128731612</v>
       </c>
       <c r="B23" t="n">
-        <v>98669</v>
+        <v>91533</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>569692</v>
+        <v>569752</v>
       </c>
       <c r="R23" t="n">
-        <v>6958094</v>
+        <v>6958091</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2887,11 +2897,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ca</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2918,32 +2923,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128743252</v>
+        <v>128728022</v>
       </c>
       <c r="B24" t="n">
-        <v>98669</v>
+        <v>91497</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2953,10 +2958,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>569610</v>
+        <v>569583</v>
       </c>
       <c r="R24" t="n">
-        <v>6958005</v>
+        <v>6958204</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2989,11 +2994,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>2 exemplar</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3020,32 +3020,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128728022</v>
+        <v>128743262</v>
       </c>
       <c r="B25" t="n">
-        <v>91497</v>
+        <v>79039</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3055,10 +3055,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>569583</v>
+        <v>569732</v>
       </c>
       <c r="R25" t="n">
-        <v>6958204</v>
+        <v>6957870</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3117,10 +3117,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128743262</v>
+        <v>128739020</v>
       </c>
       <c r="B26" t="n">
-        <v>79039</v>
+        <v>57725</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3128,34 +3128,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>569732</v>
+        <v>569542</v>
       </c>
       <c r="R26" t="n">
-        <v>6957870</v>
+        <v>6958049</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3188,6 +3193,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3214,10 +3224,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128739020</v>
+        <v>128732359</v>
       </c>
       <c r="B27" t="n">
-        <v>57725</v>
+        <v>91533</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3225,39 +3235,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>569542</v>
+        <v>569820</v>
       </c>
       <c r="R27" t="n">
-        <v>6958049</v>
+        <v>6958107</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3290,11 +3295,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3733,54 +3733,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128728767</v>
+        <v>128730513</v>
       </c>
       <c r="B32" t="n">
-        <v>92826</v>
+        <v>80144</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>569639</v>
+        <v>569656</v>
       </c>
       <c r="R32" t="n">
-        <v>6958231</v>
+        <v>6958093</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3813,11 +3804,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>4 äldre ett färskt års exemplar</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3844,10 +3830,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128730513</v>
+        <v>128730603</v>
       </c>
       <c r="B33" t="n">
-        <v>80144</v>
+        <v>57725</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3855,34 +3841,39 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>569656</v>
+        <v>569738</v>
       </c>
       <c r="R33" t="n">
-        <v>6958093</v>
+        <v>6958117</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3915,6 +3906,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Äldre exemplar av ringhack på Tall från tretåig hackspett</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3941,38 +3937,42 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128730603</v>
+        <v>128728767</v>
       </c>
       <c r="B34" t="n">
-        <v>57725</v>
+        <v>92826</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -3981,10 +3981,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>569738</v>
+        <v>569639</v>
       </c>
       <c r="R34" t="n">
-        <v>6958117</v>
+        <v>6958231</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4021,7 +4021,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Äldre exemplar av ringhack på Tall från tretåig hackspett</t>
+          <t>4 äldre ett färskt års exemplar</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -6211,10 +6211,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128732806</v>
+        <v>128728592</v>
       </c>
       <c r="B56" t="n">
-        <v>91544</v>
+        <v>80179</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6222,21 +6222,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1205</v>
+        <v>6463</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6246,10 +6246,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>569827</v>
+        <v>569604</v>
       </c>
       <c r="R56" t="n">
-        <v>6958133</v>
+        <v>6958176</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6308,32 +6308,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128732719</v>
+        <v>128730101</v>
       </c>
       <c r="B57" t="n">
-        <v>91988</v>
+        <v>80180</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1209</v>
+        <v>6464</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6343,10 +6343,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>569821</v>
+        <v>569630</v>
       </c>
       <c r="R57" t="n">
-        <v>6958151</v>
+        <v>6958139</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6405,10 +6405,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128728592</v>
+        <v>128730183</v>
       </c>
       <c r="B58" t="n">
-        <v>80179</v>
+        <v>80104</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6416,21 +6416,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6463</v>
+        <v>229497</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6440,10 +6440,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>569604</v>
+        <v>569630</v>
       </c>
       <c r="R58" t="n">
-        <v>6958176</v>
+        <v>6958129</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6502,10 +6502,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128732124</v>
+        <v>128732806</v>
       </c>
       <c r="B59" t="n">
-        <v>80179</v>
+        <v>91544</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6513,21 +6513,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6463</v>
+        <v>1205</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6537,10 +6537,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>569816</v>
+        <v>569827</v>
       </c>
       <c r="R59" t="n">
-        <v>6958081</v>
+        <v>6958133</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6599,32 +6599,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128730101</v>
+        <v>128732719</v>
       </c>
       <c r="B60" t="n">
-        <v>80180</v>
+        <v>91988</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6464</v>
+        <v>1209</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6634,10 +6634,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>569630</v>
+        <v>569821</v>
       </c>
       <c r="R60" t="n">
-        <v>6958139</v>
+        <v>6958151</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6696,10 +6696,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128731387</v>
+        <v>128732124</v>
       </c>
       <c r="B61" t="n">
-        <v>80172</v>
+        <v>80179</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6707,21 +6707,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6461</v>
+        <v>6463</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6731,10 +6731,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>569740</v>
+        <v>569816</v>
       </c>
       <c r="R61" t="n">
-        <v>6958091</v>
+        <v>6958081</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6793,50 +6793,45 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128730490</v>
+        <v>128731387</v>
       </c>
       <c r="B62" t="n">
-        <v>57725</v>
+        <v>80172</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>569707</v>
+        <v>569740</v>
       </c>
       <c r="R62" t="n">
-        <v>6958131</v>
+        <v>6958091</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6869,11 +6864,6 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Både äldre och färska spår ( Ringhack av tretåig hackspett på tall)</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6900,7 +6890,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128730422</v>
+        <v>128730490</v>
       </c>
       <c r="B63" t="n">
         <v>57725</v>
@@ -6940,10 +6930,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>569703</v>
+        <v>569707</v>
       </c>
       <c r="R63" t="n">
-        <v>6958116</v>
+        <v>6958131</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6980,7 +6970,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>Både äldre och färska spår ( Ringhack av tretåig hackspett på tall)</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7007,7 +6997,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128739287</v>
+        <v>128730422</v>
       </c>
       <c r="B64" t="n">
         <v>57725</v>
@@ -7047,10 +7037,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>569481</v>
+        <v>569703</v>
       </c>
       <c r="R64" t="n">
-        <v>6958122</v>
+        <v>6958116</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7087,7 +7077,7 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7114,45 +7104,50 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128730183</v>
+        <v>128739287</v>
       </c>
       <c r="B65" t="n">
-        <v>80104</v>
+        <v>57725</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>229497</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>569630</v>
+        <v>569481</v>
       </c>
       <c r="R65" t="n">
-        <v>6958129</v>
+        <v>6958122</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7185,6 +7180,11 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8742,10 +8742,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128728434</v>
+        <v>128731226</v>
       </c>
       <c r="B81" t="n">
-        <v>57725</v>
+        <v>91551</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8753,39 +8753,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>569608</v>
+        <v>569705</v>
       </c>
       <c r="R81" t="n">
-        <v>6958227</v>
+        <v>6958098</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8818,11 +8813,6 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8849,10 +8839,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128731226</v>
+        <v>128743244</v>
       </c>
       <c r="B82" t="n">
-        <v>91551</v>
+        <v>91533</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8860,21 +8850,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8884,10 +8874,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>569705</v>
+        <v>569736</v>
       </c>
       <c r="R82" t="n">
-        <v>6958098</v>
+        <v>6957867</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8946,10 +8936,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128743244</v>
+        <v>128728434</v>
       </c>
       <c r="B83" t="n">
-        <v>91533</v>
+        <v>57725</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8957,34 +8947,39 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>569736</v>
+        <v>569608</v>
       </c>
       <c r="R83" t="n">
-        <v>6957867</v>
+        <v>6958227</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9017,6 +9012,11 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9246,32 +9246,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128738599</v>
+        <v>128729069</v>
       </c>
       <c r="B86" t="n">
-        <v>80104</v>
+        <v>79039</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9281,10 +9281,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>569608</v>
+        <v>569699</v>
       </c>
       <c r="R86" t="n">
-        <v>6958048</v>
+        <v>6958200</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9343,7 +9343,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128729069</v>
+        <v>128728419</v>
       </c>
       <c r="B87" t="n">
         <v>79039</v>
@@ -9378,10 +9378,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>569699</v>
+        <v>569608</v>
       </c>
       <c r="R87" t="n">
-        <v>6958200</v>
+        <v>6958227</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9414,6 +9414,11 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>Riklig förekomst inom området</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9440,7 +9445,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128728419</v>
+        <v>128743261</v>
       </c>
       <c r="B88" t="n">
         <v>79039</v>
@@ -9475,10 +9480,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>569608</v>
+        <v>569495</v>
       </c>
       <c r="R88" t="n">
-        <v>6958227</v>
+        <v>6958117</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9511,11 +9516,6 @@
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>Riklig förekomst inom området</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9542,10 +9542,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128743261</v>
+        <v>128727978</v>
       </c>
       <c r="B89" t="n">
-        <v>79039</v>
+        <v>57725</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9553,34 +9553,39 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P89" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>569495</v>
+        <v>569564</v>
       </c>
       <c r="R89" t="n">
-        <v>6958117</v>
+        <v>6958213</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9613,6 +9618,11 @@
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9639,7 +9649,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128727978</v>
+        <v>128729666</v>
       </c>
       <c r="B90" t="n">
         <v>57725</v>
@@ -9679,10 +9689,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>569564</v>
+        <v>569706</v>
       </c>
       <c r="R90" t="n">
-        <v>6958213</v>
+        <v>6958159</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9719,7 +9729,7 @@
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9746,50 +9756,45 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128729666</v>
+        <v>128738599</v>
       </c>
       <c r="B91" t="n">
-        <v>57725</v>
+        <v>80104</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>100109</v>
+        <v>229497</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P91" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>569706</v>
+        <v>569608</v>
       </c>
       <c r="R91" t="n">
-        <v>6958159</v>
+        <v>6958048</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9822,11 +9827,6 @@
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD91" t="b">

--- a/artfynd/A 39666-2025 artfynd.xlsx
+++ b/artfynd/A 39666-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128732386</v>
+        <v>128743246</v>
       </c>
       <c r="B2" t="n">
-        <v>80144</v>
+        <v>57727</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>569785</v>
+        <v>569648</v>
       </c>
       <c r="R2" t="n">
-        <v>6958124</v>
+        <v>6957944</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,6 +746,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall ( äldre och färska spår)</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128743246</v>
+        <v>128728526</v>
       </c>
       <c r="B3" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -801,16 +806,21 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>569648</v>
+        <v>569616</v>
       </c>
       <c r="R3" t="n">
-        <v>6957944</v>
+        <v>6958208</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -847,7 +857,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall ( äldre och färska spår)</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -874,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128728526</v>
+        <v>128739007</v>
       </c>
       <c r="B4" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -914,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>569616</v>
+        <v>569542</v>
       </c>
       <c r="R4" t="n">
-        <v>6958208</v>
+        <v>6958069</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,38 +991,37 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128739007</v>
+        <v>128728896</v>
       </c>
       <c r="B5" t="n">
-        <v>57725</v>
+        <v>98678</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>6</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1021,10 +1030,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>569542</v>
+        <v>569601</v>
       </c>
       <c r="R5" t="n">
-        <v>6958069</v>
+        <v>6958191</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1057,11 +1066,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1088,10 +1092,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128728896</v>
+        <v>128732983</v>
       </c>
       <c r="B6" t="n">
-        <v>98669</v>
+        <v>98678</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1118,7 +1122,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1127,10 +1131,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>569601</v>
+        <v>569873</v>
       </c>
       <c r="R6" t="n">
-        <v>6958191</v>
+        <v>6958099</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1189,49 +1193,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128732983</v>
+        <v>128732386</v>
       </c>
       <c r="B7" t="n">
-        <v>98669</v>
+        <v>80146</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>569873</v>
+        <v>569785</v>
       </c>
       <c r="R7" t="n">
-        <v>6958099</v>
+        <v>6958124</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1290,10 +1290,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128730130</v>
+        <v>128729409</v>
       </c>
       <c r="B8" t="n">
-        <v>57725</v>
+        <v>91542</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1301,39 +1301,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>569713</v>
+        <v>569700</v>
       </c>
       <c r="R8" t="n">
-        <v>6958138</v>
+        <v>6958164</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1366,11 +1361,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1397,10 +1387,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128729409</v>
+        <v>128730130</v>
       </c>
       <c r="B9" t="n">
-        <v>91533</v>
+        <v>57727</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1408,34 +1398,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>569700</v>
+        <v>569713</v>
       </c>
       <c r="R9" t="n">
-        <v>6958164</v>
+        <v>6958138</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1468,6 +1463,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1494,10 +1494,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128730571</v>
+        <v>128732765</v>
       </c>
       <c r="B10" t="n">
-        <v>91551</v>
+        <v>91827</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1505,21 +1505,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1529,10 +1529,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>569660</v>
+        <v>569827</v>
       </c>
       <c r="R10" t="n">
-        <v>6958074</v>
+        <v>6958133</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1591,32 +1591,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128732765</v>
+        <v>128733181</v>
       </c>
       <c r="B11" t="n">
-        <v>91818</v>
+        <v>98595</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>658</v>
+        <v>219790</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1626,10 +1626,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>569827</v>
+        <v>569900</v>
       </c>
       <c r="R11" t="n">
-        <v>6958133</v>
+        <v>6958101</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1688,10 +1688,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128732276</v>
+        <v>128730571</v>
       </c>
       <c r="B12" t="n">
-        <v>57725</v>
+        <v>91560</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1699,39 +1699,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>569841</v>
+        <v>569660</v>
       </c>
       <c r="R12" t="n">
-        <v>6958102</v>
+        <v>6958074</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1764,11 +1759,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1795,10 +1785,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128743245</v>
+        <v>128732276</v>
       </c>
       <c r="B13" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1824,16 +1814,21 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>569590</v>
+        <v>569841</v>
       </c>
       <c r="R13" t="n">
-        <v>6958014</v>
+        <v>6958102</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1870,7 +1865,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall ( färska spår)</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1897,10 +1892,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128732217</v>
+        <v>128743245</v>
       </c>
       <c r="B14" t="n">
-        <v>57885</v>
+        <v>57727</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1908,48 +1903,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>569777</v>
+        <v>569590</v>
       </c>
       <c r="R14" t="n">
-        <v>6958189</v>
+        <v>6958014</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1986,7 +1967,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>2 talltitor kommer flygandes väldigt närgånget och varnar</t>
+          <t>Ringhack av tretåig hackspett på Tall ( färska spår)</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2013,45 +1994,59 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128733181</v>
+        <v>128732217</v>
       </c>
       <c r="B15" t="n">
-        <v>98586</v>
+        <v>57887</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219790</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>569900</v>
+        <v>569777</v>
       </c>
       <c r="R15" t="n">
-        <v>6958101</v>
+        <v>6958189</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2084,6 +2079,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>2 talltitor kommer flygandes väldigt närgånget och varnar</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2110,37 +2110,38 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128731490</v>
+        <v>128731601</v>
       </c>
       <c r="B16" t="n">
-        <v>98669</v>
+        <v>57727</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>20</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2149,10 +2150,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>569759</v>
+        <v>569752</v>
       </c>
       <c r="R16" t="n">
-        <v>6958118</v>
+        <v>6958091</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2185,6 +2186,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2211,10 +2217,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128730429</v>
+        <v>128731490</v>
       </c>
       <c r="B17" t="n">
-        <v>98669</v>
+        <v>98678</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2241,7 +2247,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2250,10 +2256,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>569683</v>
+        <v>569759</v>
       </c>
       <c r="R17" t="n">
-        <v>6958128</v>
+        <v>6958118</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2312,45 +2318,49 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128728515</v>
+        <v>128730429</v>
       </c>
       <c r="B18" t="n">
-        <v>97540</v>
+        <v>98678</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>569608</v>
+        <v>569683</v>
       </c>
       <c r="R18" t="n">
-        <v>6958227</v>
+        <v>6958128</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2409,50 +2419,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128731601</v>
+        <v>128728515</v>
       </c>
       <c r="B19" t="n">
-        <v>57725</v>
+        <v>97549</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>569752</v>
+        <v>569608</v>
       </c>
       <c r="R19" t="n">
-        <v>6958091</v>
+        <v>6958227</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2485,11 +2490,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2516,10 +2516,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128731107</v>
+        <v>128732359</v>
       </c>
       <c r="B20" t="n">
-        <v>57885</v>
+        <v>91542</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2527,39 +2527,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>569705</v>
+        <v>569820</v>
       </c>
       <c r="R20" t="n">
-        <v>6958098</v>
+        <v>6958107</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2618,49 +2613,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128730720</v>
+        <v>128731612</v>
       </c>
       <c r="B21" t="n">
-        <v>98669</v>
+        <v>91542</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>569692</v>
+        <v>569752</v>
       </c>
       <c r="R21" t="n">
-        <v>6958094</v>
+        <v>6958091</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2693,11 +2684,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ca</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2724,32 +2710,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128743252</v>
+        <v>128728022</v>
       </c>
       <c r="B22" t="n">
-        <v>98669</v>
+        <v>91506</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2759,10 +2745,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>569610</v>
+        <v>569583</v>
       </c>
       <c r="R22" t="n">
-        <v>6958005</v>
+        <v>6958204</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2795,11 +2781,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>2 exemplar</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2826,10 +2807,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128731612</v>
+        <v>128743262</v>
       </c>
       <c r="B23" t="n">
-        <v>91533</v>
+        <v>79041</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2837,21 +2818,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2861,10 +2842,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>569752</v>
+        <v>569732</v>
       </c>
       <c r="R23" t="n">
-        <v>6958091</v>
+        <v>6957870</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2923,45 +2904,50 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128728022</v>
+        <v>128731107</v>
       </c>
       <c r="B24" t="n">
-        <v>91497</v>
+        <v>57887</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5447</v>
+        <v>103021</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>569583</v>
+        <v>569705</v>
       </c>
       <c r="R24" t="n">
-        <v>6958204</v>
+        <v>6958098</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3020,10 +3006,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128743262</v>
+        <v>128739020</v>
       </c>
       <c r="B25" t="n">
-        <v>79039</v>
+        <v>57727</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3031,34 +3017,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>569732</v>
+        <v>569542</v>
       </c>
       <c r="R25" t="n">
-        <v>6957870</v>
+        <v>6958049</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3091,6 +3082,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3117,38 +3113,37 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128739020</v>
+        <v>128730720</v>
       </c>
       <c r="B26" t="n">
-        <v>57725</v>
+        <v>98678</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>50</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3157,10 +3152,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>569542</v>
+        <v>569692</v>
       </c>
       <c r="R26" t="n">
-        <v>6958049</v>
+        <v>6958094</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3197,7 +3192,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ca</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3224,32 +3219,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128732359</v>
+        <v>128743252</v>
       </c>
       <c r="B27" t="n">
-        <v>91533</v>
+        <v>98678</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3259,10 +3254,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>569820</v>
+        <v>569610</v>
       </c>
       <c r="R27" t="n">
-        <v>6958107</v>
+        <v>6958005</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3295,6 +3290,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>2 exemplar</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3321,45 +3321,50 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128729068</v>
+        <v>128731291</v>
       </c>
       <c r="B28" t="n">
-        <v>80173</v>
+        <v>57727</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>569604</v>
+        <v>569726</v>
       </c>
       <c r="R28" t="n">
-        <v>6958176</v>
+        <v>6958097</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3392,6 +3397,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på tall</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3418,50 +3428,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128731291</v>
+        <v>128729068</v>
       </c>
       <c r="B29" t="n">
-        <v>57725</v>
+        <v>80175</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>569726</v>
+        <v>569604</v>
       </c>
       <c r="R29" t="n">
-        <v>6958097</v>
+        <v>6958176</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3494,11 +3499,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på tall</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3525,38 +3525,37 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128728019</v>
+        <v>128731489</v>
       </c>
       <c r="B30" t="n">
-        <v>57725</v>
+        <v>98678</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>45</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3565,10 +3564,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>569577</v>
+        <v>569752</v>
       </c>
       <c r="R30" t="n">
-        <v>6958213</v>
+        <v>6958091</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3601,11 +3600,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3632,37 +3626,38 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128731489</v>
+        <v>128728019</v>
       </c>
       <c r="B31" t="n">
-        <v>98669</v>
+        <v>57727</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>45</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -3671,10 +3666,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>569752</v>
+        <v>569577</v>
       </c>
       <c r="R31" t="n">
-        <v>6958091</v>
+        <v>6958213</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3707,6 +3702,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3733,10 +3733,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128730513</v>
+        <v>128730603</v>
       </c>
       <c r="B32" t="n">
-        <v>80144</v>
+        <v>57727</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3744,34 +3744,39 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>569656</v>
+        <v>569738</v>
       </c>
       <c r="R32" t="n">
-        <v>6958093</v>
+        <v>6958117</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3804,6 +3809,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Äldre exemplar av ringhack på Tall från tretåig hackspett</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3830,10 +3840,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128730603</v>
+        <v>128730513</v>
       </c>
       <c r="B33" t="n">
-        <v>57725</v>
+        <v>80146</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3841,39 +3851,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>569738</v>
+        <v>569656</v>
       </c>
       <c r="R33" t="n">
-        <v>6958117</v>
+        <v>6958093</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3906,11 +3911,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Äldre exemplar av ringhack på Tall från tretåig hackspett</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3940,7 +3940,7 @@
         <v>128728767</v>
       </c>
       <c r="B34" t="n">
-        <v>92826</v>
+        <v>92835</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4051,7 +4051,7 @@
         <v>128728318</v>
       </c>
       <c r="B35" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4148,7 +4148,7 @@
         <v>128731677</v>
       </c>
       <c r="B36" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4242,38 +4242,37 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128729745</v>
+        <v>128732677</v>
       </c>
       <c r="B37" t="n">
-        <v>57725</v>
+        <v>98678</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>12</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4282,10 +4281,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>569694</v>
+        <v>569817</v>
       </c>
       <c r="R37" t="n">
-        <v>6958144</v>
+        <v>6958134</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4318,11 +4317,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4349,10 +4343,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128732677</v>
+        <v>128743255</v>
       </c>
       <c r="B38" t="n">
-        <v>98669</v>
+        <v>98678</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4377,21 +4371,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>569817</v>
+        <v>569613</v>
       </c>
       <c r="R38" t="n">
-        <v>6958134</v>
+        <v>6957995</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4424,6 +4414,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>28 exemplar knärot</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4450,10 +4445,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128743255</v>
+        <v>128743254</v>
       </c>
       <c r="B39" t="n">
-        <v>98669</v>
+        <v>98678</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4485,10 +4480,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>569613</v>
+        <v>569547</v>
       </c>
       <c r="R39" t="n">
-        <v>6957995</v>
+        <v>6958078</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4525,7 +4520,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>28 exemplar knärot</t>
+          <t>20 (ca) exemplar</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4552,45 +4547,50 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128743254</v>
+        <v>128729745</v>
       </c>
       <c r="B40" t="n">
-        <v>98669</v>
+        <v>57727</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>569547</v>
+        <v>569694</v>
       </c>
       <c r="R40" t="n">
-        <v>6958078</v>
+        <v>6958144</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4627,7 +4627,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>20 (ca) exemplar</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4657,7 +4657,7 @@
         <v>128729439</v>
       </c>
       <c r="B41" t="n">
-        <v>91533</v>
+        <v>91542</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4754,7 +4754,7 @@
         <v>128729962</v>
       </c>
       <c r="B42" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4848,10 +4848,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128730475</v>
+        <v>128728473</v>
       </c>
       <c r="B43" t="n">
-        <v>57725</v>
+        <v>57887</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4859,27 +4859,27 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -4888,10 +4888,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>569675</v>
+        <v>569608</v>
       </c>
       <c r="R43" t="n">
-        <v>6958098</v>
+        <v>6958227</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4924,11 +4924,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4955,10 +4950,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128728473</v>
+        <v>128730475</v>
       </c>
       <c r="B44" t="n">
-        <v>57885</v>
+        <v>57727</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4966,27 +4961,27 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -4995,10 +4990,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>569608</v>
+        <v>569675</v>
       </c>
       <c r="R44" t="n">
-        <v>6958227</v>
+        <v>6958098</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5031,6 +5026,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5057,37 +5057,38 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128732627</v>
+        <v>128728902</v>
       </c>
       <c r="B45" t="n">
-        <v>98669</v>
+        <v>57727</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>6</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -5096,10 +5097,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>569821</v>
+        <v>569673</v>
       </c>
       <c r="R45" t="n">
-        <v>6958151</v>
+        <v>6958225</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5136,7 +5137,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Kan finnas mer I blåbärsriset och mossan</t>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5163,37 +5164,38 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128728348</v>
+        <v>128731799</v>
       </c>
       <c r="B46" t="n">
-        <v>98669</v>
+        <v>57727</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>300</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -5202,10 +5204,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>569616</v>
+        <v>569774</v>
       </c>
       <c r="R46" t="n">
-        <v>6958208</v>
+        <v>6958163</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5238,6 +5240,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5264,10 +5271,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128728902</v>
+        <v>128732015</v>
       </c>
       <c r="B47" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5304,10 +5311,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>569673</v>
+        <v>569816</v>
       </c>
       <c r="R47" t="n">
-        <v>6958225</v>
+        <v>6958081</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5344,7 +5351,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5371,10 +5378,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128731799</v>
+        <v>128738187</v>
       </c>
       <c r="B48" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5402,7 +5409,7 @@
       <c r="I48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -5411,10 +5418,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>569774</v>
+        <v>569681</v>
       </c>
       <c r="R48" t="n">
-        <v>6958163</v>
+        <v>6957939</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5451,7 +5458,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5478,38 +5485,37 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128732015</v>
+        <v>128732627</v>
       </c>
       <c r="B49" t="n">
-        <v>57725</v>
+        <v>98678</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>6</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -5518,10 +5524,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>569816</v>
+        <v>569821</v>
       </c>
       <c r="R49" t="n">
-        <v>6958081</v>
+        <v>6958151</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5558,7 +5564,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Kan finnas mer I blåbärsriset och mossan</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5585,38 +5591,37 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128738187</v>
+        <v>128728348</v>
       </c>
       <c r="B50" t="n">
-        <v>57725</v>
+        <v>98678</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>300</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -5625,10 +5630,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>569681</v>
+        <v>569616</v>
       </c>
       <c r="R50" t="n">
-        <v>6957939</v>
+        <v>6958208</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5661,11 +5666,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5695,7 +5695,7 @@
         <v>128729573</v>
       </c>
       <c r="B51" t="n">
-        <v>98669</v>
+        <v>98678</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5796,7 +5796,7 @@
         <v>128731302</v>
       </c>
       <c r="B52" t="n">
-        <v>80104</v>
+        <v>80106</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5893,7 +5893,7 @@
         <v>128731037</v>
       </c>
       <c r="B53" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6000,7 +6000,7 @@
         <v>128738306</v>
       </c>
       <c r="B54" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6107,7 +6107,7 @@
         <v>128732183</v>
       </c>
       <c r="B55" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6211,10 +6211,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128728592</v>
+        <v>128732806</v>
       </c>
       <c r="B56" t="n">
-        <v>80179</v>
+        <v>91553</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6222,21 +6222,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6463</v>
+        <v>1205</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6246,10 +6246,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>569604</v>
+        <v>569827</v>
       </c>
       <c r="R56" t="n">
-        <v>6958176</v>
+        <v>6958133</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6308,32 +6308,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128730101</v>
+        <v>128732719</v>
       </c>
       <c r="B57" t="n">
-        <v>80180</v>
+        <v>91997</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6464</v>
+        <v>1209</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6343,10 +6343,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>569630</v>
+        <v>569821</v>
       </c>
       <c r="R57" t="n">
-        <v>6958139</v>
+        <v>6958151</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6405,45 +6405,50 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128730183</v>
+        <v>128730490</v>
       </c>
       <c r="B58" t="n">
-        <v>80104</v>
+        <v>57727</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>229497</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>569630</v>
+        <v>569707</v>
       </c>
       <c r="R58" t="n">
-        <v>6958129</v>
+        <v>6958131</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6476,6 +6481,11 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Både äldre och färska spår ( Ringhack av tretåig hackspett på tall)</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6502,45 +6512,50 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128732806</v>
+        <v>128730422</v>
       </c>
       <c r="B59" t="n">
-        <v>91544</v>
+        <v>57727</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1205</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>569827</v>
+        <v>569703</v>
       </c>
       <c r="R59" t="n">
-        <v>6958133</v>
+        <v>6958116</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6573,6 +6588,11 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6599,45 +6619,50 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128732719</v>
+        <v>128739287</v>
       </c>
       <c r="B60" t="n">
-        <v>91988</v>
+        <v>57727</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>569821</v>
+        <v>569481</v>
       </c>
       <c r="R60" t="n">
-        <v>6958151</v>
+        <v>6958122</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6670,6 +6695,11 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6696,10 +6726,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128732124</v>
+        <v>128728592</v>
       </c>
       <c r="B61" t="n">
-        <v>80179</v>
+        <v>80181</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6731,10 +6761,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>569816</v>
+        <v>569604</v>
       </c>
       <c r="R61" t="n">
-        <v>6958081</v>
+        <v>6958176</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6793,10 +6823,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128731387</v>
+        <v>128732124</v>
       </c>
       <c r="B62" t="n">
-        <v>80172</v>
+        <v>80181</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6804,21 +6834,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6461</v>
+        <v>6463</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6828,10 +6858,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>569740</v>
+        <v>569816</v>
       </c>
       <c r="R62" t="n">
-        <v>6958091</v>
+        <v>6958081</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6890,50 +6920,45 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128730490</v>
+        <v>128730101</v>
       </c>
       <c r="B63" t="n">
-        <v>57725</v>
+        <v>80182</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>569707</v>
+        <v>569630</v>
       </c>
       <c r="R63" t="n">
-        <v>6958131</v>
+        <v>6958139</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6966,11 +6991,6 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Både äldre och färska spår ( Ringhack av tretåig hackspett på tall)</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6997,50 +7017,45 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128730422</v>
+        <v>128731387</v>
       </c>
       <c r="B64" t="n">
-        <v>57725</v>
+        <v>80174</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>569703</v>
+        <v>569740</v>
       </c>
       <c r="R64" t="n">
-        <v>6958116</v>
+        <v>6958091</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7073,11 +7088,6 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7104,50 +7114,45 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128739287</v>
+        <v>128730183</v>
       </c>
       <c r="B65" t="n">
-        <v>57725</v>
+        <v>80106</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>229497</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>569481</v>
+        <v>569630</v>
       </c>
       <c r="R65" t="n">
-        <v>6958122</v>
+        <v>6958129</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7180,11 +7185,6 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7214,7 +7214,7 @@
         <v>128729077</v>
       </c>
       <c r="B66" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         <v>128732112</v>
       </c>
       <c r="B67" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7408,7 +7408,7 @@
         <v>128730273</v>
       </c>
       <c r="B68" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7502,10 +7502,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128731693</v>
+        <v>128728149</v>
       </c>
       <c r="B69" t="n">
-        <v>91533</v>
+        <v>57727</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7513,34 +7513,39 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>569793</v>
+        <v>569585</v>
       </c>
       <c r="R69" t="n">
-        <v>6958092</v>
+        <v>6958190</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7573,6 +7578,11 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7599,45 +7609,50 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128743263</v>
+        <v>128732493</v>
       </c>
       <c r="B70" t="n">
-        <v>92862</v>
+        <v>57727</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>5964</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>569517</v>
+        <v>569795</v>
       </c>
       <c r="R70" t="n">
-        <v>6958123</v>
+        <v>6958154</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7674,7 +7689,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>3 exemplar</t>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7701,10 +7716,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128728149</v>
+        <v>128730998</v>
       </c>
       <c r="B71" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7741,10 +7756,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>569585</v>
+        <v>569670</v>
       </c>
       <c r="R71" t="n">
-        <v>6958190</v>
+        <v>6958060</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7781,7 +7796,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på tall. Även äldre</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7808,10 +7823,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128732493</v>
+        <v>128730928</v>
       </c>
       <c r="B72" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7837,21 +7852,24 @@
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
       <c r="M72" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>569795</v>
+        <v>569673</v>
       </c>
       <c r="R72" t="n">
-        <v>6958154</v>
+        <v>6958076</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7888,7 +7906,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>Påbörjat bobygge av sannolikt tretåig hackspett. Ser ut att vara relativt färskt. 2 meter upp i död gran. Omkring 4,5 cm i diameter.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7915,10 +7933,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128730998</v>
+        <v>128731693</v>
       </c>
       <c r="B73" t="n">
-        <v>57725</v>
+        <v>91542</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7926,39 +7944,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>569670</v>
+        <v>569793</v>
       </c>
       <c r="R73" t="n">
-        <v>6958060</v>
+        <v>6958092</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7991,11 +8004,6 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Ringhack på tall. Även äldre</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8022,53 +8030,45 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128730928</v>
+        <v>128743263</v>
       </c>
       <c r="B74" t="n">
-        <v>57725</v>
+        <v>92871</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100109</v>
+        <v>5964</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>569673</v>
+        <v>569517</v>
       </c>
       <c r="R74" t="n">
-        <v>6958076</v>
+        <v>6958123</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8105,7 +8105,7 @@
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Påbörjat bobygge av sannolikt tretåig hackspett. Ser ut att vara relativt färskt. 2 meter upp i död gran. Omkring 4,5 cm i diameter.</t>
+          <t>3 exemplar</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8135,7 +8135,7 @@
         <v>128731284</v>
       </c>
       <c r="B75" t="n">
-        <v>57885</v>
+        <v>57887</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8234,45 +8234,49 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128731100</v>
+        <v>128732718</v>
       </c>
       <c r="B76" t="n">
-        <v>91551</v>
+        <v>98678</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>569688</v>
+        <v>569834</v>
       </c>
       <c r="R76" t="n">
-        <v>6958069</v>
+        <v>6958143</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8331,45 +8335,49 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128743247</v>
+        <v>128733005</v>
       </c>
       <c r="B77" t="n">
-        <v>57725</v>
+        <v>98678</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>569714</v>
+        <v>569882</v>
       </c>
       <c r="R77" t="n">
-        <v>6957901</v>
+        <v>6958106</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8402,11 +8410,6 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på gran ( färska spår)</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8433,10 +8436,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128732848</v>
+        <v>128731100</v>
       </c>
       <c r="B78" t="n">
-        <v>57725</v>
+        <v>91560</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8444,39 +8447,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>569873</v>
+        <v>569688</v>
       </c>
       <c r="R78" t="n">
-        <v>6958099</v>
+        <v>6958069</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8509,11 +8507,6 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8540,49 +8533,45 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128732718</v>
+        <v>128743247</v>
       </c>
       <c r="B79" t="n">
-        <v>98669</v>
+        <v>57727</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>569834</v>
+        <v>569714</v>
       </c>
       <c r="R79" t="n">
-        <v>6958143</v>
+        <v>6957901</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8615,6 +8604,11 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på gran ( färska spår)</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8641,37 +8635,38 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128733005</v>
+        <v>128732848</v>
       </c>
       <c r="B80" t="n">
-        <v>98669</v>
+        <v>57727</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>7</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
@@ -8680,10 +8675,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>569882</v>
+        <v>569873</v>
       </c>
       <c r="R80" t="n">
-        <v>6958106</v>
+        <v>6958099</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8716,6 +8711,11 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8745,7 +8745,7 @@
         <v>128731226</v>
       </c>
       <c r="B81" t="n">
-        <v>91551</v>
+        <v>91560</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8839,45 +8839,49 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128743244</v>
+        <v>128729895</v>
       </c>
       <c r="B82" t="n">
-        <v>91533</v>
+        <v>98678</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>569736</v>
+        <v>569713</v>
       </c>
       <c r="R82" t="n">
-        <v>6957867</v>
+        <v>6958138</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8936,50 +8940,45 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128728434</v>
+        <v>128743257</v>
       </c>
       <c r="B83" t="n">
-        <v>57725</v>
+        <v>98678</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>569608</v>
+        <v>569656</v>
       </c>
       <c r="R83" t="n">
-        <v>6958227</v>
+        <v>6957942</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9016,7 +9015,7 @@
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>23 exemplar (ca)</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9043,49 +9042,45 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128729895</v>
+        <v>128743244</v>
       </c>
       <c r="B84" t="n">
-        <v>98669</v>
+        <v>91542</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>569713</v>
+        <v>569736</v>
       </c>
       <c r="R84" t="n">
-        <v>6958138</v>
+        <v>6957867</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9144,45 +9139,50 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128743257</v>
+        <v>128728434</v>
       </c>
       <c r="B85" t="n">
-        <v>98669</v>
+        <v>57727</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>569656</v>
+        <v>569608</v>
       </c>
       <c r="R85" t="n">
-        <v>6957942</v>
+        <v>6958227</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9219,7 +9219,7 @@
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>23 exemplar (ca)</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9246,10 +9246,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128729069</v>
+        <v>128727978</v>
       </c>
       <c r="B86" t="n">
-        <v>79039</v>
+        <v>57727</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9257,34 +9257,39 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P86" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>569699</v>
+        <v>569564</v>
       </c>
       <c r="R86" t="n">
-        <v>6958200</v>
+        <v>6958213</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9317,6 +9322,11 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9343,10 +9353,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128728419</v>
+        <v>128729666</v>
       </c>
       <c r="B87" t="n">
-        <v>79039</v>
+        <v>57727</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9354,34 +9364,39 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>569608</v>
+        <v>569706</v>
       </c>
       <c r="R87" t="n">
-        <v>6958227</v>
+        <v>6958159</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9418,7 +9433,7 @@
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>Riklig förekomst inom området</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9445,10 +9460,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128743261</v>
+        <v>128728419</v>
       </c>
       <c r="B88" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9480,10 +9495,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>569495</v>
+        <v>569608</v>
       </c>
       <c r="R88" t="n">
-        <v>6958117</v>
+        <v>6958227</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9516,6 +9531,11 @@
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>Riklig förekomst inom området</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9542,10 +9562,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128727978</v>
+        <v>128743261</v>
       </c>
       <c r="B89" t="n">
-        <v>57725</v>
+        <v>79041</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9553,39 +9573,34 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P89" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>569564</v>
+        <v>569495</v>
       </c>
       <c r="R89" t="n">
-        <v>6958213</v>
+        <v>6958117</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9618,11 +9633,6 @@
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9649,10 +9659,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128729666</v>
+        <v>128729069</v>
       </c>
       <c r="B90" t="n">
-        <v>57725</v>
+        <v>79041</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9660,39 +9670,34 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P90" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>569706</v>
+        <v>569699</v>
       </c>
       <c r="R90" t="n">
-        <v>6958159</v>
+        <v>6958200</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9725,11 +9730,6 @@
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9759,7 +9759,7 @@
         <v>128738599</v>
       </c>
       <c r="B91" t="n">
-        <v>80104</v>
+        <v>80106</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9853,10 +9853,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128728152</v>
+        <v>128728274</v>
       </c>
       <c r="B92" t="n">
-        <v>91533</v>
+        <v>57727</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9864,34 +9864,39 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>569577</v>
+        <v>569599</v>
       </c>
       <c r="R92" t="n">
-        <v>6958213</v>
+        <v>6958201</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9924,6 +9929,11 @@
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>Både äldre och färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -9950,38 +9960,37 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128728274</v>
+        <v>128731648</v>
       </c>
       <c r="B93" t="n">
-        <v>57725</v>
+        <v>98678</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr"/>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>119</t>
         </is>
       </c>
       <c r="P93" t="inlineStr">
@@ -9990,10 +9999,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>569599</v>
+        <v>569766</v>
       </c>
       <c r="R93" t="n">
-        <v>6958201</v>
+        <v>6958144</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10030,7 +10039,7 @@
       </c>
       <c r="AC93" t="inlineStr">
         <is>
-          <t>Både äldre och färska ringhack på tall</t>
+          <t>Ca ( möjligtvis fler)</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10057,10 +10066,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128731648</v>
+        <v>128743253</v>
       </c>
       <c r="B94" t="n">
-        <v>98669</v>
+        <v>98678</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10085,21 +10094,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>119</t>
-        </is>
-      </c>
+      <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>569766</v>
+        <v>569641</v>
       </c>
       <c r="R94" t="n">
-        <v>6958144</v>
+        <v>6957953</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10136,7 +10141,7 @@
       </c>
       <c r="AC94" t="inlineStr">
         <is>
-          <t>Ca ( möjligtvis fler)</t>
+          <t>55 exemplar knärötter</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10163,10 +10168,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128743253</v>
+        <v>128743256</v>
       </c>
       <c r="B95" t="n">
-        <v>98669</v>
+        <v>98678</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10198,10 +10203,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>569641</v>
+        <v>569647</v>
       </c>
       <c r="R95" t="n">
-        <v>6957953</v>
+        <v>6957950</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10238,7 +10243,7 @@
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>55 exemplar knärötter</t>
+          <t>23 exemplar</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10265,32 +10270,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128743256</v>
+        <v>128728152</v>
       </c>
       <c r="B96" t="n">
-        <v>98669</v>
+        <v>91542</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10300,10 +10305,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>569647</v>
+        <v>569577</v>
       </c>
       <c r="R96" t="n">
-        <v>6957950</v>
+        <v>6958213</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10336,11 +10341,6 @@
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>23 exemplar</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10370,7 +10370,7 @@
         <v>128728303</v>
       </c>
       <c r="B97" t="n">
-        <v>57717</v>
+        <v>57719</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>

--- a/artfynd/A 39666-2025 artfynd.xlsx
+++ b/artfynd/A 39666-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128743246</v>
+        <v>128732386</v>
       </c>
       <c r="B2" t="n">
-        <v>57727</v>
+        <v>80146</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>569648</v>
+        <v>569785</v>
       </c>
       <c r="R2" t="n">
-        <v>6957944</v>
+        <v>6958124</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall ( äldre och färska spår)</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,7 +772,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128728526</v>
+        <v>128743246</v>
       </c>
       <c r="B3" t="n">
         <v>57727</v>
@@ -806,21 +801,16 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>569616</v>
+        <v>569648</v>
       </c>
       <c r="R3" t="n">
-        <v>6958208</v>
+        <v>6957944</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +847,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack av tretåig hackspett på Tall ( äldre och färska spår)</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,7 +874,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128739007</v>
+        <v>128728526</v>
       </c>
       <c r="B4" t="n">
         <v>57727</v>
@@ -924,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>569542</v>
+        <v>569616</v>
       </c>
       <c r="R4" t="n">
-        <v>6958069</v>
+        <v>6958208</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -991,37 +981,38 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128728896</v>
+        <v>128739007</v>
       </c>
       <c r="B5" t="n">
-        <v>98678</v>
+        <v>57727</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>6</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1030,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>569601</v>
+        <v>569542</v>
       </c>
       <c r="R5" t="n">
-        <v>6958191</v>
+        <v>6958069</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,6 +1057,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1092,7 +1088,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128732983</v>
+        <v>128728896</v>
       </c>
       <c r="B6" t="n">
         <v>98678</v>
@@ -1122,7 +1118,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1131,10 +1127,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>569873</v>
+        <v>569601</v>
       </c>
       <c r="R6" t="n">
-        <v>6958099</v>
+        <v>6958191</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1193,45 +1189,49 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128732386</v>
+        <v>128732983</v>
       </c>
       <c r="B7" t="n">
-        <v>80146</v>
+        <v>98678</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>569785</v>
+        <v>569873</v>
       </c>
       <c r="R7" t="n">
-        <v>6958124</v>
+        <v>6958099</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1494,10 +1494,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128732765</v>
+        <v>128732217</v>
       </c>
       <c r="B10" t="n">
-        <v>91827</v>
+        <v>57887</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1505,34 +1505,48 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>658</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>569827</v>
+        <v>569777</v>
       </c>
       <c r="R10" t="n">
-        <v>6958133</v>
+        <v>6958189</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1565,6 +1579,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>2 talltitor kommer flygandes väldigt närgånget och varnar</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1688,10 +1707,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128730571</v>
+        <v>128732765</v>
       </c>
       <c r="B12" t="n">
-        <v>91560</v>
+        <v>91827</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1699,21 +1718,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1723,10 +1742,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>569660</v>
+        <v>569827</v>
       </c>
       <c r="R12" t="n">
-        <v>6958074</v>
+        <v>6958133</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1785,10 +1804,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128732276</v>
+        <v>128730571</v>
       </c>
       <c r="B13" t="n">
-        <v>57727</v>
+        <v>91560</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1796,39 +1815,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>569841</v>
+        <v>569660</v>
       </c>
       <c r="R13" t="n">
-        <v>6958102</v>
+        <v>6958074</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1861,11 +1875,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1892,7 +1901,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128743245</v>
+        <v>128732276</v>
       </c>
       <c r="B14" t="n">
         <v>57727</v>
@@ -1921,16 +1930,21 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>569590</v>
+        <v>569841</v>
       </c>
       <c r="R14" t="n">
-        <v>6958014</v>
+        <v>6958102</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1967,7 +1981,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall ( färska spår)</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1994,10 +2008,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128732217</v>
+        <v>128743245</v>
       </c>
       <c r="B15" t="n">
-        <v>57887</v>
+        <v>57727</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2005,48 +2019,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>569777</v>
+        <v>569590</v>
       </c>
       <c r="R15" t="n">
-        <v>6958189</v>
+        <v>6958014</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2083,7 +2083,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>2 talltitor kommer flygandes väldigt närgånget och varnar</t>
+          <t>Ringhack av tretåig hackspett på Tall ( färska spår)</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2217,49 +2217,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128731490</v>
+        <v>128728515</v>
       </c>
       <c r="B17" t="n">
-        <v>98678</v>
+        <v>97549</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>569759</v>
+        <v>569608</v>
       </c>
       <c r="R17" t="n">
-        <v>6958118</v>
+        <v>6958227</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2419,45 +2415,49 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128728515</v>
+        <v>128731490</v>
       </c>
       <c r="B19" t="n">
-        <v>97549</v>
+        <v>98678</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>569608</v>
+        <v>569759</v>
       </c>
       <c r="R19" t="n">
-        <v>6958227</v>
+        <v>6958118</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2516,10 +2516,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128732359</v>
+        <v>128731107</v>
       </c>
       <c r="B20" t="n">
-        <v>91542</v>
+        <v>57887</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2527,34 +2527,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>569820</v>
+        <v>569705</v>
       </c>
       <c r="R20" t="n">
-        <v>6958107</v>
+        <v>6958098</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2613,45 +2618,49 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128731612</v>
+        <v>128730720</v>
       </c>
       <c r="B21" t="n">
-        <v>91542</v>
+        <v>98678</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>569752</v>
+        <v>569692</v>
       </c>
       <c r="R21" t="n">
-        <v>6958091</v>
+        <v>6958094</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2684,6 +2693,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ca</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2710,32 +2724,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128728022</v>
+        <v>128743252</v>
       </c>
       <c r="B22" t="n">
-        <v>91506</v>
+        <v>98678</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2745,10 +2759,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>569583</v>
+        <v>569610</v>
       </c>
       <c r="R22" t="n">
-        <v>6958204</v>
+        <v>6958005</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2781,6 +2795,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>2 exemplar</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2807,10 +2826,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128743262</v>
+        <v>128739020</v>
       </c>
       <c r="B23" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2818,34 +2837,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>569732</v>
+        <v>569542</v>
       </c>
       <c r="R23" t="n">
-        <v>6957870</v>
+        <v>6958049</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2878,6 +2902,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2904,50 +2933,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128731107</v>
+        <v>128728022</v>
       </c>
       <c r="B24" t="n">
-        <v>57887</v>
+        <v>91506</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103021</v>
+        <v>5447</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>569705</v>
+        <v>569583</v>
       </c>
       <c r="R24" t="n">
-        <v>6958098</v>
+        <v>6958204</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3006,10 +3030,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128739020</v>
+        <v>128732359</v>
       </c>
       <c r="B25" t="n">
-        <v>57727</v>
+        <v>91542</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3017,39 +3041,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>569542</v>
+        <v>569820</v>
       </c>
       <c r="R25" t="n">
-        <v>6958049</v>
+        <v>6958107</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3082,11 +3101,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3113,49 +3127,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128730720</v>
+        <v>128731612</v>
       </c>
       <c r="B26" t="n">
-        <v>98678</v>
+        <v>91542</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>569692</v>
+        <v>569752</v>
       </c>
       <c r="R26" t="n">
-        <v>6958094</v>
+        <v>6958091</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3188,11 +3198,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ca</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3219,32 +3224,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128743252</v>
+        <v>128743262</v>
       </c>
       <c r="B27" t="n">
-        <v>98678</v>
+        <v>79041</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3254,10 +3259,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>569610</v>
+        <v>569732</v>
       </c>
       <c r="R27" t="n">
-        <v>6958005</v>
+        <v>6957870</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3290,11 +3295,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>2 exemplar</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3321,38 +3321,37 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128731291</v>
+        <v>128731489</v>
       </c>
       <c r="B28" t="n">
-        <v>57727</v>
+        <v>98678</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>45</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3361,10 +3360,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>569726</v>
+        <v>569752</v>
       </c>
       <c r="R28" t="n">
-        <v>6958097</v>
+        <v>6958091</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3397,11 +3396,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på tall</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3428,45 +3422,50 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128729068</v>
+        <v>128731291</v>
       </c>
       <c r="B29" t="n">
-        <v>80175</v>
+        <v>57727</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>569604</v>
+        <v>569726</v>
       </c>
       <c r="R29" t="n">
-        <v>6958176</v>
+        <v>6958097</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3499,6 +3498,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på tall</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3525,37 +3529,38 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128731489</v>
+        <v>128728019</v>
       </c>
       <c r="B30" t="n">
-        <v>98678</v>
+        <v>57727</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>45</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3564,10 +3569,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>569752</v>
+        <v>569577</v>
       </c>
       <c r="R30" t="n">
-        <v>6958091</v>
+        <v>6958213</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3600,6 +3605,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3626,50 +3636,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128728019</v>
+        <v>128729068</v>
       </c>
       <c r="B31" t="n">
-        <v>57727</v>
+        <v>80175</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>569577</v>
+        <v>569604</v>
       </c>
       <c r="R31" t="n">
-        <v>6958213</v>
+        <v>6958176</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3702,11 +3707,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3733,10 +3733,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128730603</v>
+        <v>128730513</v>
       </c>
       <c r="B32" t="n">
-        <v>57727</v>
+        <v>80146</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3744,39 +3744,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>569738</v>
+        <v>569656</v>
       </c>
       <c r="R32" t="n">
-        <v>6958117</v>
+        <v>6958093</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3809,11 +3804,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Äldre exemplar av ringhack på Tall från tretåig hackspett</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3840,45 +3830,54 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128730513</v>
+        <v>128728767</v>
       </c>
       <c r="B33" t="n">
-        <v>80146</v>
+        <v>92835</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>569656</v>
+        <v>569639</v>
       </c>
       <c r="R33" t="n">
-        <v>6958093</v>
+        <v>6958231</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3911,6 +3910,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>4 äldre ett färskt års exemplar</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3937,42 +3941,38 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128728767</v>
+        <v>128730603</v>
       </c>
       <c r="B34" t="n">
-        <v>92835</v>
+        <v>57727</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -3981,10 +3981,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>569639</v>
+        <v>569738</v>
       </c>
       <c r="R34" t="n">
-        <v>6958231</v>
+        <v>6958117</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4021,7 +4021,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>4 äldre ett färskt års exemplar</t>
+          <t>Äldre exemplar av ringhack på Tall från tretåig hackspett</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4848,10 +4848,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128728473</v>
+        <v>128730475</v>
       </c>
       <c r="B43" t="n">
-        <v>57887</v>
+        <v>57727</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4859,27 +4859,27 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -4888,10 +4888,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>569608</v>
+        <v>569675</v>
       </c>
       <c r="R43" t="n">
-        <v>6958227</v>
+        <v>6958098</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4924,6 +4924,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4950,10 +4955,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128730475</v>
+        <v>128728473</v>
       </c>
       <c r="B44" t="n">
-        <v>57727</v>
+        <v>57887</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4961,27 +4966,27 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -4990,10 +4995,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>569675</v>
+        <v>569608</v>
       </c>
       <c r="R44" t="n">
-        <v>6958098</v>
+        <v>6958227</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5026,11 +5031,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6211,45 +6211,50 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128732806</v>
+        <v>128730490</v>
       </c>
       <c r="B56" t="n">
-        <v>91553</v>
+        <v>57727</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1205</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>569827</v>
+        <v>569707</v>
       </c>
       <c r="R56" t="n">
-        <v>6958133</v>
+        <v>6958131</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6282,6 +6287,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Både äldre och färska spår ( Ringhack av tretåig hackspett på tall)</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6308,45 +6318,50 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128732719</v>
+        <v>128730422</v>
       </c>
       <c r="B57" t="n">
-        <v>91997</v>
+        <v>57727</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>569821</v>
+        <v>569703</v>
       </c>
       <c r="R57" t="n">
-        <v>6958151</v>
+        <v>6958116</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6379,6 +6394,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6405,50 +6425,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128730490</v>
+        <v>128730183</v>
       </c>
       <c r="B58" t="n">
-        <v>57727</v>
+        <v>80106</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>229497</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>569707</v>
+        <v>569630</v>
       </c>
       <c r="R58" t="n">
-        <v>6958131</v>
+        <v>6958129</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6481,11 +6496,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Både äldre och färska spår ( Ringhack av tretåig hackspett på tall)</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6512,7 +6522,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128730422</v>
+        <v>128739287</v>
       </c>
       <c r="B59" t="n">
         <v>57727</v>
@@ -6552,10 +6562,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>569703</v>
+        <v>569481</v>
       </c>
       <c r="R59" t="n">
-        <v>6958116</v>
+        <v>6958122</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6592,7 +6602,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6619,50 +6629,45 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128739287</v>
+        <v>128732806</v>
       </c>
       <c r="B60" t="n">
-        <v>57727</v>
+        <v>91553</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>1205</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>569481</v>
+        <v>569827</v>
       </c>
       <c r="R60" t="n">
-        <v>6958122</v>
+        <v>6958133</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6695,11 +6700,6 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6726,32 +6726,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128728592</v>
+        <v>128732719</v>
       </c>
       <c r="B61" t="n">
-        <v>80181</v>
+        <v>91997</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6463</v>
+        <v>1209</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6761,10 +6761,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>569604</v>
+        <v>569821</v>
       </c>
       <c r="R61" t="n">
-        <v>6958176</v>
+        <v>6958151</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6823,7 +6823,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128732124</v>
+        <v>128728592</v>
       </c>
       <c r="B62" t="n">
         <v>80181</v>
@@ -6858,10 +6858,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>569816</v>
+        <v>569604</v>
       </c>
       <c r="R62" t="n">
-        <v>6958081</v>
+        <v>6958176</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6920,10 +6920,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128730101</v>
+        <v>128732124</v>
       </c>
       <c r="B63" t="n">
-        <v>80182</v>
+        <v>80181</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6931,21 +6931,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6464</v>
+        <v>6463</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6955,10 +6955,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>569630</v>
+        <v>569816</v>
       </c>
       <c r="R63" t="n">
-        <v>6958139</v>
+        <v>6958081</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7017,10 +7017,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128731387</v>
+        <v>128730101</v>
       </c>
       <c r="B64" t="n">
-        <v>80174</v>
+        <v>80182</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7028,21 +7028,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6461</v>
+        <v>6464</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7052,10 +7052,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>569740</v>
+        <v>569630</v>
       </c>
       <c r="R64" t="n">
-        <v>6958091</v>
+        <v>6958139</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7114,10 +7114,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128730183</v>
+        <v>128731387</v>
       </c>
       <c r="B65" t="n">
-        <v>80106</v>
+        <v>80174</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7125,21 +7125,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>229497</v>
+        <v>6461</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7149,10 +7149,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>569630</v>
+        <v>569740</v>
       </c>
       <c r="R65" t="n">
-        <v>6958129</v>
+        <v>6958091</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7211,10 +7211,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128729077</v>
+        <v>128730273</v>
       </c>
       <c r="B66" t="n">
-        <v>80146</v>
+        <v>79041</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7222,21 +7222,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7246,10 +7246,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>569604</v>
+        <v>569692</v>
       </c>
       <c r="R66" t="n">
-        <v>6958176</v>
+        <v>6958127</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7405,10 +7405,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128730273</v>
+        <v>128729077</v>
       </c>
       <c r="B68" t="n">
-        <v>79041</v>
+        <v>80146</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7416,21 +7416,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7440,10 +7440,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>569692</v>
+        <v>569604</v>
       </c>
       <c r="R68" t="n">
-        <v>6958127</v>
+        <v>6958176</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7502,10 +7502,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128728149</v>
+        <v>128731693</v>
       </c>
       <c r="B69" t="n">
-        <v>57727</v>
+        <v>91542</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7513,39 +7513,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>569585</v>
+        <v>569793</v>
       </c>
       <c r="R69" t="n">
-        <v>6958190</v>
+        <v>6958092</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7578,11 +7573,6 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7609,50 +7599,45 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128732493</v>
+        <v>128743263</v>
       </c>
       <c r="B70" t="n">
-        <v>57727</v>
+        <v>92871</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>5964</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>569795</v>
+        <v>569517</v>
       </c>
       <c r="R70" t="n">
-        <v>6958154</v>
+        <v>6958123</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7689,7 +7674,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>3 exemplar</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7716,7 +7701,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128730998</v>
+        <v>128728149</v>
       </c>
       <c r="B71" t="n">
         <v>57727</v>
@@ -7756,10 +7741,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>569670</v>
+        <v>569585</v>
       </c>
       <c r="R71" t="n">
-        <v>6958060</v>
+        <v>6958190</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7796,7 +7781,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Ringhack på tall. Även äldre</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7823,7 +7808,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128730928</v>
+        <v>128732493</v>
       </c>
       <c r="B72" t="n">
         <v>57727</v>
@@ -7852,24 +7837,21 @@
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
       <c r="M72" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N72" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>569673</v>
+        <v>569795</v>
       </c>
       <c r="R72" t="n">
-        <v>6958076</v>
+        <v>6958154</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7906,7 +7888,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Påbörjat bobygge av sannolikt tretåig hackspett. Ser ut att vara relativt färskt. 2 meter upp i död gran. Omkring 4,5 cm i diameter.</t>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7933,10 +7915,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128731693</v>
+        <v>128730998</v>
       </c>
       <c r="B73" t="n">
-        <v>91542</v>
+        <v>57727</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7944,34 +7926,39 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>569793</v>
+        <v>569670</v>
       </c>
       <c r="R73" t="n">
-        <v>6958092</v>
+        <v>6958060</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8004,6 +7991,11 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Ringhack på tall. Även äldre</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8030,45 +8022,53 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128743263</v>
+        <v>128730928</v>
       </c>
       <c r="B74" t="n">
-        <v>92871</v>
+        <v>57727</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>5964</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>569517</v>
+        <v>569673</v>
       </c>
       <c r="R74" t="n">
-        <v>6958123</v>
+        <v>6958076</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8105,7 +8105,7 @@
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>3 exemplar</t>
+          <t>Påbörjat bobygge av sannolikt tretåig hackspett. Ser ut att vara relativt färskt. 2 meter upp i död gran. Omkring 4,5 cm i diameter.</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8132,10 +8132,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128731284</v>
+        <v>128731100</v>
       </c>
       <c r="B75" t="n">
-        <v>57887</v>
+        <v>91560</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8143,39 +8143,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>569677</v>
+        <v>569688</v>
       </c>
       <c r="R75" t="n">
-        <v>6958066</v>
+        <v>6958069</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8234,49 +8229,45 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128732718</v>
+        <v>128743247</v>
       </c>
       <c r="B76" t="n">
-        <v>98678</v>
+        <v>57727</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>569834</v>
+        <v>569714</v>
       </c>
       <c r="R76" t="n">
-        <v>6958143</v>
+        <v>6957901</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8309,6 +8300,11 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på gran ( färska spår)</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8335,37 +8331,38 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128733005</v>
+        <v>128732848</v>
       </c>
       <c r="B77" t="n">
-        <v>98678</v>
+        <v>57727</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>7</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
@@ -8374,10 +8371,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>569882</v>
+        <v>569873</v>
       </c>
       <c r="R77" t="n">
-        <v>6958106</v>
+        <v>6958099</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8410,6 +8407,11 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8436,10 +8438,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128731100</v>
+        <v>128731284</v>
       </c>
       <c r="B78" t="n">
-        <v>91560</v>
+        <v>57887</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8447,34 +8449,39 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>569688</v>
+        <v>569677</v>
       </c>
       <c r="R78" t="n">
-        <v>6958069</v>
+        <v>6958066</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8533,45 +8540,49 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128743247</v>
+        <v>128732718</v>
       </c>
       <c r="B79" t="n">
-        <v>57727</v>
+        <v>98678</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>569714</v>
+        <v>569834</v>
       </c>
       <c r="R79" t="n">
-        <v>6957901</v>
+        <v>6958143</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8604,11 +8615,6 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på gran ( färska spår)</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8635,38 +8641,37 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128732848</v>
+        <v>128733005</v>
       </c>
       <c r="B80" t="n">
-        <v>57727</v>
+        <v>98678</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>7</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
@@ -8675,10 +8680,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>569873</v>
+        <v>569882</v>
       </c>
       <c r="R80" t="n">
-        <v>6958099</v>
+        <v>6958106</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8711,11 +8716,6 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8839,37 +8839,38 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128729895</v>
+        <v>128728434</v>
       </c>
       <c r="B82" t="n">
-        <v>98678</v>
+        <v>57727</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>26</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
@@ -8878,10 +8879,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>569713</v>
+        <v>569608</v>
       </c>
       <c r="R82" t="n">
-        <v>6958138</v>
+        <v>6958227</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8914,6 +8915,11 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8940,32 +8946,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128743257</v>
+        <v>128743244</v>
       </c>
       <c r="B83" t="n">
-        <v>98678</v>
+        <v>91542</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8975,10 +8981,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>569656</v>
+        <v>569736</v>
       </c>
       <c r="R83" t="n">
-        <v>6957942</v>
+        <v>6957867</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9011,11 +9017,6 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>23 exemplar (ca)</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9042,45 +9043,49 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128743244</v>
+        <v>128729895</v>
       </c>
       <c r="B84" t="n">
-        <v>91542</v>
+        <v>98678</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>569736</v>
+        <v>569713</v>
       </c>
       <c r="R84" t="n">
-        <v>6957867</v>
+        <v>6958138</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9139,50 +9144,45 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128728434</v>
+        <v>128743257</v>
       </c>
       <c r="B85" t="n">
-        <v>57727</v>
+        <v>98678</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>569608</v>
+        <v>569656</v>
       </c>
       <c r="R85" t="n">
-        <v>6958227</v>
+        <v>6957942</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9219,7 +9219,7 @@
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>23 exemplar (ca)</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9246,10 +9246,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128727978</v>
+        <v>128729069</v>
       </c>
       <c r="B86" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9257,39 +9257,34 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P86" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>569564</v>
+        <v>569699</v>
       </c>
       <c r="R86" t="n">
-        <v>6958213</v>
+        <v>6958200</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9322,11 +9317,6 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9353,10 +9343,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128729666</v>
+        <v>128728419</v>
       </c>
       <c r="B87" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9364,39 +9354,34 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>569706</v>
+        <v>569608</v>
       </c>
       <c r="R87" t="n">
-        <v>6958159</v>
+        <v>6958227</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9433,7 +9418,7 @@
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Riklig förekomst inom området</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9460,7 +9445,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128728419</v>
+        <v>128743261</v>
       </c>
       <c r="B88" t="n">
         <v>79041</v>
@@ -9495,10 +9480,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>569608</v>
+        <v>569495</v>
       </c>
       <c r="R88" t="n">
-        <v>6958227</v>
+        <v>6958117</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9531,11 +9516,6 @@
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>Riklig förekomst inom området</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9562,10 +9542,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128743261</v>
+        <v>128727978</v>
       </c>
       <c r="B89" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9573,34 +9553,39 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P89" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>569495</v>
+        <v>569564</v>
       </c>
       <c r="R89" t="n">
-        <v>6958117</v>
+        <v>6958213</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9633,6 +9618,11 @@
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9659,10 +9649,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128729069</v>
+        <v>128729666</v>
       </c>
       <c r="B90" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9670,34 +9660,39 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P90" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>569699</v>
+        <v>569706</v>
       </c>
       <c r="R90" t="n">
-        <v>6958200</v>
+        <v>6958159</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9730,6 +9725,11 @@
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9853,10 +9853,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128728274</v>
+        <v>128728152</v>
       </c>
       <c r="B92" t="n">
-        <v>57727</v>
+        <v>91542</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9864,39 +9864,34 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>569599</v>
+        <v>569577</v>
       </c>
       <c r="R92" t="n">
-        <v>6958201</v>
+        <v>6958213</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9929,11 +9924,6 @@
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC92" t="inlineStr">
-        <is>
-          <t>Både äldre och färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -9960,37 +9950,38 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128731648</v>
+        <v>128728274</v>
       </c>
       <c r="B93" t="n">
-        <v>98678</v>
+        <v>57727</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>119</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P93" t="inlineStr">
@@ -9999,10 +9990,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>569766</v>
+        <v>569599</v>
       </c>
       <c r="R93" t="n">
-        <v>6958144</v>
+        <v>6958201</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10039,7 +10030,7 @@
       </c>
       <c r="AC93" t="inlineStr">
         <is>
-          <t>Ca ( möjligtvis fler)</t>
+          <t>Både äldre och färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10066,7 +10057,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128743253</v>
+        <v>128731648</v>
       </c>
       <c r="B94" t="n">
         <v>98678</v>
@@ -10094,17 +10085,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I94" t="inlineStr"/>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
       <c r="P94" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>569641</v>
+        <v>569766</v>
       </c>
       <c r="R94" t="n">
-        <v>6957953</v>
+        <v>6958144</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10141,7 +10136,7 @@
       </c>
       <c r="AC94" t="inlineStr">
         <is>
-          <t>55 exemplar knärötter</t>
+          <t>Ca ( möjligtvis fler)</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10168,7 +10163,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128743256</v>
+        <v>128743253</v>
       </c>
       <c r="B95" t="n">
         <v>98678</v>
@@ -10203,10 +10198,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>569647</v>
+        <v>569641</v>
       </c>
       <c r="R95" t="n">
-        <v>6957950</v>
+        <v>6957953</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10243,7 +10238,7 @@
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>23 exemplar</t>
+          <t>55 exemplar knärötter</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10270,32 +10265,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128728152</v>
+        <v>128743256</v>
       </c>
       <c r="B96" t="n">
-        <v>91542</v>
+        <v>98678</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10305,10 +10300,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>569577</v>
+        <v>569647</v>
       </c>
       <c r="R96" t="n">
-        <v>6958213</v>
+        <v>6957950</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10341,6 +10336,11 @@
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>23 exemplar</t>
         </is>
       </c>
       <c r="AD96" t="b">
